--- a/downloadable-data/LA.xlsx
+++ b/downloadable-data/LA.xlsx
@@ -353,27 +353,27 @@
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">Alliance for Gun Responsibility</t>
+          <t xml:space="preserve">Alpha Gamma Delta Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">9/12/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="66">
-        <v>70.44</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">Alpha Gamma Delta Foundation, Inc.</t>
+          <t xml:space="preserve">Alpha Kappa Psi Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
+          <t xml:space="preserve">1/8/2027</t>
         </is>
       </c>
       <c r="C12" s="65">
@@ -383,117 +383,117 @@
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">Alpha Kappa Psi Foundation</t>
+          <t xml:space="preserve">ALTA Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">1/8/2027</t>
-        </is>
-      </c>
-      <c r="C13" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C13" s="66">
+        <v>48.00</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">ALTA Charitable Foundation</t>
+          <t xml:space="preserve">Alternate ROOTS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C14" s="66">
-        <v>48.00</v>
+          <t xml:space="preserve">1/1/2027</t>
+        </is>
+      </c>
+      <c r="C14" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">Alternate ROOTS, Inc.</t>
+          <t xml:space="preserve">America's Survival, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">1/1/2027</t>
-        </is>
-      </c>
-      <c r="C15" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C15" s="66">
+        <v>90.07</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">America's Survival, Inc.</t>
+          <t xml:space="preserve">American Association of Family and Consumer Scienc</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C16" s="66">
-        <v>90.07</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">American Association of Family and Consumer Scienc</t>
+          <t xml:space="preserve">American Association of State Troopers, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C17" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="66">
+        <v>23.00</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">American Association of State Troopers, Inc.</t>
+          <t xml:space="preserve">American Bible Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">3/27/2027</t>
         </is>
       </c>
       <c r="C18" s="66">
-        <v>23.00</v>
+        <v>76.00</v>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">American Bible Society</t>
+          <t xml:space="preserve">American Civil Liberties Union Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
-        </is>
-      </c>
-      <c r="C19" s="66">
-        <v>76.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">American Civil Liberties Union Foundation, Inc.</t>
+          <t xml:space="preserve">American Council of the Blind, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
+          <t xml:space="preserve">10/16/2026</t>
         </is>
       </c>
       <c r="C20" s="65">
@@ -503,162 +503,162 @@
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">American Council of the Blind, Inc.</t>
+          <t xml:space="preserve">American Diabetes Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">10/16/2026</t>
-        </is>
-      </c>
-      <c r="C21" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/26/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="66">
+        <v>79.18</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">American Diabetes Association</t>
+          <t xml:space="preserve">American Indian College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
+          <t xml:space="preserve">11/13/2026</t>
         </is>
       </c>
       <c r="C22" s="66">
-        <v>79.18</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">American Indian College Fund</t>
+          <t xml:space="preserve">American Institute for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">11/13/2026</t>
+          <t xml:space="preserve">9/18/2026</t>
         </is>
       </c>
       <c r="C23" s="66">
-        <v>78.00</v>
+        <v>62.00</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">American Institute for Cancer Research</t>
+          <t xml:space="preserve">American Institute for Economic Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">9/18/2026</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C24" s="66">
-        <v>62.00</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">American Institute for Economic Research</t>
+          <t xml:space="preserve">American Kidney Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">10/14/2026</t>
         </is>
       </c>
       <c r="C25" s="66">
-        <v>78.63</v>
+        <v>95.70</v>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">American Kidney Fund, Inc.</t>
+          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C26" s="66">
-        <v>95.70</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
+          <t xml:space="preserve">American Roentgen Ray Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">10/9/2026</t>
         </is>
       </c>
       <c r="C27" s="66">
-        <v>75.08</v>
+        <v>52.00</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">American Roentgen Ray Society</t>
+          <t xml:space="preserve">Americans For Fair Treatment</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
-        </is>
-      </c>
-      <c r="C28" s="66">
-        <v>52.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">Americans For Fair Treatment</t>
+          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C29" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/14/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="66">
+        <v>71.00</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
+          <t xml:space="preserve">Animals' Angels, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
-        </is>
-      </c>
-      <c r="C30" s="66">
-        <v>71.00</v>
+          <t xml:space="preserve">9/22/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">Animals' Angels, Incorporated</t>
+          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C31" s="65">
@@ -668,12 +668,12 @@
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
+          <t xml:space="preserve">Association of American Education Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C32" s="65">
@@ -683,82 +683,82 @@
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">Association of American Education Foundation</t>
+          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C33" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/23/2027</t>
+        </is>
+      </c>
+      <c r="C33" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
+          <t xml:space="preserve">Autism Speaks, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">3/23/2027</t>
-        </is>
-      </c>
-      <c r="C34" s="66">
-        <v>81.00</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C34" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">Autism Speaks, Inc.</t>
+          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C35" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C35" s="66">
+        <v>44.00</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
+          <t xml:space="preserve">B'nai B'rith International</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C36" s="66">
-        <v>44.00</v>
+          <t xml:space="preserve">12/18/2026</t>
+        </is>
+      </c>
+      <c r="C36" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">B'nai B'rith International</t>
+          <t xml:space="preserve">Back Bay Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C37" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/16/2027</t>
+        </is>
+      </c>
+      <c r="C37" s="66">
+        <v>83.67</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">Back Bay Mission, Inc.</t>
+          <t xml:space="preserve">Base Ministry</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
@@ -767,258 +767,258 @@
         </is>
       </c>
       <c r="C38" s="66">
-        <v>83.67</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">Base Ministry</t>
+          <t xml:space="preserve">Blood Cancer United, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C39" s="66">
-        <v>71.89</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">Blood Cancer United, Inc.</t>
+          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C40" s="66">
-        <v>75.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
+          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C41" s="66">
-        <v>71.00</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
+          <t xml:space="preserve">Business Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C42" s="66">
-        <v>78.58</v>
+        <v>54.00</v>
       </c>
     </row>
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">Business Action Fund</t>
+          <t xml:space="preserve">Cair-Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">1/14/2027</t>
         </is>
       </c>
       <c r="C43" s="66">
-        <v>54.00</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">Cair-Foundation, Inc.</t>
+          <t xml:space="preserve">Captain Joseph House Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C44" s="66">
-        <v>66.00</v>
+        <v>67.20</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">Captain Joseph House Foundation</t>
+          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">10/14/2026</t>
         </is>
       </c>
       <c r="C45" s="66">
-        <v>67.20</v>
+        <v>97.00</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
+          <t xml:space="preserve">Center for Community Change Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C46" s="66">
-        <v>97.00</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">Center for Community Change Action</t>
+          <t xml:space="preserve">Central Asia Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C47" s="66">
-        <v>95.00</v>
+        <v>77.29</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">Central Asia Institute</t>
+          <t xml:space="preserve">Charities Aid Foundation America</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C48" s="66">
-        <v>77.29</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">Charities Aid Foundation America</t>
+          <t xml:space="preserve">Childhelp, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">6/30/2027</t>
         </is>
       </c>
       <c r="C49" s="66">
-        <v>0.01</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">ChildFund International, USA</t>
+          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">9/8/2026</t>
-        </is>
-      </c>
-      <c r="C50" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">12/18/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">Childhelp, Inc.</t>
+          <t xml:space="preserve">Children's Miracle Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">6/30/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C51" s="66">
-        <v>70.00</v>
+        <v>80.77</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
+          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C52" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C52" s="66">
+        <v>89.98</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">Children's Miracle Network</t>
+          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C53" s="66">
-        <v>80.77</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C53" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
+          <t xml:space="preserve">Christian Relief Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">2/10/2027</t>
         </is>
       </c>
       <c r="C54" s="66">
-        <v>89.98</v>
+        <v>90.70</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
+          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C55" s="65">
@@ -1028,102 +1028,102 @@
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">Christian Relief Services, Inc.</t>
+          <t xml:space="preserve">Christian Union, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
-        </is>
-      </c>
-      <c r="C56" s="66">
-        <v>90.70</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C56" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
+          <t xml:space="preserve">City Year, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C57" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C57" s="66">
+        <v>82.62</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">Christian Union, Inc.</t>
+          <t xml:space="preserve">Civil Rights Corps</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C58" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="66">
+        <v>82.10</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">City Year, Inc.</t>
+          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C59" s="66">
-        <v>82.62</v>
+          <t xml:space="preserve">11/20/2026</t>
+        </is>
+      </c>
+      <c r="C59" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Civil Rights Corps</t>
+          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C60" s="66">
-        <v>82.10</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C60" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
+          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">11/20/2026</t>
-        </is>
-      </c>
-      <c r="C61" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/9/2027</t>
+        </is>
+      </c>
+      <c r="C61" s="66">
+        <v>65.99</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
+          <t xml:space="preserve">Concerns of Police Survivors</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C62" s="65">
@@ -1133,27 +1133,27 @@
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
+          <t xml:space="preserve">Consumer Reports, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C63" s="66">
-        <v>65.99</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">Concerns of Police Survivors</t>
+          <t xml:space="preserve">Cooperative for Assistance and Relief Everywhere</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">10/1/2026</t>
         </is>
       </c>
       <c r="C64" s="65">
@@ -1163,237 +1163,237 @@
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">Consumer Reports, Inc.</t>
+          <t xml:space="preserve">Covenant House</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C65" s="66">
-        <v>84.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">Cooperative for Assistance and Relief Everywhere</t>
+          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
-        </is>
-      </c>
-      <c r="C66" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/4/2026</t>
+        </is>
+      </c>
+      <c r="C66" s="66">
+        <v>84.38</v>
       </c>
     </row>
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">Covenant House</t>
+          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">12/4/2026</t>
         </is>
       </c>
       <c r="C67" s="66">
-        <v>80.00</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
+          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C68" s="66">
-        <v>84.38</v>
+        <v>64.30</v>
       </c>
     </row>
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
+          <t xml:space="preserve">Daring Girls</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
-        </is>
-      </c>
-      <c r="C69" s="66">
-        <v>70.00</v>
+          <t xml:space="preserve">9/26/2026</t>
+        </is>
+      </c>
+      <c r="C69" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
+          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C70" s="66">
-        <v>64.30</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C70" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">Daring Girls</t>
+          <t xml:space="preserve">Disabled American Veterans</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
-        </is>
-      </c>
-      <c r="C71" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/18/2026</t>
+        </is>
+      </c>
+      <c r="C71" s="66">
+        <v>67.00</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
+          <t xml:space="preserve">Disabled Veterans National Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C72" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/25/2026</t>
+        </is>
+      </c>
+      <c r="C72" s="66">
+        <v>20.85</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">Disabled American Veterans</t>
+          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">9/18/2026</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C73" s="66">
-        <v>67.00</v>
+        <v>49.00</v>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">Disabled Veterans National Foundation</t>
+          <t xml:space="preserve">East Carolina University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">9/25/2026</t>
+          <t xml:space="preserve">10/10/2026</t>
         </is>
       </c>
       <c r="C74" s="66">
-        <v>20.85</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
+          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C75" s="66">
-        <v>49.00</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">DTCare</t>
+          <t xml:space="preserve">Easter Seals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">9/8/2026</t>
-        </is>
-      </c>
-      <c r="C76" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/15/2026</t>
+        </is>
+      </c>
+      <c r="C76" s="66">
+        <v>68.00</v>
       </c>
     </row>
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">East Carolina University Foundation, Inc.</t>
+          <t xml:space="preserve">EB Research Partnership, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
-        </is>
-      </c>
-      <c r="C77" s="66">
-        <v>55.44</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C77" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
+          <t xml:space="preserve">Economic Policy Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">9/26/2026</t>
         </is>
       </c>
       <c r="C78" s="66">
-        <v>61.48</v>
+        <v>83.70</v>
       </c>
     </row>
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">Easter Seals, Inc.</t>
+          <t xml:space="preserve">Einstein School Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">9/17/2026</t>
         </is>
       </c>
       <c r="C79" s="66">
-        <v>68.00</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">EB Research Partnership, Inc.</t>
+          <t xml:space="preserve">ELT Ventures</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C80" s="65">
@@ -1403,207 +1403,207 @@
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">Economic Policy Institute</t>
+          <t xml:space="preserve">Empire State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C81" s="66">
-        <v>83.70</v>
+        <v>82.78</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Einstein School Foundation</t>
+          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">9/17/2026</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C82" s="66">
-        <v>87.00</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">ELT Ventures</t>
+          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C83" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/6/2027</t>
+        </is>
+      </c>
+      <c r="C83" s="66">
+        <v>87.00</v>
       </c>
     </row>
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Empire State University Foundation</t>
+          <t xml:space="preserve">Family Policy Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C84" s="66">
-        <v>82.78</v>
+        <v>80.48</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
+          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C85" s="66">
-        <v>48.32</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
+          <t xml:space="preserve">Feeding America</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">3/6/2027</t>
+          <t xml:space="preserve">10/6/2026</t>
         </is>
       </c>
       <c r="C86" s="66">
-        <v>87.00</v>
+        <v>98.40</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Family Policy Alliance</t>
+          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">4/9/2027</t>
         </is>
       </c>
       <c r="C87" s="66">
-        <v>80.48</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
+          <t xml:space="preserve">Firefighters Charitable Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C88" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/16/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="66">
+        <v>8.20</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">Feeding America</t>
+          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C89" s="66">
-        <v>98.40</v>
+        <v>89.30</v>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
+          <t xml:space="preserve">For Others Collective, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
-        </is>
-      </c>
-      <c r="C90" s="66">
-        <v>82.48</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C90" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Firefighters Charitable Foundation, Inc.</t>
+          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">9/16/2026</t>
-        </is>
-      </c>
-      <c r="C91" s="66">
-        <v>8.20</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C91" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
+          <t xml:space="preserve">Fractracker Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C92" s="66">
-        <v>89.30</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">For Others Collective, Inc.</t>
+          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C93" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/1/2027</t>
+        </is>
+      </c>
+      <c r="C93" s="66">
+        <v>68.41</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
+          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C94" s="65">
@@ -1613,42 +1613,42 @@
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Fractracker Alliance</t>
+          <t xml:space="preserve">Friends of KEXP</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">10/10/2026</t>
         </is>
       </c>
       <c r="C95" s="66">
-        <v>77.78</v>
+        <v>66.97</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
+          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
+          <t xml:space="preserve">9/22/2026</t>
         </is>
       </c>
       <c r="C96" s="66">
-        <v>68.41</v>
+        <v>67.76</v>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
+          <t xml:space="preserve">Futures Without Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C97" s="65">
@@ -1658,177 +1658,177 @@
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Friends of KEXP</t>
+          <t xml:space="preserve">Givinga Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
+          <t xml:space="preserve">10/30/2026</t>
         </is>
       </c>
       <c r="C98" s="66">
-        <v>66.97</v>
+        <v>94.03</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
+          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
+          <t xml:space="preserve">3/11/2027</t>
         </is>
       </c>
       <c r="C99" s="66">
-        <v>67.76</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">Futures Without Violence</t>
+          <t xml:space="preserve">Go Campaign</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C100" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/20/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="66">
+        <v>77.86</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Givinga Foundation</t>
+          <t xml:space="preserve">Green America</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">10/30/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C101" s="66">
-        <v>94.03</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
+          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">3/11/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C102" s="66">
-        <v>49.91</v>
+        <v>76.85</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Go Campaign</t>
+          <t xml:space="preserve">Greenpeace, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C103" s="66">
-        <v>77.86</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">Green America</t>
+          <t xml:space="preserve">Gustavus Adolphus College</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">2/24/2027</t>
         </is>
       </c>
       <c r="C104" s="66">
-        <v>87.47</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
+          <t xml:space="preserve">Habitat for Horses, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C105" s="66">
-        <v>76.85</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Greenpeace, Inc.</t>
+          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C106" s="66">
-        <v>62.56</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Gustavus Adolphus College</t>
+          <t xml:space="preserve">Healing Protectors</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">2/24/2027</t>
+          <t xml:space="preserve">3/2/2027</t>
         </is>
       </c>
       <c r="C107" s="66">
-        <v>93.00</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">Habitat for Horses, Inc.</t>
+          <t xml:space="preserve">Heifer Project International</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C108" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/19/2027</t>
+        </is>
+      </c>
+      <c r="C108" s="66">
+        <v>72.90</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
+          <t xml:space="preserve">Help Me See, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
+          <t xml:space="preserve">10/3/2026</t>
         </is>
       </c>
       <c r="C109" s="65">
@@ -1838,42 +1838,42 @@
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">Healing Protectors</t>
+          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
-        </is>
-      </c>
-      <c r="C110" s="66">
-        <v>47.19</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">Heifer Project International</t>
+          <t xml:space="preserve">Heroes on the Water</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">3/19/2027</t>
+          <t xml:space="preserve">10/1/2026</t>
         </is>
       </c>
       <c r="C111" s="66">
-        <v>72.90</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">Help Me See, Inc.</t>
+          <t xml:space="preserve">HIAS Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">10/3/2026</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C112" s="65">
@@ -1883,12 +1883,12 @@
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
+          <t xml:space="preserve">Home Builders Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C113" s="65">
@@ -1898,132 +1898,132 @@
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Heroes on the Water</t>
+          <t xml:space="preserve">Houston Christian Broadcasters, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
+          <t xml:space="preserve">10/6/2026</t>
         </is>
       </c>
       <c r="C114" s="66">
-        <v>75.00</v>
+        <v>84.40</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">HIAS Foundation, Inc.</t>
+          <t xml:space="preserve">Human Appeal, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C115" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/12/2027</t>
+        </is>
+      </c>
+      <c r="C115" s="66">
+        <v>54.20</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">Home Builders Institute</t>
+          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C116" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="66">
+        <v>63.39</v>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Houston Christian Broadcasters, Inc.</t>
+          <t xml:space="preserve">Human Rights Watch, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C117" s="66">
-        <v>84.40</v>
+        <v>72.65</v>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">Human Appeal, Inc.</t>
+          <t xml:space="preserve">Humane World for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">1/12/2027</t>
+          <t xml:space="preserve">9/15/2026</t>
         </is>
       </c>
       <c r="C118" s="66">
-        <v>54.20</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
+          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C119" s="66">
-        <v>63.39</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C119" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">Human Rights Watch, Inc.</t>
+          <t xml:space="preserve">In Medias Res</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C120" s="66">
-        <v>72.65</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C120" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">Humane World for Animals, Inc.</t>
+          <t xml:space="preserve">Independent Council on Women's Sport</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">9/15/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C121" s="66">
-        <v>75.00</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
+          <t xml:space="preserve">INROADS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">9/24/2026</t>
         </is>
       </c>
       <c r="C122" s="65">
@@ -2033,12 +2033,12 @@
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">In Medias Res</t>
+          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">12/1/2026</t>
         </is>
       </c>
       <c r="C123" s="65">
@@ -2048,27 +2048,27 @@
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">Independent Council on Women's Sport</t>
+          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C124" s="66">
-        <v>94.44</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C124" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">INROADS, Inc.</t>
+          <t xml:space="preserve">International Justice Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">9/24/2026</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C125" s="65">
@@ -2078,207 +2078,207 @@
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
+          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C126" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C126" s="66">
+        <v>83.13</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
+          <t xml:space="preserve">International Union of Police Associations</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C127" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="66">
+        <v>47.90</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">International Justice Mission</t>
+          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
-        </is>
-      </c>
-      <c r="C128" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/27/2027</t>
+        </is>
+      </c>
+      <c r="C128" s="66">
+        <v>75.43</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
+          <t xml:space="preserve">Jewish Democratic Council of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C129" s="66">
-        <v>83.13</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">International Union of Police Associations</t>
+          <t xml:space="preserve">Jewish Voice Ministries International</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C130" s="66">
-        <v>47.90</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
+          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C131" s="66">
-        <v>75.43</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">Jewish Democratic Council of America</t>
+          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">9/22/2026</t>
         </is>
       </c>
       <c r="C132" s="66">
-        <v>50.07</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">Jewish Voice Ministries International</t>
+          <t xml:space="preserve">Khan Academy, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C133" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/14/2027</t>
+        </is>
+      </c>
+      <c r="C133" s="66">
+        <v>86.36</v>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
+          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
-        </is>
-      </c>
-      <c r="C134" s="66">
-        <v>89.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
+          <t xml:space="preserve">L.E.A.D. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
-        </is>
-      </c>
-      <c r="C135" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C135" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">Khan Academy, Inc.</t>
+          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
-        </is>
-      </c>
-      <c r="C136" s="66">
-        <v>86.36</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">Kids Wish Network, Inc</t>
+          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">9/12/2026</t>
+          <t xml:space="preserve">10/28/2026</t>
         </is>
       </c>
       <c r="C137" s="66">
-        <v>35.00</v>
+        <v>96.80</v>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
+          <t xml:space="preserve">Living Waters for the World</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C138" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="66">
+        <v>78.81</v>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">L.E.A.D. Inc.</t>
+          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">4/23/2027</t>
         </is>
       </c>
       <c r="C139" s="65">
@@ -2288,162 +2288,162 @@
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
+          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C140" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/29/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="66">
+        <v>70.18</v>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
+          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">10/28/2026</t>
-        </is>
-      </c>
-      <c r="C141" s="66">
-        <v>96.80</v>
+          <t xml:space="preserve">9/25/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">Living Waters for the World</t>
+          <t xml:space="preserve">MAP International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">11/3/2026</t>
         </is>
       </c>
       <c r="C142" s="66">
-        <v>78.81</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
+          <t xml:space="preserve">March of Dimes</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C143" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/30/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="66">
+        <v>74.00</v>
       </c>
     </row>
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
+          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">10/29/2026</t>
-        </is>
-      </c>
-      <c r="C144" s="66">
-        <v>70.18</v>
+          <t xml:space="preserve">12/8/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
+          <t xml:space="preserve">Mercy for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">9/25/2026</t>
-        </is>
-      </c>
-      <c r="C145" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="66">
+        <v>75.82</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">Madison House</t>
+          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">9/8/2026</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C146" s="66">
-        <v>77.76</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">MAP International, Inc.</t>
+          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C147" s="66">
-        <v>99.00</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">March of Dimes</t>
+          <t xml:space="preserve">Mount Saint Marys University</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">12/30/2026</t>
-        </is>
-      </c>
-      <c r="C148" s="66">
-        <v>74.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">Marist University</t>
+          <t xml:space="preserve">Mountain States Legal Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">9/9/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C149" s="66">
-        <v>91.26</v>
+        <v>69.99</v>
       </c>
     </row>
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
+          <t xml:space="preserve">MrCharity, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">12/8/2026</t>
+          <t xml:space="preserve">2/23/2027</t>
         </is>
       </c>
       <c r="C150" s="65">
@@ -2453,87 +2453,87 @@
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Mercy Corp</t>
+          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">9/11/2026</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C151" s="66">
-        <v>76.20</v>
+        <v>54.00</v>
       </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">Mercy for Animals, Inc.</t>
+          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">12/19/2026</t>
         </is>
       </c>
       <c r="C152" s="66">
-        <v>75.82</v>
+        <v>66.90</v>
       </c>
     </row>
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">Military Heritage Foundation</t>
+          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">9/9/2026</t>
-        </is>
-      </c>
-      <c r="C153" s="66">
-        <v>67.00</v>
+          <t xml:space="preserve">7/16/2027</t>
+        </is>
+      </c>
+      <c r="C153" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
+          <t xml:space="preserve">National Council of Nonprofits</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
-        </is>
-      </c>
-      <c r="C154" s="66">
-        <v>88.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C154" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
+          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C155" s="66">
-        <v>94.50</v>
+        <v>49.00</v>
       </c>
     </row>
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">Mount Saint Marys University</t>
+          <t xml:space="preserve">National Foundation for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
+          <t xml:space="preserve">12/1/2026</t>
         </is>
       </c>
       <c r="C156" s="65">
@@ -2543,72 +2543,72 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">Mountain States Legal Foundation</t>
+          <t xml:space="preserve">National Geographic Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">3/18/2027</t>
         </is>
       </c>
       <c r="C157" s="66">
-        <v>69.99</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">MrCharity, Inc.</t>
+          <t xml:space="preserve">National Museum of Women in the Arts, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
-        </is>
-      </c>
-      <c r="C158" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/3/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="66">
+        <v>72.00</v>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
+          <t xml:space="preserve">National Organization for Women, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C159" s="66">
-        <v>54.00</v>
+          <t xml:space="preserve">9/19/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
+          <t xml:space="preserve">National Park Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">12/19/2026</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C160" s="66">
-        <v>66.90</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
+          <t xml:space="preserve">National PKU Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C161" s="65">
@@ -2618,12 +2618,12 @@
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">National Council of Nonprofits</t>
+          <t xml:space="preserve">National Rifle Association of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">9/17/2026</t>
         </is>
       </c>
       <c r="C162" s="65">
@@ -2633,27 +2633,27 @@
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
+          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C163" s="66">
-        <v>49.00</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C163" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">National Foundation for Cancer Research</t>
+          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
+          <t xml:space="preserve">1/9/2027</t>
         </is>
       </c>
       <c r="C164" s="65">
@@ -2663,117 +2663,117 @@
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">National Geographic Society</t>
+          <t xml:space="preserve">National Space Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">3/18/2027</t>
-        </is>
-      </c>
-      <c r="C165" s="66">
-        <v>77.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C165" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">National Museum of Women in the Arts, Inc.</t>
+          <t xml:space="preserve">National University</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">10/3/2026</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C166" s="66">
-        <v>72.00</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">National Organization for Women, Inc</t>
+          <t xml:space="preserve">National Veterans Memorial and Museum</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">9/19/2026</t>
-        </is>
-      </c>
-      <c r="C167" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C167" s="66">
+        <v>72.63</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">National Park Foundation</t>
+          <t xml:space="preserve">National Wheelchair Basketball Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C168" s="66">
-        <v>72.00</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">National PKU Alliance, Inc.</t>
+          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C169" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/22/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="66">
+        <v>2.90</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">National Rifle Association of America</t>
+          <t xml:space="preserve">Network for Good, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">9/17/2026</t>
-        </is>
-      </c>
-      <c r="C170" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C170" s="66">
+        <v>97.80</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
+          <t xml:space="preserve">New Harvest, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C171" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="66">
+        <v>88.49</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
+          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C172" s="65">
@@ -2783,7 +2783,7 @@
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">National Space Society</t>
+          <t xml:space="preserve">Nurse-Family Partnership</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
@@ -2798,117 +2798,117 @@
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">National University</t>
+          <t xml:space="preserve">Ocean Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C174" s="66">
-        <v>42.69</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">National Veterans Memorial and Museum</t>
+          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C175" s="66">
-        <v>72.63</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C175" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">National Wheelchair Basketball Association</t>
+          <t xml:space="preserve">OneHope, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">10/1/2026</t>
         </is>
       </c>
       <c r="C176" s="66">
-        <v>77.80</v>
+        <v>82.72</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
+          <t xml:space="preserve">Operation Smile, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
-        </is>
-      </c>
-      <c r="C177" s="66">
-        <v>2.90</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C177" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">Network for Good, Inc</t>
+          <t xml:space="preserve">Our Change Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C178" s="66">
-        <v>97.80</v>
+        <v>80.46</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">New Harvest, Inc.</t>
+          <t xml:space="preserve">Oxfam-America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">10/6/2026</t>
         </is>
       </c>
       <c r="C179" s="66">
-        <v>88.49</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
+          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C180" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C180" s="66">
+        <v>55.43</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">Nurse-Family Partnership</t>
+          <t xml:space="preserve">Parkinson Research Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">9/25/2026</t>
         </is>
       </c>
       <c r="C181" s="65">
@@ -2918,27 +2918,27 @@
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">Ocean Conservancy</t>
+          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">2/9/2027</t>
         </is>
       </c>
       <c r="C182" s="66">
-        <v>74.06</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
+          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C183" s="65">
@@ -2948,87 +2948,87 @@
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">OneHope, Inc.</t>
+          <t xml:space="preserve">People for the American Way</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
+          <t xml:space="preserve">9/18/2026</t>
         </is>
       </c>
       <c r="C184" s="66">
-        <v>82.72</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">Operation Smile, Inc.</t>
+          <t xml:space="preserve">People for the American Way Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C185" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/18/2026</t>
+        </is>
+      </c>
+      <c r="C185" s="66">
+        <v>55.83</v>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">Our Change Foundation</t>
+          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C186" s="66">
-        <v>80.46</v>
+        <v>58.00</v>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">Oxfam-America, Inc.</t>
+          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
-        </is>
-      </c>
-      <c r="C187" s="66">
-        <v>71.00</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C187" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
+          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C188" s="66">
-        <v>55.43</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C188" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">Parkinson Research Foundation, Inc.</t>
+          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">9/25/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C189" s="65">
@@ -3038,87 +3038,87 @@
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
+          <t xml:space="preserve">Pledgeling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">2/9/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C190" s="66">
-        <v>90.00</v>
+        <v>65.93</v>
       </c>
     </row>
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
+          <t xml:space="preserve">Polar Bears International</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
-        </is>
-      </c>
-      <c r="C191" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/2/2027</t>
+        </is>
+      </c>
+      <c r="C191" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">People for the American Way</t>
+          <t xml:space="preserve">Political Economy Research Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">9/18/2026</t>
+          <t xml:space="preserve">9/16/2026</t>
         </is>
       </c>
       <c r="C192" s="66">
-        <v>46.61</v>
+        <v>75.98</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">People for the American Way Foundation</t>
+          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">9/18/2026</t>
+          <t xml:space="preserve">3/27/2027</t>
         </is>
       </c>
       <c r="C193" s="66">
-        <v>55.83</v>
+        <v>85.54</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
+          <t xml:space="preserve">Pratt Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
-        </is>
-      </c>
-      <c r="C194" s="66">
-        <v>58.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C194" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
+          <t xml:space="preserve">Primo Cares, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C195" s="65">
@@ -3128,117 +3128,117 @@
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
+          <t xml:space="preserve">Project Cure, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C196" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/14/2026</t>
+        </is>
+      </c>
+      <c r="C196" s="66">
+        <v>23.00</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
+          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C197" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C197" s="66">
+        <v>88.71</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">Pledgeling Foundation</t>
+          <t xml:space="preserve">Project Orbis International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
-        </is>
-      </c>
-      <c r="C198" s="66">
-        <v>65.93</v>
+          <t xml:space="preserve">10/7/2026</t>
+        </is>
+      </c>
+      <c r="C198" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">Polar Bears International</t>
+          <t xml:space="preserve">Proteus Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">2/2/2027</t>
+          <t xml:space="preserve">3/2/2027</t>
         </is>
       </c>
       <c r="C199" s="66">
-        <v>86.00</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">Political Economy Research Center, Inc.</t>
+          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">9/16/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C200" s="66">
-        <v>75.98</v>
+        <v>84.22</v>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
+          <t xml:space="preserve">Re:Power</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
-        </is>
-      </c>
-      <c r="C201" s="66">
-        <v>85.54</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C201" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">Pratt Institute</t>
+          <t xml:space="preserve">RezilientKidz</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C202" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/19/2026</t>
+        </is>
+      </c>
+      <c r="C202" s="66">
+        <v>94.67</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">Primo Cares, Inc.</t>
+          <t xml:space="preserve">Rodale Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C203" s="65">
@@ -3248,42 +3248,42 @@
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">Project Cure, Inc.</t>
+          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
-        </is>
-      </c>
-      <c r="C204" s="66">
-        <v>23.00</v>
+          <t xml:space="preserve">12/12/2026</t>
+        </is>
+      </c>
+      <c r="C204" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">10/7/2026</t>
         </is>
       </c>
       <c r="C205" s="66">
-        <v>88.71</v>
+        <v>45.00</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">Project Orbis International, Inc.</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C206" s="65">
@@ -3293,72 +3293,72 @@
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">Proteus Fund, Inc.</t>
+          <t xml:space="preserve">Rutgers University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
-        </is>
-      </c>
-      <c r="C207" s="66">
-        <v>81.25</v>
+          <t xml:space="preserve">9/15/2026</t>
+        </is>
+      </c>
+      <c r="C207" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
+          <t xml:space="preserve">Sagamore Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">9/22/2026</t>
         </is>
       </c>
       <c r="C208" s="66">
-        <v>84.22</v>
+        <v>91.52</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">Re:Power</t>
+          <t xml:space="preserve">Saint John's University</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C209" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C209" s="66">
+        <v>92.84</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">RezilientKidz</t>
+          <t xml:space="preserve">Save the Chimps, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">9/19/2026</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C210" s="66">
-        <v>94.67</v>
+        <v>79.70</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">Rodale Institute</t>
+          <t xml:space="preserve">Seattle Pacific University</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C211" s="65">
@@ -3368,42 +3368,42 @@
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
+          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">12/12/2026</t>
-        </is>
-      </c>
-      <c r="C212" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C212" s="66">
+        <v>97.29</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
+          <t xml:space="preserve">Sierra  Club</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
+          <t xml:space="preserve">12/22/2026</t>
         </is>
       </c>
       <c r="C213" s="66">
-        <v>45.00</v>
+        <v>82.00</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
+          <t xml:space="preserve">Sister Rising Worldwide</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">1/28/2027</t>
         </is>
       </c>
       <c r="C214" s="65">
@@ -3413,72 +3413,72 @@
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">Rutgers University Foundation</t>
+          <t xml:space="preserve">Sixpoint, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">9/15/2026</t>
-        </is>
-      </c>
-      <c r="C215" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/9/2027</t>
+        </is>
+      </c>
+      <c r="C215" s="66">
+        <v>77.16</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">Sagamore Institute, Inc.</t>
+          <t xml:space="preserve">Social Purpose Corrections</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C216" s="66">
-        <v>91.52</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">Saint John's University</t>
+          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
-        </is>
-      </c>
-      <c r="C217" s="66">
-        <v>92.84</v>
+          <t xml:space="preserve">10/15/2026</t>
+        </is>
+      </c>
+      <c r="C217" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">Save the Chimps, Inc.</t>
+          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">7/29/2027</t>
         </is>
       </c>
       <c r="C218" s="66">
-        <v>79.70</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">Seattle Pacific University</t>
+          <t xml:space="preserve">South Dakota State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C219" s="65">
@@ -3488,42 +3488,42 @@
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
+          <t xml:space="preserve">Southern Poverty Law Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C220" s="66">
-        <v>97.29</v>
+          <t xml:space="preserve">9/17/2026</t>
+        </is>
+      </c>
+      <c r="C220" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">Sierra  Club</t>
+          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">12/22/2026</t>
-        </is>
-      </c>
-      <c r="C221" s="66">
-        <v>82.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C221" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">Sister Rising Worldwide</t>
+          <t xml:space="preserve">Special Olympics, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">1/28/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C222" s="65">
@@ -3533,42 +3533,42 @@
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">Sixpoint, Inc.</t>
+          <t xml:space="preserve">SPLC Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
-        </is>
-      </c>
-      <c r="C223" s="66">
-        <v>77.16</v>
+          <t xml:space="preserve">9/17/2026</t>
+        </is>
+      </c>
+      <c r="C223" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">Social Purpose Corrections</t>
+          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C224" s="66">
-        <v>12.95</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C224" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
+          <t xml:space="preserve">Students for Life Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">11/7/2026</t>
         </is>
       </c>
       <c r="C225" s="65">
@@ -3578,57 +3578,57 @@
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">Soldiers' Angels</t>
+          <t xml:space="preserve">Students for Life of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">9/8/2026</t>
+          <t xml:space="preserve">10/10/2026</t>
         </is>
       </c>
       <c r="C226" s="66">
-        <v>90.51</v>
+        <v>82.00</v>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
+          <t xml:space="preserve">The Actors' Fund of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">7/29/2027</t>
+          <t xml:space="preserve">12/10/2026</t>
         </is>
       </c>
       <c r="C227" s="66">
-        <v>86.00</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">South Dakota State University Foundation</t>
+          <t xml:space="preserve">The American University</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C228" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/6/2026</t>
+        </is>
+      </c>
+      <c r="C228" s="66">
+        <v>92.06</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">Southern Poverty Law Center, Inc.</t>
+          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">9/17/2026</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C229" s="65">
@@ -3638,12 +3638,12 @@
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
+          <t xml:space="preserve">The Anthony Davis Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">11/24/2026</t>
         </is>
       </c>
       <c r="C230" s="65">
@@ -3653,57 +3653,57 @@
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">Special Olympics, Inc.</t>
+          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C231" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/24/2026</t>
+        </is>
+      </c>
+      <c r="C231" s="66">
+        <v>90.00</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">SPLC Action Fund</t>
+          <t xml:space="preserve">The Barack Obama Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">9/17/2026</t>
-        </is>
-      </c>
-      <c r="C232" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C232" s="66">
+        <v>55.90</v>
       </c>
     </row>
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
+          <t xml:space="preserve">The Center for Alcohol Policy</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C233" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/16/2027</t>
+        </is>
+      </c>
+      <c r="C233" s="66">
+        <v>73.40</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">Students for Life Action, Inc.</t>
+          <t xml:space="preserve">The Center for Investigative Reporting</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">11/7/2026</t>
+          <t xml:space="preserve">12/9/2026</t>
         </is>
       </c>
       <c r="C234" s="65">
@@ -3713,387 +3713,387 @@
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">Students for Life of America</t>
+          <t xml:space="preserve">The Colorado College</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
+          <t xml:space="preserve">10/29/2027</t>
         </is>
       </c>
       <c r="C235" s="66">
-        <v>82.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">The Actors' Fund of America</t>
+          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
-        </is>
-      </c>
-      <c r="C236" s="66">
-        <v>86.73</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C236" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">The American University</t>
+          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
-        </is>
-      </c>
-      <c r="C237" s="66">
-        <v>92.06</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C237" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+          <t xml:space="preserve">The Heritage Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C238" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C238" s="66">
+        <v>83.00</v>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">The Anthony Davis Foundation</t>
+          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">11/24/2026</t>
-        </is>
-      </c>
-      <c r="C239" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C239" s="66">
+        <v>83.06</v>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
+          <t xml:space="preserve">The Memorial Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">10/24/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C240" s="66">
-        <v>90.00</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">The Barack Obama Foundation</t>
+          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">12/1/2026</t>
         </is>
       </c>
       <c r="C241" s="66">
-        <v>55.90</v>
+        <v>80.87</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">The Center for Alcohol Policy</t>
+          <t xml:space="preserve">The Nature Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">10/9/2026</t>
         </is>
       </c>
       <c r="C242" s="66">
-        <v>73.40</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">The Center for Investigative Reporting</t>
+          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C243" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C243" s="66">
+        <v>80.64</v>
       </c>
     </row>
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">The Colorado College</t>
+          <t xml:space="preserve">The Ohio University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">10/29/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C244" s="66">
-        <v>90.00</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+          <t xml:space="preserve">The OneStar Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C245" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/14/2027</t>
+        </is>
+      </c>
+      <c r="C245" s="66">
+        <v>62.50</v>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C246" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C246" s="66">
+        <v>88.30</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">The Heritage Foundation</t>
+          <t xml:space="preserve">The Planetary Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">7/14/2027</t>
         </is>
       </c>
       <c r="C247" s="66">
-        <v>83.00</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+          <t xml:space="preserve">The Purchase College Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C248" s="66">
-        <v>83.06</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">The Memorial Foundation</t>
+          <t xml:space="preserve">The Ruth Collective</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C249" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C249" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C250" s="66">
-        <v>80.87</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">The Nature Conservancy</t>
+          <t xml:space="preserve">The University of Arizona Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
+          <t xml:space="preserve">9/29/2026</t>
         </is>
       </c>
       <c r="C251" s="66">
-        <v>70.00</v>
+        <v>76.49</v>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">4/13/2027</t>
         </is>
       </c>
       <c r="C252" s="66">
-        <v>80.64</v>
+        <v>82.20</v>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">The Ohio University Foundation</t>
+          <t xml:space="preserve">The University of Montana Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C253" s="66">
-        <v>74.14</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C253" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">The OneStar Foundation</t>
+          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
-        </is>
-      </c>
-      <c r="C254" s="66">
-        <v>62.50</v>
+          <t xml:space="preserve">10/15/2026</t>
+        </is>
+      </c>
+      <c r="C254" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C255" s="66">
-        <v>88.30</v>
+        <v>79.51</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">The Parker Family Legacy Foundation</t>
+          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">9/9/2026</t>
-        </is>
-      </c>
-      <c r="C256" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/26/2026</t>
+        </is>
+      </c>
+      <c r="C256" s="66">
+        <v>89.50</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">The Planetary Society</t>
+          <t xml:space="preserve">Turning Point USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">7/14/2027</t>
-        </is>
-      </c>
-      <c r="C257" s="66">
-        <v>66.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C257" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">The Purchase College Foundation</t>
+          <t xml:space="preserve">Twelveacres, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C258" s="66">
-        <v>78.12</v>
+        <v>79.93</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
+          <t xml:space="preserve">UATX</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">9/9/2026</t>
-        </is>
-      </c>
-      <c r="C259" s="66">
-        <v>77.87</v>
+          <t xml:space="preserve">2/1/2027</t>
+        </is>
+      </c>
+      <c r="C259" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">The Ruth Collective</t>
+          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C260" s="65">
@@ -4103,147 +4103,147 @@
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+          <t xml:space="preserve">UMKC Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C261" s="66">
-        <v>94.00</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">The University of Arizona Foundation</t>
+          <t xml:space="preserve">Unified Youth</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">9/29/2026</t>
-        </is>
-      </c>
-      <c r="C262" s="66">
-        <v>76.49</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C262" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">4/13/2027</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C263" s="66">
-        <v>82.20</v>
+        <v>86.96</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">The University of Montana Foundation</t>
+          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C264" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C264" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
+          <t xml:space="preserve">united Service Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
-        </is>
-      </c>
-      <c r="C265" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/10/2026</t>
+        </is>
+      </c>
+      <c r="C265" s="66">
+        <v>67.94</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+          <t xml:space="preserve">United States Center for SafeSport</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C266" s="66">
-        <v>79.51</v>
+        <v>72.74</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+          <t xml:space="preserve">University of Colorado</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
-        </is>
-      </c>
-      <c r="C267" s="66">
-        <v>89.50</v>
+          <t xml:space="preserve">10/7/2026</t>
+        </is>
+      </c>
+      <c r="C267" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">Turning Point USA, Inc.</t>
+          <t xml:space="preserve">University of Georgia Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C268" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/26/2026</t>
+        </is>
+      </c>
+      <c r="C268" s="66">
+        <v>94.00</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">Twelveacres, Incorporated</t>
+          <t xml:space="preserve">University of Nebraska Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">7/15/2027</t>
         </is>
       </c>
       <c r="C269" s="66">
-        <v>79.93</v>
+        <v>81.10</v>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">UATX</t>
+          <t xml:space="preserve">University of Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">2/1/2027</t>
+          <t xml:space="preserve">11/12/2026</t>
         </is>
       </c>
       <c r="C270" s="65">
@@ -4253,42 +4253,42 @@
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C271" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C271" s="66">
+        <v>28.00</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">UMKC Foundation</t>
+          <t xml:space="preserve">VoteAmerica, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C272" s="66">
-        <v>95.00</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">Unified Youth</t>
+          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C273" s="65">
@@ -4298,72 +4298,72 @@
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+          <t xml:space="preserve">Washington State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">7/8/2027</t>
         </is>
       </c>
       <c r="C274" s="66">
-        <v>86.96</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">11/5/2026</t>
         </is>
       </c>
       <c r="C275" s="66">
-        <v>85.00</v>
+        <v>82.68</v>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">united Service Organizations, Inc.</t>
+          <t xml:space="preserve">Women for Women International</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">11/10/2026</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C276" s="66">
-        <v>67.94</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">United States Center for SafeSport</t>
+          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C277" s="66">
-        <v>72.74</v>
+        <v>71.40</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">University of Colorado</t>
+          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
+          <t xml:space="preserve">2/20/2027</t>
         </is>
       </c>
       <c r="C278" s="65">
@@ -4373,195 +4373,15 @@
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">University of Georgia Foundation</t>
+          <t xml:space="preserve">YMCA of the Rockies</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C279" s="66">
-        <v>94.00</v>
-      </c>
-    </row>
-    <row r="280">
-      <c t="inlineStr" r="A280">
-        <is>
-          <t xml:space="preserve">University of Nebraska Foundation</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B280">
-        <is>
-          <t xml:space="preserve">7/15/2027</t>
-        </is>
-      </c>
-      <c r="C280" s="66">
-        <v>81.10</v>
-      </c>
-    </row>
-    <row r="281">
-      <c t="inlineStr" r="A281">
-        <is>
-          <t xml:space="preserve">University of Northern Iowa Foundation</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B281">
-        <is>
-          <t xml:space="preserve">9/10/2026</t>
-        </is>
-      </c>
-      <c r="C281" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c t="inlineStr" r="A282">
-        <is>
-          <t xml:space="preserve">University of Pacific</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B282">
-        <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C282" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c t="inlineStr" r="A283">
-        <is>
-          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B283">
-        <is>
-          <t xml:space="preserve">11/5/2026</t>
-        </is>
-      </c>
-      <c r="C283" s="66">
-        <v>28.00</v>
-      </c>
-    </row>
-    <row r="284">
-      <c t="inlineStr" r="A284">
-        <is>
-          <t xml:space="preserve">VoteAmerica, Inc.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B284">
-        <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C284" s="66">
-        <v>93.37</v>
-      </c>
-    </row>
-    <row r="285">
-      <c t="inlineStr" r="A285">
-        <is>
-          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B285">
-        <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C285" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286">
-      <c t="inlineStr" r="A286">
-        <is>
-          <t xml:space="preserve">Washington State University Foundation</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B286">
-        <is>
-          <t xml:space="preserve">7/8/2027</t>
-        </is>
-      </c>
-      <c r="C286" s="66">
-        <v>75.03</v>
-      </c>
-    </row>
-    <row r="287">
-      <c t="inlineStr" r="A287">
-        <is>
-          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B287">
-        <is>
-          <t xml:space="preserve">11/5/2026</t>
-        </is>
-      </c>
-      <c r="C287" s="66">
-        <v>82.68</v>
-      </c>
-    </row>
-    <row r="288">
-      <c t="inlineStr" r="A288">
-        <is>
-          <t xml:space="preserve">Women for Women International</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B288">
-        <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C288" s="66">
-        <v>79.06</v>
-      </c>
-    </row>
-    <row r="289">
-      <c t="inlineStr" r="A289">
-        <is>
-          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B289">
-        <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C289" s="66">
-        <v>71.40</v>
-      </c>
-    </row>
-    <row r="290">
-      <c t="inlineStr" r="A290">
-        <is>
-          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B290">
-        <is>
-          <t xml:space="preserve">2/20/2027</t>
-        </is>
-      </c>
-      <c r="C290" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291">
-      <c t="inlineStr" r="A291">
-        <is>
-          <t xml:space="preserve">YMCA of the Rockies</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B291">
-        <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C291" s="66">
         <v>81.65</v>
       </c>
     </row>

--- a/downloadable-data/LA.xlsx
+++ b/downloadable-data/LA.xlsx
@@ -233,207 +233,207 @@
     <row r="3">
       <c t="inlineStr" r="A3">
         <is>
-          <t xml:space="preserve">1776 Project Foundation</t>
+          <t xml:space="preserve">#iGiveCatholic</t>
         </is>
       </c>
       <c t="inlineStr" r="B3">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/9/2027</t>
+        </is>
+      </c>
+      <c r="C3" s="66">
+        <v>98.30</v>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">70 Faces Media, Inc.</t>
+          <t xml:space="preserve">1776 Project Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
-        </is>
-      </c>
-      <c r="C4" s="66">
-        <v>80.74</v>
+          <t xml:space="preserve">12/18/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">Action Against Hunger</t>
+          <t xml:space="preserve">32 North Media, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C5" s="66">
-        <v>90.00</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">AFA Action, Inc.</t>
+          <t xml:space="preserve">70 Faces Media, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">3/27/2027</t>
         </is>
       </c>
       <c r="C6" s="66">
-        <v>67.56</v>
+        <v>80.74</v>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">Air &amp; Space Force Association</t>
+          <t xml:space="preserve">A Hope to Dream, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
+          <t xml:space="preserve">7/14/2027</t>
         </is>
       </c>
       <c r="C7" s="66">
-        <v>79.11</v>
+        <v>91.36</v>
       </c>
     </row>
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">Al-Mawrid United States, Inc.</t>
+          <t xml:space="preserve">Abilene Christian University</t>
         </is>
       </c>
       <c t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/12/2027</t>
+        </is>
+      </c>
+      <c r="C8" s="66">
+        <v>70.00</v>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">Alaska Conservation Foundation</t>
+          <t xml:space="preserve">ACT for America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C9" s="66">
-        <v>78.77</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">All God's Children International</t>
+          <t xml:space="preserve">Action Against Hunger</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">2/23/2027</t>
         </is>
       </c>
       <c r="C10" s="66">
-        <v>87.31</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">Alpha Gamma Delta Foundation, Inc.</t>
+          <t xml:space="preserve">Adventist Development and Relief Agency Int.</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/28/2027</t>
+        </is>
+      </c>
+      <c r="C11" s="66">
+        <v>87.00</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">Alpha Kappa Psi Foundation</t>
+          <t xml:space="preserve">AFA Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">1/8/2027</t>
-        </is>
-      </c>
-      <c r="C12" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/14/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="66">
+        <v>67.56</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">ALTA Charitable Foundation</t>
+          <t xml:space="preserve">Air &amp; Space Force Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">2/10/2027</t>
         </is>
       </c>
       <c r="C13" s="66">
-        <v>48.00</v>
+        <v>79.11</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">Alternate ROOTS, Inc.</t>
+          <t xml:space="preserve">Air Force Academy Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">1/1/2027</t>
-        </is>
-      </c>
-      <c r="C14" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/6/2027</t>
+        </is>
+      </c>
+      <c r="C14" s="66">
+        <v>85.57</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">America's Survival, Inc.</t>
+          <t xml:space="preserve">Air Transport Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">4/20/2027</t>
         </is>
       </c>
       <c r="C15" s="66">
-        <v>90.07</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">American Association of Family and Consumer Scienc</t>
+          <t xml:space="preserve">Al-Mawrid United States, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
+          <t xml:space="preserve">10/6/2026</t>
         </is>
       </c>
       <c r="C16" s="65">
@@ -443,222 +443,222 @@
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">American Association of State Troopers, Inc.</t>
+          <t xml:space="preserve">Alaska Conservation Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C17" s="66">
-        <v>23.00</v>
+        <v>79.96</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">American Bible Society</t>
+          <t xml:space="preserve">All God's Children International</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C18" s="66">
-        <v>76.00</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">American Civil Liberties Union Foundation, Inc.</t>
+          <t xml:space="preserve">All Hands and Hearts Smart Response</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C19" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/29/2027</t>
+        </is>
+      </c>
+      <c r="C19" s="66">
+        <v>93.41</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">American Council of the Blind, Inc.</t>
+          <t xml:space="preserve">Alliance for Gun Responsibility</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">10/16/2026</t>
-        </is>
-      </c>
-      <c r="C20" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C20" s="66">
+        <v>75.80</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">American Diabetes Association</t>
+          <t xml:space="preserve">Alpha Gamma Delta Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
-        </is>
-      </c>
-      <c r="C21" s="66">
-        <v>79.18</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">American Indian College Fund</t>
+          <t xml:space="preserve">Alpha Kappa Psi Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">11/13/2026</t>
-        </is>
-      </c>
-      <c r="C22" s="66">
-        <v>78.00</v>
+          <t xml:space="preserve">1/8/2027</t>
+        </is>
+      </c>
+      <c r="C22" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">American Institute for Cancer Research</t>
+          <t xml:space="preserve">ALTA Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">9/18/2026</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C23" s="66">
-        <v>62.00</v>
+        <v>48.00</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">American Institute for Economic Research</t>
+          <t xml:space="preserve">Alternate ROOTS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C24" s="66">
-        <v>78.63</v>
+          <t xml:space="preserve">1/1/2027</t>
+        </is>
+      </c>
+      <c r="C24" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">American Kidney Fund, Inc.</t>
+          <t xml:space="preserve">America's Survival, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C25" s="66">
-        <v>95.70</v>
+        <v>90.07</v>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
+          <t xml:space="preserve">American Association of Family and Consumer Scienc</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
-        </is>
-      </c>
-      <c r="C26" s="66">
-        <v>75.08</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">American Roentgen Ray Society</t>
+          <t xml:space="preserve">American Association of State Troopers, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C27" s="66">
-        <v>52.00</v>
+        <v>23.00</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">Americans For Fair Treatment</t>
+          <t xml:space="preserve">American Bible Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C28" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/27/2027</t>
+        </is>
+      </c>
+      <c r="C28" s="66">
+        <v>76.00</v>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
+          <t xml:space="preserve">American Civil Liberties Union Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
-        </is>
-      </c>
-      <c r="C29" s="66">
-        <v>71.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">Animals' Angels, Incorporated</t>
+          <t xml:space="preserve">American Congress for Truth, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
-        </is>
-      </c>
-      <c r="C30" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/28/2027</t>
+        </is>
+      </c>
+      <c r="C30" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
+          <t xml:space="preserve">American Council of the Blind, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/16/2026</t>
         </is>
       </c>
       <c r="C31" s="65">
@@ -668,327 +668,327 @@
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">Association of American Education Foundation</t>
+          <t xml:space="preserve">American Diabetes Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C32" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/26/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="66">
+        <v>79.18</v>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
+          <t xml:space="preserve">American Foundation for the Blind, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">3/23/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C33" s="66">
-        <v>81.00</v>
+        <v>66.78</v>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">Autism Speaks, Inc.</t>
+          <t xml:space="preserve">American Indian College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C34" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/13/2026</t>
+        </is>
+      </c>
+      <c r="C34" s="66">
+        <v>78.00</v>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
+          <t xml:space="preserve">American Institute for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C35" s="66">
-        <v>44.00</v>
+        <v>67.00</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">B'nai B'rith International</t>
+          <t xml:space="preserve">American Institute for Economic Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C36" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C36" s="66">
+        <v>78.63</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">Back Bay Mission, Inc.</t>
+          <t xml:space="preserve">American Kidney Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">5/12/2027</t>
         </is>
       </c>
       <c r="C37" s="66">
-        <v>83.67</v>
+        <v>95.70</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">Base Ministry</t>
+          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C38" s="66">
-        <v>71.89</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">Blood Cancer United, Inc.</t>
+          <t xml:space="preserve">American Lung Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">5/26/2027</t>
         </is>
       </c>
       <c r="C39" s="66">
-        <v>75.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
+          <t xml:space="preserve">American Near East Refugee Aid, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C40" s="66">
-        <v>71.00</v>
+        <v>95.44</v>
       </c>
     </row>
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
+          <t xml:space="preserve">American Roentgen Ray Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">10/9/2026</t>
         </is>
       </c>
       <c r="C41" s="66">
-        <v>78.58</v>
+        <v>52.00</v>
       </c>
     </row>
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">Business Action Fund</t>
+          <t xml:space="preserve">Americans For Fair Treatment</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
-        </is>
-      </c>
-      <c r="C42" s="66">
-        <v>54.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">Cair-Foundation, Inc.</t>
+          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">10/14/2026</t>
         </is>
       </c>
       <c r="C43" s="66">
-        <v>66.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">Captain Joseph House Foundation</t>
+          <t xml:space="preserve">Animals' Angels, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C44" s="66">
-        <v>67.20</v>
+          <t xml:space="preserve">9/22/2026</t>
+        </is>
+      </c>
+      <c r="C44" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
+          <t xml:space="preserve">Anti-Defamation League</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C45" s="66">
-        <v>97.00</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">Center for Community Change Action</t>
+          <t xml:space="preserve">Arkansas Tech University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C46" s="66">
-        <v>95.00</v>
+        <v>94.06</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">Central Asia Institute</t>
+          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C47" s="66">
-        <v>77.29</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C47" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">Charities Aid Foundation America</t>
+          <t xml:space="preserve">Association of American Education Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C48" s="66">
-        <v>0.01</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">Childhelp, Inc.</t>
+          <t xml:space="preserve">Austin College</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">6/30/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C49" s="66">
-        <v>70.00</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
+          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C50" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/23/2027</t>
+        </is>
+      </c>
+      <c r="C50" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">Children's Miracle Network</t>
+          <t xml:space="preserve">Autism Speaks, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C51" s="66">
-        <v>80.77</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C51" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
+          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C52" s="66">
-        <v>89.98</v>
+        <v>44.00</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
+          <t xml:space="preserve">B'nai B'rith International</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">12/18/2026</t>
         </is>
       </c>
       <c r="C53" s="65">
@@ -998,237 +998,237 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Christian Relief Services, Inc.</t>
+          <t xml:space="preserve">Back Bay Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C54" s="66">
-        <v>90.70</v>
+        <v>83.67</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
+          <t xml:space="preserve">Base Ministry</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C55" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/16/2027</t>
+        </is>
+      </c>
+      <c r="C55" s="66">
+        <v>71.89</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">Christian Union, Inc.</t>
+          <t xml:space="preserve">Blood Cancer United, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C56" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C56" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">City Year, Inc.</t>
+          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C57" s="66">
-        <v>82.62</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">Civil Rights Corps</t>
+          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C58" s="66">
-        <v>82.10</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
+          <t xml:space="preserve">Business Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">11/20/2026</t>
-        </is>
-      </c>
-      <c r="C59" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/30/2027</t>
+        </is>
+      </c>
+      <c r="C59" s="66">
+        <v>54.00</v>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
+          <t xml:space="preserve">Cair-Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C60" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/14/2027</t>
+        </is>
+      </c>
+      <c r="C60" s="66">
+        <v>66.00</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
+          <t xml:space="preserve">CAMFED USA Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C61" s="66">
-        <v>65.99</v>
+        <v>91.78</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Concerns of Police Survivors</t>
+          <t xml:space="preserve">Captain Joseph House Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C62" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C62" s="66">
+        <v>67.20</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Consumer Reports, Inc.</t>
+          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">10/14/2026</t>
         </is>
       </c>
       <c r="C63" s="66">
-        <v>84.00</v>
+        <v>97.00</v>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">Cooperative for Assistance and Relief Everywhere</t>
+          <t xml:space="preserve">Center for Community Change Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
-        </is>
-      </c>
-      <c r="C64" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/27/2027</t>
+        </is>
+      </c>
+      <c r="C64" s="66">
+        <v>95.00</v>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">Covenant House</t>
+          <t xml:space="preserve">Central Asia Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C65" s="66">
-        <v>80.00</v>
+        <v>77.29</v>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
+          <t xml:space="preserve">Chapel Haven Schleifer Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C66" s="66">
-        <v>84.38</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
+          <t xml:space="preserve">Charities Aid Foundation America</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C67" s="66">
-        <v>70.00</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
+          <t xml:space="preserve">Childhelp, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">6/30/2027</t>
         </is>
       </c>
       <c r="C68" s="66">
-        <v>64.30</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">Daring Girls</t>
+          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
+          <t xml:space="preserve">12/18/2026</t>
         </is>
       </c>
       <c r="C69" s="65">
@@ -1238,162 +1238,162 @@
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
+          <t xml:space="preserve">Children's Miracle Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C70" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/20/2026</t>
+        </is>
+      </c>
+      <c r="C70" s="66">
+        <v>80.77</v>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">Disabled American Veterans</t>
+          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">9/18/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C71" s="66">
-        <v>67.00</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">Disabled Veterans National Foundation</t>
+          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">9/25/2026</t>
-        </is>
-      </c>
-      <c r="C72" s="66">
-        <v>20.85</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C72" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
+          <t xml:space="preserve">Christian Relief Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
+          <t xml:space="preserve">2/10/2027</t>
         </is>
       </c>
       <c r="C73" s="66">
-        <v>49.00</v>
+        <v>90.70</v>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">East Carolina University Foundation, Inc.</t>
+          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
-        </is>
-      </c>
-      <c r="C74" s="66">
-        <v>55.44</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C74" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
+          <t xml:space="preserve">Christian Union, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
-        </is>
-      </c>
-      <c r="C75" s="66">
-        <v>61.48</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C75" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">Easter Seals, Inc.</t>
+          <t xml:space="preserve">City Rescue Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C76" s="66">
-        <v>68.00</v>
+        <v>85.32</v>
       </c>
     </row>
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">EB Research Partnership, Inc.</t>
+          <t xml:space="preserve">City Year, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C77" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C77" s="66">
+        <v>82.62</v>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">Economic Policy Institute</t>
+          <t xml:space="preserve">Civil Rights Corps</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C78" s="66">
-        <v>83.70</v>
+        <v>82.10</v>
       </c>
     </row>
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">Einstein School Foundation</t>
+          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">9/17/2026</t>
-        </is>
-      </c>
-      <c r="C79" s="66">
-        <v>87.00</v>
+          <t xml:space="preserve">11/20/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">ELT Ventures</t>
+          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C80" s="65">
@@ -1403,207 +1403,207 @@
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">Empire State University Foundation</t>
+          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">4/9/2027</t>
         </is>
       </c>
       <c r="C81" s="66">
-        <v>82.78</v>
+        <v>65.99</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
+          <t xml:space="preserve">Compassion and Choices</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C82" s="66">
-        <v>48.32</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
+          <t xml:space="preserve">Compassion and Choices Action Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">3/6/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C83" s="66">
-        <v>87.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Family Policy Alliance</t>
+          <t xml:space="preserve">Concerns of Police Survivors</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
-        </is>
-      </c>
-      <c r="C84" s="66">
-        <v>80.48</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
+          <t xml:space="preserve">Consumer Reports, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C85" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/14/2027</t>
+        </is>
+      </c>
+      <c r="C85" s="66">
+        <v>84.00</v>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Feeding America</t>
+          <t xml:space="preserve">Cooperative for Assistance and Relief Everywhere</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
-        </is>
-      </c>
-      <c r="C86" s="66">
-        <v>98.40</v>
+          <t xml:space="preserve">10/1/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
+          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C87" s="66">
-        <v>82.48</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Firefighters Charitable Foundation, Inc.</t>
+          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">9/16/2026</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C88" s="66">
-        <v>8.20</v>
+        <v>74.54</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
+          <t xml:space="preserve">Covenant House</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C89" s="66">
-        <v>89.30</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">For Others Collective, Inc.</t>
+          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C90" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/4/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="66">
+        <v>84.38</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
+          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C91" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/30/2027</t>
+        </is>
+      </c>
+      <c r="C91" s="66">
+        <v>85.18</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">Fractracker Alliance</t>
+          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C92" s="66">
-        <v>77.78</v>
+        <v>64.30</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
+          <t xml:space="preserve">Daring Girls</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
-        </is>
-      </c>
-      <c r="C93" s="66">
-        <v>68.41</v>
+          <t xml:space="preserve">9/26/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
+          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C94" s="65">
@@ -1613,417 +1613,417 @@
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Friends of KEXP</t>
+          <t xml:space="preserve">Deep South Today</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C95" s="66">
-        <v>66.97</v>
+        <v>74.56</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
+          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
+          <t xml:space="preserve">6/6/2027</t>
         </is>
       </c>
       <c r="C96" s="66">
-        <v>67.76</v>
+        <v>68.82</v>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Futures Without Violence</t>
+          <t xml:space="preserve">Disabled Veterans National Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C97" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/25/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="66">
+        <v>20.85</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Givinga Foundation</t>
+          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">10/30/2026</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C98" s="66">
-        <v>94.03</v>
+        <v>49.00</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
+          <t xml:space="preserve">East Carolina University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">3/11/2027</t>
+          <t xml:space="preserve">10/10/2026</t>
         </is>
       </c>
       <c r="C99" s="66">
-        <v>49.91</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">Go Campaign</t>
+          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C100" s="66">
-        <v>77.86</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Green America</t>
+          <t xml:space="preserve">Easter Seals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C101" s="66">
-        <v>87.47</v>
+        <v>68.00</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
+          <t xml:space="preserve">EB Research Partnership, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C102" s="66">
-        <v>76.85</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C102" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Greenpeace, Inc.</t>
+          <t xml:space="preserve">Economic Policy Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">9/26/2026</t>
         </is>
       </c>
       <c r="C103" s="66">
-        <v>62.56</v>
+        <v>83.70</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">Gustavus Adolphus College</t>
+          <t xml:space="preserve">ELT Ventures</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">2/24/2027</t>
-        </is>
-      </c>
-      <c r="C104" s="66">
-        <v>93.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C104" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Habitat for Horses, Inc.</t>
+          <t xml:space="preserve">Empire State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C105" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C105" s="66">
+        <v>82.78</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
+          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C106" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C106" s="66">
+        <v>48.32</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Healing Protectors</t>
+          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
+          <t xml:space="preserve">3/6/2027</t>
         </is>
       </c>
       <c r="C107" s="66">
-        <v>47.19</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">Heifer Project International</t>
+          <t xml:space="preserve">Fairplay, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">3/19/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C108" s="66">
-        <v>72.90</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">Help Me See, Inc.</t>
+          <t xml:space="preserve">Faith and Freedom Coalition, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="C109" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C109" s="66">
+        <v>72.00</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
+          <t xml:space="preserve">Family Policy Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C110" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C110" s="66">
+        <v>80.48</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">Heroes on the Water</t>
+          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
-        </is>
-      </c>
-      <c r="C111" s="66">
-        <v>75.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">HIAS Foundation, Inc.</t>
+          <t xml:space="preserve">Feed The Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C112" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/19/2027</t>
+        </is>
+      </c>
+      <c r="C112" s="66">
+        <v>91.00</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">Home Builders Institute</t>
+          <t xml:space="preserve">Feeding America</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C113" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/6/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="66">
+        <v>98.40</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Houston Christian Broadcasters, Inc.</t>
+          <t xml:space="preserve">Feeding Pets of the Homeless</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C114" s="66">
-        <v>84.40</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">Human Appeal, Inc.</t>
+          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">1/12/2027</t>
+          <t xml:space="preserve">4/9/2027</t>
         </is>
       </c>
       <c r="C115" s="66">
-        <v>54.20</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
+          <t xml:space="preserve">FINCA International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">5/7/2027</t>
         </is>
       </c>
       <c r="C116" s="66">
-        <v>63.39</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Human Rights Watch, Inc.</t>
+          <t xml:space="preserve">Find The Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C117" s="66">
-        <v>72.65</v>
+        <v>50.00</v>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">Humane World for Animals, Inc.</t>
+          <t xml:space="preserve">Food Bank of Northeast Louisiana, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">9/15/2026</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C118" s="66">
-        <v>75.00</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
+          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C119" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/9/2027</t>
+        </is>
+      </c>
+      <c r="C119" s="66">
+        <v>89.30</v>
       </c>
     </row>
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">In Medias Res</t>
+          <t xml:space="preserve">Food for the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C120" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/4/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">Independent Council on Women's Sport</t>
+          <t xml:space="preserve">For Others Collective, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C121" s="66">
-        <v>94.44</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C121" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">INROADS, Inc.</t>
+          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">9/24/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C122" s="65">
@@ -2033,42 +2033,42 @@
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
+          <t xml:space="preserve">Fractracker Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C123" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C123" s="66">
+        <v>77.78</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
+          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C124" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/1/2027</t>
+        </is>
+      </c>
+      <c r="C124" s="66">
+        <v>68.41</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">International Justice Mission</t>
+          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C125" s="65">
@@ -2078,352 +2078,352 @@
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
+          <t xml:space="preserve">Friends of KEXP</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/10/2026</t>
         </is>
       </c>
       <c r="C126" s="66">
-        <v>83.13</v>
+        <v>66.97</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">International Union of Police Associations</t>
+          <t xml:space="preserve">Friends of the Neuberger Museum of Art, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C127" s="66">
-        <v>47.90</v>
+        <v>66.80</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
+          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C128" s="66">
-        <v>75.43</v>
+        <v>75.34</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">Jewish Democratic Council of America</t>
+          <t xml:space="preserve">Futures Without Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C129" s="66">
-        <v>50.07</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C129" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">Jewish Voice Ministries International</t>
+          <t xml:space="preserve">Givinga Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C130" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/30/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="66">
+        <v>94.03</v>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
+          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
+          <t xml:space="preserve">3/11/2027</t>
         </is>
       </c>
       <c r="C131" s="66">
-        <v>89.00</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
+          <t xml:space="preserve">Go Campaign</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C132" s="66">
-        <v>80.00</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">Khan Academy, Inc.</t>
+          <t xml:space="preserve">Green America</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C133" s="66">
-        <v>86.36</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
+          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C134" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="66">
+        <v>76.85</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">L.E.A.D. Inc.</t>
+          <t xml:space="preserve">Greenpeace, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C135" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="66">
+        <v>62.56</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
+          <t xml:space="preserve">Gustavus Adolphus College</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C136" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/24/2027</t>
+        </is>
+      </c>
+      <c r="C136" s="66">
+        <v>93.00</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
+          <t xml:space="preserve">Habitat for Horses, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">10/28/2026</t>
-        </is>
-      </c>
-      <c r="C137" s="66">
-        <v>96.80</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">Living Waters for the World</t>
+          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C138" s="66">
-        <v>78.81</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
+          <t xml:space="preserve">Healing Justice Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C139" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C139" s="66">
+        <v>82.48</v>
       </c>
     </row>
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
+          <t xml:space="preserve">Healing Protectors</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">10/29/2026</t>
+          <t xml:space="preserve">3/2/2027</t>
         </is>
       </c>
       <c r="C140" s="66">
-        <v>70.18</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
+          <t xml:space="preserve">Heifer Project International</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">9/25/2026</t>
-        </is>
-      </c>
-      <c r="C141" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/19/2027</t>
+        </is>
+      </c>
+      <c r="C141" s="66">
+        <v>72.90</v>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">MAP International, Inc.</t>
+          <t xml:space="preserve">Help Me See, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C142" s="66">
-        <v>99.00</v>
+          <t xml:space="preserve">10/3/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">March of Dimes</t>
+          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">12/30/2026</t>
-        </is>
-      </c>
-      <c r="C143" s="66">
-        <v>74.00</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
+          <t xml:space="preserve">Heroes on the Water</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">12/8/2026</t>
-        </is>
-      </c>
-      <c r="C144" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/1/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">Mercy for Animals, Inc.</t>
+          <t xml:space="preserve">HIAS Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C145" s="66">
-        <v>75.82</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C145" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
+          <t xml:space="preserve">Home Builders Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
-        </is>
-      </c>
-      <c r="C146" s="66">
-        <v>88.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C146" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
+          <t xml:space="preserve">Houston Christian Broadcasters, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">10/6/2026</t>
         </is>
       </c>
       <c r="C147" s="66">
-        <v>94.50</v>
+        <v>84.40</v>
       </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">Mount Saint Marys University</t>
+          <t xml:space="preserve">Human Appeal, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C148" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/12/2027</t>
+        </is>
+      </c>
+      <c r="C148" s="66">
+        <v>54.20</v>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">Mountain States Legal Foundation</t>
+          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
@@ -2432,63 +2432,63 @@
         </is>
       </c>
       <c r="C149" s="66">
-        <v>69.99</v>
+        <v>63.39</v>
       </c>
     </row>
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">MrCharity, Inc.</t>
+          <t xml:space="preserve">Human Rights Watch, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
-        </is>
-      </c>
-      <c r="C150" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/20/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="66">
+        <v>72.65</v>
       </c>
     </row>
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
+          <t xml:space="preserve">Humane Society of Missouri</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">8/7/2027</t>
         </is>
       </c>
       <c r="C151" s="66">
-        <v>54.00</v>
+        <v>80.50</v>
       </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
+          <t xml:space="preserve">Illinois State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">12/19/2026</t>
+          <t xml:space="preserve">5/21/2027</t>
         </is>
       </c>
       <c r="C152" s="66">
-        <v>66.90</v>
+        <v>61.30</v>
       </c>
     </row>
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
+          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C153" s="65">
@@ -2498,7 +2498,7 @@
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">National Council of Nonprofits</t>
+          <t xml:space="preserve">In Medias Res</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
@@ -2513,72 +2513,72 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
+          <t xml:space="preserve">Independent Council on Women's Sport</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C155" s="66">
-        <v>49.00</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">National Foundation for Cancer Research</t>
+          <t xml:space="preserve">Infact</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C156" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C156" s="66">
+        <v>89.97</v>
       </c>
     </row>
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">National Geographic Society</t>
+          <t xml:space="preserve">INROADS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">3/18/2027</t>
-        </is>
-      </c>
-      <c r="C157" s="66">
-        <v>77.00</v>
+          <t xml:space="preserve">9/24/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">National Museum of Women in the Arts, Inc.</t>
+          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="C158" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">National Organization for Women, Inc</t>
+          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">9/19/2026</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C159" s="65">
@@ -2588,192 +2588,192 @@
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">National Park Foundation</t>
+          <t xml:space="preserve">International Justice Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C160" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">3/24/2027</t>
+        </is>
+      </c>
+      <c r="C160" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">National PKU Alliance, Inc.</t>
+          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C161" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C161" s="66">
+        <v>83.13</v>
       </c>
     </row>
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">National Rifle Association of America</t>
+          <t xml:space="preserve">International Union of Police Associations</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">9/17/2026</t>
-        </is>
-      </c>
-      <c r="C162" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="66">
+        <v>47.90</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
+          <t xml:space="preserve">Iona University</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C163" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C163" s="66">
+        <v>89.81</v>
       </c>
     </row>
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
+          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C164" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/27/2027</t>
+        </is>
+      </c>
+      <c r="C164" s="66">
+        <v>75.43</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">National Space Society</t>
+          <t xml:space="preserve">Jewish Democratic Council of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C165" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C165" s="66">
+        <v>50.07</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">National University</t>
+          <t xml:space="preserve">Jewish Voice Ministries International</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C166" s="66">
-        <v>42.69</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C166" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">National Veterans Memorial and Museum</t>
+          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C167" s="66">
-        <v>72.63</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">National Wheelchair Basketball Association</t>
+          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C168" s="66">
-        <v>77.80</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
+          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C169" s="66">
-        <v>2.90</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">Network for Good, Inc</t>
+          <t xml:space="preserve">Khan Academy, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C170" s="66">
-        <v>97.80</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">New Harvest, Inc.</t>
+          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C171" s="66">
-        <v>88.49</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
+          <t xml:space="preserve">L.E.A.D. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C172" s="65">
@@ -2783,127 +2783,127 @@
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">Nurse-Family Partnership</t>
+          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C173" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C173" s="66">
+        <v>63.00</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">Ocean Conservancy</t>
+          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C174" s="66">
-        <v>74.06</v>
+        <v>10.60</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
+          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C175" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/28/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="66">
+        <v>96.80</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">OneHope, Inc.</t>
+          <t xml:space="preserve">Life Teen, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C176" s="66">
-        <v>82.72</v>
+        <v>76.40</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">Operation Smile, Inc.</t>
+          <t xml:space="preserve">Live Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C177" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C177" s="66">
+        <v>81.13</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">Our Change Foundation</t>
+          <t xml:space="preserve">Living Waters for the World</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C178" s="66">
-        <v>80.46</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">Oxfam-America, Inc.</t>
+          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
-        </is>
-      </c>
-      <c r="C179" s="66">
-        <v>71.00</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C179" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
+          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">10/29/2026</t>
         </is>
       </c>
       <c r="C180" s="66">
-        <v>55.43</v>
+        <v>70.18</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">Parkinson Research Foundation, Inc.</t>
+          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
@@ -2918,102 +2918,102 @@
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
+          <t xml:space="preserve">Madison House</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">2/9/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C182" s="66">
-        <v>90.00</v>
+        <v>77.79</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
+          <t xml:space="preserve">MAP International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
-        </is>
-      </c>
-      <c r="C183" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="66">
+        <v>99.00</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">People for the American Way</t>
+          <t xml:space="preserve">March of Dimes</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">9/18/2026</t>
+          <t xml:space="preserve">12/30/2026</t>
         </is>
       </c>
       <c r="C184" s="66">
-        <v>46.61</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">People for the American Way Foundation</t>
+          <t xml:space="preserve">Marist University</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">9/18/2026</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C185" s="66">
-        <v>55.83</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
+          <t xml:space="preserve">Meals on Wheels America</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">5/27/2027</t>
         </is>
       </c>
       <c r="C186" s="66">
-        <v>58.00</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
+          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C187" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/9/2027</t>
+        </is>
+      </c>
+      <c r="C187" s="66">
+        <v>80.94</v>
       </c>
     </row>
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
+          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
+          <t xml:space="preserve">12/8/2026</t>
         </is>
       </c>
       <c r="C188" s="65">
@@ -3023,102 +3023,102 @@
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
+          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C189" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C189" s="66">
+        <v>91.00</v>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">Pledgeling Foundation</t>
+          <t xml:space="preserve">Mercatus Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C190" s="66">
-        <v>65.93</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">Polar Bears International</t>
+          <t xml:space="preserve">Mercy for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">2/2/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C191" s="66">
-        <v>86.00</v>
+        <v>75.82</v>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">Political Economy Research Center, Inc.</t>
+          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">9/16/2026</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C192" s="66">
-        <v>75.98</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
+          <t xml:space="preserve">Miracle Flights</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C193" s="66">
-        <v>85.54</v>
+        <v>52.00</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">Pratt Institute</t>
+          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C194" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C194" s="66">
+        <v>94.50</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">Primo Cares, Inc.</t>
+          <t xml:space="preserve">Mount Saint Marys University</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C195" s="65">
@@ -3128,132 +3128,132 @@
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">Project Cure, Inc.</t>
+          <t xml:space="preserve">Mountain States Legal Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C196" s="66">
-        <v>23.00</v>
+        <v>69.99</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
+          <t xml:space="preserve">MrCharity, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C197" s="66">
-        <v>88.71</v>
+          <t xml:space="preserve">2/23/2027</t>
+        </is>
+      </c>
+      <c r="C197" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">Project Orbis International, Inc.</t>
+          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
-        </is>
-      </c>
-      <c r="C198" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/20/2026</t>
+        </is>
+      </c>
+      <c r="C198" s="66">
+        <v>54.00</v>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">Proteus Fund, Inc.</t>
+          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
+          <t xml:space="preserve">6/24/2027</t>
         </is>
       </c>
       <c r="C199" s="66">
-        <v>81.25</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
+          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">12/19/2026</t>
         </is>
       </c>
       <c r="C200" s="66">
-        <v>84.22</v>
+        <v>66.90</v>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">Re:Power</t>
+          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C201" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C201" s="66">
+        <v>65.00</v>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">RezilientKidz</t>
+          <t xml:space="preserve">National Audubon Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">9/19/2026</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C202" s="66">
-        <v>94.67</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">Rodale Institute</t>
+          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C203" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C203" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
+          <t xml:space="preserve">National Council of Nonprofits</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">12/12/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C204" s="65">
@@ -3263,27 +3263,27 @@
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
+          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C205" s="66">
-        <v>45.00</v>
+        <v>49.00</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
+          <t xml:space="preserve">National Foundation for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">12/1/2026</t>
         </is>
       </c>
       <c r="C206" s="65">
@@ -3293,72 +3293,72 @@
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">Rutgers University Foundation</t>
+          <t xml:space="preserve">National Geographic Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">9/15/2026</t>
-        </is>
-      </c>
-      <c r="C207" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/18/2027</t>
+        </is>
+      </c>
+      <c r="C207" s="66">
+        <v>77.00</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">Sagamore Institute, Inc.</t>
+          <t xml:space="preserve">National Museum of Women in the Arts, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
+          <t xml:space="preserve">10/3/2026</t>
         </is>
       </c>
       <c r="C208" s="66">
-        <v>91.52</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">Saint John's University</t>
+          <t xml:space="preserve">National Park Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C209" s="66">
-        <v>92.84</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">Save the Chimps, Inc.</t>
+          <t xml:space="preserve">National PKU Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
-        </is>
-      </c>
-      <c r="C210" s="66">
-        <v>79.70</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C210" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">Seattle Pacific University</t>
+          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">1/9/2027</t>
         </is>
       </c>
       <c r="C211" s="65">
@@ -3368,132 +3368,132 @@
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
+          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C212" s="66">
-        <v>97.29</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C212" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">Sierra  Club</t>
+          <t xml:space="preserve">National Space Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">12/22/2026</t>
-        </is>
-      </c>
-      <c r="C213" s="66">
-        <v>82.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C213" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">Sister Rising Worldwide</t>
+          <t xml:space="preserve">National University</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">1/28/2027</t>
-        </is>
-      </c>
-      <c r="C214" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C214" s="66">
+        <v>42.69</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">Sixpoint, Inc.</t>
+          <t xml:space="preserve">National Veterans Memorial and Museum</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C215" s="66">
-        <v>77.16</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">Social Purpose Corrections</t>
+          <t xml:space="preserve">National Wheelchair Basketball Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C216" s="66">
-        <v>12.95</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
+          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
-        </is>
-      </c>
-      <c r="C217" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/22/2026</t>
+        </is>
+      </c>
+      <c r="C217" s="66">
+        <v>2.90</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
+          <t xml:space="preserve">Network for Good, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">7/29/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C218" s="66">
-        <v>86.00</v>
+        <v>97.80</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">South Dakota State University Foundation</t>
+          <t xml:space="preserve">New Harvest, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C219" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C219" s="66">
+        <v>88.49</v>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">Southern Poverty Law Center, Inc.</t>
+          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">9/17/2026</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C220" s="65">
@@ -3503,12 +3503,12 @@
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
+          <t xml:space="preserve">Nurse-Family Partnership</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C221" s="65">
@@ -3518,27 +3518,27 @@
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">Special Olympics, Inc.</t>
+          <t xml:space="preserve">Ocean Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C222" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C222" s="66">
+        <v>74.06</v>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">SPLC Action Fund</t>
+          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">9/17/2026</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C223" s="65">
@@ -3548,27 +3548,27 @@
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
+          <t xml:space="preserve">OneHope, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C224" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/1/2026</t>
+        </is>
+      </c>
+      <c r="C224" s="66">
+        <v>82.72</v>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">Students for Life Action, Inc.</t>
+          <t xml:space="preserve">Operation Smile, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">11/7/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C225" s="65">
@@ -3578,37 +3578,37 @@
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">Students for Life of America</t>
+          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
+          <t xml:space="preserve">8/18/2027</t>
         </is>
       </c>
       <c r="C226" s="66">
-        <v>82.00</v>
+        <v>77.59</v>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">The Actors' Fund of America</t>
+          <t xml:space="preserve">Our Change Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C227" s="66">
-        <v>86.73</v>
+        <v>80.46</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">The American University</t>
+          <t xml:space="preserve">Oxfam-America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
@@ -3617,93 +3617,93 @@
         </is>
       </c>
       <c r="C228" s="66">
-        <v>92.06</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+          <t xml:space="preserve">Pace University</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C229" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/1/2027</t>
+        </is>
+      </c>
+      <c r="C229" s="66">
+        <v>88.30</v>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">The Anthony Davis Foundation</t>
+          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">11/24/2026</t>
-        </is>
-      </c>
-      <c r="C230" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C230" s="66">
+        <v>55.43</v>
       </c>
     </row>
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
+          <t xml:space="preserve">Panorama Global</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">10/24/2026</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C231" s="66">
-        <v>90.00</v>
+        <v>84.52</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">The Barack Obama Foundation</t>
+          <t xml:space="preserve">Parkinson Research Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C232" s="66">
-        <v>55.90</v>
+          <t xml:space="preserve">9/25/2026</t>
+        </is>
+      </c>
+      <c r="C232" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">The Center for Alcohol Policy</t>
+          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">2/9/2027</t>
         </is>
       </c>
       <c r="C233" s="66">
-        <v>73.40</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">The Center for Investigative Reporting</t>
+          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C234" s="65">
@@ -3713,282 +3713,282 @@
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">The Colorado College</t>
+          <t xml:space="preserve">Pathfinder International</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">10/29/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C235" s="66">
-        <v>90.00</v>
+        <v>85.33</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C236" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C236" s="66">
+        <v>83.76</v>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C237" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/12/2027</t>
+        </is>
+      </c>
+      <c r="C237" s="66">
+        <v>58.00</v>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">The Heritage Foundation</t>
+          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C238" s="66">
-        <v>83.00</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C238" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C239" s="66">
-        <v>83.06</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C239" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">The Memorial Foundation</t>
+          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C240" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C240" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+          <t xml:space="preserve">Pledgeling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C241" s="66">
-        <v>80.87</v>
+        <v>65.93</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">The Nature Conservancy</t>
+          <t xml:space="preserve">Polar Bears International</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
+          <t xml:space="preserve">2/2/2027</t>
         </is>
       </c>
       <c r="C242" s="66">
-        <v>70.00</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">3/27/2027</t>
         </is>
       </c>
       <c r="C243" s="66">
-        <v>80.64</v>
+        <v>85.54</v>
       </c>
     </row>
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">The Ohio University Foundation</t>
+          <t xml:space="preserve">Pratt Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C244" s="66">
-        <v>74.14</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C244" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">The OneStar Foundation</t>
+          <t xml:space="preserve">Primo Cares, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
-        </is>
-      </c>
-      <c r="C245" s="66">
-        <v>62.50</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C245" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+          <t xml:space="preserve">Project Cure, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">10/14/2026</t>
         </is>
       </c>
       <c r="C246" s="66">
-        <v>88.30</v>
+        <v>23.00</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">The Planetary Society</t>
+          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">7/14/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C247" s="66">
-        <v>66.00</v>
+        <v>88.71</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">The Purchase College Foundation</t>
+          <t xml:space="preserve">Project Orbis International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
-        </is>
-      </c>
-      <c r="C248" s="66">
-        <v>78.12</v>
+          <t xml:space="preserve">10/7/2026</t>
+        </is>
+      </c>
+      <c r="C248" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">The Ruth Collective</t>
+          <t xml:space="preserve">Proteus Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C249" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/2/2027</t>
+        </is>
+      </c>
+      <c r="C249" s="66">
+        <v>81.25</v>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+          <t xml:space="preserve">Providence House</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C250" s="66">
-        <v>94.00</v>
+        <v>92.06</v>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">The University of Arizona Foundation</t>
+          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">9/29/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C251" s="66">
-        <v>76.49</v>
+        <v>84.22</v>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+          <t xml:space="preserve">Re:Power</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">4/13/2027</t>
-        </is>
-      </c>
-      <c r="C252" s="66">
-        <v>82.20</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C252" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">The University of Montana Foundation</t>
+          <t xml:space="preserve">Rodale Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C253" s="65">
@@ -3998,12 +3998,12 @@
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
+          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">12/12/2026</t>
         </is>
       </c>
       <c r="C254" s="65">
@@ -4013,277 +4013,277 @@
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">10/7/2026</t>
         </is>
       </c>
       <c r="C255" s="66">
-        <v>79.51</v>
+        <v>45.00</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
-        </is>
-      </c>
-      <c r="C256" s="66">
-        <v>89.50</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C256" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">Turning Point USA, Inc.</t>
+          <t xml:space="preserve">Rush University Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C257" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/23/2027</t>
+        </is>
+      </c>
+      <c r="C257" s="66">
+        <v>91.41</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">Twelveacres, Incorporated</t>
+          <t xml:space="preserve">Sagamore Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C258" s="66">
-        <v>79.93</v>
+        <v>91.61</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">UATX</t>
+          <t xml:space="preserve">Saint John's University</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">2/1/2027</t>
-        </is>
-      </c>
-      <c r="C259" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C259" s="66">
+        <v>92.84</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+          <t xml:space="preserve">Save the Chimps, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C260" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/27/2027</t>
+        </is>
+      </c>
+      <c r="C260" s="66">
+        <v>79.70</v>
       </c>
     </row>
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">UMKC Foundation</t>
+          <t xml:space="preserve">Seattle Pacific University</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
-        </is>
-      </c>
-      <c r="C261" s="66">
-        <v>95.00</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C261" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">Unified Youth</t>
+          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C262" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C262" s="66">
+        <v>94.00</v>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C263" s="66">
-        <v>86.96</v>
+        <v>97.29</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Sierra  Club</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">12/22/2026</t>
         </is>
       </c>
       <c r="C264" s="66">
-        <v>85.00</v>
+        <v>82.00</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">united Service Organizations, Inc.</t>
+          <t xml:space="preserve">Sister Rising Worldwide</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">11/10/2026</t>
-        </is>
-      </c>
-      <c r="C265" s="66">
-        <v>67.94</v>
+          <t xml:space="preserve">1/28/2027</t>
+        </is>
+      </c>
+      <c r="C265" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">United States Center for SafeSport</t>
+          <t xml:space="preserve">Sixpoint, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C266" s="66">
-        <v>72.74</v>
+        <v>77.16</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">University of Colorado</t>
+          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
-        </is>
-      </c>
-      <c r="C267" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/22/2027</t>
+        </is>
+      </c>
+      <c r="C267" s="66">
+        <v>90.00</v>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">University of Georgia Foundation</t>
+          <t xml:space="preserve">Social Purpose Corrections</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C268" s="66">
-        <v>94.00</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">University of Nebraska Foundation</t>
+          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">7/15/2027</t>
-        </is>
-      </c>
-      <c r="C269" s="66">
-        <v>81.10</v>
+          <t xml:space="preserve">10/15/2026</t>
+        </is>
+      </c>
+      <c r="C269" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">University of Pacific</t>
+          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C270" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/29/2027</t>
+        </is>
+      </c>
+      <c r="C270" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+          <t xml:space="preserve">South Dakota State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
-        </is>
-      </c>
-      <c r="C271" s="66">
-        <v>28.00</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C271" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">VoteAmerica, Inc.</t>
+          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C272" s="66">
-        <v>93.37</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C272" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+          <t xml:space="preserve">Special Olympics, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
@@ -4298,91 +4298,1351 @@
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">Washington State University Foundation</t>
+          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">7/8/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C274" s="66">
-        <v>75.03</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
-        </is>
-      </c>
-      <c r="C275" s="66">
-        <v>82.68</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C275" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">Women for Women International</t>
+          <t xml:space="preserve">Students for Life Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C276" s="66">
-        <v>79.06</v>
+          <t xml:space="preserve">11/7/2026</t>
+        </is>
+      </c>
+      <c r="C276" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+          <t xml:space="preserve">Students for Life of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">10/10/2026</t>
         </is>
       </c>
       <c r="C277" s="66">
-        <v>71.40</v>
+        <v>82.00</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">2/20/2027</t>
-        </is>
-      </c>
-      <c r="C278" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/12/2027</t>
+        </is>
+      </c>
+      <c r="C278" s="66">
+        <v>89.29</v>
       </c>
     </row>
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
+          <t xml:space="preserve">Teacher Freedom Alliance</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B279">
+        <is>
+          <t xml:space="preserve">6/24/2027</t>
+        </is>
+      </c>
+      <c r="C279" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c t="inlineStr" r="A280">
+        <is>
+          <t xml:space="preserve">The Actors' Fund of America</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B280">
+        <is>
+          <t xml:space="preserve">12/10/2026</t>
+        </is>
+      </c>
+      <c r="C280" s="66">
+        <v>86.73</v>
+      </c>
+    </row>
+    <row r="281">
+      <c t="inlineStr" r="A281">
+        <is>
+          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B281">
+        <is>
+          <t xml:space="preserve">6/15/2027</t>
+        </is>
+      </c>
+      <c r="C281" s="66">
+        <v>39.00</v>
+      </c>
+    </row>
+    <row r="282">
+      <c t="inlineStr" r="A282">
+        <is>
+          <t xml:space="preserve">The American University</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B282">
+        <is>
+          <t xml:space="preserve">10/6/2026</t>
+        </is>
+      </c>
+      <c r="C282" s="66">
+        <v>92.06</v>
+      </c>
+    </row>
+    <row r="283">
+      <c t="inlineStr" r="A283">
+        <is>
+          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B283">
+        <is>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C283" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c t="inlineStr" r="A284">
+        <is>
+          <t xml:space="preserve">The Anthony Davis Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B284">
+        <is>
+          <t xml:space="preserve">11/24/2026</t>
+        </is>
+      </c>
+      <c r="C284" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c t="inlineStr" r="A285">
+        <is>
+          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B285">
+        <is>
+          <t xml:space="preserve">10/24/2026</t>
+        </is>
+      </c>
+      <c r="C285" s="66">
+        <v>90.00</v>
+      </c>
+    </row>
+    <row r="286">
+      <c t="inlineStr" r="A286">
+        <is>
+          <t xml:space="preserve">The Barack Obama Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B286">
+        <is>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C286" s="66">
+        <v>55.90</v>
+      </c>
+    </row>
+    <row r="287">
+      <c t="inlineStr" r="A287">
+        <is>
+          <t xml:space="preserve">The Baruch College Fund</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B287">
+        <is>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C287" s="66">
+        <v>84.00</v>
+      </c>
+    </row>
+    <row r="288">
+      <c t="inlineStr" r="A288">
+        <is>
+          <t xml:space="preserve">The Call of Duty Endowment</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B288">
+        <is>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C288" s="66">
+        <v>73.00</v>
+      </c>
+    </row>
+    <row r="289">
+      <c t="inlineStr" r="A289">
+        <is>
+          <t xml:space="preserve">The Center for Alcohol Policy</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B289">
+        <is>
+          <t xml:space="preserve">1/16/2027</t>
+        </is>
+      </c>
+      <c r="C289" s="66">
+        <v>73.40</v>
+      </c>
+    </row>
+    <row r="290">
+      <c t="inlineStr" r="A290">
+        <is>
+          <t xml:space="preserve">The Center for Investigative Reporting</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B290">
+        <is>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C290" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c t="inlineStr" r="A291">
+        <is>
+          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B291">
+        <is>
+          <t xml:space="preserve">6/15/2027</t>
+        </is>
+      </c>
+      <c r="C291" s="66">
+        <v>71.00</v>
+      </c>
+    </row>
+    <row r="292">
+      <c t="inlineStr" r="A292">
+        <is>
+          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B292">
+        <is>
+          <t xml:space="preserve">7/6/2027</t>
+        </is>
+      </c>
+      <c r="C292" s="66">
+        <v>71.00</v>
+      </c>
+    </row>
+    <row r="293">
+      <c t="inlineStr" r="A293">
+        <is>
+          <t xml:space="preserve">The Colorado College</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B293">
+        <is>
+          <t xml:space="preserve">10/29/2027</t>
+        </is>
+      </c>
+      <c r="C293" s="66">
+        <v>90.00</v>
+      </c>
+    </row>
+    <row r="294">
+      <c t="inlineStr" r="A294">
+        <is>
+          <t xml:space="preserve">The Denver Rescue Mission</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B294">
+        <is>
+          <t xml:space="preserve">7/20/2027</t>
+        </is>
+      </c>
+      <c r="C294" s="66">
+        <v>82.96</v>
+      </c>
+    </row>
+    <row r="295">
+      <c t="inlineStr" r="A295">
+        <is>
+          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B295">
+        <is>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C295" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c t="inlineStr" r="A296">
+        <is>
+          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B296">
+        <is>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C296" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c t="inlineStr" r="A297">
+        <is>
+          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B297">
+        <is>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C297" s="66">
+        <v>76.48</v>
+      </c>
+    </row>
+    <row r="298">
+      <c t="inlineStr" r="A298">
+        <is>
+          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B298">
+        <is>
+          <t xml:space="preserve">5/15/2027</t>
+        </is>
+      </c>
+      <c r="C298" s="66">
+        <v>85.00</v>
+      </c>
+    </row>
+    <row r="299">
+      <c t="inlineStr" r="A299">
+        <is>
+          <t xml:space="preserve">The Heritage Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B299">
+        <is>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C299" s="66">
+        <v>83.00</v>
+      </c>
+    </row>
+    <row r="300">
+      <c t="inlineStr" r="A300">
+        <is>
+          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B300">
+        <is>
+          <t xml:space="preserve">7/28/2027</t>
+        </is>
+      </c>
+      <c r="C300" s="66">
+        <v>89.00</v>
+      </c>
+    </row>
+    <row r="301">
+      <c t="inlineStr" r="A301">
+        <is>
+          <t xml:space="preserve">The Independent Institute</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B301">
+        <is>
+          <t xml:space="preserve">5/29/2027</t>
+        </is>
+      </c>
+      <c r="C301" s="66">
+        <v>77.51</v>
+      </c>
+    </row>
+    <row r="302">
+      <c t="inlineStr" r="A302">
+        <is>
+          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B302">
+        <is>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C302" s="66">
+        <v>84.00</v>
+      </c>
+    </row>
+    <row r="303">
+      <c t="inlineStr" r="A303">
+        <is>
+          <t xml:space="preserve">The Kansas University Endowment Association</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B303">
+        <is>
+          <t xml:space="preserve">7/21/2027</t>
+        </is>
+      </c>
+      <c r="C303" s="66">
+        <v>91.34</v>
+      </c>
+    </row>
+    <row r="304">
+      <c t="inlineStr" r="A304">
+        <is>
+          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B304">
+        <is>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C304" s="66">
+        <v>83.06</v>
+      </c>
+    </row>
+    <row r="305">
+      <c t="inlineStr" r="A305">
+        <is>
+          <t xml:space="preserve">The Memorial Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B305">
+        <is>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C305" s="66">
+        <v>72.00</v>
+      </c>
+    </row>
+    <row r="306">
+      <c t="inlineStr" r="A306">
+        <is>
+          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B306">
+        <is>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C306" s="66">
+        <v>80.87</v>
+      </c>
+    </row>
+    <row r="307">
+      <c t="inlineStr" r="A307">
+        <is>
+          <t xml:space="preserve">The National World War II Museum, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B307">
+        <is>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C307" s="66">
+        <v>80.00</v>
+      </c>
+    </row>
+    <row r="308">
+      <c t="inlineStr" r="A308">
+        <is>
+          <t xml:space="preserve">The Nature Conservancy</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B308">
+        <is>
+          <t xml:space="preserve">10/9/2026</t>
+        </is>
+      </c>
+      <c r="C308" s="66">
+        <v>70.00</v>
+      </c>
+    </row>
+    <row r="309">
+      <c t="inlineStr" r="A309">
+        <is>
+          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B309">
+        <is>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C309" s="66">
+        <v>80.64</v>
+      </c>
+    </row>
+    <row r="310">
+      <c t="inlineStr" r="A310">
+        <is>
+          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B310">
+        <is>
+          <t xml:space="preserve">7/30/2027</t>
+        </is>
+      </c>
+      <c r="C310" s="66">
+        <v>87.40</v>
+      </c>
+    </row>
+    <row r="311">
+      <c t="inlineStr" r="A311">
+        <is>
+          <t xml:space="preserve">The Ohio University Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B311">
+        <is>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C311" s="66">
+        <v>74.14</v>
+      </c>
+    </row>
+    <row r="312">
+      <c t="inlineStr" r="A312">
+        <is>
+          <t xml:space="preserve">The OneStar Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B312">
+        <is>
+          <t xml:space="preserve">1/14/2027</t>
+        </is>
+      </c>
+      <c r="C312" s="66">
+        <v>62.50</v>
+      </c>
+    </row>
+    <row r="313">
+      <c t="inlineStr" r="A313">
+        <is>
+          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B313">
+        <is>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C313" s="66">
+        <v>88.30</v>
+      </c>
+    </row>
+    <row r="314">
+      <c t="inlineStr" r="A314">
+        <is>
+          <t xml:space="preserve">The Planetary Society</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B314">
+        <is>
+          <t xml:space="preserve">7/14/2027</t>
+        </is>
+      </c>
+      <c r="C314" s="66">
+        <v>66.00</v>
+      </c>
+    </row>
+    <row r="315">
+      <c t="inlineStr" r="A315">
+        <is>
+          <t xml:space="preserve">The Purchase College Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B315">
+        <is>
+          <t xml:space="preserve">3/24/2027</t>
+        </is>
+      </c>
+      <c r="C315" s="66">
+        <v>78.12</v>
+      </c>
+    </row>
+    <row r="316">
+      <c t="inlineStr" r="A316">
+        <is>
+          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B316">
+        <is>
+          <t xml:space="preserve">8/17/2027</t>
+        </is>
+      </c>
+      <c r="C316" s="66">
+        <v>81.26</v>
+      </c>
+    </row>
+    <row r="317">
+      <c t="inlineStr" r="A317">
+        <is>
+          <t xml:space="preserve">The Ruth Collective</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B317">
+        <is>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C317" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c t="inlineStr" r="A318">
+        <is>
+          <t xml:space="preserve">The Society of the Cincinnati</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B318">
+        <is>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C318" s="66">
+        <v>73.00</v>
+      </c>
+    </row>
+    <row r="319">
+      <c t="inlineStr" r="A319">
+        <is>
+          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B319">
+        <is>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C319" s="66">
+        <v>94.00</v>
+      </c>
+    </row>
+    <row r="320">
+      <c t="inlineStr" r="A320">
+        <is>
+          <t xml:space="preserve">The University of Arizona Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B320">
+        <is>
+          <t xml:space="preserve">9/29/2026</t>
+        </is>
+      </c>
+      <c r="C320" s="66">
+        <v>76.49</v>
+      </c>
+    </row>
+    <row r="321">
+      <c t="inlineStr" r="A321">
+        <is>
+          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B321">
+        <is>
+          <t xml:space="preserve">4/13/2027</t>
+        </is>
+      </c>
+      <c r="C321" s="66">
+        <v>82.20</v>
+      </c>
+    </row>
+    <row r="322">
+      <c t="inlineStr" r="A322">
+        <is>
+          <t xml:space="preserve">The University of Montana Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B322">
+        <is>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C322" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c t="inlineStr" r="A323">
+        <is>
+          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B323">
+        <is>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C323" s="66">
+        <v>76.00</v>
+      </c>
+    </row>
+    <row r="324">
+      <c t="inlineStr" r="A324">
+        <is>
+          <t xml:space="preserve">The Visiting Angels Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B324">
+        <is>
+          <t xml:space="preserve">7/20/2027</t>
+        </is>
+      </c>
+      <c r="C324" s="66">
+        <v>94.00</v>
+      </c>
+    </row>
+    <row r="325">
+      <c t="inlineStr" r="A325">
+        <is>
+          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B325">
+        <is>
+          <t xml:space="preserve">10/15/2026</t>
+        </is>
+      </c>
+      <c r="C325" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c t="inlineStr" r="A326">
+        <is>
+          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B326">
+        <is>
+          <t xml:space="preserve">1/30/2027</t>
+        </is>
+      </c>
+      <c r="C326" s="66">
+        <v>79.51</v>
+      </c>
+    </row>
+    <row r="327">
+      <c t="inlineStr" r="A327">
+        <is>
+          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B327">
+        <is>
+          <t xml:space="preserve">4/21/2027</t>
+        </is>
+      </c>
+      <c r="C327" s="66">
+        <v>85.00</v>
+      </c>
+    </row>
+    <row r="328">
+      <c t="inlineStr" r="A328">
+        <is>
+          <t xml:space="preserve">Trevecca Nazarene University</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B328">
+        <is>
+          <t xml:space="preserve">7/30/2027</t>
+        </is>
+      </c>
+      <c r="C328" s="66">
+        <v>87.82</v>
+      </c>
+    </row>
+    <row r="329">
+      <c t="inlineStr" r="A329">
+        <is>
+          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B329">
+        <is>
+          <t xml:space="preserve">9/26/2026</t>
+        </is>
+      </c>
+      <c r="C329" s="66">
+        <v>89.50</v>
+      </c>
+    </row>
+    <row r="330">
+      <c t="inlineStr" r="A330">
+        <is>
+          <t xml:space="preserve">Trustees of Tufts College</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B330">
+        <is>
+          <t xml:space="preserve">7/2/2027</t>
+        </is>
+      </c>
+      <c r="C330" s="66">
+        <v>85.00</v>
+      </c>
+    </row>
+    <row r="331">
+      <c t="inlineStr" r="A331">
+        <is>
+          <t xml:space="preserve">Turning Point USA, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B331">
+        <is>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C331" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c t="inlineStr" r="A332">
+        <is>
+          <t xml:space="preserve">Twelveacres, Incorporated</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B332">
+        <is>
+          <t xml:space="preserve">1/16/2027</t>
+        </is>
+      </c>
+      <c r="C332" s="66">
+        <v>79.93</v>
+      </c>
+    </row>
+    <row r="333">
+      <c t="inlineStr" r="A333">
+        <is>
+          <t xml:space="preserve">UATX</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B333">
+        <is>
+          <t xml:space="preserve">2/1/2027</t>
+        </is>
+      </c>
+      <c r="C333" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c t="inlineStr" r="A334">
+        <is>
+          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B334">
+        <is>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C334" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c t="inlineStr" r="A335">
+        <is>
+          <t xml:space="preserve">UMKC Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B335">
+        <is>
+          <t xml:space="preserve">1/27/2027</t>
+        </is>
+      </c>
+      <c r="C335" s="66">
+        <v>95.00</v>
+      </c>
+    </row>
+    <row r="336">
+      <c t="inlineStr" r="A336">
+        <is>
+          <t xml:space="preserve">Unified Youth</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B336">
+        <is>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C336" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c t="inlineStr" r="A337">
+        <is>
+          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B337">
+        <is>
+          <t xml:space="preserve">8/1/2027</t>
+        </is>
+      </c>
+      <c r="C337" s="66">
+        <v>88.00</v>
+      </c>
+    </row>
+    <row r="338">
+      <c t="inlineStr" r="A338">
+        <is>
+          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B338">
+        <is>
+          <t xml:space="preserve">8/17/2027</t>
+        </is>
+      </c>
+      <c r="C338" s="66">
+        <v>84.01</v>
+      </c>
+    </row>
+    <row r="339">
+      <c t="inlineStr" r="A339">
+        <is>
+          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B339">
+        <is>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C339" s="66">
+        <v>85.00</v>
+      </c>
+    </row>
+    <row r="340">
+      <c t="inlineStr" r="A340">
+        <is>
+          <t xml:space="preserve">united Service Organizations, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B340">
+        <is>
+          <t xml:space="preserve">11/10/2026</t>
+        </is>
+      </c>
+      <c r="C340" s="66">
+        <v>67.94</v>
+      </c>
+    </row>
+    <row r="341">
+      <c t="inlineStr" r="A341">
+        <is>
+          <t xml:space="preserve">United States Association for UNHCR</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B341">
+        <is>
+          <t xml:space="preserve">6/1/2027</t>
+        </is>
+      </c>
+      <c r="C341" s="66">
+        <v>61.00</v>
+      </c>
+    </row>
+    <row r="342">
+      <c t="inlineStr" r="A342">
+        <is>
+          <t xml:space="preserve">United States Center for SafeSport</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B342">
+        <is>
+          <t xml:space="preserve">2/27/2027</t>
+        </is>
+      </c>
+      <c r="C342" s="66">
+        <v>72.74</v>
+      </c>
+    </row>
+    <row r="343">
+      <c t="inlineStr" r="A343">
+        <is>
+          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B343">
+        <is>
+          <t xml:space="preserve">7/31/2027</t>
+        </is>
+      </c>
+      <c r="C343" s="66">
+        <v>99.30</v>
+      </c>
+    </row>
+    <row r="344">
+      <c t="inlineStr" r="A344">
+        <is>
+          <t xml:space="preserve">University of Colorado</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B344">
+        <is>
+          <t xml:space="preserve">10/7/2026</t>
+        </is>
+      </c>
+      <c r="C344" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c t="inlineStr" r="A345">
+        <is>
+          <t xml:space="preserve">University of Georgia Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B345">
+        <is>
+          <t xml:space="preserve">9/26/2026</t>
+        </is>
+      </c>
+      <c r="C345" s="66">
+        <v>94.00</v>
+      </c>
+    </row>
+    <row r="346">
+      <c t="inlineStr" r="A346">
+        <is>
+          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B346">
+        <is>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C346" s="66">
+        <v>93.00</v>
+      </c>
+    </row>
+    <row r="347">
+      <c t="inlineStr" r="A347">
+        <is>
+          <t xml:space="preserve">University of Nebraska Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B347">
+        <is>
+          <t xml:space="preserve">7/15/2027</t>
+        </is>
+      </c>
+      <c r="C347" s="66">
+        <v>81.10</v>
+      </c>
+    </row>
+    <row r="348">
+      <c t="inlineStr" r="A348">
+        <is>
+          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B348">
+        <is>
+          <t xml:space="preserve">6/23/2027</t>
+        </is>
+      </c>
+      <c r="C348" s="66">
+        <v>77.00</v>
+      </c>
+    </row>
+    <row r="349">
+      <c t="inlineStr" r="A349">
+        <is>
+          <t xml:space="preserve">University of Pacific</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B349">
+        <is>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C349" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c t="inlineStr" r="A350">
+        <is>
+          <t xml:space="preserve">University of Richmond</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B350">
+        <is>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C350" s="66">
+        <v>82.18</v>
+      </c>
+    </row>
+    <row r="351">
+      <c t="inlineStr" r="A351">
+        <is>
+          <t xml:space="preserve">Veterans Community Project</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B351">
+        <is>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C351" s="66">
+        <v>88.83</v>
+      </c>
+    </row>
+    <row r="352">
+      <c t="inlineStr" r="A352">
+        <is>
+          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B352">
+        <is>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C352" s="66">
+        <v>28.00</v>
+      </c>
+    </row>
+    <row r="353">
+      <c t="inlineStr" r="A353">
+        <is>
+          <t xml:space="preserve">VoteAmerica, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B353">
+        <is>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C353" s="66">
+        <v>93.37</v>
+      </c>
+    </row>
+    <row r="354">
+      <c t="inlineStr" r="A354">
+        <is>
+          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B354">
+        <is>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C354" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c t="inlineStr" r="A355">
+        <is>
+          <t xml:space="preserve">Washington State University Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B355">
+        <is>
+          <t xml:space="preserve">7/8/2027</t>
+        </is>
+      </c>
+      <c r="C355" s="66">
+        <v>75.03</v>
+      </c>
+    </row>
+    <row r="356">
+      <c t="inlineStr" r="A356">
+        <is>
+          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B356">
+        <is>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C356" s="66">
+        <v>82.68</v>
+      </c>
+    </row>
+    <row r="357">
+      <c t="inlineStr" r="A357">
+        <is>
+          <t xml:space="preserve">Winning for Women, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B357">
+        <is>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C357" s="66">
+        <v>66.70</v>
+      </c>
+    </row>
+    <row r="358">
+      <c t="inlineStr" r="A358">
+        <is>
+          <t xml:space="preserve">Women for Women International</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B358">
+        <is>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C358" s="66">
+        <v>79.06</v>
+      </c>
+    </row>
+    <row r="359">
+      <c t="inlineStr" r="A359">
+        <is>
+          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B359">
+        <is>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C359" s="66">
+        <v>71.40</v>
+      </c>
+    </row>
+    <row r="360">
+      <c t="inlineStr" r="A360">
+        <is>
+          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B360">
+        <is>
+          <t xml:space="preserve">2/20/2027</t>
+        </is>
+      </c>
+      <c r="C360" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c t="inlineStr" r="A361">
+        <is>
+          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B361">
+        <is>
+          <t xml:space="preserve">5/20/2027</t>
+        </is>
+      </c>
+      <c r="C361" s="66">
+        <v>79.00</v>
+      </c>
+    </row>
+    <row r="362">
+      <c t="inlineStr" r="A362">
+        <is>
           <t xml:space="preserve">YMCA of the Rockies</t>
         </is>
       </c>
-      <c t="inlineStr" r="B279">
+      <c t="inlineStr" r="B362">
         <is>
           <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
-      <c r="C279" s="66">
+      <c r="C362" s="66">
         <v>81.65</v>
+      </c>
+    </row>
+    <row r="363">
+      <c t="inlineStr" r="A363">
+        <is>
+          <t xml:space="preserve">Young Judaea Global, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B363">
+        <is>
+          <t xml:space="preserve">6/25/2027</t>
+        </is>
+      </c>
+      <c r="C363" s="66">
+        <v>71.20</v>
       </c>
     </row>
   </sheetData>

--- a/downloadable-data/LA.xlsx
+++ b/downloadable-data/LA.xlsx
@@ -323,207 +323,207 @@
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">ACT for America, Inc.</t>
+          <t xml:space="preserve">AbleLight, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">8/14/2027</t>
         </is>
       </c>
       <c r="C9" s="66">
-        <v>75.00</v>
+        <v>84.60</v>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">Action Against Hunger</t>
+          <t xml:space="preserve">ACT for America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C10" s="66">
-        <v>90.00</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">Adventist Development and Relief Agency Int.</t>
+          <t xml:space="preserve">Action Against Hunger</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">2/23/2027</t>
         </is>
       </c>
       <c r="C11" s="66">
-        <v>87.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">AFA Action, Inc.</t>
+          <t xml:space="preserve">Adventist Development and Relief Agency Int.</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C12" s="66">
-        <v>67.56</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">Air &amp; Space Force Association</t>
+          <t xml:space="preserve">AFA Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C13" s="66">
-        <v>79.11</v>
+        <v>69.57</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">Air Force Academy Foundation</t>
+          <t xml:space="preserve">Air &amp; Space Force Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">7/6/2027</t>
+          <t xml:space="preserve">2/10/2027</t>
         </is>
       </c>
       <c r="C14" s="66">
-        <v>85.57</v>
+        <v>79.11</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">Air Transport Services, Inc.</t>
+          <t xml:space="preserve">Air Force Academy Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">4/20/2027</t>
+          <t xml:space="preserve">7/6/2027</t>
         </is>
       </c>
       <c r="C15" s="66">
-        <v>99.00</v>
+        <v>85.57</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">Al-Mawrid United States, Inc.</t>
+          <t xml:space="preserve">Air Transport Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/20/2027</t>
+        </is>
+      </c>
+      <c r="C16" s="66">
+        <v>99.00</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">Alaska Conservation Foundation</t>
+          <t xml:space="preserve">Al-Mawrid United States, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
-        </is>
-      </c>
-      <c r="C17" s="66">
-        <v>79.96</v>
+          <t xml:space="preserve">10/6/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">All God's Children International</t>
+          <t xml:space="preserve">Alaska Conservation Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C18" s="66">
-        <v>87.31</v>
+        <v>79.96</v>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">All Hands and Hearts Smart Response</t>
+          <t xml:space="preserve">All God's Children International</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C19" s="66">
-        <v>93.41</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">Alliance for Gun Responsibility</t>
+          <t xml:space="preserve">All Hands and Hearts Smart Response</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C20" s="66">
-        <v>75.80</v>
+        <v>93.41</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">Alpha Gamma Delta Foundation, Inc.</t>
+          <t xml:space="preserve">Alliance for Gun Responsibility</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C21" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C21" s="66">
+        <v>75.80</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">Alpha Kappa Psi Foundation</t>
+          <t xml:space="preserve">Alpha Gamma Delta Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">1/8/2027</t>
+          <t xml:space="preserve">11/3/2026</t>
         </is>
       </c>
       <c r="C22" s="65">
@@ -533,462 +533,462 @@
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">ALTA Charitable Foundation</t>
+          <t xml:space="preserve">Alpha Kappa Psi Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C23" s="66">
-        <v>48.00</v>
+          <t xml:space="preserve">1/8/2027</t>
+        </is>
+      </c>
+      <c r="C23" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">Alternate ROOTS, Inc.</t>
+          <t xml:space="preserve">ALTA Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">1/1/2027</t>
-        </is>
-      </c>
-      <c r="C24" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C24" s="66">
+        <v>48.00</v>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">America's Survival, Inc.</t>
+          <t xml:space="preserve">Alternate ROOTS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C25" s="66">
-        <v>90.07</v>
+          <t xml:space="preserve">1/1/2027</t>
+        </is>
+      </c>
+      <c r="C25" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">American Association of Family and Consumer Scienc</t>
+          <t xml:space="preserve">America's Survival, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C26" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C26" s="66">
+        <v>90.07</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">American Association of State Troopers, Inc.</t>
+          <t xml:space="preserve">American Association of Family and Consumer Scienc</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C27" s="66">
-        <v>23.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">American Bible Society</t>
+          <t xml:space="preserve">American Association of State Troopers, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C28" s="66">
-        <v>76.00</v>
+        <v>23.00</v>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">American Civil Liberties Union Foundation, Inc.</t>
+          <t xml:space="preserve">American Bible Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C29" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/27/2027</t>
+        </is>
+      </c>
+      <c r="C29" s="66">
+        <v>76.00</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">American Congress for Truth, Inc.</t>
+          <t xml:space="preserve">American Civil Liberties Union Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
-        </is>
-      </c>
-      <c r="C30" s="66">
-        <v>75.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">American Council of the Blind, Inc.</t>
+          <t xml:space="preserve">American Congress for Truth, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">10/16/2026</t>
-        </is>
-      </c>
-      <c r="C31" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/28/2027</t>
+        </is>
+      </c>
+      <c r="C31" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">American Diabetes Association</t>
+          <t xml:space="preserve">American Council of the Blind, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
-        </is>
-      </c>
-      <c r="C32" s="66">
-        <v>79.18</v>
+          <t xml:space="preserve">10/16/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">American Foundation for the Blind, Inc.</t>
+          <t xml:space="preserve">American Diabetes Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C33" s="66">
-        <v>66.78</v>
+        <v>79.60</v>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">American Indian College Fund</t>
+          <t xml:space="preserve">American Foundation for the Blind, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">11/13/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C34" s="66">
-        <v>78.00</v>
+        <v>66.78</v>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">American Institute for Cancer Research</t>
+          <t xml:space="preserve">American Heart Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C35" s="66">
-        <v>67.00</v>
+          <t xml:space="preserve">8/18/2027</t>
+        </is>
+      </c>
+      <c r="C35" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">American Institute for Economic Research</t>
+          <t xml:space="preserve">American Indian College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">11/13/2026</t>
         </is>
       </c>
       <c r="C36" s="66">
-        <v>78.63</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">American Kidney Fund, Inc.</t>
+          <t xml:space="preserve">American Institute for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">5/12/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C37" s="66">
-        <v>95.70</v>
+        <v>67.00</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
+          <t xml:space="preserve">American Institute for Economic Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C38" s="66">
-        <v>75.08</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">American Lung Association</t>
+          <t xml:space="preserve">American Institute of Chemical Engineers</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">5/26/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C39" s="66">
-        <v>85.00</v>
+        <v>82.15</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">American Near East Refugee Aid, Inc</t>
+          <t xml:space="preserve">American Kidney Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">5/12/2027</t>
         </is>
       </c>
       <c r="C40" s="66">
-        <v>95.44</v>
+        <v>95.70</v>
       </c>
     </row>
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">American Roentgen Ray Society</t>
+          <t xml:space="preserve">American Lebanese Syrian Associated Charities, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C41" s="66">
-        <v>52.00</v>
+        <v>75.96</v>
       </c>
     </row>
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">Americans For Fair Treatment</t>
+          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C42" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/26/2027</t>
+        </is>
+      </c>
+      <c r="C42" s="66">
+        <v>75.08</v>
       </c>
     </row>
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
+          <t xml:space="preserve">American Lung Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">5/26/2027</t>
         </is>
       </c>
       <c r="C43" s="66">
-        <v>71.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">Animals' Angels, Incorporated</t>
+          <t xml:space="preserve">American Near East Refugee Aid, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
-        </is>
-      </c>
-      <c r="C44" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C44" s="66">
+        <v>95.44</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">Anti-Defamation League</t>
+          <t xml:space="preserve">American Roentgen Ray Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">10/9/2026</t>
         </is>
       </c>
       <c r="C45" s="66">
-        <v>75.00</v>
+        <v>52.00</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">Arkansas Tech University Foundation</t>
+          <t xml:space="preserve">Americans For Fair Treatment</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C46" s="66">
-        <v>94.06</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
+          <t xml:space="preserve">Americares Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C47" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/24/2027</t>
+        </is>
+      </c>
+      <c r="C47" s="66">
+        <v>98.06</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">Association of American Education Foundation</t>
+          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C48" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/14/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="66">
+        <v>71.00</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">Austin College</t>
+          <t xml:space="preserve">Animals' Angels, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">9/12/2027</t>
         </is>
       </c>
       <c r="C49" s="66">
-        <v>85.11</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
+          <t xml:space="preserve">Anti-Defamation League</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">3/23/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C50" s="66">
-        <v>81.00</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">Autism Speaks, Inc.</t>
+          <t xml:space="preserve">Arkansas Tech University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C51" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C51" s="66">
+        <v>94.06</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
+          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C52" s="66">
-        <v>44.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C52" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">B'nai B'rith International</t>
+          <t xml:space="preserve">Association of American Education Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C53" s="65">
@@ -998,37 +998,37 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Back Bay Mission, Inc.</t>
+          <t xml:space="preserve">Austin College</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C54" s="66">
-        <v>83.67</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">Base Ministry</t>
+          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">3/23/2027</t>
         </is>
       </c>
       <c r="C55" s="66">
-        <v>71.89</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">Blood Cancer United, Inc.</t>
+          <t xml:space="preserve">Autism Speaks, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
@@ -1036,359 +1036,359 @@
           <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
-      <c r="C56" s="66">
-        <v>75.00</v>
+      <c r="C56" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
+          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C57" s="66">
-        <v>71.00</v>
+        <v>44.00</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
+          <t xml:space="preserve">B'nai B'rith International</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
-        </is>
-      </c>
-      <c r="C58" s="66">
-        <v>78.58</v>
+          <t xml:space="preserve">12/18/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">Business Action Fund</t>
+          <t xml:space="preserve">Back Bay Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C59" s="66">
-        <v>54.00</v>
+        <v>83.67</v>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Cair-Foundation, Inc.</t>
+          <t xml:space="preserve">Base Ministry</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C60" s="66">
-        <v>66.00</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">CAMFED USA Foundation</t>
+          <t xml:space="preserve">Blessings International</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
+          <t xml:space="preserve">9/2/2027</t>
         </is>
       </c>
       <c r="C61" s="66">
-        <v>91.78</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Captain Joseph House Foundation</t>
+          <t xml:space="preserve">Blood Cancer United, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C62" s="66">
-        <v>67.20</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
+          <t xml:space="preserve">Brady Campaign to Prevent Gun Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C63" s="66">
-        <v>97.00</v>
+        <v>45.00</v>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">Center for Community Change Action</t>
+          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C64" s="66">
-        <v>95.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">Central Asia Institute</t>
+          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C65" s="66">
-        <v>77.29</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">Chapel Haven Schleifer Center, Inc.</t>
+          <t xml:space="preserve">Business Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C66" s="66">
-        <v>81.41</v>
+        <v>54.00</v>
       </c>
     </row>
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">Charities Aid Foundation America</t>
+          <t xml:space="preserve">Cair-Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">1/14/2027</t>
         </is>
       </c>
       <c r="C67" s="66">
-        <v>0.01</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">Childhelp, Inc.</t>
+          <t xml:space="preserve">CAMFED USA Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">6/30/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C68" s="66">
-        <v>70.00</v>
+        <v>91.78</v>
       </c>
     </row>
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
+          <t xml:space="preserve">Captain Joseph House Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C69" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C69" s="66">
+        <v>67.20</v>
       </c>
     </row>
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Children's Miracle Network</t>
+          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">10/14/2026</t>
         </is>
       </c>
       <c r="C70" s="66">
-        <v>80.77</v>
+        <v>97.00</v>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
+          <t xml:space="preserve">Center for Community Change Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C71" s="66">
-        <v>89.98</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
+          <t xml:space="preserve">Central Asia Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C72" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C72" s="66">
+        <v>77.29</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">Christian Relief Services, Inc.</t>
+          <t xml:space="preserve">Chapel Haven Schleifer Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C73" s="66">
-        <v>90.70</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
+          <t xml:space="preserve">Charities Aid Foundation America</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C74" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C74" s="66">
+        <v>0.01</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">Christian Union, Inc.</t>
+          <t xml:space="preserve">ChildFund International, USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C75" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C75" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">City Rescue Mission, Inc.</t>
+          <t xml:space="preserve">Childhelp, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">6/30/2027</t>
         </is>
       </c>
       <c r="C76" s="66">
-        <v>85.32</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">City Year, Inc.</t>
+          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C77" s="66">
-        <v>82.62</v>
+          <t xml:space="preserve">12/18/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">Civil Rights Corps</t>
+          <t xml:space="preserve">Children's Miracle Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C78" s="66">
-        <v>82.10</v>
+        <v>80.77</v>
       </c>
     </row>
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
+          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">11/20/2026</t>
-        </is>
-      </c>
-      <c r="C79" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C79" s="66">
+        <v>89.98</v>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
+          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
@@ -1403,57 +1403,57 @@
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
+          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">9/10/2027</t>
         </is>
       </c>
       <c r="C81" s="66">
-        <v>65.99</v>
+        <v>96.00</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Compassion and Choices</t>
+          <t xml:space="preserve">Christian Relief Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">2/10/2027</t>
         </is>
       </c>
       <c r="C82" s="66">
-        <v>84.00</v>
+        <v>90.70</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">Compassion and Choices Action Network</t>
+          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
-        </is>
-      </c>
-      <c r="C83" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C83" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Concerns of Police Survivors</t>
+          <t xml:space="preserve">Christian Union, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">12/5/2026</t>
         </is>
       </c>
       <c r="C84" s="65">
@@ -1463,12 +1463,12 @@
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Consumer Reports, Inc.</t>
+          <t xml:space="preserve">Church World Service, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">8/25/2027</t>
         </is>
       </c>
       <c r="C85" s="66">
@@ -1478,132 +1478,132 @@
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Cooperative for Assistance and Relief Everywhere</t>
+          <t xml:space="preserve">City Rescue Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
-        </is>
-      </c>
-      <c r="C86" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C86" s="66">
+        <v>85.32</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
+          <t xml:space="preserve">City Year, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">6/25/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C87" s="66">
-        <v>73.00</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
+          <t xml:space="preserve">Civil Rights Corps</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C88" s="66">
-        <v>74.54</v>
+        <v>82.10</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">Covenant House</t>
+          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
-        </is>
-      </c>
-      <c r="C89" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">11/20/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
+          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
-        </is>
-      </c>
-      <c r="C90" s="66">
-        <v>84.38</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C90" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
+          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">4/9/2027</t>
         </is>
       </c>
       <c r="C91" s="66">
-        <v>85.18</v>
+        <v>65.99</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
+          <t xml:space="preserve">Compassion and Choices</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C92" s="66">
-        <v>64.30</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">Daring Girls</t>
+          <t xml:space="preserve">Compassion and Choices Action Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
-        </is>
-      </c>
-      <c r="C93" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C93" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
+          <t xml:space="preserve">Concerns of Police Survivors</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C94" s="65">
@@ -1613,142 +1613,142 @@
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Deep South Today</t>
+          <t xml:space="preserve">Consumer Reports, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C95" s="66">
-        <v>74.56</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
+          <t xml:space="preserve">Cooperative for Assistance and Relief Everywhere</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">6/6/2027</t>
-        </is>
-      </c>
-      <c r="C96" s="66">
-        <v>68.82</v>
+          <t xml:space="preserve">10/1/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Disabled Veterans National Foundation</t>
+          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">9/25/2026</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C97" s="66">
-        <v>20.85</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
+          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C98" s="66">
-        <v>49.00</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">East Carolina University Foundation, Inc.</t>
+          <t xml:space="preserve">Covenant House</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C99" s="66">
-        <v>55.44</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
+          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">12/4/2026</t>
         </is>
       </c>
       <c r="C100" s="66">
-        <v>61.48</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Easter Seals, Inc.</t>
+          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C101" s="66">
-        <v>68.00</v>
+        <v>85.18</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">EB Research Partnership, Inc.</t>
+          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C102" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C102" s="66">
+        <v>64.30</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Economic Policy Institute</t>
+          <t xml:space="preserve">D.A.R.E. America</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C103" s="66">
-        <v>83.70</v>
+        <v>44.00</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">ELT Ventures</t>
+          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
@@ -1763,507 +1763,507 @@
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Empire State University Foundation</t>
+          <t xml:space="preserve">Deep South Today</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C105" s="66">
-        <v>82.78</v>
+        <v>74.56</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
+          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">6/6/2027</t>
         </is>
       </c>
       <c r="C106" s="66">
-        <v>48.32</v>
+        <v>68.82</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
+          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">3/6/2027</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C107" s="66">
-        <v>87.00</v>
+        <v>49.00</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">Fairplay, Inc.</t>
+          <t xml:space="preserve">DTCare</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">6/25/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C108" s="66">
-        <v>83.42</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">Faith and Freedom Coalition, Inc.</t>
+          <t xml:space="preserve">East Carolina University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">10/10/2026</t>
         </is>
       </c>
       <c r="C109" s="66">
-        <v>72.00</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">Family Policy Alliance</t>
+          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C110" s="66">
-        <v>80.48</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
+          <t xml:space="preserve">Easter Seals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C111" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/15/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="66">
+        <v>68.00</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">Feed The Children, Inc.</t>
+          <t xml:space="preserve">EB Research Partnership, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
-        </is>
-      </c>
-      <c r="C112" s="66">
-        <v>91.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C112" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">Feeding America</t>
+          <t xml:space="preserve">ELT Ventures</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
-        </is>
-      </c>
-      <c r="C113" s="66">
-        <v>98.40</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C113" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Feeding Pets of the Homeless</t>
+          <t xml:space="preserve">Empire State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C114" s="66">
-        <v>75.17</v>
+        <v>82.78</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
+          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C115" s="66">
-        <v>82.48</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">FINCA International, Inc.</t>
+          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">5/7/2027</t>
+          <t xml:space="preserve">3/6/2027</t>
         </is>
       </c>
       <c r="C116" s="66">
-        <v>81.47</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Find The Children</t>
+          <t xml:space="preserve">Fairplay, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C117" s="66">
-        <v>50.00</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">Food Bank of Northeast Louisiana, Inc.</t>
+          <t xml:space="preserve">Faith and Freedom Coalition, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C118" s="66">
-        <v>99.00</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
+          <t xml:space="preserve">Family Policy Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C119" s="66">
-        <v>89.30</v>
+        <v>80.48</v>
       </c>
     </row>
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">Food for the Hungry, Inc.</t>
+          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="C120" s="66">
-        <v>75.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">For Others Collective, Inc.</t>
+          <t xml:space="preserve">Feed The Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C121" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/19/2027</t>
+        </is>
+      </c>
+      <c r="C121" s="66">
+        <v>91.00</v>
       </c>
     </row>
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
+          <t xml:space="preserve">Feeding America</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C122" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/6/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="66">
+        <v>98.40</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">Fractracker Alliance</t>
+          <t xml:space="preserve">Feeding Pets of the Homeless</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C123" s="66">
-        <v>77.78</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
+          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
+          <t xml:space="preserve">4/9/2027</t>
         </is>
       </c>
       <c r="C124" s="66">
-        <v>68.41</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
+          <t xml:space="preserve">FINCA International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C125" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/7/2027</t>
+        </is>
+      </c>
+      <c r="C125" s="66">
+        <v>81.47</v>
       </c>
     </row>
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">Friends of KEXP</t>
+          <t xml:space="preserve">Find The Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C126" s="66">
-        <v>66.97</v>
+        <v>50.00</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">Friends of the Neuberger Museum of Art, Inc.</t>
+          <t xml:space="preserve">Food Bank of Northeast Louisiana, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C127" s="66">
-        <v>66.80</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
+          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C128" s="66">
-        <v>75.34</v>
+        <v>89.30</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">Futures Without Violence</t>
+          <t xml:space="preserve">Food for the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C129" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/4/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">Givinga Foundation</t>
+          <t xml:space="preserve">For Others Collective, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">10/30/2026</t>
-        </is>
-      </c>
-      <c r="C130" s="66">
-        <v>94.03</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C130" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
+          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">3/11/2027</t>
-        </is>
-      </c>
-      <c r="C131" s="66">
-        <v>49.91</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C131" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">Go Campaign</t>
+          <t xml:space="preserve">Fractracker Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C132" s="66">
-        <v>77.86</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">Green America</t>
+          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">7/1/2027</t>
         </is>
       </c>
       <c r="C133" s="66">
-        <v>87.47</v>
+        <v>68.41</v>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
+          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C134" s="66">
-        <v>76.85</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C134" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">Greenpeace, Inc.</t>
+          <t xml:space="preserve">Friends of KEXP</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C135" s="66">
-        <v>62.56</v>
+        <v>65.74</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">Gustavus Adolphus College</t>
+          <t xml:space="preserve">Friends of the Neuberger Museum of Art, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">2/24/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C136" s="66">
-        <v>93.00</v>
+        <v>66.80</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">Habitat for Horses, Inc.</t>
+          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C137" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C137" s="66">
+        <v>75.34</v>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
+          <t xml:space="preserve">Futures Without Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C138" s="65">
@@ -2273,222 +2273,222 @@
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">Healing Justice Project</t>
+          <t xml:space="preserve">Girls Who Code, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">7/24/2027</t>
         </is>
       </c>
       <c r="C139" s="66">
-        <v>82.48</v>
+        <v>73.24</v>
       </c>
     </row>
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">Healing Protectors</t>
+          <t xml:space="preserve">Givinga Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
+          <t xml:space="preserve">10/30/2026</t>
         </is>
       </c>
       <c r="C140" s="66">
-        <v>47.19</v>
+        <v>94.03</v>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">Heifer Project International</t>
+          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">3/19/2027</t>
+          <t xml:space="preserve">3/11/2027</t>
         </is>
       </c>
       <c r="C141" s="66">
-        <v>72.90</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">Help Me See, Inc.</t>
+          <t xml:space="preserve">Go Campaign</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="C142" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/20/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="66">
+        <v>77.86</v>
       </c>
     </row>
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
+          <t xml:space="preserve">Goodwill Industries International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C143" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/9/2027</t>
+        </is>
+      </c>
+      <c r="C143" s="66">
+        <v>87.00</v>
       </c>
     </row>
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">Heroes on the Water</t>
+          <t xml:space="preserve">Green America</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C144" s="66">
-        <v>75.00</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">HIAS Foundation, Inc.</t>
+          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C145" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="66">
+        <v>76.85</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">Home Builders Institute</t>
+          <t xml:space="preserve">Greenpeace, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C146" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="66">
+        <v>62.56</v>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">Houston Christian Broadcasters, Inc.</t>
+          <t xml:space="preserve">Gustavus Adolphus College</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
+          <t xml:space="preserve">2/24/2027</t>
         </is>
       </c>
       <c r="C147" s="66">
-        <v>84.40</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">Human Appeal, Inc.</t>
+          <t xml:space="preserve">Habitat for Horses, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">1/12/2027</t>
-        </is>
-      </c>
-      <c r="C148" s="66">
-        <v>54.20</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
+          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C149" s="66">
-        <v>63.39</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">Human Rights Watch, Inc.</t>
+          <t xml:space="preserve">Healing Justice Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C150" s="66">
-        <v>72.65</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Humane Society of Missouri</t>
+          <t xml:space="preserve">Healing Protectors</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
+          <t xml:space="preserve">3/2/2027</t>
         </is>
       </c>
       <c r="C151" s="66">
-        <v>80.50</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">Illinois State University Foundation</t>
+          <t xml:space="preserve">Heifer Project International</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">5/21/2027</t>
+          <t xml:space="preserve">3/19/2027</t>
         </is>
       </c>
       <c r="C152" s="66">
-        <v>61.30</v>
+        <v>72.90</v>
       </c>
     </row>
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
+          <t xml:space="preserve">Help Me See, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">10/3/2026</t>
         </is>
       </c>
       <c r="C153" s="65">
@@ -2498,12 +2498,12 @@
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">In Medias Res</t>
+          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/22/2026</t>
         </is>
       </c>
       <c r="C154" s="65">
@@ -2513,57 +2513,57 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">Independent Council on Women's Sport</t>
+          <t xml:space="preserve">Heroes on the Water</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/1/2026</t>
         </is>
       </c>
       <c r="C155" s="66">
-        <v>94.44</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">Infact</t>
+          <t xml:space="preserve">HIAS Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
-        </is>
-      </c>
-      <c r="C156" s="66">
-        <v>89.97</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C156" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">INROADS, Inc.</t>
+          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">9/24/2026</t>
-        </is>
-      </c>
-      <c r="C157" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C157" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
+          <t xml:space="preserve">Home Builders Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C158" s="65">
@@ -2573,117 +2573,117 @@
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
+          <t xml:space="preserve">Houston Christian Broadcasters, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C159" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/6/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="66">
+        <v>84.40</v>
       </c>
     </row>
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">International Justice Mission</t>
+          <t xml:space="preserve">Human Appeal, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
-        </is>
-      </c>
-      <c r="C160" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/12/2027</t>
+        </is>
+      </c>
+      <c r="C160" s="66">
+        <v>54.20</v>
       </c>
     </row>
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
+          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C161" s="66">
-        <v>83.13</v>
+        <v>63.39</v>
       </c>
     </row>
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">International Union of Police Associations</t>
+          <t xml:space="preserve">Human Rights Watch, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C162" s="66">
-        <v>47.90</v>
+        <v>72.65</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">Iona University</t>
+          <t xml:space="preserve">Human-I-T</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">8/30/2027</t>
         </is>
       </c>
       <c r="C163" s="66">
-        <v>89.81</v>
+        <v>1.00</v>
       </c>
     </row>
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
+          <t xml:space="preserve">Humane Society of Missouri</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
+          <t xml:space="preserve">8/7/2027</t>
         </is>
       </c>
       <c r="C164" s="66">
-        <v>75.43</v>
+        <v>80.50</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">Jewish Democratic Council of America</t>
+          <t xml:space="preserve">Illinois State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">5/21/2027</t>
         </is>
       </c>
       <c r="C165" s="66">
-        <v>50.07</v>
+        <v>61.30</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">Jewish Voice Ministries International</t>
+          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C166" s="65">
@@ -2693,72 +2693,72 @@
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
+          <t xml:space="preserve">In Medias Res</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
-        </is>
-      </c>
-      <c r="C167" s="66">
-        <v>89.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C167" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
+          <t xml:space="preserve">Independent Council on Women's Sport</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C168" s="66">
-        <v>75.00</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
+          <t xml:space="preserve">Infact</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C169" s="66">
-        <v>98.28</v>
+        <v>89.97</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">Khan Academy, Inc.</t>
+          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
-        </is>
-      </c>
-      <c r="C170" s="66">
-        <v>86.36</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C170" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
+          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C171" s="65">
@@ -2768,12 +2768,12 @@
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">L.E.A.D. Inc.</t>
+          <t xml:space="preserve">International Justice Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C172" s="65">
@@ -2783,132 +2783,132 @@
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
+          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C173" s="66">
-        <v>63.00</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
+          <t xml:space="preserve">International Union of Police Associations</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C174" s="66">
-        <v>10.60</v>
+        <v>47.90</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
+          <t xml:space="preserve">Iona University</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">10/28/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C175" s="66">
-        <v>96.80</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">Life Teen, Inc.</t>
+          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">4/27/2027</t>
         </is>
       </c>
       <c r="C176" s="66">
-        <v>76.40</v>
+        <v>75.43</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">Live Action</t>
+          <t xml:space="preserve">Jewish Democratic Council of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C177" s="66">
-        <v>81.13</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">Living Waters for the World</t>
+          <t xml:space="preserve">Jewish Voice Ministries International</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C178" s="66">
-        <v>78.81</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
+          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C179" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/4/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="66">
+        <v>89.00</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
+          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">10/29/2026</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C180" s="66">
-        <v>70.18</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
+          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">9/25/2026</t>
+          <t xml:space="preserve">9/5/2027</t>
         </is>
       </c>
       <c r="C181" s="65">
@@ -2918,447 +2918,447 @@
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">Madison House</t>
+          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C182" s="66">
-        <v>77.79</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">MAP International, Inc.</t>
+          <t xml:space="preserve">Khan Academy, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C183" s="66">
-        <v>99.00</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">March of Dimes</t>
+          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">12/30/2026</t>
-        </is>
-      </c>
-      <c r="C184" s="66">
-        <v>74.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C184" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">Marist University</t>
+          <t xml:space="preserve">L.E.A.D. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
-        </is>
-      </c>
-      <c r="C185" s="66">
-        <v>91.00</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C185" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">Meals on Wheels America</t>
+          <t xml:space="preserve">La Leche League International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">5/27/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C186" s="66">
-        <v>59.00</v>
+        <v>57.00</v>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
+          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">6/9/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C187" s="66">
-        <v>80.94</v>
+        <v>63.00</v>
       </c>
     </row>
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
+          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">12/8/2026</t>
-        </is>
-      </c>
-      <c r="C188" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/15/2027</t>
+        </is>
+      </c>
+      <c r="C188" s="66">
+        <v>10.60</v>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
+          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">10/28/2026</t>
         </is>
       </c>
       <c r="C189" s="66">
-        <v>91.00</v>
+        <v>96.80</v>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">Mercatus Center, Inc.</t>
+          <t xml:space="preserve">Life Teen, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C190" s="66">
-        <v>90.25</v>
+        <v>76.40</v>
       </c>
     </row>
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">Mercy for Animals, Inc.</t>
+          <t xml:space="preserve">Live Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C191" s="66">
-        <v>75.82</v>
+        <v>81.13</v>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
+          <t xml:space="preserve">Living Waters for the World</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C192" s="66">
-        <v>88.00</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">Miracle Flights</t>
+          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C193" s="66">
-        <v>52.00</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C193" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
+          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C194" s="66">
-        <v>94.50</v>
+        <v>76.03</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">Mount Saint Marys University</t>
+          <t xml:space="preserve">Madison House</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C195" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C195" s="66">
+        <v>77.79</v>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">Mountain States Legal Foundation</t>
+          <t xml:space="preserve">MAP International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">11/3/2026</t>
         </is>
       </c>
       <c r="C196" s="66">
-        <v>69.99</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">MrCharity, Inc.</t>
+          <t xml:space="preserve">March of Dimes</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
-        </is>
-      </c>
-      <c r="C197" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/30/2026</t>
+        </is>
+      </c>
+      <c r="C197" s="66">
+        <v>74.00</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
+          <t xml:space="preserve">Marist University</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C198" s="66">
-        <v>54.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
+          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C199" s="66">
-        <v>77.80</v>
+        <v>91.74</v>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
+          <t xml:space="preserve">Meals on Wheels America</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">12/19/2026</t>
+          <t xml:space="preserve">5/27/2027</t>
         </is>
       </c>
       <c r="C200" s="66">
-        <v>66.90</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
+          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">6/9/2027</t>
         </is>
       </c>
       <c r="C201" s="66">
-        <v>65.00</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">National Audubon Society, Inc.</t>
+          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C202" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">12/8/2026</t>
+        </is>
+      </c>
+      <c r="C202" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
+          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C203" s="66">
-        <v>81.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">National Council of Nonprofits</t>
+          <t xml:space="preserve">Mercatus Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C204" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C204" s="66">
+        <v>90.25</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
+          <t xml:space="preserve">Mercy for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C205" s="66">
-        <v>49.00</v>
+        <v>75.82</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">National Foundation for Cancer Research</t>
+          <t xml:space="preserve">Mercy Ships</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C206" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/26/2027</t>
+        </is>
+      </c>
+      <c r="C206" s="66">
+        <v>78.18</v>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">National Geographic Society</t>
+          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">3/18/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C207" s="66">
-        <v>77.00</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">National Museum of Women in the Arts, Inc.</t>
+          <t xml:space="preserve">Minutes Matter-MCADD</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="C208" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">7/19/2027</t>
+        </is>
+      </c>
+      <c r="C208" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">National Park Foundation</t>
+          <t xml:space="preserve">Miracle Flights</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C209" s="66">
-        <v>72.00</v>
+        <v>52.00</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">National PKU Alliance, Inc.</t>
+          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C210" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C210" s="66">
+        <v>94.50</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
+          <t xml:space="preserve">Mount Saint Marys University</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C211" s="65">
@@ -3368,27 +3368,27 @@
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
+          <t xml:space="preserve">Mountain States Legal Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C212" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C212" s="66">
+        <v>69.99</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">National Space Society</t>
+          <t xml:space="preserve">MrCharity, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">2/23/2027</t>
         </is>
       </c>
       <c r="C213" s="65">
@@ -3398,282 +3398,282 @@
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">National University</t>
+          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C214" s="66">
-        <v>42.69</v>
+        <v>54.00</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">National Veterans Memorial and Museum</t>
+          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">6/24/2027</t>
         </is>
       </c>
       <c r="C215" s="66">
-        <v>72.63</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">National Wheelchair Basketball Association</t>
+          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">12/19/2026</t>
         </is>
       </c>
       <c r="C216" s="66">
-        <v>77.80</v>
+        <v>66.90</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
+          <t xml:space="preserve">Naropa University</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">9/22/2026</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C217" s="66">
-        <v>2.90</v>
+        <v>76.21</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">Network for Good, Inc</t>
+          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C218" s="66">
-        <v>97.80</v>
+        <v>65.00</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">New Harvest, Inc.</t>
+          <t xml:space="preserve">National Audubon Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C219" s="66">
-        <v>88.49</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
+          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C220" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C220" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">Nurse-Family Partnership</t>
+          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C221" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/7/2027</t>
+        </is>
+      </c>
+      <c r="C221" s="66">
+        <v>92.28</v>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">Ocean Conservancy</t>
+          <t xml:space="preserve">National Council of Nonprofits</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C222" s="66">
-        <v>74.06</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C222" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
+          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C223" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C223" s="66">
+        <v>49.00</v>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">OneHope, Inc.</t>
+          <t xml:space="preserve">National Foundation for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
-        </is>
-      </c>
-      <c r="C224" s="66">
-        <v>82.72</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C224" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">Operation Smile, Inc.</t>
+          <t xml:space="preserve">National Geographic Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C225" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/18/2027</t>
+        </is>
+      </c>
+      <c r="C225" s="66">
+        <v>77.00</v>
       </c>
     </row>
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
+          <t xml:space="preserve">National Museum of Women in the Arts, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">8/18/2027</t>
+          <t xml:space="preserve">10/3/2026</t>
         </is>
       </c>
       <c r="C226" s="66">
-        <v>77.59</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">Our Change Foundation</t>
+          <t xml:space="preserve">National Network of Abortion Funds</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
-        </is>
-      </c>
-      <c r="C227" s="66">
-        <v>80.46</v>
+          <t xml:space="preserve">9/11/2027</t>
+        </is>
+      </c>
+      <c r="C227" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">Oxfam-America, Inc.</t>
+          <t xml:space="preserve">National Park Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C228" s="66">
-        <v>71.00</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">Pace University</t>
+          <t xml:space="preserve">National PKU Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
-        </is>
-      </c>
-      <c r="C229" s="66">
-        <v>88.30</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C229" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
+          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C230" s="66">
-        <v>55.43</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C230" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">Panorama Global</t>
+          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
-        </is>
-      </c>
-      <c r="C231" s="66">
-        <v>84.52</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C231" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">Parkinson Research Foundation, Inc.</t>
+          <t xml:space="preserve">National Space Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">9/25/2026</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C232" s="65">
@@ -3683,102 +3683,102 @@
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
+          <t xml:space="preserve">National University</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">2/9/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C233" s="66">
-        <v>90.00</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
+          <t xml:space="preserve">National Veterans Memorial and Museum</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
-        </is>
-      </c>
-      <c r="C234" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C234" s="66">
+        <v>72.63</v>
       </c>
     </row>
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">Pathfinder International</t>
+          <t xml:space="preserve">National Wheelchair Basketball Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C235" s="66">
-        <v>85.33</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
+          <t xml:space="preserve">National Wildlife Federation</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C236" s="66">
-        <v>83.76</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
+          <t xml:space="preserve">Network for Good, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C237" s="66">
-        <v>58.00</v>
+        <v>97.80</v>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
+          <t xml:space="preserve">New Harvest, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C238" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C238" s="66">
+        <v>88.49</v>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
+          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C239" s="65">
@@ -3788,12 +3788,12 @@
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
+          <t xml:space="preserve">Nurse-Family Partnership</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C240" s="65">
@@ -3803,57 +3803,57 @@
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">Pledgeling Foundation</t>
+          <t xml:space="preserve">Ocean Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C241" s="66">
-        <v>65.93</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">Polar Bears International</t>
+          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">2/2/2027</t>
-        </is>
-      </c>
-      <c r="C242" s="66">
-        <v>86.00</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C242" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
+          <t xml:space="preserve">OneHope, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
+          <t xml:space="preserve">10/1/2026</t>
         </is>
       </c>
       <c r="C243" s="66">
-        <v>85.54</v>
+        <v>82.72</v>
       </c>
     </row>
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">Pratt Institute</t>
+          <t xml:space="preserve">Operation Smile, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C244" s="65">
@@ -3863,82 +3863,82 @@
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">Primo Cares, Inc.</t>
+          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C245" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/18/2027</t>
+        </is>
+      </c>
+      <c r="C245" s="66">
+        <v>77.59</v>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">Project Cure, Inc.</t>
+          <t xml:space="preserve">Our Change Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C246" s="66">
-        <v>23.00</v>
+        <v>80.46</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
+          <t xml:space="preserve">Oxfam-America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">10/6/2026</t>
         </is>
       </c>
       <c r="C247" s="66">
-        <v>88.71</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">Project Orbis International, Inc.</t>
+          <t xml:space="preserve">Pace University</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
-        </is>
-      </c>
-      <c r="C248" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/1/2027</t>
+        </is>
+      </c>
+      <c r="C248" s="66">
+        <v>88.30</v>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">Proteus Fund, Inc.</t>
+          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C249" s="66">
-        <v>81.25</v>
+        <v>55.43</v>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">Providence House</t>
+          <t xml:space="preserve">Panorama Global</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
@@ -3947,48 +3947,48 @@
         </is>
       </c>
       <c r="C250" s="66">
-        <v>92.06</v>
+        <v>84.52</v>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
+          <t xml:space="preserve">Paralyzed Veterans of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C251" s="66">
-        <v>84.22</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">Re:Power</t>
+          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C252" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/9/2027</t>
+        </is>
+      </c>
+      <c r="C252" s="66">
+        <v>90.00</v>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">Rodale Institute</t>
+          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C253" s="65">
@@ -3998,117 +3998,117 @@
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
+          <t xml:space="preserve">Pathfinder International</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">12/12/2026</t>
-        </is>
-      </c>
-      <c r="C254" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C254" s="66">
+        <v>85.33</v>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
+          <t xml:space="preserve">patriotic Hearts, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C255" s="66">
-        <v>45.00</v>
+        <v>56.00</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
+          <t xml:space="preserve">People for the American Way Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C256" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C256" s="66">
+        <v>60.00</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">Rush University Medical Center</t>
+          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C257" s="66">
-        <v>91.41</v>
+        <v>83.76</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">Sagamore Institute, Inc.</t>
+          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C258" s="66">
-        <v>91.61</v>
+        <v>58.00</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">Saint John's University</t>
+          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">8/28/2027</t>
         </is>
       </c>
       <c r="C259" s="66">
-        <v>92.84</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">Save the Chimps, Inc.</t>
+          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
-        </is>
-      </c>
-      <c r="C260" s="66">
-        <v>79.70</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C260" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">Seattle Pacific University</t>
+          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">11/3/2026</t>
         </is>
       </c>
       <c r="C261" s="65">
@@ -4118,147 +4118,147 @@
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
+          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
-        </is>
-      </c>
-      <c r="C262" s="66">
-        <v>94.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C262" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
+          <t xml:space="preserve">Pledgeling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C263" s="66">
-        <v>97.29</v>
+        <v>65.93</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">Sierra  Club</t>
+          <t xml:space="preserve">Polar Bears International</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">12/22/2026</t>
+          <t xml:space="preserve">2/2/2027</t>
         </is>
       </c>
       <c r="C264" s="66">
-        <v>82.00</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">Sister Rising Worldwide</t>
+          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">1/28/2027</t>
-        </is>
-      </c>
-      <c r="C265" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/27/2027</t>
+        </is>
+      </c>
+      <c r="C265" s="66">
+        <v>85.54</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">Sixpoint, Inc.</t>
+          <t xml:space="preserve">Pratt Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
-        </is>
-      </c>
-      <c r="C266" s="66">
-        <v>77.16</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C266" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
+          <t xml:space="preserve">Primo Cares, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">4/22/2027</t>
-        </is>
-      </c>
-      <c r="C267" s="66">
-        <v>90.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C267" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">Social Purpose Corrections</t>
+          <t xml:space="preserve">Prison Fellowship Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C268" s="66">
-        <v>12.95</v>
+        <v>68.60</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
+          <t xml:space="preserve">Project Cure, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
-        </is>
-      </c>
-      <c r="C269" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C269" s="66">
+        <v>27.00</v>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
+          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">7/29/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C270" s="66">
-        <v>86.00</v>
+        <v>88.71</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">South Dakota State University Foundation</t>
+          <t xml:space="preserve">Project Orbis International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">10/7/2026</t>
         </is>
       </c>
       <c r="C271" s="65">
@@ -4268,57 +4268,57 @@
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
+          <t xml:space="preserve">Proteus Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C272" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/2/2027</t>
+        </is>
+      </c>
+      <c r="C272" s="66">
+        <v>81.25</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">Special Olympics, Inc.</t>
+          <t xml:space="preserve">Providence House</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C273" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C273" s="66">
+        <v>92.06</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
+          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C274" s="66">
-        <v>85.31</v>
+        <v>84.22</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
+          <t xml:space="preserve">Re:Power</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C275" s="65">
@@ -4328,267 +4328,267 @@
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">Students for Life Action, Inc.</t>
+          <t xml:space="preserve">Reproductive Freedom for All</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">11/7/2026</t>
-        </is>
-      </c>
-      <c r="C276" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C276" s="66">
+        <v>70.00</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">Students for Life of America</t>
+          <t xml:space="preserve">Rodale Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
-        </is>
-      </c>
-      <c r="C277" s="66">
-        <v>82.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C277" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
+          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">8/12/2027</t>
-        </is>
-      </c>
-      <c r="C278" s="66">
-        <v>89.29</v>
+          <t xml:space="preserve">12/12/2026</t>
+        </is>
+      </c>
+      <c r="C278" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">Teacher Freedom Alliance</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
-        </is>
-      </c>
-      <c r="C279" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/7/2026</t>
+        </is>
+      </c>
+      <c r="C279" s="66">
+        <v>45.00</v>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">The Actors' Fund of America</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
-        </is>
-      </c>
-      <c r="C280" s="66">
-        <v>86.73</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C280" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Rush University Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C281" s="66">
-        <v>39.00</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">The American University</t>
+          <t xml:space="preserve">Rutgers University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C282" s="66">
-        <v>92.06</v>
+        <v>87.46</v>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+          <t xml:space="preserve">Sagamore Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C283" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C283" s="66">
+        <v>91.61</v>
       </c>
     </row>
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">The Anthony Davis Foundation</t>
+          <t xml:space="preserve">Saint John's University</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">11/24/2026</t>
-        </is>
-      </c>
-      <c r="C284" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/31/2027</t>
+        </is>
+      </c>
+      <c r="C284" s="66">
+        <v>88.76</v>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
+          <t xml:space="preserve">Save the Chimps, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">10/24/2026</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C285" s="66">
-        <v>90.00</v>
+        <v>79.70</v>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">The Barack Obama Foundation</t>
+          <t xml:space="preserve">Seattle Pacific University</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C286" s="66">
-        <v>55.90</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C286" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">The Baruch College Fund</t>
+          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C287" s="66">
-        <v>84.00</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">The Call of Duty Endowment</t>
+          <t xml:space="preserve">Share Our Strength</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C288" s="66">
-        <v>73.00</v>
+        <v>58.73</v>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">The Center for Alcohol Policy</t>
+          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C289" s="66">
-        <v>73.40</v>
+        <v>97.29</v>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">The Center for Investigative Reporting</t>
+          <t xml:space="preserve">Sierra  Club</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C290" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/22/2026</t>
+        </is>
+      </c>
+      <c r="C290" s="66">
+        <v>82.00</v>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
+          <t xml:space="preserve">Sister Rising Worldwide</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
-        </is>
-      </c>
-      <c r="C291" s="66">
-        <v>71.00</v>
+          <t xml:space="preserve">1/28/2027</t>
+        </is>
+      </c>
+      <c r="C291" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
+          <t xml:space="preserve">Sixpoint, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">7/6/2027</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C292" s="66">
-        <v>71.00</v>
+        <v>77.16</v>
       </c>
     </row>
     <row r="293">
       <c t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">The Colorado College</t>
+          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">10/29/2027</t>
+          <t xml:space="preserve">4/22/2027</t>
         </is>
       </c>
       <c r="C293" s="66">
@@ -4598,27 +4598,27 @@
     <row r="294">
       <c t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">The Denver Rescue Mission</t>
+          <t xml:space="preserve">Social Purpose Corrections</t>
         </is>
       </c>
       <c t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C294" s="66">
-        <v>82.96</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="295">
       <c t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
         </is>
       </c>
       <c t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C295" s="65">
@@ -4628,327 +4628,327 @@
     <row r="296">
       <c t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C296" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/29/2027</t>
+        </is>
+      </c>
+      <c r="C296" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="297">
       <c t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
+          <t xml:space="preserve">South Dakota State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
-        </is>
-      </c>
-      <c r="C297" s="66">
-        <v>76.48</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C297" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
+          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">5/15/2027</t>
-        </is>
-      </c>
-      <c r="C298" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C298" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">The Heritage Foundation</t>
+          <t xml:space="preserve">Special Olympics, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C299" s="66">
-        <v>83.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C299" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
+          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C300" s="66">
-        <v>89.00</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">The Independent Institute</t>
+          <t xml:space="preserve">State University of Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">9/4/2027</t>
         </is>
       </c>
       <c r="C301" s="66">
-        <v>77.51</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
+          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
-        </is>
-      </c>
-      <c r="C302" s="66">
-        <v>84.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C302" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">The Kansas University Endowment Association</t>
+          <t xml:space="preserve">Students for Life Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">7/21/2027</t>
-        </is>
-      </c>
-      <c r="C303" s="66">
-        <v>91.34</v>
+          <t xml:space="preserve">11/7/2026</t>
+        </is>
+      </c>
+      <c r="C303" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+          <t xml:space="preserve">Students for Life of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">10/10/2026</t>
         </is>
       </c>
       <c r="C304" s="66">
-        <v>83.06</v>
+        <v>82.00</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">The Memorial Foundation</t>
+          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/12/2027</t>
         </is>
       </c>
       <c r="C305" s="66">
-        <v>72.00</v>
+        <v>89.29</v>
       </c>
     </row>
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+          <t xml:space="preserve">Teacher Freedom Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C306" s="66">
-        <v>80.87</v>
+          <t xml:space="preserve">6/24/2027</t>
+        </is>
+      </c>
+      <c r="C306" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">The National World War II Museum, Inc.</t>
+          <t xml:space="preserve">The Actors' Fund of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">12/10/2026</t>
         </is>
       </c>
       <c r="C307" s="66">
-        <v>80.00</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">The Nature Conservancy</t>
+          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C308" s="66">
-        <v>70.00</v>
+        <v>39.00</v>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+          <t xml:space="preserve">The American University</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C309" s="66">
-        <v>80.64</v>
+        <v>90.23</v>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
+          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
-        </is>
-      </c>
-      <c r="C310" s="66">
-        <v>87.40</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C310" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">The Ohio University Foundation</t>
+          <t xml:space="preserve">The Anthony Davis Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C311" s="66">
-        <v>74.14</v>
+          <t xml:space="preserve">11/24/2026</t>
+        </is>
+      </c>
+      <c r="C311" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">The OneStar Foundation</t>
+          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">10/24/2026</t>
         </is>
       </c>
       <c r="C312" s="66">
-        <v>62.50</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+          <t xml:space="preserve">The Barack Obama Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C313" s="66">
-        <v>88.30</v>
+        <v>55.90</v>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">The Planetary Society</t>
+          <t xml:space="preserve">The Baruch College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">7/14/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C314" s="66">
-        <v>66.00</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">The Purchase College Foundation</t>
+          <t xml:space="preserve">The Call of Duty Endowment</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C315" s="66">
-        <v>78.12</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
+          <t xml:space="preserve">The Center for Alcohol Policy</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C316" s="66">
-        <v>81.26</v>
+        <v>73.40</v>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">The Ruth Collective</t>
+          <t xml:space="preserve">The Center for Investigative Reporting</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">12/9/2026</t>
         </is>
       </c>
       <c r="C317" s="65">
@@ -4958,117 +4958,117 @@
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">The Society of the Cincinnati</t>
+          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C318" s="66">
-        <v>73.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+          <t xml:space="preserve">The Center for Victims of Torture</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C319" s="66">
-        <v>94.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">The University of Arizona Foundation</t>
+          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">9/29/2026</t>
+          <t xml:space="preserve">7/6/2027</t>
         </is>
       </c>
       <c r="C320" s="66">
-        <v>76.49</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+          <t xml:space="preserve">The Colorado College</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">4/13/2027</t>
+          <t xml:space="preserve">10/29/2027</t>
         </is>
       </c>
       <c r="C321" s="66">
-        <v>82.20</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">The University of Montana Foundation</t>
+          <t xml:space="preserve">The Denver Rescue Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C322" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/20/2027</t>
+        </is>
+      </c>
+      <c r="C322" s="66">
+        <v>82.96</v>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
+          <t xml:space="preserve">The Edison Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C323" s="66">
-        <v>76.00</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">The Visiting Angels Foundation</t>
+          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
-        </is>
-      </c>
-      <c r="C324" s="66">
-        <v>94.00</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C324" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
+          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
         </is>
       </c>
       <c t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">4/23/2027</t>
         </is>
       </c>
       <c r="C325" s="65">
@@ -5078,27 +5078,27 @@
     <row r="326">
       <c t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
         </is>
       </c>
       <c t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C326" s="66">
-        <v>79.51</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="327">
       <c t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
+          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">4/21/2027</t>
+          <t xml:space="preserve">5/15/2027</t>
         </is>
       </c>
       <c r="C327" s="66">
@@ -5108,540 +5108,1155 @@
     <row r="328">
       <c t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">Trevecca Nazarene University</t>
+          <t xml:space="preserve">The Heritage Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C328" s="66">
-        <v>87.82</v>
+        <v>83.00</v>
       </c>
     </row>
     <row r="329">
       <c t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C329" s="66">
-        <v>89.50</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="330">
       <c t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">Trustees of Tufts College</t>
+          <t xml:space="preserve">The Independent Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">7/2/2027</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C330" s="66">
-        <v>85.00</v>
+        <v>77.51</v>
       </c>
     </row>
     <row r="331">
       <c t="inlineStr" r="A331">
         <is>
-          <t xml:space="preserve">Turning Point USA, Inc.</t>
+          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B331">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C331" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C331" s="66">
+        <v>84.00</v>
       </c>
     </row>
     <row r="332">
       <c t="inlineStr" r="A332">
         <is>
-          <t xml:space="preserve">Twelveacres, Incorporated</t>
+          <t xml:space="preserve">The Just Trust for Education</t>
         </is>
       </c>
       <c t="inlineStr" r="B332">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C332" s="66">
-        <v>79.93</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="333">
       <c t="inlineStr" r="A333">
         <is>
-          <t xml:space="preserve">UATX</t>
+          <t xml:space="preserve">The Kansas University Endowment Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B333">
         <is>
-          <t xml:space="preserve">2/1/2027</t>
-        </is>
-      </c>
-      <c r="C333" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/21/2027</t>
+        </is>
+      </c>
+      <c r="C333" s="66">
+        <v>91.34</v>
       </c>
     </row>
     <row r="334">
       <c t="inlineStr" r="A334">
         <is>
-          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B334">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C334" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C334" s="66">
+        <v>83.06</v>
       </c>
     </row>
     <row r="335">
       <c t="inlineStr" r="A335">
         <is>
-          <t xml:space="preserve">UMKC Foundation</t>
+          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B335">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C335" s="66">
-        <v>95.00</v>
+        <v>91.99</v>
       </c>
     </row>
     <row r="336">
       <c t="inlineStr" r="A336">
         <is>
-          <t xml:space="preserve">Unified Youth</t>
+          <t xml:space="preserve">The Memorial Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B336">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C336" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C336" s="66">
+        <v>72.00</v>
       </c>
     </row>
     <row r="337">
       <c t="inlineStr" r="A337">
         <is>
-          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B337">
         <is>
-          <t xml:space="preserve">8/1/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C337" s="66">
-        <v>88.00</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="338">
       <c t="inlineStr" r="A338">
         <is>
-          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
+          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B338">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C338" s="66">
-        <v>84.01</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="339">
       <c t="inlineStr" r="A339">
         <is>
-          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">The National World War II Museum, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B339">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C339" s="66">
-        <v>85.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="340">
       <c t="inlineStr" r="A340">
         <is>
-          <t xml:space="preserve">united Service Organizations, Inc.</t>
+          <t xml:space="preserve">The Nature Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B340">
         <is>
-          <t xml:space="preserve">11/10/2026</t>
+          <t xml:space="preserve">10/9/2026</t>
         </is>
       </c>
       <c r="C340" s="66">
-        <v>67.94</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="341">
       <c t="inlineStr" r="A341">
         <is>
-          <t xml:space="preserve">United States Association for UNHCR</t>
+          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
         </is>
       </c>
       <c t="inlineStr" r="B341">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C341" s="66">
-        <v>61.00</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="342">
       <c t="inlineStr" r="A342">
         <is>
-          <t xml:space="preserve">United States Center for SafeSport</t>
+          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
         </is>
       </c>
       <c t="inlineStr" r="B342">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C342" s="66">
-        <v>72.74</v>
+        <v>87.40</v>
       </c>
     </row>
     <row r="343">
       <c t="inlineStr" r="A343">
         <is>
-          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
+          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B343">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">8/24/2027</t>
         </is>
       </c>
       <c r="C343" s="66">
-        <v>99.30</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="344">
       <c t="inlineStr" r="A344">
         <is>
-          <t xml:space="preserve">University of Colorado</t>
+          <t xml:space="preserve">The Ohio University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B344">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
-        </is>
-      </c>
-      <c r="C344" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C344" s="66">
+        <v>74.14</v>
       </c>
     </row>
     <row r="345">
       <c t="inlineStr" r="A345">
         <is>
-          <t xml:space="preserve">University of Georgia Foundation</t>
+          <t xml:space="preserve">The OneStar Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B345">
         <is>
-          <t xml:space="preserve">9/26/2026</t>
+          <t xml:space="preserve">1/14/2027</t>
         </is>
       </c>
       <c r="C345" s="66">
-        <v>94.00</v>
+        <v>62.50</v>
       </c>
     </row>
     <row r="346">
       <c t="inlineStr" r="A346">
         <is>
-          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
+          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B346">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C346" s="66">
-        <v>93.00</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="347">
       <c t="inlineStr" r="A347">
         <is>
-          <t xml:space="preserve">University of Nebraska Foundation</t>
+          <t xml:space="preserve">The Planetary Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B347">
         <is>
-          <t xml:space="preserve">7/15/2027</t>
+          <t xml:space="preserve">7/14/2027</t>
         </is>
       </c>
       <c r="C347" s="66">
-        <v>81.10</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="348">
       <c t="inlineStr" r="A348">
         <is>
-          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
+          <t xml:space="preserve">The Purchase College Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B348">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C348" s="66">
-        <v>77.00</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="349">
       <c t="inlineStr" r="A349">
         <is>
-          <t xml:space="preserve">University of Pacific</t>
+          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
         </is>
       </c>
       <c t="inlineStr" r="B349">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C349" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/17/2027</t>
+        </is>
+      </c>
+      <c r="C349" s="66">
+        <v>81.26</v>
       </c>
     </row>
     <row r="350">
       <c t="inlineStr" r="A350">
         <is>
-          <t xml:space="preserve">University of Richmond</t>
+          <t xml:space="preserve">The Ruth Collective</t>
         </is>
       </c>
       <c t="inlineStr" r="B350">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
-        </is>
-      </c>
-      <c r="C350" s="66">
-        <v>82.18</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C350" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="351">
       <c t="inlineStr" r="A351">
         <is>
-          <t xml:space="preserve">Veterans Community Project</t>
+          <t xml:space="preserve">The Society of the Cincinnati</t>
         </is>
       </c>
       <c t="inlineStr" r="B351">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C351" s="66">
-        <v>88.83</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="352">
       <c t="inlineStr" r="A352">
         <is>
-          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
         </is>
       </c>
       <c t="inlineStr" r="B352">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C352" s="66">
-        <v>28.00</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="353">
       <c t="inlineStr" r="A353">
         <is>
-          <t xml:space="preserve">VoteAmerica, Inc.</t>
+          <t xml:space="preserve">The University of Arizona Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B353">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">9/29/2026</t>
         </is>
       </c>
       <c r="C353" s="66">
-        <v>93.37</v>
+        <v>76.49</v>
       </c>
     </row>
     <row r="354">
       <c t="inlineStr" r="A354">
         <is>
-          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B354">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C354" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/13/2027</t>
+        </is>
+      </c>
+      <c r="C354" s="66">
+        <v>82.20</v>
       </c>
     </row>
     <row r="355">
       <c t="inlineStr" r="A355">
         <is>
-          <t xml:space="preserve">Washington State University Foundation</t>
+          <t xml:space="preserve">The University of Montana Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B355">
         <is>
-          <t xml:space="preserve">7/8/2027</t>
-        </is>
-      </c>
-      <c r="C355" s="66">
-        <v>75.03</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C355" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="356">
       <c t="inlineStr" r="A356">
         <is>
-          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B356">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C356" s="66">
-        <v>82.68</v>
+        <v>76.00</v>
       </c>
     </row>
     <row r="357">
       <c t="inlineStr" r="A357">
         <is>
-          <t xml:space="preserve">Winning for Women, Inc.</t>
+          <t xml:space="preserve">The Visiting Angels Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B357">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">7/20/2027</t>
         </is>
       </c>
       <c r="C357" s="66">
-        <v>66.70</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="358">
       <c t="inlineStr" r="A358">
         <is>
-          <t xml:space="preserve">Women for Women International</t>
+          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B358">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C358" s="66">
-        <v>79.06</v>
+          <t xml:space="preserve">10/15/2026</t>
+        </is>
+      </c>
+      <c r="C358" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="359">
       <c t="inlineStr" r="A359">
         <is>
-          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B359">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C359" s="66">
-        <v>71.40</v>
+        <v>79.51</v>
       </c>
     </row>
     <row r="360">
       <c t="inlineStr" r="A360">
         <is>
-          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+          <t xml:space="preserve">The Wilderness Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B360">
         <is>
-          <t xml:space="preserve">2/20/2027</t>
-        </is>
-      </c>
-      <c r="C360" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C360" s="66">
+        <v>73.00</v>
       </c>
     </row>
     <row r="361">
       <c t="inlineStr" r="A361">
         <is>
-          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B361">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
+          <t xml:space="preserve">4/21/2027</t>
         </is>
       </c>
       <c r="C361" s="66">
-        <v>79.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="362">
       <c t="inlineStr" r="A362">
         <is>
-          <t xml:space="preserve">YMCA of the Rockies</t>
+          <t xml:space="preserve">Together Making Changes</t>
         </is>
       </c>
       <c t="inlineStr" r="B362">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C362" s="66">
-        <v>81.65</v>
+        <v>90.26</v>
       </c>
     </row>
     <row r="363">
       <c t="inlineStr" r="A363">
         <is>
+          <t xml:space="preserve">Trevecca Nazarene University</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B363">
+        <is>
+          <t xml:space="preserve">7/30/2027</t>
+        </is>
+      </c>
+      <c r="C363" s="66">
+        <v>87.82</v>
+      </c>
+    </row>
+    <row r="364">
+      <c t="inlineStr" r="A364">
+        <is>
+          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B364">
+        <is>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C364" s="66">
+        <v>94.50</v>
+      </c>
+    </row>
+    <row r="365">
+      <c t="inlineStr" r="A365">
+        <is>
+          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B365">
+        <is>
+          <t xml:space="preserve">9/9/2027</t>
+        </is>
+      </c>
+      <c r="C365" s="66">
+        <v>89.90</v>
+      </c>
+    </row>
+    <row r="366">
+      <c t="inlineStr" r="A366">
+        <is>
+          <t xml:space="preserve">Trustees of Tufts College</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B366">
+        <is>
+          <t xml:space="preserve">7/2/2027</t>
+        </is>
+      </c>
+      <c r="C366" s="66">
+        <v>85.00</v>
+      </c>
+    </row>
+    <row r="367">
+      <c t="inlineStr" r="A367">
+        <is>
+          <t xml:space="preserve">Turning Point USA, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B367">
+        <is>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C367" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c t="inlineStr" r="A368">
+        <is>
+          <t xml:space="preserve">Twelveacres, Incorporated</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B368">
+        <is>
+          <t xml:space="preserve">1/16/2027</t>
+        </is>
+      </c>
+      <c r="C368" s="66">
+        <v>79.93</v>
+      </c>
+    </row>
+    <row r="369">
+      <c t="inlineStr" r="A369">
+        <is>
+          <t xml:space="preserve">UATX</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B369">
+        <is>
+          <t xml:space="preserve">2/1/2027</t>
+        </is>
+      </c>
+      <c r="C369" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c t="inlineStr" r="A370">
+        <is>
+          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B370">
+        <is>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C370" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c t="inlineStr" r="A371">
+        <is>
+          <t xml:space="preserve">UMKC Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B371">
+        <is>
+          <t xml:space="preserve">1/27/2027</t>
+        </is>
+      </c>
+      <c r="C371" s="66">
+        <v>95.00</v>
+      </c>
+    </row>
+    <row r="372">
+      <c t="inlineStr" r="A372">
+        <is>
+          <t xml:space="preserve">Unified Youth</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B372">
+        <is>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C372" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c t="inlineStr" r="A373">
+        <is>
+          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B373">
+        <is>
+          <t xml:space="preserve">8/1/2027</t>
+        </is>
+      </c>
+      <c r="C373" s="66">
+        <v>88.00</v>
+      </c>
+    </row>
+    <row r="374">
+      <c t="inlineStr" r="A374">
+        <is>
+          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B374">
+        <is>
+          <t xml:space="preserve">8/17/2027</t>
+        </is>
+      </c>
+      <c r="C374" s="66">
+        <v>84.01</v>
+      </c>
+    </row>
+    <row r="375">
+      <c t="inlineStr" r="A375">
+        <is>
+          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B375">
+        <is>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C375" s="66">
+        <v>85.00</v>
+      </c>
+    </row>
+    <row r="376">
+      <c t="inlineStr" r="A376">
+        <is>
+          <t xml:space="preserve">united Service Organizations, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B376">
+        <is>
+          <t xml:space="preserve">11/10/2026</t>
+        </is>
+      </c>
+      <c r="C376" s="66">
+        <v>67.94</v>
+      </c>
+    </row>
+    <row r="377">
+      <c t="inlineStr" r="A377">
+        <is>
+          <t xml:space="preserve">United States Association for UNHCR</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B377">
+        <is>
+          <t xml:space="preserve">6/1/2027</t>
+        </is>
+      </c>
+      <c r="C377" s="66">
+        <v>61.00</v>
+      </c>
+    </row>
+    <row r="378">
+      <c t="inlineStr" r="A378">
+        <is>
+          <t xml:space="preserve">United States Center for SafeSport</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B378">
+        <is>
+          <t xml:space="preserve">2/27/2027</t>
+        </is>
+      </c>
+      <c r="C378" s="66">
+        <v>72.74</v>
+      </c>
+    </row>
+    <row r="379">
+      <c t="inlineStr" r="A379">
+        <is>
+          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B379">
+        <is>
+          <t xml:space="preserve">9/9/2027</t>
+        </is>
+      </c>
+      <c r="C379" s="66">
+        <v>38.00</v>
+      </c>
+    </row>
+    <row r="380">
+      <c t="inlineStr" r="A380">
+        <is>
+          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B380">
+        <is>
+          <t xml:space="preserve">7/31/2027</t>
+        </is>
+      </c>
+      <c r="C380" s="66">
+        <v>99.30</v>
+      </c>
+    </row>
+    <row r="381">
+      <c t="inlineStr" r="A381">
+        <is>
+          <t xml:space="preserve">University of Colorado</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B381">
+        <is>
+          <t xml:space="preserve">10/7/2026</t>
+        </is>
+      </c>
+      <c r="C381" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c t="inlineStr" r="A382">
+        <is>
+          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B382">
+        <is>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C382" s="66">
+        <v>93.00</v>
+      </c>
+    </row>
+    <row r="383">
+      <c t="inlineStr" r="A383">
+        <is>
+          <t xml:space="preserve">University of Nebraska Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B383">
+        <is>
+          <t xml:space="preserve">7/15/2027</t>
+        </is>
+      </c>
+      <c r="C383" s="66">
+        <v>81.10</v>
+      </c>
+    </row>
+    <row r="384">
+      <c t="inlineStr" r="A384">
+        <is>
+          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B384">
+        <is>
+          <t xml:space="preserve">6/23/2027</t>
+        </is>
+      </c>
+      <c r="C384" s="66">
+        <v>77.00</v>
+      </c>
+    </row>
+    <row r="385">
+      <c t="inlineStr" r="A385">
+        <is>
+          <t xml:space="preserve">University of Pacific</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B385">
+        <is>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C385" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c t="inlineStr" r="A386">
+        <is>
+          <t xml:space="preserve">University of Richmond</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B386">
+        <is>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C386" s="66">
+        <v>82.18</v>
+      </c>
+    </row>
+    <row r="387">
+      <c t="inlineStr" r="A387">
+        <is>
+          <t xml:space="preserve">Veterans Community Project</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B387">
+        <is>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C387" s="66">
+        <v>88.83</v>
+      </c>
+    </row>
+    <row r="388">
+      <c t="inlineStr" r="A388">
+        <is>
+          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B388">
+        <is>
+          <t xml:space="preserve">7/13/2027</t>
+        </is>
+      </c>
+      <c r="C388" s="66">
+        <v>72.00</v>
+      </c>
+    </row>
+    <row r="389">
+      <c t="inlineStr" r="A389">
+        <is>
+          <t xml:space="preserve">Violet Research Institute, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B389">
+        <is>
+          <t xml:space="preserve">7/28/2027</t>
+        </is>
+      </c>
+      <c r="C389" s="66">
+        <v>80.00</v>
+      </c>
+    </row>
+    <row r="390">
+      <c t="inlineStr" r="A390">
+        <is>
+          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B390">
+        <is>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C390" s="66">
+        <v>28.00</v>
+      </c>
+    </row>
+    <row r="391">
+      <c t="inlineStr" r="A391">
+        <is>
+          <t xml:space="preserve">VoteAmerica, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B391">
+        <is>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C391" s="66">
+        <v>93.37</v>
+      </c>
+    </row>
+    <row r="392">
+      <c t="inlineStr" r="A392">
+        <is>
+          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B392">
+        <is>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C392" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c t="inlineStr" r="A393">
+        <is>
+          <t xml:space="preserve">Washington State University Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B393">
+        <is>
+          <t xml:space="preserve">7/8/2027</t>
+        </is>
+      </c>
+      <c r="C393" s="66">
+        <v>75.03</v>
+      </c>
+    </row>
+    <row r="394">
+      <c t="inlineStr" r="A394">
+        <is>
+          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B394">
+        <is>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C394" s="66">
+        <v>82.68</v>
+      </c>
+    </row>
+    <row r="395">
+      <c t="inlineStr" r="A395">
+        <is>
+          <t xml:space="preserve">Wildlife Conservation Network</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B395">
+        <is>
+          <t xml:space="preserve">8/13/2027</t>
+        </is>
+      </c>
+      <c r="C395" s="66">
+        <v>92.13</v>
+      </c>
+    </row>
+    <row r="396">
+      <c t="inlineStr" r="A396">
+        <is>
+          <t xml:space="preserve">Winning for Women, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B396">
+        <is>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C396" s="66">
+        <v>66.70</v>
+      </c>
+    </row>
+    <row r="397">
+      <c t="inlineStr" r="A397">
+        <is>
+          <t xml:space="preserve">Women for Women International</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B397">
+        <is>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C397" s="66">
+        <v>79.06</v>
+      </c>
+    </row>
+    <row r="398">
+      <c t="inlineStr" r="A398">
+        <is>
+          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B398">
+        <is>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C398" s="66">
+        <v>71.40</v>
+      </c>
+    </row>
+    <row r="399">
+      <c t="inlineStr" r="A399">
+        <is>
+          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B399">
+        <is>
+          <t xml:space="preserve">2/20/2027</t>
+        </is>
+      </c>
+      <c r="C399" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c t="inlineStr" r="A400">
+        <is>
+          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B400">
+        <is>
+          <t xml:space="preserve">5/20/2027</t>
+        </is>
+      </c>
+      <c r="C400" s="66">
+        <v>79.00</v>
+      </c>
+    </row>
+    <row r="401">
+      <c t="inlineStr" r="A401">
+        <is>
+          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B401">
+        <is>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C401" s="66">
+        <v>70.36</v>
+      </c>
+    </row>
+    <row r="402">
+      <c t="inlineStr" r="A402">
+        <is>
+          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B402">
+        <is>
+          <t xml:space="preserve">8/24/2027</t>
+        </is>
+      </c>
+      <c r="C402" s="66">
+        <v>39.45</v>
+      </c>
+    </row>
+    <row r="403">
+      <c t="inlineStr" r="A403">
+        <is>
+          <t xml:space="preserve">YMCA of the Rockies</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B403">
+        <is>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C403" s="66">
+        <v>81.65</v>
+      </c>
+    </row>
+    <row r="404">
+      <c t="inlineStr" r="A404">
+        <is>
           <t xml:space="preserve">Young Judaea Global, Inc.</t>
         </is>
       </c>
-      <c t="inlineStr" r="B363">
+      <c t="inlineStr" r="B404">
         <is>
           <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
-      <c r="C363" s="66">
+      <c r="C404" s="66">
         <v>71.20</v>
       </c>
     </row>

--- a/downloadable-data/LA.xlsx
+++ b/downloadable-data/LA.xlsx
@@ -578,382 +578,382 @@
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">America's Survival, Inc.</t>
+          <t xml:space="preserve">Amateur Athletic Union of the United States. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">9/28/2027</t>
         </is>
       </c>
       <c r="C26" s="66">
-        <v>90.07</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">American Association of Family and Consumer Scienc</t>
+          <t xml:space="preserve">America's Survival, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C27" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C27" s="66">
+        <v>90.07</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">American Association of State Troopers, Inc.</t>
+          <t xml:space="preserve">American Association of Family and Consumer Scienc</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C28" s="66">
-        <v>23.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">American Bible Society</t>
+          <t xml:space="preserve">American Association of State Troopers, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C29" s="66">
-        <v>76.00</v>
+        <v>23.00</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">American Civil Liberties Union Foundation, Inc.</t>
+          <t xml:space="preserve">American Bible Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C30" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/27/2027</t>
+        </is>
+      </c>
+      <c r="C30" s="66">
+        <v>76.00</v>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">American Congress for Truth, Inc.</t>
+          <t xml:space="preserve">American Civil Liberties Union Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
-        </is>
-      </c>
-      <c r="C31" s="66">
-        <v>75.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">American Council of the Blind, Inc.</t>
+          <t xml:space="preserve">American Congress for Truth, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">10/16/2026</t>
-        </is>
-      </c>
-      <c r="C32" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/28/2027</t>
+        </is>
+      </c>
+      <c r="C32" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">American Diabetes Association</t>
+          <t xml:space="preserve">American Council of the Blind, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
-        </is>
-      </c>
-      <c r="C33" s="66">
-        <v>79.60</v>
+          <t xml:space="preserve">10/16/2026</t>
+        </is>
+      </c>
+      <c r="C33" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">American Foundation for the Blind, Inc.</t>
+          <t xml:space="preserve">American Diabetes Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C34" s="66">
-        <v>66.78</v>
+        <v>79.60</v>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">American Heart Association, Inc.</t>
+          <t xml:space="preserve">American Foundation for the Blind, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">8/18/2027</t>
-        </is>
-      </c>
-      <c r="C35" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C35" s="66">
+        <v>66.78</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">American Indian College Fund</t>
+          <t xml:space="preserve">American Heart Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">11/13/2026</t>
-        </is>
-      </c>
-      <c r="C36" s="66">
-        <v>78.00</v>
+          <t xml:space="preserve">8/18/2027</t>
+        </is>
+      </c>
+      <c r="C36" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">American Institute for Cancer Research</t>
+          <t xml:space="preserve">American Indian College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">11/13/2026</t>
         </is>
       </c>
       <c r="C37" s="66">
-        <v>67.00</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">American Institute for Economic Research</t>
+          <t xml:space="preserve">American Institute for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C38" s="66">
-        <v>78.63</v>
+        <v>67.00</v>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">American Institute of Chemical Engineers</t>
+          <t xml:space="preserve">American Institute for Economic Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C39" s="66">
-        <v>82.15</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">American Kidney Fund, Inc.</t>
+          <t xml:space="preserve">American Institute of Chemical Engineers</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">5/12/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C40" s="66">
-        <v>95.70</v>
+        <v>82.15</v>
       </c>
     </row>
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">American Lebanese Syrian Associated Charities, Inc</t>
+          <t xml:space="preserve">American Kidney Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">5/12/2027</t>
         </is>
       </c>
       <c r="C41" s="66">
-        <v>75.96</v>
+        <v>95.70</v>
       </c>
     </row>
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
+          <t xml:space="preserve">American Lebanese Syrian Associated Charities, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C42" s="66">
-        <v>75.08</v>
+        <v>75.96</v>
       </c>
     </row>
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">American Lung Association</t>
+          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">5/26/2027</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C43" s="66">
-        <v>85.00</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">American Near East Refugee Aid, Inc</t>
+          <t xml:space="preserve">American Lung Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">5/26/2027</t>
         </is>
       </c>
       <c r="C44" s="66">
-        <v>95.44</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">American Roentgen Ray Society</t>
+          <t xml:space="preserve">American Near East Refugee Aid, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C45" s="66">
-        <v>52.00</v>
+        <v>95.44</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">Americans For Fair Treatment</t>
+          <t xml:space="preserve">American Roentgen Ray Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C46" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/9/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="66">
+        <v>52.00</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">Americares Foundation, Inc.</t>
+          <t xml:space="preserve">Americans For Fair Treatment</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
-        </is>
-      </c>
-      <c r="C47" s="66">
-        <v>98.06</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
+          <t xml:space="preserve">Americares Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C48" s="66">
-        <v>71.00</v>
+        <v>98.06</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">Animals' Angels, Incorporated</t>
+          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">9/12/2027</t>
+          <t xml:space="preserve">10/14/2026</t>
         </is>
       </c>
       <c r="C49" s="66">
-        <v>77.41</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">Anti-Defamation League</t>
+          <t xml:space="preserve">Animals' Angels, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">9/12/2027</t>
         </is>
       </c>
       <c r="C50" s="66">
-        <v>75.00</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">Arkansas Tech University Foundation</t>
+          <t xml:space="preserve">Anti-Defamation League</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
@@ -962,33 +962,33 @@
         </is>
       </c>
       <c r="C51" s="66">
-        <v>94.06</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
+          <t xml:space="preserve">Arkansas Tech University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C52" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C52" s="66">
+        <v>94.06</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">Association of American Education Foundation</t>
+          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C53" s="65">
@@ -998,97 +998,97 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Austin College</t>
+          <t xml:space="preserve">Association of American Education Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
-        </is>
-      </c>
-      <c r="C54" s="66">
-        <v>85.11</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C54" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
+          <t xml:space="preserve">Austin College</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">3/23/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C55" s="66">
-        <v>81.00</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">Autism Speaks, Inc.</t>
+          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C56" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/23/2027</t>
+        </is>
+      </c>
+      <c r="C56" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
+          <t xml:space="preserve">Autism Speaks, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C57" s="66">
-        <v>44.00</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C57" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">B'nai B'rith International</t>
+          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C58" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="66">
+        <v>44.00</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">Back Bay Mission, Inc.</t>
+          <t xml:space="preserve">B'nai B'rith International</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
-        </is>
-      </c>
-      <c r="C59" s="66">
-        <v>83.67</v>
+          <t xml:space="preserve">12/18/2026</t>
+        </is>
+      </c>
+      <c r="C59" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Base Ministry</t>
+          <t xml:space="preserve">Back Bay Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
@@ -1097,58 +1097,58 @@
         </is>
       </c>
       <c r="C60" s="66">
-        <v>71.89</v>
+        <v>83.67</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">Blessings International</t>
+          <t xml:space="preserve">Base Ministry</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">9/2/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C61" s="66">
-        <v>91.00</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Blood Cancer United, Inc.</t>
+          <t xml:space="preserve">Blessings International</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">9/2/2027</t>
         </is>
       </c>
       <c r="C62" s="66">
-        <v>75.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Brady Campaign to Prevent Gun Violence</t>
+          <t xml:space="preserve">Blood Cancer United, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C63" s="66">
-        <v>45.00</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
+          <t xml:space="preserve">Brady Campaign to Prevent Gun Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
@@ -1157,243 +1157,243 @@
         </is>
       </c>
       <c r="C64" s="66">
-        <v>71.00</v>
+        <v>45.00</v>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
+          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C65" s="66">
-        <v>78.58</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">Business Action Fund</t>
+          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C66" s="66">
-        <v>54.00</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">Cair-Foundation, Inc.</t>
+          <t xml:space="preserve">Business Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C67" s="66">
-        <v>66.00</v>
+        <v>54.00</v>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">CAMFED USA Foundation</t>
+          <t xml:space="preserve">Cair-Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
+          <t xml:space="preserve">1/14/2027</t>
         </is>
       </c>
       <c r="C68" s="66">
-        <v>91.78</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">Captain Joseph House Foundation</t>
+          <t xml:space="preserve">CAMFED USA Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C69" s="66">
-        <v>67.20</v>
+        <v>91.78</v>
       </c>
     </row>
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
+          <t xml:space="preserve">Captain Joseph House Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C70" s="66">
-        <v>97.00</v>
+        <v>67.20</v>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">Center for Community Change Action</t>
+          <t xml:space="preserve">Carolina Tiger Rescue</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">9/18/2027</t>
         </is>
       </c>
       <c r="C71" s="66">
-        <v>95.00</v>
+        <v>68.00</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">Central Asia Institute</t>
+          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">10/14/2026</t>
         </is>
       </c>
       <c r="C72" s="66">
-        <v>77.29</v>
+        <v>97.00</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">Chapel Haven Schleifer Center, Inc.</t>
+          <t xml:space="preserve">Center for Community Change Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C73" s="66">
-        <v>81.41</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">Charities Aid Foundation America</t>
+          <t xml:space="preserve">Central Asia Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C74" s="66">
-        <v>0.01</v>
+        <v>77.29</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">ChildFund International, USA</t>
+          <t xml:space="preserve">CHADD, Inc. (Children &amp; Adults with Attention-Defi</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">6/30/2027</t>
         </is>
       </c>
       <c r="C75" s="66">
-        <v>75.00</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">Childhelp, Inc.</t>
+          <t xml:space="preserve">Chapel Haven Schleifer Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">6/30/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C76" s="66">
-        <v>70.00</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
+          <t xml:space="preserve">Charities Aid Foundation America</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C77" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="66">
+        <v>0.01</v>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">Children's Miracle Network</t>
+          <t xml:space="preserve">ChildFund International, USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C78" s="66">
-        <v>80.77</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
+          <t xml:space="preserve">Childhelp, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">6/30/2027</t>
         </is>
       </c>
       <c r="C79" s="66">
-        <v>89.98</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
+          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">12/18/2026</t>
         </is>
       </c>
       <c r="C80" s="65">
@@ -1403,42 +1403,42 @@
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
+          <t xml:space="preserve">Children's Miracle Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">9/10/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C81" s="66">
-        <v>96.00</v>
+        <v>80.77</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Christian Relief Services, Inc.</t>
+          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C82" s="66">
-        <v>90.70</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
+          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C83" s="65">
@@ -1448,177 +1448,177 @@
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Christian Union, Inc.</t>
+          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C84" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/10/2027</t>
+        </is>
+      </c>
+      <c r="C84" s="66">
+        <v>96.00</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Church World Service, Inc.</t>
+          <t xml:space="preserve">Christian Relief Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">8/25/2027</t>
+          <t xml:space="preserve">2/10/2027</t>
         </is>
       </c>
       <c r="C85" s="66">
-        <v>84.00</v>
+        <v>90.70</v>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">City Rescue Mission, Inc.</t>
+          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
-        </is>
-      </c>
-      <c r="C86" s="66">
-        <v>85.32</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C86" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">City Year, Inc.</t>
+          <t xml:space="preserve">Christian Union, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C87" s="66">
-        <v>82.62</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Civil Rights Corps</t>
+          <t xml:space="preserve">Church World Service, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/25/2027</t>
         </is>
       </c>
       <c r="C88" s="66">
-        <v>82.10</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
+          <t xml:space="preserve">City Rescue Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">11/20/2026</t>
-        </is>
-      </c>
-      <c r="C89" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C89" s="66">
+        <v>85.32</v>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
+          <t xml:space="preserve">City Year, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C90" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C90" s="66">
+        <v>82.62</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
+          <t xml:space="preserve">Civil Rights Corps</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C91" s="66">
-        <v>65.99</v>
+        <v>82.10</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">Compassion and Choices</t>
+          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
-        </is>
-      </c>
-      <c r="C92" s="66">
-        <v>84.00</v>
+          <t xml:space="preserve">11/20/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">Compassion and Choices Action Network</t>
+          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
-        </is>
-      </c>
-      <c r="C93" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C93" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Concerns of Police Survivors</t>
+          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C94" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/9/2027</t>
+        </is>
+      </c>
+      <c r="C94" s="66">
+        <v>65.99</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Consumer Reports, Inc.</t>
+          <t xml:space="preserve">Compassion and Choices</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C95" s="66">
@@ -1628,901 +1628,901 @@
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Cooperative for Assistance and Relief Everywhere</t>
+          <t xml:space="preserve">Compassion and Choices Action Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
-        </is>
-      </c>
-      <c r="C96" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C96" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
+          <t xml:space="preserve">Concerns of Police Survivors</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">6/25/2027</t>
-        </is>
-      </c>
-      <c r="C97" s="66">
-        <v>73.00</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
+          <t xml:space="preserve">Consumer Reports, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C98" s="66">
-        <v>74.25</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">Covenant House</t>
+          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C99" s="66">
-        <v>80.00</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
+          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C100" s="66">
-        <v>84.38</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
+          <t xml:space="preserve">Covenant House</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C101" s="66">
-        <v>85.18</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
+          <t xml:space="preserve">Covenant House New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">7/28/2028</t>
         </is>
       </c>
       <c r="C102" s="66">
-        <v>64.30</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">D.A.R.E. America</t>
+          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">12/4/2026</t>
         </is>
       </c>
       <c r="C103" s="66">
-        <v>44.00</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
+          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C104" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/30/2027</t>
+        </is>
+      </c>
+      <c r="C104" s="66">
+        <v>85.18</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Deep South Today</t>
+          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C105" s="66">
-        <v>74.56</v>
+        <v>64.30</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
+          <t xml:space="preserve">D.A.R.E. America</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">6/6/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C106" s="66">
-        <v>68.82</v>
+        <v>44.00</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
+          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
-        </is>
-      </c>
-      <c r="C107" s="66">
-        <v>49.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C107" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">DTCare</t>
+          <t xml:space="preserve">Deep South Today</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C108" s="66">
-        <v>55.44</v>
+        <v>74.56</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">East Carolina University Foundation, Inc.</t>
+          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
+          <t xml:space="preserve">6/6/2027</t>
         </is>
       </c>
       <c r="C109" s="66">
-        <v>55.44</v>
+        <v>68.82</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
+          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C110" s="66">
-        <v>61.48</v>
+        <v>49.00</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">Easter Seals, Inc.</t>
+          <t xml:space="preserve">DTCare</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C111" s="66">
-        <v>68.00</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">EB Research Partnership, Inc.</t>
+          <t xml:space="preserve">East Carolina University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C112" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/10/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="66">
+        <v>55.44</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">ELT Ventures</t>
+          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C113" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/14/2027</t>
+        </is>
+      </c>
+      <c r="C113" s="66">
+        <v>61.48</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Empire State University Foundation</t>
+          <t xml:space="preserve">Easter Seals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C114" s="66">
-        <v>82.78</v>
+        <v>68.00</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
+          <t xml:space="preserve">EB Research Partnership, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C115" s="66">
-        <v>48.32</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C115" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
+          <t xml:space="preserve">ELT Ventures</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">3/6/2027</t>
-        </is>
-      </c>
-      <c r="C116" s="66">
-        <v>87.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C116" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Fairplay, Inc.</t>
+          <t xml:space="preserve">Empire State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">6/25/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C117" s="66">
-        <v>83.42</v>
+        <v>82.78</v>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">Faith and Freedom Coalition, Inc.</t>
+          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C118" s="66">
-        <v>72.00</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">Family Policy Alliance</t>
+          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">3/6/2027</t>
         </is>
       </c>
       <c r="C119" s="66">
-        <v>80.48</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
+          <t xml:space="preserve">Fairplay, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C120" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/25/2027</t>
+        </is>
+      </c>
+      <c r="C120" s="66">
+        <v>83.42</v>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">Feed The Children, Inc.</t>
+          <t xml:space="preserve">Faith and Freedom Coalition, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C121" s="66">
-        <v>91.00</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">Feeding America</t>
+          <t xml:space="preserve">Family Policy Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C122" s="66">
-        <v>98.40</v>
+        <v>80.48</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">Feeding Pets of the Homeless</t>
+          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
-        </is>
-      </c>
-      <c r="C123" s="66">
-        <v>75.17</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
+          <t xml:space="preserve">Feed The Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">5/19/2027</t>
         </is>
       </c>
       <c r="C124" s="66">
-        <v>82.48</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">FINCA International, Inc.</t>
+          <t xml:space="preserve">Feeding America</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">5/7/2027</t>
+          <t xml:space="preserve">10/6/2026</t>
         </is>
       </c>
       <c r="C125" s="66">
-        <v>81.47</v>
+        <v>98.40</v>
       </c>
     </row>
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">Find The Children</t>
+          <t xml:space="preserve">Feeding Pets of the Homeless</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C126" s="66">
-        <v>50.00</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">Food Bank of Northeast Louisiana, Inc.</t>
+          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">4/9/2027</t>
         </is>
       </c>
       <c r="C127" s="66">
-        <v>99.00</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
+          <t xml:space="preserve">FINCA International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">5/7/2027</t>
         </is>
       </c>
       <c r="C128" s="66">
-        <v>89.30</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">Food for the Hungry, Inc.</t>
+          <t xml:space="preserve">Find The Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C129" s="66">
-        <v>75.00</v>
+        <v>50.00</v>
       </c>
     </row>
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">For Others Collective, Inc.</t>
+          <t xml:space="preserve">Food Bank of Northeast Louisiana, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C130" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C130" s="66">
+        <v>99.00</v>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
+          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C131" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/9/2027</t>
+        </is>
+      </c>
+      <c r="C131" s="66">
+        <v>89.30</v>
       </c>
     </row>
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">Fractracker Alliance</t>
+          <t xml:space="preserve">For Others Collective, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C132" s="66">
-        <v>77.78</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C132" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
+          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
-        </is>
-      </c>
-      <c r="C133" s="66">
-        <v>68.41</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C133" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
+          <t xml:space="preserve">Fractracker Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C134" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C134" s="66">
+        <v>77.78</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">Friends of KEXP</t>
+          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">7/1/2027</t>
         </is>
       </c>
       <c r="C135" s="66">
-        <v>65.74</v>
+        <v>68.41</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">Friends of the Neuberger Museum of Art, Inc.</t>
+          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C136" s="66">
-        <v>66.80</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C136" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
+          <t xml:space="preserve">Friends of KEXP</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C137" s="66">
-        <v>75.34</v>
+        <v>65.74</v>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">Futures Without Violence</t>
+          <t xml:space="preserve">Friends of the Neuberger Museum of Art, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C138" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C138" s="66">
+        <v>66.80</v>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">Girls Who Code, Inc.</t>
+          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">7/24/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C139" s="66">
-        <v>73.24</v>
+        <v>75.34</v>
       </c>
     </row>
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">Givinga Foundation</t>
+          <t xml:space="preserve">Futures Without Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">10/30/2026</t>
-        </is>
-      </c>
-      <c r="C140" s="66">
-        <v>94.03</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C140" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
+          <t xml:space="preserve">Girls Who Code, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">3/11/2027</t>
+          <t xml:space="preserve">7/24/2027</t>
         </is>
       </c>
       <c r="C141" s="66">
-        <v>49.91</v>
+        <v>73.24</v>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">Go Campaign</t>
+          <t xml:space="preserve">Givinga Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">10/30/2026</t>
         </is>
       </c>
       <c r="C142" s="66">
-        <v>77.86</v>
+        <v>94.03</v>
       </c>
     </row>
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">Goodwill Industries International, Inc</t>
+          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">3/11/2027</t>
         </is>
       </c>
       <c r="C143" s="66">
-        <v>87.00</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">Green America</t>
+          <t xml:space="preserve">Go Campaign</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C144" s="66">
-        <v>87.47</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
+          <t xml:space="preserve">Goodwill Industries International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C145" s="66">
-        <v>76.85</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">Greenpeace, Inc.</t>
+          <t xml:space="preserve">Green America</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C146" s="66">
-        <v>62.56</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">Gustavus Adolphus College</t>
+          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">2/24/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C147" s="66">
-        <v>93.00</v>
+        <v>76.85</v>
       </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">Habitat for Horses, Inc.</t>
+          <t xml:space="preserve">Greenpeace, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C148" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="66">
+        <v>62.56</v>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
+          <t xml:space="preserve">Gustavus Adolphus College</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C149" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/24/2027</t>
+        </is>
+      </c>
+      <c r="C149" s="66">
+        <v>93.00</v>
       </c>
     </row>
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">Healing Justice Project</t>
+          <t xml:space="preserve">Habitat for Horses, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
-        </is>
-      </c>
-      <c r="C150" s="66">
-        <v>82.48</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Healing Protectors</t>
+          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
-        </is>
-      </c>
-      <c r="C151" s="66">
-        <v>47.19</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">Heifer Project International</t>
+          <t xml:space="preserve">Healing Justice Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">3/19/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C152" s="66">
-        <v>72.90</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">Help Me See, Inc.</t>
+          <t xml:space="preserve">Healing Protectors</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="C153" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/2/2027</t>
+        </is>
+      </c>
+      <c r="C153" s="66">
+        <v>47.19</v>
       </c>
     </row>
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
+          <t xml:space="preserve">Heifer Project International</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C154" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/19/2027</t>
+        </is>
+      </c>
+      <c r="C154" s="66">
+        <v>72.90</v>
       </c>
     </row>
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">Heroes on the Water</t>
+          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
-        </is>
-      </c>
-      <c r="C155" s="66">
-        <v>75.00</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -3113,282 +3113,282 @@
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">Madison House</t>
+          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C195" s="66">
-        <v>77.79</v>
+        <v>62.00</v>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">MAP International, Inc.</t>
+          <t xml:space="preserve">Madison House</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C196" s="66">
-        <v>99.00</v>
+        <v>77.79</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">March of Dimes</t>
+          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">12/30/2026</t>
+          <t xml:space="preserve">8/6/2027</t>
         </is>
       </c>
       <c r="C197" s="66">
-        <v>74.00</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">Marist University</t>
+          <t xml:space="preserve">MAP International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C198" s="66">
-        <v>91.00</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
+          <t xml:space="preserve">March of Dimes</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">12/30/2026</t>
         </is>
       </c>
       <c r="C199" s="66">
-        <v>91.74</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">Meals on Wheels America</t>
+          <t xml:space="preserve">Marist University</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">5/27/2027</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C200" s="66">
-        <v>59.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
+          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">6/9/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C201" s="66">
-        <v>80.94</v>
+        <v>91.74</v>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
+          <t xml:space="preserve">Meals on Wheels America</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">12/8/2026</t>
-        </is>
-      </c>
-      <c r="C202" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/27/2027</t>
+        </is>
+      </c>
+      <c r="C202" s="66">
+        <v>59.00</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
+          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">6/9/2027</t>
         </is>
       </c>
       <c r="C203" s="66">
-        <v>91.00</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">Mercatus Center, Inc.</t>
+          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
-        </is>
-      </c>
-      <c r="C204" s="66">
-        <v>90.25</v>
+          <t xml:space="preserve">12/8/2026</t>
+        </is>
+      </c>
+      <c r="C204" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">Mercy for Animals, Inc.</t>
+          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C205" s="66">
-        <v>75.82</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">Mercy Ships</t>
+          <t xml:space="preserve">Mercatus Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">8/26/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C206" s="66">
-        <v>78.18</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
+          <t xml:space="preserve">Mercy for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C207" s="66">
-        <v>88.00</v>
+        <v>75.82</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">Minutes Matter-MCADD</t>
+          <t xml:space="preserve">Mercy Ships</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">7/19/2027</t>
-        </is>
-      </c>
-      <c r="C208" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/26/2027</t>
+        </is>
+      </c>
+      <c r="C208" s="66">
+        <v>78.18</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">Miracle Flights</t>
+          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C209" s="66">
-        <v>52.00</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
+          <t xml:space="preserve">Minutes Matter-MCADD</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C210" s="66">
-        <v>94.50</v>
+          <t xml:space="preserve">7/19/2027</t>
+        </is>
+      </c>
+      <c r="C210" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">Mount Saint Marys University</t>
+          <t xml:space="preserve">Miracle Flights</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C211" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C211" s="66">
+        <v>52.00</v>
       </c>
     </row>
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">Mountain States Legal Foundation</t>
+          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C212" s="66">
-        <v>69.99</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">MrCharity, Inc.</t>
+          <t xml:space="preserve">Mount Saint Marys University</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C213" s="65">
@@ -3398,162 +3398,162 @@
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
+          <t xml:space="preserve">Mountain States Legal Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C214" s="66">
-        <v>54.00</v>
+        <v>69.99</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
+          <t xml:space="preserve">MrCharity, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
-        </is>
-      </c>
-      <c r="C215" s="66">
-        <v>77.80</v>
+          <t xml:space="preserve">2/23/2027</t>
+        </is>
+      </c>
+      <c r="C215" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
+          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">12/19/2026</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C216" s="66">
-        <v>66.90</v>
+        <v>54.00</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">Naropa University</t>
+          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">6/24/2027</t>
         </is>
       </c>
       <c r="C217" s="66">
-        <v>76.21</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
+          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">12/19/2026</t>
         </is>
       </c>
       <c r="C218" s="66">
-        <v>65.00</v>
+        <v>66.90</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">National Audubon Society, Inc.</t>
+          <t xml:space="preserve">Naropa University</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C219" s="66">
-        <v>80.00</v>
+        <v>76.21</v>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
+          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C220" s="66">
-        <v>81.00</v>
+        <v>65.00</v>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
+          <t xml:space="preserve">National Audubon Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C221" s="66">
-        <v>92.28</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">National Council of Nonprofits</t>
+          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C222" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C222" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
+          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/7/2027</t>
         </is>
       </c>
       <c r="C223" s="66">
-        <v>49.00</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">National Foundation for Cancer Research</t>
+          <t xml:space="preserve">National Council of Nonprofits</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C224" s="65">
@@ -3563,87 +3563,87 @@
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">National Geographic Society</t>
+          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">3/18/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C225" s="66">
-        <v>77.00</v>
+        <v>49.00</v>
       </c>
     </row>
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">National Museum of Women in the Arts, Inc.</t>
+          <t xml:space="preserve">National Foundation for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="C226" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C226" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">National Network of Abortion Funds</t>
+          <t xml:space="preserve">National Geographic Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
-        </is>
-      </c>
-      <c r="C227" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/18/2027</t>
+        </is>
+      </c>
+      <c r="C227" s="66">
+        <v>77.00</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">National Park Foundation</t>
+          <t xml:space="preserve">National Network of Abortion Funds</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C228" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">9/11/2027</t>
+        </is>
+      </c>
+      <c r="C228" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">National PKU Alliance, Inc.</t>
+          <t xml:space="preserve">National Park Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C229" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/20/2026</t>
+        </is>
+      </c>
+      <c r="C229" s="66">
+        <v>72.00</v>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
+          <t xml:space="preserve">National PKU Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C230" s="65">
@@ -3653,7 +3653,7 @@
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
+          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
@@ -3668,12 +3668,12 @@
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">National Space Society</t>
+          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">1/9/2027</t>
         </is>
       </c>
       <c r="C232" s="65">
@@ -3683,117 +3683,117 @@
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">National University</t>
+          <t xml:space="preserve">National Space Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C233" s="66">
-        <v>42.69</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C233" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">National Veterans Memorial and Museum</t>
+          <t xml:space="preserve">National University</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C234" s="66">
-        <v>72.63</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">National Wheelchair Basketball Association</t>
+          <t xml:space="preserve">National Veterans Memorial and Museum</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C235" s="66">
-        <v>77.80</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">National Wildlife Federation</t>
+          <t xml:space="preserve">National Wheelchair Basketball Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C236" s="66">
-        <v>86.00</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">Network for Good, Inc</t>
+          <t xml:space="preserve">National Wildlife Federation</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C237" s="66">
-        <v>97.80</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">New Harvest, Inc.</t>
+          <t xml:space="preserve">Network for Good, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C238" s="66">
-        <v>88.49</v>
+        <v>97.80</v>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
+          <t xml:space="preserve">New Harvest, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C239" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C239" s="66">
+        <v>88.49</v>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">Nurse-Family Partnership</t>
+          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C240" s="65">
@@ -3803,46 +3803,46 @@
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">Ocean Conservancy</t>
+          <t xml:space="preserve">Nurse-Family Partnership</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C241" s="66">
-        <v>74.06</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C241" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
+          <t xml:space="preserve">Ocean Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C242" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C242" s="66">
+        <v>74.06</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">OneHope, Inc.</t>
+          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">10/1/2026</t>
-        </is>
-      </c>
-      <c r="C243" s="66">
-        <v>82.72</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C243" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -4223,147 +4223,147 @@
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">Project Cure, Inc.</t>
+          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
-        </is>
-      </c>
-      <c r="C269" s="66">
-        <v>27.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C269" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
+          <t xml:space="preserve">Project Cure, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C270" s="66">
-        <v>88.71</v>
+        <v>27.00</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">Project Orbis International, Inc.</t>
+          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
-        </is>
-      </c>
-      <c r="C271" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C271" s="66">
+        <v>88.71</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">Proteus Fund, Inc.</t>
+          <t xml:space="preserve">Project Orbis International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
-        </is>
-      </c>
-      <c r="C272" s="66">
-        <v>81.25</v>
+          <t xml:space="preserve">10/7/2026</t>
+        </is>
+      </c>
+      <c r="C272" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">Providence House</t>
+          <t xml:space="preserve">Proteus Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">3/2/2027</t>
         </is>
       </c>
       <c r="C273" s="66">
-        <v>92.06</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
+          <t xml:space="preserve">Providence House</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C274" s="66">
-        <v>84.22</v>
+        <v>92.06</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">Re:Power</t>
+          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C275" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C275" s="66">
+        <v>84.22</v>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">Reproductive Freedom for All</t>
+          <t xml:space="preserve">Re:Power</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
-        </is>
-      </c>
-      <c r="C276" s="66">
-        <v>70.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C276" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">Rodale Institute</t>
+          <t xml:space="preserve">Reproductive Freedom for All</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C277" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C277" s="66">
+        <v>70.00</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
+          <t xml:space="preserve">Rodale Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">12/12/2026</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C278" s="65">
@@ -4373,282 +4373,282 @@
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
+          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
-        </is>
-      </c>
-      <c r="C279" s="66">
-        <v>45.00</v>
+          <t xml:space="preserve">12/12/2026</t>
+        </is>
+      </c>
+      <c r="C279" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C280" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/7/2026</t>
+        </is>
+      </c>
+      <c r="C280" s="66">
+        <v>45.00</v>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">Rush University Medical Center</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
-        </is>
-      </c>
-      <c r="C281" s="66">
-        <v>91.41</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C281" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">Rutgers University Foundation</t>
+          <t xml:space="preserve">Rush University Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C282" s="66">
-        <v>87.46</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">Sagamore Institute, Inc.</t>
+          <t xml:space="preserve">Rutgers University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C283" s="66">
-        <v>91.61</v>
+        <v>87.46</v>
       </c>
     </row>
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">Saint John's University</t>
+          <t xml:space="preserve">Sagamore Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C284" s="66">
-        <v>88.76</v>
+        <v>91.61</v>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">Save the Chimps, Inc.</t>
+          <t xml:space="preserve">Saint John's University</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C285" s="66">
-        <v>79.70</v>
+        <v>88.76</v>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">Seattle Pacific University</t>
+          <t xml:space="preserve">Save the Chimps, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C286" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/27/2027</t>
+        </is>
+      </c>
+      <c r="C286" s="66">
+        <v>79.70</v>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
+          <t xml:space="preserve">Seattle Pacific University</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
-        </is>
-      </c>
-      <c r="C287" s="66">
-        <v>94.00</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C287" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">Share Our Strength</t>
+          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C288" s="66">
-        <v>58.73</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
+          <t xml:space="preserve">Share Our Strength</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C289" s="66">
-        <v>97.29</v>
+        <v>58.73</v>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">Sierra  Club</t>
+          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">12/22/2026</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C290" s="66">
-        <v>82.00</v>
+        <v>97.29</v>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">Sister Rising Worldwide</t>
+          <t xml:space="preserve">Sierra  Club</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">1/28/2027</t>
-        </is>
-      </c>
-      <c r="C291" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/22/2026</t>
+        </is>
+      </c>
+      <c r="C291" s="66">
+        <v>82.00</v>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">Sixpoint, Inc.</t>
+          <t xml:space="preserve">Sister Rising Worldwide</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
-        </is>
-      </c>
-      <c r="C292" s="66">
-        <v>77.16</v>
+          <t xml:space="preserve">1/28/2027</t>
+        </is>
+      </c>
+      <c r="C292" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="293">
       <c t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
+          <t xml:space="preserve">Sixpoint, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">4/22/2027</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C293" s="66">
-        <v>90.00</v>
+        <v>77.16</v>
       </c>
     </row>
     <row r="294">
       <c t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">Social Purpose Corrections</t>
+          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">4/22/2027</t>
         </is>
       </c>
       <c r="C294" s="66">
-        <v>12.95</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="295">
       <c t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
+          <t xml:space="preserve">Social Purpose Corrections</t>
         </is>
       </c>
       <c t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
-        </is>
-      </c>
-      <c r="C295" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C295" s="66">
+        <v>12.95</v>
       </c>
     </row>
     <row r="296">
       <c t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
+          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">7/29/2027</t>
+          <t xml:space="preserve">9/2/2027</t>
         </is>
       </c>
       <c r="C296" s="66">
-        <v>86.00</v>
+        <v>72.80</v>
       </c>
     </row>
     <row r="297">
       <c t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">South Dakota State University Foundation</t>
+          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
         </is>
       </c>
       <c t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C297" s="65">
@@ -4658,27 +4658,27 @@
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
+          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C298" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/29/2027</t>
+        </is>
+      </c>
+      <c r="C298" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">Special Olympics, Inc.</t>
+          <t xml:space="preserve">South Dakota State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C299" s="65">
@@ -4688,162 +4688,162 @@
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
+          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
-        </is>
-      </c>
-      <c r="C300" s="66">
-        <v>85.31</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C300" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">State University of Iowa Foundation</t>
+          <t xml:space="preserve">Special Olympics, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">9/4/2027</t>
-        </is>
-      </c>
-      <c r="C301" s="66">
-        <v>79.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C301" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
+          <t xml:space="preserve">SPLC Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C302" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/17/2027</t>
+        </is>
+      </c>
+      <c r="C302" s="66">
+        <v>72.81</v>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">Students for Life Action, Inc.</t>
+          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">11/7/2026</t>
-        </is>
-      </c>
-      <c r="C303" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/31/2027</t>
+        </is>
+      </c>
+      <c r="C303" s="66">
+        <v>85.31</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">Students for Life of America</t>
+          <t xml:space="preserve">State University of Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
+          <t xml:space="preserve">9/4/2027</t>
         </is>
       </c>
       <c r="C304" s="66">
-        <v>82.00</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
+          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">8/12/2027</t>
-        </is>
-      </c>
-      <c r="C305" s="66">
-        <v>89.29</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C305" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">Teacher Freedom Alliance</t>
+          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
-        </is>
-      </c>
-      <c r="C306" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/24/2027</t>
+        </is>
+      </c>
+      <c r="C306" s="66">
+        <v>92.00</v>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">The Actors' Fund of America</t>
+          <t xml:space="preserve">Students for Life Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
-        </is>
-      </c>
-      <c r="C307" s="66">
-        <v>86.73</v>
+          <t xml:space="preserve">11/7/2026</t>
+        </is>
+      </c>
+      <c r="C307" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Students for Life of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">10/10/2026</t>
         </is>
       </c>
       <c r="C308" s="66">
-        <v>39.00</v>
+        <v>82.00</v>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">The American University</t>
+          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">8/12/2027</t>
         </is>
       </c>
       <c r="C309" s="66">
-        <v>90.23</v>
+        <v>89.29</v>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+          <t xml:space="preserve">Teacher Freedom Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">6/24/2027</t>
         </is>
       </c>
       <c r="C310" s="65">
@@ -4853,717 +4853,717 @@
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">The Anthony Davis Foundation</t>
+          <t xml:space="preserve">The Actors' Fund of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">11/24/2026</t>
-        </is>
-      </c>
-      <c r="C311" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/10/2026</t>
+        </is>
+      </c>
+      <c r="C311" s="66">
+        <v>86.73</v>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
+          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">10/24/2026</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C312" s="66">
-        <v>90.00</v>
+        <v>39.00</v>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">The Barack Obama Foundation</t>
+          <t xml:space="preserve">The American University</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C313" s="66">
-        <v>55.90</v>
+        <v>90.23</v>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">The Baruch College Fund</t>
+          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
-        </is>
-      </c>
-      <c r="C314" s="66">
-        <v>84.00</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C314" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">The Call of Duty Endowment</t>
+          <t xml:space="preserve">The Anthony Davis Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
-        </is>
-      </c>
-      <c r="C315" s="66">
-        <v>73.00</v>
+          <t xml:space="preserve">11/24/2026</t>
+        </is>
+      </c>
+      <c r="C315" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">The Center for Alcohol Policy</t>
+          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">10/24/2026</t>
         </is>
       </c>
       <c r="C316" s="66">
-        <v>73.40</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">The Center for Investigative Reporting</t>
+          <t xml:space="preserve">The Barack Obama Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C317" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C317" s="66">
+        <v>55.90</v>
       </c>
     </row>
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
+          <t xml:space="preserve">The Baruch College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C318" s="66">
-        <v>71.00</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">The Center for Victims of Torture</t>
+          <t xml:space="preserve">The Call of Duty Endowment</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C319" s="66">
-        <v>74.00</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
+          <t xml:space="preserve">The Center for Alcohol Policy</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">7/6/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C320" s="66">
-        <v>71.00</v>
+        <v>73.40</v>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">The Colorado College</t>
+          <t xml:space="preserve">The Center for Investigative Reporting</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">10/29/2027</t>
-        </is>
-      </c>
-      <c r="C321" s="66">
-        <v>90.00</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C321" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">The Denver Rescue Mission</t>
+          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C322" s="66">
-        <v>82.96</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">The Edison Institute</t>
+          <t xml:space="preserve">The Center for Victims of Torture</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C323" s="66">
-        <v>78.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C324" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/6/2027</t>
+        </is>
+      </c>
+      <c r="C324" s="66">
+        <v>71.00</v>
       </c>
     </row>
     <row r="325">
       <c t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+          <t xml:space="preserve">The Colorado College</t>
         </is>
       </c>
       <c t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C325" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/29/2027</t>
+        </is>
+      </c>
+      <c r="C325" s="66">
+        <v>90.00</v>
       </c>
     </row>
     <row r="326">
       <c t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
+          <t xml:space="preserve">The Denver Rescue Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">7/20/2027</t>
         </is>
       </c>
       <c r="C326" s="66">
-        <v>76.48</v>
+        <v>82.96</v>
       </c>
     </row>
     <row r="327">
       <c t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
+          <t xml:space="preserve">The Edison Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">5/15/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C327" s="66">
-        <v>85.00</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="328">
       <c t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">The Heritage Foundation</t>
+          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C328" s="66">
-        <v>83.00</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C328" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
+          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
         </is>
       </c>
       <c t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
-        </is>
-      </c>
-      <c r="C329" s="66">
-        <v>89.00</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C329" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">The Independent Institute</t>
+          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
         </is>
       </c>
       <c t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C330" s="66">
-        <v>77.51</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="331">
       <c t="inlineStr" r="A331">
         <is>
-          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
+          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B331">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">5/15/2027</t>
         </is>
       </c>
       <c r="C331" s="66">
-        <v>84.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="332">
       <c t="inlineStr" r="A332">
         <is>
-          <t xml:space="preserve">The Just Trust for Education</t>
+          <t xml:space="preserve">The Heritage Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B332">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C332" s="66">
-        <v>85.13</v>
+        <v>83.00</v>
       </c>
     </row>
     <row r="333">
       <c t="inlineStr" r="A333">
         <is>
-          <t xml:space="preserve">The Kansas University Endowment Association</t>
+          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B333">
         <is>
-          <t xml:space="preserve">7/21/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C333" s="66">
-        <v>91.34</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="334">
       <c t="inlineStr" r="A334">
         <is>
-          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+          <t xml:space="preserve">The Independent Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B334">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C334" s="66">
-        <v>83.06</v>
+        <v>77.51</v>
       </c>
     </row>
     <row r="335">
       <c t="inlineStr" r="A335">
         <is>
-          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
+          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B335">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C335" s="66">
-        <v>91.99</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="336">
       <c t="inlineStr" r="A336">
         <is>
-          <t xml:space="preserve">The Memorial Foundation</t>
+          <t xml:space="preserve">The Just Trust for Education</t>
         </is>
       </c>
       <c t="inlineStr" r="B336">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C336" s="66">
-        <v>72.00</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="337">
       <c t="inlineStr" r="A337">
         <is>
-          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+          <t xml:space="preserve">The Kansas University Endowment Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B337">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">7/21/2027</t>
         </is>
       </c>
       <c r="C337" s="66">
-        <v>74.58</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="338">
       <c t="inlineStr" r="A338">
         <is>
-          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
+          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B338">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C338" s="66">
-        <v>60.00</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="339">
       <c t="inlineStr" r="A339">
         <is>
-          <t xml:space="preserve">The National World War II Museum, Inc.</t>
+          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B339">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C339" s="66">
-        <v>80.00</v>
+        <v>91.99</v>
       </c>
     </row>
     <row r="340">
       <c t="inlineStr" r="A340">
         <is>
-          <t xml:space="preserve">The Nature Conservancy</t>
+          <t xml:space="preserve">The Memorial Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B340">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C340" s="66">
-        <v>70.00</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="341">
       <c t="inlineStr" r="A341">
         <is>
-          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B341">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C341" s="66">
-        <v>80.64</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="342">
       <c t="inlineStr" r="A342">
         <is>
-          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
+          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B342">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C342" s="66">
-        <v>87.40</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="343">
       <c t="inlineStr" r="A343">
         <is>
-          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
+          <t xml:space="preserve">The National World War II Museum, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B343">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C343" s="66">
-        <v>60.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="344">
       <c t="inlineStr" r="A344">
         <is>
-          <t xml:space="preserve">The Ohio University Foundation</t>
+          <t xml:space="preserve">The Nature Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B344">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">10/9/2026</t>
         </is>
       </c>
       <c r="C344" s="66">
-        <v>74.14</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="345">
       <c t="inlineStr" r="A345">
         <is>
-          <t xml:space="preserve">The OneStar Foundation</t>
+          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
         </is>
       </c>
       <c t="inlineStr" r="B345">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C345" s="66">
-        <v>62.50</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="346">
       <c t="inlineStr" r="A346">
         <is>
-          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
         </is>
       </c>
       <c t="inlineStr" r="B346">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C346" s="66">
-        <v>88.30</v>
+        <v>87.40</v>
       </c>
     </row>
     <row r="347">
       <c t="inlineStr" r="A347">
         <is>
-          <t xml:space="preserve">The Planetary Society</t>
+          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B347">
         <is>
-          <t xml:space="preserve">7/14/2027</t>
+          <t xml:space="preserve">8/24/2027</t>
         </is>
       </c>
       <c r="C347" s="66">
-        <v>66.00</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="348">
       <c t="inlineStr" r="A348">
         <is>
-          <t xml:space="preserve">The Purchase College Foundation</t>
+          <t xml:space="preserve">The Ohio University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B348">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C348" s="66">
-        <v>78.12</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="349">
       <c t="inlineStr" r="A349">
         <is>
-          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
+          <t xml:space="preserve">The OneStar Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B349">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">1/14/2027</t>
         </is>
       </c>
       <c r="C349" s="66">
-        <v>81.26</v>
+        <v>62.50</v>
       </c>
     </row>
     <row r="350">
       <c t="inlineStr" r="A350">
         <is>
-          <t xml:space="preserve">The Ruth Collective</t>
+          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B350">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C350" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C350" s="66">
+        <v>88.30</v>
       </c>
     </row>
     <row r="351">
       <c t="inlineStr" r="A351">
         <is>
-          <t xml:space="preserve">The Society of the Cincinnati</t>
+          <t xml:space="preserve">The Planetary Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B351">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">7/14/2027</t>
         </is>
       </c>
       <c r="C351" s="66">
-        <v>73.00</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="352">
       <c t="inlineStr" r="A352">
         <is>
-          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+          <t xml:space="preserve">The Purchase College Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B352">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C352" s="66">
-        <v>94.00</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="353">
       <c t="inlineStr" r="A353">
         <is>
-          <t xml:space="preserve">The University of Arizona Foundation</t>
+          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
         </is>
       </c>
       <c t="inlineStr" r="B353">
         <is>
-          <t xml:space="preserve">9/29/2026</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C353" s="66">
-        <v>76.49</v>
+        <v>81.26</v>
       </c>
     </row>
     <row r="354">
       <c t="inlineStr" r="A354">
         <is>
-          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+          <t xml:space="preserve">The Ruth Collective</t>
         </is>
       </c>
       <c t="inlineStr" r="B354">
         <is>
-          <t xml:space="preserve">4/13/2027</t>
-        </is>
-      </c>
-      <c r="C354" s="66">
-        <v>82.20</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C354" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="355">
       <c t="inlineStr" r="A355">
         <is>
-          <t xml:space="preserve">The University of Montana Foundation</t>
+          <t xml:space="preserve">The Society of the Cincinnati</t>
         </is>
       </c>
       <c t="inlineStr" r="B355">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C355" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C355" s="66">
+        <v>73.00</v>
       </c>
     </row>
     <row r="356">
       <c t="inlineStr" r="A356">
         <is>
-          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
+          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
         </is>
       </c>
       <c t="inlineStr" r="B356">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C356" s="66">
-        <v>76.00</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="357">
       <c t="inlineStr" r="A357">
         <is>
-          <t xml:space="preserve">The Visiting Angels Foundation</t>
+          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B357">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">4/13/2027</t>
         </is>
       </c>
       <c r="C357" s="66">
-        <v>94.00</v>
+        <v>82.20</v>
       </c>
     </row>
     <row r="358">
       <c t="inlineStr" r="A358">
         <is>
-          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
+          <t xml:space="preserve">The University of Montana Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B358">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C358" s="65">
@@ -5573,177 +5573,177 @@
     <row r="359">
       <c t="inlineStr" r="A359">
         <is>
-          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B359">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C359" s="66">
-        <v>79.51</v>
+        <v>76.00</v>
       </c>
     </row>
     <row r="360">
       <c t="inlineStr" r="A360">
         <is>
-          <t xml:space="preserve">The Wilderness Society</t>
+          <t xml:space="preserve">The Visiting Angels Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B360">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">7/20/2027</t>
         </is>
       </c>
       <c r="C360" s="66">
-        <v>73.00</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="361">
       <c t="inlineStr" r="A361">
         <is>
-          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
+          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B361">
         <is>
-          <t xml:space="preserve">4/21/2027</t>
-        </is>
-      </c>
-      <c r="C361" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">10/15/2026</t>
+        </is>
+      </c>
+      <c r="C361" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="362">
       <c t="inlineStr" r="A362">
         <is>
-          <t xml:space="preserve">Together Making Changes</t>
+          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B362">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C362" s="66">
-        <v>90.26</v>
+        <v>79.51</v>
       </c>
     </row>
     <row r="363">
       <c t="inlineStr" r="A363">
         <is>
-          <t xml:space="preserve">Trevecca Nazarene University</t>
+          <t xml:space="preserve">The Wilderness Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B363">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C363" s="66">
-        <v>87.82</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="364">
       <c t="inlineStr" r="A364">
         <is>
-          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
+          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B364">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">4/21/2027</t>
         </is>
       </c>
       <c r="C364" s="66">
-        <v>94.50</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="365">
       <c t="inlineStr" r="A365">
         <is>
-          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+          <t xml:space="preserve">Together Making Changes</t>
         </is>
       </c>
       <c t="inlineStr" r="B365">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C365" s="66">
-        <v>89.90</v>
+        <v>90.26</v>
       </c>
     </row>
     <row r="366">
       <c t="inlineStr" r="A366">
         <is>
-          <t xml:space="preserve">Trustees of Tufts College</t>
+          <t xml:space="preserve">Trevecca Nazarene University</t>
         </is>
       </c>
       <c t="inlineStr" r="B366">
         <is>
-          <t xml:space="preserve">7/2/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C366" s="66">
-        <v>85.00</v>
+        <v>87.82</v>
       </c>
     </row>
     <row r="367">
       <c t="inlineStr" r="A367">
         <is>
-          <t xml:space="preserve">Turning Point USA, Inc.</t>
+          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B367">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C367" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C367" s="66">
+        <v>94.50</v>
       </c>
     </row>
     <row r="368">
       <c t="inlineStr" r="A368">
         <is>
-          <t xml:space="preserve">Twelveacres, Incorporated</t>
+          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
         </is>
       </c>
       <c t="inlineStr" r="B368">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C368" s="66">
-        <v>79.93</v>
+        <v>89.90</v>
       </c>
     </row>
     <row r="369">
       <c t="inlineStr" r="A369">
         <is>
-          <t xml:space="preserve">UATX</t>
+          <t xml:space="preserve">Trustees of Tufts College</t>
         </is>
       </c>
       <c t="inlineStr" r="B369">
         <is>
-          <t xml:space="preserve">2/1/2027</t>
-        </is>
-      </c>
-      <c r="C369" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/2/2027</t>
+        </is>
+      </c>
+      <c r="C369" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="370">
       <c t="inlineStr" r="A370">
         <is>
-          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+          <t xml:space="preserve">Turning Point USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B370">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C370" s="65">
@@ -5753,27 +5753,27 @@
     <row r="371">
       <c t="inlineStr" r="A371">
         <is>
-          <t xml:space="preserve">UMKC Foundation</t>
+          <t xml:space="preserve">Twelveacres, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B371">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C371" s="66">
-        <v>95.00</v>
+        <v>79.93</v>
       </c>
     </row>
     <row r="372">
       <c t="inlineStr" r="A372">
         <is>
-          <t xml:space="preserve">Unified Youth</t>
+          <t xml:space="preserve">UATX</t>
         </is>
       </c>
       <c t="inlineStr" r="B372">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">2/1/2027</t>
         </is>
       </c>
       <c r="C372" s="65">
@@ -5783,37 +5783,37 @@
     <row r="373">
       <c t="inlineStr" r="A373">
         <is>
-          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B373">
         <is>
-          <t xml:space="preserve">8/1/2027</t>
-        </is>
-      </c>
-      <c r="C373" s="66">
-        <v>88.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C373" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="374">
       <c t="inlineStr" r="A374">
         <is>
-          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
+          <t xml:space="preserve">UMKC Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B374">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C374" s="66">
-        <v>84.01</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="375">
       <c t="inlineStr" r="A375">
         <is>
-          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Unified Youth</t>
         </is>
       </c>
       <c t="inlineStr" r="B375">
@@ -5821,442 +5821,487 @@
           <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
-      <c r="C375" s="66">
-        <v>85.00</v>
+      <c r="C375" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="376">
       <c t="inlineStr" r="A376">
         <is>
-          <t xml:space="preserve">united Service Organizations, Inc.</t>
+          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B376">
         <is>
-          <t xml:space="preserve">11/10/2026</t>
+          <t xml:space="preserve">8/1/2027</t>
         </is>
       </c>
       <c r="C376" s="66">
-        <v>67.94</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="377">
       <c t="inlineStr" r="A377">
         <is>
-          <t xml:space="preserve">United States Association for UNHCR</t>
+          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B377">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C377" s="66">
-        <v>61.00</v>
+        <v>84.01</v>
       </c>
     </row>
     <row r="378">
       <c t="inlineStr" r="A378">
         <is>
-          <t xml:space="preserve">United States Center for SafeSport</t>
+          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B378">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C378" s="66">
-        <v>72.74</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="379">
       <c t="inlineStr" r="A379">
         <is>
-          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
+          <t xml:space="preserve">united Service Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B379">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">11/10/2026</t>
         </is>
       </c>
       <c r="C379" s="66">
-        <v>38.00</v>
+        <v>67.94</v>
       </c>
     </row>
     <row r="380">
       <c t="inlineStr" r="A380">
         <is>
-          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
+          <t xml:space="preserve">United States Association for UNHCR</t>
         </is>
       </c>
       <c t="inlineStr" r="B380">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C380" s="66">
-        <v>99.30</v>
+        <v>61.00</v>
       </c>
     </row>
     <row r="381">
       <c t="inlineStr" r="A381">
         <is>
-          <t xml:space="preserve">University of Colorado</t>
+          <t xml:space="preserve">United States Center for SafeSport</t>
         </is>
       </c>
       <c t="inlineStr" r="B381">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
-        </is>
-      </c>
-      <c r="C381" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/27/2027</t>
+        </is>
+      </c>
+      <c r="C381" s="66">
+        <v>72.74</v>
       </c>
     </row>
     <row r="382">
       <c t="inlineStr" r="A382">
         <is>
-          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
+          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B382">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C382" s="66">
-        <v>93.00</v>
+        <v>38.00</v>
       </c>
     </row>
     <row r="383">
       <c t="inlineStr" r="A383">
         <is>
-          <t xml:space="preserve">University of Nebraska Foundation</t>
+          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B383">
         <is>
-          <t xml:space="preserve">7/15/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C383" s="66">
-        <v>81.10</v>
+        <v>99.30</v>
       </c>
     </row>
     <row r="384">
       <c t="inlineStr" r="A384">
         <is>
-          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
+          <t xml:space="preserve">University of Colorado</t>
         </is>
       </c>
       <c t="inlineStr" r="B384">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
-        </is>
-      </c>
-      <c r="C384" s="66">
-        <v>77.00</v>
+          <t xml:space="preserve">10/7/2026</t>
+        </is>
+      </c>
+      <c r="C384" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="385">
       <c t="inlineStr" r="A385">
         <is>
-          <t xml:space="preserve">University of Pacific</t>
+          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B385">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C385" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C385" s="66">
+        <v>93.00</v>
       </c>
     </row>
     <row r="386">
       <c t="inlineStr" r="A386">
         <is>
-          <t xml:space="preserve">University of Richmond</t>
+          <t xml:space="preserve">University of Nebraska Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B386">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">7/15/2027</t>
         </is>
       </c>
       <c r="C386" s="66">
-        <v>82.18</v>
+        <v>81.10</v>
       </c>
     </row>
     <row r="387">
       <c t="inlineStr" r="A387">
         <is>
-          <t xml:space="preserve">Veterans Community Project</t>
+          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B387">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C387" s="66">
-        <v>88.83</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="388">
       <c t="inlineStr" r="A388">
         <is>
-          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
+          <t xml:space="preserve">University of Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B388">
         <is>
-          <t xml:space="preserve">7/13/2027</t>
-        </is>
-      </c>
-      <c r="C388" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C388" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="389">
       <c t="inlineStr" r="A389">
         <is>
-          <t xml:space="preserve">Violet Research Institute, Inc.</t>
+          <t xml:space="preserve">University of Richmond</t>
         </is>
       </c>
       <c t="inlineStr" r="B389">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C389" s="66">
-        <v>80.00</v>
+        <v>82.18</v>
       </c>
     </row>
     <row r="390">
       <c t="inlineStr" r="A390">
         <is>
-          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+          <t xml:space="preserve">Veterans Community Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B390">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C390" s="66">
-        <v>28.00</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="391">
       <c t="inlineStr" r="A391">
         <is>
-          <t xml:space="preserve">VoteAmerica, Inc.</t>
+          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B391">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">7/13/2027</t>
         </is>
       </c>
       <c r="C391" s="66">
-        <v>93.37</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="392">
       <c t="inlineStr" r="A392">
         <is>
-          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+          <t xml:space="preserve">Violet Research Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B392">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C392" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/28/2027</t>
+        </is>
+      </c>
+      <c r="C392" s="66">
+        <v>80.00</v>
       </c>
     </row>
     <row r="393">
       <c t="inlineStr" r="A393">
         <is>
-          <t xml:space="preserve">Washington State University Foundation</t>
+          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B393">
         <is>
-          <t xml:space="preserve">7/8/2027</t>
+          <t xml:space="preserve">11/5/2026</t>
         </is>
       </c>
       <c r="C393" s="66">
-        <v>75.03</v>
+        <v>28.00</v>
       </c>
     </row>
     <row r="394">
       <c t="inlineStr" r="A394">
         <is>
-          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+          <t xml:space="preserve">VoteAmerica, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B394">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C394" s="66">
-        <v>82.68</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="395">
       <c t="inlineStr" r="A395">
         <is>
-          <t xml:space="preserve">Wildlife Conservation Network</t>
+          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B395">
         <is>
-          <t xml:space="preserve">8/13/2027</t>
-        </is>
-      </c>
-      <c r="C395" s="66">
-        <v>92.13</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C395" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="396">
       <c t="inlineStr" r="A396">
         <is>
-          <t xml:space="preserve">Winning for Women, Inc.</t>
+          <t xml:space="preserve">Washington State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B396">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">7/8/2027</t>
         </is>
       </c>
       <c r="C396" s="66">
-        <v>66.70</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="397">
       <c t="inlineStr" r="A397">
         <is>
-          <t xml:space="preserve">Women for Women International</t>
+          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B397">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">11/5/2026</t>
         </is>
       </c>
       <c r="C397" s="66">
-        <v>79.06</v>
+        <v>82.68</v>
       </c>
     </row>
     <row r="398">
       <c t="inlineStr" r="A398">
         <is>
-          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+          <t xml:space="preserve">Wildlife Conservation Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B398">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">8/13/2027</t>
         </is>
       </c>
       <c r="C398" s="66">
-        <v>71.40</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="399">
       <c t="inlineStr" r="A399">
         <is>
-          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+          <t xml:space="preserve">Winning for Women, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B399">
         <is>
-          <t xml:space="preserve">2/20/2027</t>
-        </is>
-      </c>
-      <c r="C399" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C399" s="66">
+        <v>66.70</v>
       </c>
     </row>
     <row r="400">
       <c t="inlineStr" r="A400">
         <is>
-          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+          <t xml:space="preserve">Women for Women International</t>
         </is>
       </c>
       <c t="inlineStr" r="B400">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C400" s="66">
-        <v>79.00</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="401">
       <c t="inlineStr" r="A401">
         <is>
-          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B401">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C401" s="66">
-        <v>70.36</v>
+        <v>71.40</v>
       </c>
     </row>
     <row r="402">
       <c t="inlineStr" r="A402">
         <is>
-          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
+          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B402">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
-        </is>
-      </c>
-      <c r="C402" s="66">
-        <v>39.45</v>
+          <t xml:space="preserve">2/20/2027</t>
+        </is>
+      </c>
+      <c r="C402" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="403">
       <c t="inlineStr" r="A403">
         <is>
-          <t xml:space="preserve">YMCA of the Rockies</t>
+          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B403">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">5/20/2027</t>
         </is>
       </c>
       <c r="C403" s="66">
-        <v>81.65</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="404">
       <c t="inlineStr" r="A404">
         <is>
+          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B404">
+        <is>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C404" s="66">
+        <v>70.36</v>
+      </c>
+    </row>
+    <row r="405">
+      <c t="inlineStr" r="A405">
+        <is>
+          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B405">
+        <is>
+          <t xml:space="preserve">8/24/2027</t>
+        </is>
+      </c>
+      <c r="C405" s="66">
+        <v>39.45</v>
+      </c>
+    </row>
+    <row r="406">
+      <c t="inlineStr" r="A406">
+        <is>
+          <t xml:space="preserve">YMCA of the Rockies</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B406">
+        <is>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C406" s="66">
+        <v>81.65</v>
+      </c>
+    </row>
+    <row r="407">
+      <c t="inlineStr" r="A407">
+        <is>
           <t xml:space="preserve">Young Judaea Global, Inc.</t>
         </is>
       </c>
-      <c t="inlineStr" r="B404">
+      <c t="inlineStr" r="B407">
         <is>
           <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
-      <c r="C404" s="66">
+      <c r="C407" s="66">
         <v>71.20</v>
       </c>
     </row>

--- a/downloadable-data/LA.xlsx
+++ b/downloadable-data/LA.xlsx
@@ -443,87 +443,87 @@
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">Al-Mawrid United States, Inc.</t>
+          <t xml:space="preserve">Alaska Conservation Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
-        </is>
-      </c>
-      <c r="C17" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/23/2027</t>
+        </is>
+      </c>
+      <c r="C17" s="66">
+        <v>79.96</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">Alaska Conservation Foundation</t>
+          <t xml:space="preserve">All God's Children International</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C18" s="66">
-        <v>79.96</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">All God's Children International</t>
+          <t xml:space="preserve">All Hands and Hearts Smart Response</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C19" s="66">
-        <v>87.31</v>
+        <v>93.41</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">All Hands and Hearts Smart Response</t>
+          <t xml:space="preserve">Alliance for Gun Responsibility</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C20" s="66">
-        <v>93.41</v>
+        <v>75.80</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">Alliance for Gun Responsibility</t>
+          <t xml:space="preserve">Alpha Gamma Delta Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
-        </is>
-      </c>
-      <c r="C21" s="66">
-        <v>75.80</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">Alpha Gamma Delta Foundation, Inc.</t>
+          <t xml:space="preserve">Alpha Kappa Psi Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
+          <t xml:space="preserve">1/8/2027</t>
         </is>
       </c>
       <c r="C22" s="65">
@@ -533,76 +533,76 @@
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">Alpha Kappa Psi Foundation</t>
+          <t xml:space="preserve">ALTA Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">1/8/2027</t>
-        </is>
-      </c>
-      <c r="C23" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C23" s="66">
+        <v>48.00</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">ALTA Charitable Foundation</t>
+          <t xml:space="preserve">Alternate ROOTS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C24" s="66">
-        <v>48.00</v>
+          <t xml:space="preserve">1/1/2027</t>
+        </is>
+      </c>
+      <c r="C24" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">Alternate ROOTS, Inc.</t>
+          <t xml:space="preserve">Amateur Athletic Union of the United States. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">1/1/2027</t>
-        </is>
-      </c>
-      <c r="C25" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/28/2027</t>
+        </is>
+      </c>
+      <c r="C25" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">Amateur Athletic Union of the United States. Inc.</t>
+          <t xml:space="preserve">America's Survival, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">9/28/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C26" s="66">
-        <v>75.00</v>
+        <v>90.07</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">America's Survival, Inc.</t>
+          <t xml:space="preserve">American Association for the Advancement of Scienc</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C27" s="66">
-        <v>90.07</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="28">
@@ -658,11 +658,11 @@
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C31" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C31" s="66">
+        <v>83.50</v>
       </c>
     </row>
     <row r="32">
@@ -878,82 +878,82 @@
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">American Roentgen Ray Society</t>
+          <t xml:space="preserve">Americans For Fair Treatment</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
-        </is>
-      </c>
-      <c r="C46" s="66">
-        <v>52.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">Americans For Fair Treatment</t>
+          <t xml:space="preserve">Americares Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C47" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/24/2027</t>
+        </is>
+      </c>
+      <c r="C47" s="66">
+        <v>98.06</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">Americares Foundation, Inc.</t>
+          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
+          <t xml:space="preserve">10/14/2026</t>
         </is>
       </c>
       <c r="C48" s="66">
-        <v>98.06</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
+          <t xml:space="preserve">Animals' Angels, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">9/12/2027</t>
         </is>
       </c>
       <c r="C49" s="66">
-        <v>71.00</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">Animals' Angels, Incorporated</t>
+          <t xml:space="preserve">Anti-Defamation League</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">9/12/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C50" s="66">
-        <v>77.41</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">Anti-Defamation League</t>
+          <t xml:space="preserve">Arkansas Tech University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
@@ -962,33 +962,33 @@
         </is>
       </c>
       <c r="C51" s="66">
-        <v>75.00</v>
+        <v>94.06</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">Arkansas Tech University Foundation</t>
+          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C52" s="66">
-        <v>94.06</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C52" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
+          <t xml:space="preserve">Association of American Education Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C53" s="65">
@@ -998,97 +998,97 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Association of American Education Foundation</t>
+          <t xml:space="preserve">Austin College</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C54" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C54" s="66">
+        <v>85.11</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">Austin College</t>
+          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">3/23/2027</t>
         </is>
       </c>
       <c r="C55" s="66">
-        <v>85.11</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
+          <t xml:space="preserve">Autism Speaks, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">3/23/2027</t>
-        </is>
-      </c>
-      <c r="C56" s="66">
-        <v>81.00</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C56" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">Autism Speaks, Inc.</t>
+          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C57" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C57" s="66">
+        <v>44.00</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
+          <t xml:space="preserve">B'nai B'rith International</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C58" s="66">
-        <v>44.00</v>
+          <t xml:space="preserve">12/18/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">B'nai B'rith International</t>
+          <t xml:space="preserve">Back Bay Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C59" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/16/2027</t>
+        </is>
+      </c>
+      <c r="C59" s="66">
+        <v>83.67</v>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Back Bay Mission, Inc.</t>
+          <t xml:space="preserve">Base Ministry</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
@@ -1097,52 +1097,52 @@
         </is>
       </c>
       <c r="C60" s="66">
-        <v>83.67</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">Base Ministry</t>
+          <t xml:space="preserve">Blessings International</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">9/2/2027</t>
         </is>
       </c>
       <c r="C61" s="66">
-        <v>71.89</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Blessings International</t>
+          <t xml:space="preserve">Blood Cancer United, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">9/2/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C62" s="66">
-        <v>91.00</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Blood Cancer United, Inc.</t>
+          <t xml:space="preserve">Bobby Jones Chiari &amp; Syringomyelia Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C63" s="66">
-        <v>75.00</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="64">
@@ -1868,57 +1868,57 @@
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">East Carolina University Foundation, Inc.</t>
+          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C112" s="66">
-        <v>55.44</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
+          <t xml:space="preserve">Easter Seals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C113" s="66">
-        <v>61.48</v>
+        <v>68.00</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Easter Seals, Inc.</t>
+          <t xml:space="preserve">EB Research Partnership, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
-        </is>
-      </c>
-      <c r="C114" s="66">
-        <v>68.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C114" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">EB Research Partnership, Inc.</t>
+          <t xml:space="preserve">ELT Ventures</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C115" s="65">
@@ -1928,46 +1928,46 @@
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">ELT Ventures</t>
+          <t xml:space="preserve">Empire State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C116" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C116" s="66">
+        <v>82.78</v>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Empire State University Foundation</t>
+          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C117" s="66">
-        <v>82.78</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
+          <t xml:space="preserve">Environmental Defense Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">9/25/2027</t>
         </is>
       </c>
       <c r="C118" s="66">
-        <v>48.32</v>
+        <v>88.20</v>
       </c>
     </row>
     <row r="119">
@@ -2063,76 +2063,76 @@
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">Feeding America</t>
+          <t xml:space="preserve">Feeding Pets of the Homeless</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C125" s="66">
-        <v>98.40</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">Feeding Pets of the Homeless</t>
+          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
+          <t xml:space="preserve">4/9/2027</t>
         </is>
       </c>
       <c r="C126" s="66">
-        <v>75.17</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
+          <t xml:space="preserve">FINCA International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">5/7/2027</t>
         </is>
       </c>
       <c r="C127" s="66">
-        <v>82.48</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">FINCA International, Inc.</t>
+          <t xml:space="preserve">Find The Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">5/7/2027</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C128" s="66">
-        <v>81.47</v>
+        <v>50.00</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">Find The Children</t>
+          <t xml:space="preserve">Firefighters Charitable Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
+          <t xml:space="preserve">9/23/2027</t>
         </is>
       </c>
       <c r="C129" s="66">
-        <v>50.00</v>
+        <v>8.20</v>
       </c>
     </row>
     <row r="130">
@@ -2528,12 +2528,12 @@
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">HIAS Foundation, Inc.</t>
+          <t xml:space="preserve">Herzog Tomorrow Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C156" s="65">
@@ -2543,46 +2543,46 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
+          <t xml:space="preserve">HIAS Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
-        </is>
-      </c>
-      <c r="C157" s="66">
-        <v>81.00</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C157" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">Home Builders Institute</t>
+          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C158" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C158" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">Houston Christian Broadcasters, Inc.</t>
+          <t xml:space="preserve">Home Builders Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
-        </is>
-      </c>
-      <c r="C159" s="66">
-        <v>84.40</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C159" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -2828,147 +2828,147 @@
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
+          <t xml:space="preserve">Isaad Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
+          <t xml:space="preserve">9/18/2027</t>
         </is>
       </c>
       <c r="C176" s="66">
-        <v>75.43</v>
+        <v>96.30</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">Jewish Democratic Council of America</t>
+          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">4/27/2027</t>
         </is>
       </c>
       <c r="C177" s="66">
-        <v>50.07</v>
+        <v>75.43</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">Jewish Voice Ministries International</t>
+          <t xml:space="preserve">Jewish Democratic Council of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C178" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C178" s="66">
+        <v>50.07</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
+          <t xml:space="preserve">Jewish Voice Ministries International</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
-        </is>
-      </c>
-      <c r="C179" s="66">
-        <v>89.00</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
+          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C180" s="66">
-        <v>75.00</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
+          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">9/5/2027</t>
-        </is>
-      </c>
-      <c r="C181" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/17/2027</t>
+        </is>
+      </c>
+      <c r="C181" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
+          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C182" s="66">
-        <v>98.28</v>
+          <t xml:space="preserve">9/5/2027</t>
+        </is>
+      </c>
+      <c r="C182" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">Khan Academy, Inc.</t>
+          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C183" s="66">
-        <v>86.36</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
+          <t xml:space="preserve">Khan Academy, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C184" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/14/2027</t>
+        </is>
+      </c>
+      <c r="C184" s="66">
+        <v>86.36</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">L.E.A.D. Inc.</t>
+          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">11/12/2026</t>
         </is>
       </c>
       <c r="C185" s="65">
@@ -2978,447 +2978,447 @@
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">La Leche League International, Inc.</t>
+          <t xml:space="preserve">L.E.A.D. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
-        </is>
-      </c>
-      <c r="C186" s="66">
-        <v>57.00</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C186" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
+          <t xml:space="preserve">La Leche League International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C187" s="66">
-        <v>63.00</v>
+        <v>57.00</v>
       </c>
     </row>
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
+          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C188" s="66">
-        <v>10.60</v>
+        <v>63.00</v>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
+          <t xml:space="preserve">Lasell University</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">10/28/2026</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C189" s="66">
-        <v>96.80</v>
+        <v>86.90</v>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">Life Teen, Inc.</t>
+          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C190" s="66">
-        <v>76.40</v>
+        <v>10.60</v>
       </c>
     </row>
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">Live Action</t>
+          <t xml:space="preserve">League of Conservation Voters, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">9/23/2027</t>
         </is>
       </c>
       <c r="C191" s="66">
-        <v>81.13</v>
+        <v>92.00</v>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">Living Waters for the World</t>
+          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">10/28/2026</t>
         </is>
       </c>
       <c r="C192" s="66">
-        <v>78.81</v>
+        <v>96.80</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
+          <t xml:space="preserve">Life Teen, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C193" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C193" s="66">
+        <v>76.40</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
+          <t xml:space="preserve">Live Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C194" s="66">
-        <v>76.03</v>
+        <v>81.13</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
+          <t xml:space="preserve">Living Waters for the World</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C195" s="66">
-        <v>62.00</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">Madison House</t>
+          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
-        </is>
-      </c>
-      <c r="C196" s="66">
-        <v>77.79</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C196" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
+          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">8/6/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C197" s="66">
-        <v>86.00</v>
+        <v>76.03</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">MAP International, Inc.</t>
+          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C198" s="66">
-        <v>99.00</v>
+        <v>62.00</v>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">March of Dimes</t>
+          <t xml:space="preserve">Madison House</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">12/30/2026</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C199" s="66">
-        <v>74.00</v>
+        <v>77.79</v>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">Marist University</t>
+          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">8/6/2027</t>
         </is>
       </c>
       <c r="C200" s="66">
-        <v>91.00</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
+          <t xml:space="preserve">MAP International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C201" s="66">
-        <v>91.74</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">Meals on Wheels America</t>
+          <t xml:space="preserve">March of Dimes</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">5/27/2027</t>
+          <t xml:space="preserve">12/30/2026</t>
         </is>
       </c>
       <c r="C202" s="66">
-        <v>59.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
+          <t xml:space="preserve">Marist University</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">6/9/2027</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C203" s="66">
-        <v>80.94</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
+          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">12/8/2026</t>
-        </is>
-      </c>
-      <c r="C204" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/17/2027</t>
+        </is>
+      </c>
+      <c r="C204" s="66">
+        <v>91.74</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
+          <t xml:space="preserve">Meals on Wheels America</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">5/27/2027</t>
         </is>
       </c>
       <c r="C205" s="66">
-        <v>91.00</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">Mercatus Center, Inc.</t>
+          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">6/9/2027</t>
         </is>
       </c>
       <c r="C206" s="66">
-        <v>90.25</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">Mercy for Animals, Inc.</t>
+          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C207" s="66">
-        <v>75.82</v>
+          <t xml:space="preserve">12/8/2026</t>
+        </is>
+      </c>
+      <c r="C207" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">Mercy Ships</t>
+          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">8/26/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C208" s="66">
-        <v>78.18</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
+          <t xml:space="preserve">Mercatus Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C209" s="66">
-        <v>88.00</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">Minutes Matter-MCADD</t>
+          <t xml:space="preserve">Mercy for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">7/19/2027</t>
-        </is>
-      </c>
-      <c r="C210" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C210" s="66">
+        <v>75.82</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">Miracle Flights</t>
+          <t xml:space="preserve">Mercy Hospital, Cedar Rapids, Iowa Endowment Found</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C211" s="66">
-        <v>52.00</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
+          <t xml:space="preserve">Mercy Ships</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">8/26/2027</t>
         </is>
       </c>
       <c r="C212" s="66">
-        <v>94.50</v>
+        <v>78.18</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">Mount Saint Marys University</t>
+          <t xml:space="preserve">Middle East Policy Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C213" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/16/2027</t>
+        </is>
+      </c>
+      <c r="C213" s="66">
+        <v>73.83</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">Mountain States Legal Foundation</t>
+          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C214" s="66">
-        <v>69.99</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">MrCharity, Inc.</t>
+          <t xml:space="preserve">Minutes Matter-MCADD</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
+          <t xml:space="preserve">7/19/2027</t>
         </is>
       </c>
       <c r="C215" s="65">
@@ -3428,222 +3428,222 @@
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
+          <t xml:space="preserve">Miracle Flights</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C216" s="66">
-        <v>54.00</v>
+        <v>52.00</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
+          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C217" s="66">
-        <v>77.80</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
+          <t xml:space="preserve">mothers2mothers United States, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">12/19/2026</t>
+          <t xml:space="preserve">4/27/2027</t>
         </is>
       </c>
       <c r="C218" s="66">
-        <v>66.90</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">Naropa University</t>
+          <t xml:space="preserve">Mount Saint Marys University</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
-        </is>
-      </c>
-      <c r="C219" s="66">
-        <v>76.21</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C219" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
+          <t xml:space="preserve">Mountain States Legal Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C220" s="66">
-        <v>65.00</v>
+        <v>69.99</v>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">National Audubon Society, Inc.</t>
+          <t xml:space="preserve">MrCharity, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C221" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">2/23/2027</t>
+        </is>
+      </c>
+      <c r="C221" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
+          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C222" s="66">
-        <v>81.00</v>
+        <v>54.00</v>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
+          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
+          <t xml:space="preserve">6/24/2027</t>
         </is>
       </c>
       <c r="C223" s="66">
-        <v>92.28</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">National Council of Nonprofits</t>
+          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C224" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/19/2026</t>
+        </is>
+      </c>
+      <c r="C224" s="66">
+        <v>66.90</v>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
+          <t xml:space="preserve">Naropa University</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C225" s="66">
-        <v>49.00</v>
+        <v>76.21</v>
       </c>
     </row>
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">National Foundation for Cancer Research</t>
+          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C226" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C226" s="66">
+        <v>65.00</v>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">National Geographic Society</t>
+          <t xml:space="preserve">National Audubon Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">3/18/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C227" s="66">
-        <v>77.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">National Network of Abortion Funds</t>
+          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
-        </is>
-      </c>
-      <c r="C228" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C228" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">National Park Foundation</t>
+          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">8/7/2027</t>
         </is>
       </c>
       <c r="C229" s="66">
-        <v>72.00</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">National PKU Alliance, Inc.</t>
+          <t xml:space="preserve">National Council of Nonprofits</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C230" s="65">
@@ -3653,27 +3653,27 @@
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
+          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C231" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C231" s="66">
+        <v>49.00</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
+          <t xml:space="preserve">National Foundation for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
+          <t xml:space="preserve">12/1/2026</t>
         </is>
       </c>
       <c r="C232" s="65">
@@ -3683,117 +3683,117 @@
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">National Space Society</t>
+          <t xml:space="preserve">National Geographic Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C233" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/18/2027</t>
+        </is>
+      </c>
+      <c r="C233" s="66">
+        <v>77.00</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">National University</t>
+          <t xml:space="preserve">National LGBTQ Task Force</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C234" s="66">
-        <v>42.69</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">National Veterans Memorial and Museum</t>
+          <t xml:space="preserve">National Network of Abortion Funds</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C235" s="66">
-        <v>72.63</v>
+          <t xml:space="preserve">9/11/2027</t>
+        </is>
+      </c>
+      <c r="C235" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">National Wheelchair Basketball Association</t>
+          <t xml:space="preserve">National Park Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C236" s="66">
-        <v>77.80</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">National Wildlife Federation</t>
+          <t xml:space="preserve">National PKU Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
-        </is>
-      </c>
-      <c r="C237" s="66">
-        <v>86.00</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C237" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">Network for Good, Inc</t>
+          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C238" s="66">
-        <v>97.80</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C238" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">New Harvest, Inc.</t>
+          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C239" s="66">
-        <v>88.49</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C239" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
+          <t xml:space="preserve">National Space Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C240" s="65">
@@ -3803,22 +3803,22 @@
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">Nurse-Family Partnership</t>
+          <t xml:space="preserve">National University</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C241" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C241" s="66">
+        <v>42.69</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">Ocean Conservancy</t>
+          <t xml:space="preserve">National Veterans Memorial and Museum</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
@@ -3827,273 +3827,273 @@
         </is>
       </c>
       <c r="C242" s="66">
-        <v>74.06</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
+          <t xml:space="preserve">National Wheelchair Basketball Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C243" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/12/2027</t>
+        </is>
+      </c>
+      <c r="C243" s="66">
+        <v>77.80</v>
       </c>
     </row>
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">Operation Smile, Inc.</t>
+          <t xml:space="preserve">National Wildlife Federation</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C244" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C244" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
+          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">8/18/2027</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C245" s="66">
-        <v>77.59</v>
+        <v>1.60</v>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">Our Change Foundation</t>
+          <t xml:space="preserve">Network for Good, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C246" s="66">
-        <v>80.46</v>
+        <v>97.80</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">Oxfam-America, Inc.</t>
+          <t xml:space="preserve">New Harvest, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">10/6/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C247" s="66">
-        <v>71.00</v>
+        <v>88.49</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">Pace University</t>
+          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
-        </is>
-      </c>
-      <c r="C248" s="66">
-        <v>88.30</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C248" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
+          <t xml:space="preserve">Nurse-Family Partnership</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C249" s="66">
-        <v>55.43</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C249" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">Panorama Global</t>
+          <t xml:space="preserve">Ocean Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C250" s="66">
-        <v>84.52</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">Paralyzed Veterans of America</t>
+          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
-        </is>
-      </c>
-      <c r="C251" s="66">
-        <v>59.00</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C251" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
+          <t xml:space="preserve">Operation Smile, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">2/9/2027</t>
-        </is>
-      </c>
-      <c r="C252" s="66">
-        <v>90.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C252" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
+          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
-        </is>
-      </c>
-      <c r="C253" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/18/2027</t>
+        </is>
+      </c>
+      <c r="C253" s="66">
+        <v>77.59</v>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">Pathfinder International</t>
+          <t xml:space="preserve">Our Change Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C254" s="66">
-        <v>85.33</v>
+        <v>80.46</v>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">patriotic Hearts, Inc.</t>
+          <t xml:space="preserve">Pace University</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">7/1/2027</t>
         </is>
       </c>
       <c r="C255" s="66">
-        <v>56.00</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">People for the American Way Foundation</t>
+          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C256" s="66">
-        <v>60.00</v>
+        <v>55.43</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
+          <t xml:space="preserve">Panorama Global</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C257" s="66">
-        <v>83.76</v>
+        <v>84.52</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
+          <t xml:space="preserve">Paralyzed Veterans of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C258" s="66">
-        <v>58.00</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
+          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">8/28/2027</t>
+          <t xml:space="preserve">2/9/2027</t>
         </is>
       </c>
       <c r="C259" s="66">
-        <v>79.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
+          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C260" s="65">
@@ -4103,102 +4103,102 @@
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
+          <t xml:space="preserve">Pathfinder International</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C261" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C261" s="66">
+        <v>85.33</v>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
+          <t xml:space="preserve">patriotic Hearts, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C262" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/27/2027</t>
+        </is>
+      </c>
+      <c r="C262" s="66">
+        <v>56.00</v>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">Pledgeling Foundation</t>
+          <t xml:space="preserve">People for the American Way Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C263" s="66">
-        <v>65.93</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">Polar Bears International</t>
+          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">2/2/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C264" s="66">
-        <v>86.00</v>
+        <v>83.76</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
+          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C265" s="66">
-        <v>85.54</v>
+        <v>58.00</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">Pratt Institute</t>
+          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C266" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/28/2027</t>
+        </is>
+      </c>
+      <c r="C266" s="66">
+        <v>79.00</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">Primo Cares, Inc.</t>
+          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">11/3/2026</t>
         </is>
       </c>
       <c r="C267" s="65">
@@ -4208,22 +4208,22 @@
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries</t>
+          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C268" s="66">
-        <v>68.60</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C268" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
+          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
@@ -4238,102 +4238,102 @@
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">Project Cure, Inc.</t>
+          <t xml:space="preserve">Pledgeling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C270" s="66">
-        <v>27.00</v>
+        <v>65.93</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
+          <t xml:space="preserve">Polar Bears International</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">2/2/2027</t>
         </is>
       </c>
       <c r="C271" s="66">
-        <v>88.71</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">Project Orbis International, Inc.</t>
+          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
-        </is>
-      </c>
-      <c r="C272" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/27/2027</t>
+        </is>
+      </c>
+      <c r="C272" s="66">
+        <v>85.54</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">Proteus Fund, Inc.</t>
+          <t xml:space="preserve">Pratt Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
-        </is>
-      </c>
-      <c r="C273" s="66">
-        <v>81.25</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C273" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">Providence House</t>
+          <t xml:space="preserve">Primo Cares, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
-        </is>
-      </c>
-      <c r="C274" s="66">
-        <v>92.06</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C274" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
+          <t xml:space="preserve">Prison Fellowship Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C275" s="66">
-        <v>84.22</v>
+        <v>68.60</v>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">Re:Power</t>
+          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C276" s="65">
@@ -4343,7 +4343,7 @@
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">Reproductive Freedom for All</t>
+          <t xml:space="preserve">Project Cure, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
@@ -4352,153 +4352,153 @@
         </is>
       </c>
       <c r="C277" s="66">
-        <v>70.00</v>
+        <v>27.00</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">Rodale Institute</t>
+          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C278" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C278" s="66">
+        <v>88.71</v>
       </c>
     </row>
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
+          <t xml:space="preserve">Proteus Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">12/12/2026</t>
-        </is>
-      </c>
-      <c r="C279" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/2/2027</t>
+        </is>
+      </c>
+      <c r="C279" s="66">
+        <v>81.25</v>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
+          <t xml:space="preserve">Providence House</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C280" s="66">
-        <v>45.00</v>
+        <v>92.06</v>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
+          <t xml:space="preserve">Public Health Foundation Enterprise, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C281" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C281" s="66">
+        <v>94.97</v>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">Rush University Medical Center</t>
+          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C282" s="66">
-        <v>91.41</v>
+        <v>84.22</v>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">Rutgers University Foundation</t>
+          <t xml:space="preserve">Re:Power</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
-        </is>
-      </c>
-      <c r="C283" s="66">
-        <v>87.46</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C283" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">Sagamore Institute, Inc.</t>
+          <t xml:space="preserve">Reproductive Freedom for All</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C284" s="66">
-        <v>91.61</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">Saint John's University</t>
+          <t xml:space="preserve">RezilientKidz</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C285" s="66">
-        <v>88.76</v>
+        <v>94.35</v>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">Save the Chimps, Inc.</t>
+          <t xml:space="preserve">Rodale Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
-        </is>
-      </c>
-      <c r="C286" s="66">
-        <v>79.70</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C286" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">Seattle Pacific University</t>
+          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">12/12/2026</t>
         </is>
       </c>
       <c r="C287" s="65">
@@ -4508,192 +4508,192 @@
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
-        </is>
-      </c>
-      <c r="C288" s="66">
-        <v>94.00</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C288" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">Share Our Strength</t>
+          <t xml:space="preserve">Rush University Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C289" s="66">
-        <v>58.73</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
+          <t xml:space="preserve">Rutgers University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C290" s="66">
-        <v>97.29</v>
+        <v>87.46</v>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">Sierra  Club</t>
+          <t xml:space="preserve">Sagamore Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">12/22/2026</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C291" s="66">
-        <v>82.00</v>
+        <v>91.61</v>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">Sister Rising Worldwide</t>
+          <t xml:space="preserve">Saint John's University</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">1/28/2027</t>
-        </is>
-      </c>
-      <c r="C292" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/31/2027</t>
+        </is>
+      </c>
+      <c r="C292" s="66">
+        <v>88.76</v>
       </c>
     </row>
     <row r="293">
       <c t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">Sixpoint, Inc.</t>
+          <t xml:space="preserve">Save the Chimps, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C293" s="66">
-        <v>77.16</v>
+        <v>79.70</v>
       </c>
     </row>
     <row r="294">
       <c t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
+          <t xml:space="preserve">Seattle Pacific University</t>
         </is>
       </c>
       <c t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">4/22/2027</t>
-        </is>
-      </c>
-      <c r="C294" s="66">
-        <v>90.00</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C294" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">Social Purpose Corrections</t>
+          <t xml:space="preserve">Second Harvest Food Bank of Greater New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C295" s="66">
-        <v>12.95</v>
+          <t xml:space="preserve">5/20/2027</t>
+        </is>
+      </c>
+      <c r="C295" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
+          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
         </is>
       </c>
       <c t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">9/2/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C296" s="66">
-        <v>72.80</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="297">
       <c t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
+          <t xml:space="preserve">Share Our Strength</t>
         </is>
       </c>
       <c t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
-        </is>
-      </c>
-      <c r="C297" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C297" s="66">
+        <v>58.73</v>
       </c>
     </row>
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
+          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">7/29/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C298" s="66">
-        <v>86.00</v>
+        <v>97.29</v>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">South Dakota State University Foundation</t>
+          <t xml:space="preserve">Sierra  Club</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C299" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/22/2026</t>
+        </is>
+      </c>
+      <c r="C299" s="66">
+        <v>82.00</v>
       </c>
     </row>
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
+          <t xml:space="preserve">Sister Rising Worldwide</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">1/28/2027</t>
         </is>
       </c>
       <c r="C300" s="65">
@@ -4703,72 +4703,72 @@
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">Special Olympics, Inc.</t>
+          <t xml:space="preserve">Sixpoint, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C301" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/9/2027</t>
+        </is>
+      </c>
+      <c r="C301" s="66">
+        <v>77.16</v>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">SPLC Action Fund</t>
+          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">9/17/2027</t>
+          <t xml:space="preserve">4/22/2027</t>
         </is>
       </c>
       <c r="C302" s="66">
-        <v>72.81</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
+          <t xml:space="preserve">Social Purpose Corrections</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C303" s="66">
-        <v>85.31</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">State University of Iowa Foundation</t>
+          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">9/4/2027</t>
+          <t xml:space="preserve">9/2/2027</t>
         </is>
       </c>
       <c r="C304" s="66">
-        <v>79.00</v>
+        <v>72.80</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
+          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">10/15/2026</t>
         </is>
       </c>
       <c r="C305" s="65">
@@ -4778,27 +4778,27 @@
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
+          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
+          <t xml:space="preserve">7/29/2027</t>
         </is>
       </c>
       <c r="C306" s="66">
-        <v>92.00</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">Students for Life Action, Inc.</t>
+          <t xml:space="preserve">South Dakota State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">11/7/2026</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C307" s="65">
@@ -4808,117 +4808,117 @@
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">Students for Life of America</t>
+          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">10/10/2026</t>
-        </is>
-      </c>
-      <c r="C308" s="66">
-        <v>82.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C308" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
+          <t xml:space="preserve">Special Olympics, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">8/12/2027</t>
-        </is>
-      </c>
-      <c r="C309" s="66">
-        <v>89.29</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C309" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">Teacher Freedom Alliance</t>
+          <t xml:space="preserve">SPLC Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
-        </is>
-      </c>
-      <c r="C310" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/17/2027</t>
+        </is>
+      </c>
+      <c r="C310" s="66">
+        <v>72.81</v>
       </c>
     </row>
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">The Actors' Fund of America</t>
+          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C311" s="66">
-        <v>86.73</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">State University of Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">9/4/2027</t>
         </is>
       </c>
       <c r="C312" s="66">
-        <v>39.00</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">The American University</t>
+          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
-        </is>
-      </c>
-      <c r="C313" s="66">
-        <v>90.23</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C313" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C314" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/24/2027</t>
+        </is>
+      </c>
+      <c r="C314" s="66">
+        <v>92.00</v>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">The Anthony Davis Foundation</t>
+          <t xml:space="preserve">Students for Life Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">11/24/2026</t>
+          <t xml:space="preserve">11/7/2026</t>
         </is>
       </c>
       <c r="C315" s="65">
@@ -4928,207 +4928,207 @@
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
+          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">10/24/2026</t>
+          <t xml:space="preserve">8/12/2027</t>
         </is>
       </c>
       <c r="C316" s="66">
-        <v>90.00</v>
+        <v>89.29</v>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">The Barack Obama Foundation</t>
+          <t xml:space="preserve">Teacher Freedom Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C317" s="66">
-        <v>55.90</v>
+          <t xml:space="preserve">6/24/2027</t>
+        </is>
+      </c>
+      <c r="C317" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">The Baruch College Fund</t>
+          <t xml:space="preserve">The Actors' Fund of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">12/10/2026</t>
         </is>
       </c>
       <c r="C318" s="66">
-        <v>84.00</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">The Call of Duty Endowment</t>
+          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C319" s="66">
-        <v>73.00</v>
+        <v>39.00</v>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">The Center for Alcohol Policy</t>
+          <t xml:space="preserve">The American Society for the Prevention of Cruelty</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C320" s="66">
-        <v>73.40</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">The Center for Investigative Reporting</t>
+          <t xml:space="preserve">The American University</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C321" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/9/2027</t>
+        </is>
+      </c>
+      <c r="C321" s="66">
+        <v>90.23</v>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
+          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
-        </is>
-      </c>
-      <c r="C322" s="66">
-        <v>71.00</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C322" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">The Center for Victims of Torture</t>
+          <t xml:space="preserve">The Anthony Davis Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
-        </is>
-      </c>
-      <c r="C323" s="66">
-        <v>74.00</v>
+          <t xml:space="preserve">11/24/2026</t>
+        </is>
+      </c>
+      <c r="C323" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
+          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">7/6/2027</t>
+          <t xml:space="preserve">10/24/2026</t>
         </is>
       </c>
       <c r="C324" s="66">
-        <v>71.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="325">
       <c t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">The Colorado College</t>
+          <t xml:space="preserve">The Barack Obama Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">10/29/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C325" s="66">
-        <v>90.00</v>
+        <v>55.90</v>
       </c>
     </row>
     <row r="326">
       <c t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">The Denver Rescue Mission</t>
+          <t xml:space="preserve">The Baruch College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C326" s="66">
-        <v>82.96</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="327">
       <c t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">The Edison Institute</t>
+          <t xml:space="preserve">The Call of Duty Endowment</t>
         </is>
       </c>
       <c t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C327" s="66">
-        <v>78.00</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="328">
       <c t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+          <t xml:space="preserve">The Center for Alcohol Policy</t>
         </is>
       </c>
       <c t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C328" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/16/2027</t>
+        </is>
+      </c>
+      <c r="C328" s="66">
+        <v>73.40</v>
       </c>
     </row>
     <row r="329">
       <c t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+          <t xml:space="preserve">The Center for Investigative Reporting</t>
         </is>
       </c>
       <c t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
+          <t xml:space="preserve">12/9/2026</t>
         </is>
       </c>
       <c r="C329" s="65">
@@ -5138,307 +5138,307 @@
     <row r="330">
       <c t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
+          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C330" s="66">
-        <v>76.48</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="331">
       <c t="inlineStr" r="A331">
         <is>
-          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
+          <t xml:space="preserve">The Center for Victims of Torture</t>
         </is>
       </c>
       <c t="inlineStr" r="B331">
         <is>
-          <t xml:space="preserve">5/15/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C331" s="66">
-        <v>85.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="332">
       <c t="inlineStr" r="A332">
         <is>
-          <t xml:space="preserve">The Heritage Foundation</t>
+          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
         </is>
       </c>
       <c t="inlineStr" r="B332">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">7/6/2027</t>
         </is>
       </c>
       <c r="C332" s="66">
-        <v>83.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="333">
       <c t="inlineStr" r="A333">
         <is>
-          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
+          <t xml:space="preserve">The Colorado College</t>
         </is>
       </c>
       <c t="inlineStr" r="B333">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">10/29/2027</t>
         </is>
       </c>
       <c r="C333" s="66">
-        <v>89.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="334">
       <c t="inlineStr" r="A334">
         <is>
-          <t xml:space="preserve">The Independent Institute</t>
+          <t xml:space="preserve">The Denver Rescue Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B334">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">7/20/2027</t>
         </is>
       </c>
       <c r="C334" s="66">
-        <v>77.51</v>
+        <v>82.96</v>
       </c>
     </row>
     <row r="335">
       <c t="inlineStr" r="A335">
         <is>
-          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
+          <t xml:space="preserve">The Edison Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B335">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C335" s="66">
-        <v>84.00</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="336">
       <c t="inlineStr" r="A336">
         <is>
-          <t xml:space="preserve">The Just Trust for Education</t>
+          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B336">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
-        </is>
-      </c>
-      <c r="C336" s="66">
-        <v>85.13</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C336" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="337">
       <c t="inlineStr" r="A337">
         <is>
-          <t xml:space="preserve">The Kansas University Endowment Association</t>
+          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
         </is>
       </c>
       <c t="inlineStr" r="B337">
         <is>
-          <t xml:space="preserve">7/21/2027</t>
-        </is>
-      </c>
-      <c r="C337" s="66">
-        <v>91.34</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C337" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="338">
       <c t="inlineStr" r="A338">
         <is>
-          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
         </is>
       </c>
       <c t="inlineStr" r="B338">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C338" s="66">
-        <v>83.06</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="339">
       <c t="inlineStr" r="A339">
         <is>
-          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
+          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B339">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">5/15/2027</t>
         </is>
       </c>
       <c r="C339" s="66">
-        <v>91.99</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="340">
       <c t="inlineStr" r="A340">
         <is>
-          <t xml:space="preserve">The Memorial Foundation</t>
+          <t xml:space="preserve">The Heritage Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B340">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C340" s="66">
-        <v>72.00</v>
+        <v>83.00</v>
       </c>
     </row>
     <row r="341">
       <c t="inlineStr" r="A341">
         <is>
-          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B341">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C341" s="66">
-        <v>74.58</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="342">
       <c t="inlineStr" r="A342">
         <is>
-          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
+          <t xml:space="preserve">The Independent Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B342">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C342" s="66">
-        <v>60.00</v>
+        <v>77.51</v>
       </c>
     </row>
     <row r="343">
       <c t="inlineStr" r="A343">
         <is>
-          <t xml:space="preserve">The National World War II Museum, Inc.</t>
+          <t xml:space="preserve">The International Wildlife Rehab. Council</t>
         </is>
       </c>
       <c t="inlineStr" r="B343">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C343" s="66">
-        <v>80.00</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="344">
       <c t="inlineStr" r="A344">
         <is>
-          <t xml:space="preserve">The Nature Conservancy</t>
+          <t xml:space="preserve">The Jane Goodall Institute for Wildlife Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B344">
         <is>
-          <t xml:space="preserve">10/9/2026</t>
-        </is>
-      </c>
-      <c r="C344" s="66">
-        <v>70.00</v>
+          <t xml:space="preserve">5/19/2027</t>
+        </is>
+      </c>
+      <c r="C344" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c t="inlineStr" r="A345">
         <is>
-          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B345">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C345" s="66">
-        <v>80.64</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="346">
       <c t="inlineStr" r="A346">
         <is>
-          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
+          <t xml:space="preserve">The Just Trust for Education</t>
         </is>
       </c>
       <c t="inlineStr" r="B346">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C346" s="66">
-        <v>87.40</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="347">
       <c t="inlineStr" r="A347">
         <is>
-          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
+          <t xml:space="preserve">The Kansas University Endowment Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B347">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
+          <t xml:space="preserve">7/21/2027</t>
         </is>
       </c>
       <c r="C347" s="66">
-        <v>60.00</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="348">
       <c t="inlineStr" r="A348">
         <is>
-          <t xml:space="preserve">The Ohio University Foundation</t>
+          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B348">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C348" s="66">
-        <v>74.14</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="349">
       <c t="inlineStr" r="A349">
         <is>
-          <t xml:space="preserve">The OneStar Foundation</t>
+          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B349">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C349" s="66">
-        <v>62.50</v>
+        <v>91.99</v>
       </c>
     </row>
     <row r="350">
       <c t="inlineStr" r="A350">
         <is>
-          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+          <t xml:space="preserve">The Memorial Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B350">
@@ -5447,168 +5447,168 @@
         </is>
       </c>
       <c r="C350" s="66">
-        <v>88.30</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="351">
       <c t="inlineStr" r="A351">
         <is>
-          <t xml:space="preserve">The Planetary Society</t>
+          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B351">
         <is>
-          <t xml:space="preserve">7/14/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C351" s="66">
-        <v>66.00</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="352">
       <c t="inlineStr" r="A352">
         <is>
-          <t xml:space="preserve">The Purchase College Foundation</t>
+          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B352">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C352" s="66">
-        <v>78.12</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="353">
       <c t="inlineStr" r="A353">
         <is>
-          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
+          <t xml:space="preserve">The National World War II Museum, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B353">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C353" s="66">
-        <v>81.26</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="354">
       <c t="inlineStr" r="A354">
         <is>
-          <t xml:space="preserve">The Ruth Collective</t>
+          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
         </is>
       </c>
       <c t="inlineStr" r="B354">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C354" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C354" s="66">
+        <v>80.64</v>
       </c>
     </row>
     <row r="355">
       <c t="inlineStr" r="A355">
         <is>
-          <t xml:space="preserve">The Society of the Cincinnati</t>
+          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
         </is>
       </c>
       <c t="inlineStr" r="B355">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C355" s="66">
-        <v>73.00</v>
+        <v>87.40</v>
       </c>
     </row>
     <row r="356">
       <c t="inlineStr" r="A356">
         <is>
-          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B356">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">8/24/2027</t>
         </is>
       </c>
       <c r="C356" s="66">
-        <v>94.00</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="357">
       <c t="inlineStr" r="A357">
         <is>
-          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+          <t xml:space="preserve">The Ohio University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B357">
         <is>
-          <t xml:space="preserve">4/13/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C357" s="66">
-        <v>82.20</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="358">
       <c t="inlineStr" r="A358">
         <is>
-          <t xml:space="preserve">The University of Montana Foundation</t>
+          <t xml:space="preserve">The OneStar Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B358">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C358" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/14/2027</t>
+        </is>
+      </c>
+      <c r="C358" s="66">
+        <v>62.50</v>
       </c>
     </row>
     <row r="359">
       <c t="inlineStr" r="A359">
         <is>
-          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
+          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B359">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C359" s="66">
-        <v>76.00</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="360">
       <c t="inlineStr" r="A360">
         <is>
-          <t xml:space="preserve">The Visiting Angels Foundation</t>
+          <t xml:space="preserve">The Planetary Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B360">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">7/14/2027</t>
         </is>
       </c>
       <c r="C360" s="66">
-        <v>94.00</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="361">
       <c t="inlineStr" r="A361">
         <is>
-          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
+          <t xml:space="preserve">The Principia Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B361">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">5/19/2027</t>
         </is>
       </c>
       <c r="C361" s="65">
@@ -5618,690 +5618,840 @@
     <row r="362">
       <c t="inlineStr" r="A362">
         <is>
-          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+          <t xml:space="preserve">The Purchase College Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B362">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C362" s="66">
-        <v>79.51</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="363">
       <c t="inlineStr" r="A363">
         <is>
-          <t xml:space="preserve">The Wilderness Society</t>
+          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
         </is>
       </c>
       <c t="inlineStr" r="B363">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C363" s="66">
-        <v>73.00</v>
+        <v>81.26</v>
       </c>
     </row>
     <row r="364">
       <c t="inlineStr" r="A364">
         <is>
-          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
+          <t xml:space="preserve">The Ruth Collective</t>
         </is>
       </c>
       <c t="inlineStr" r="B364">
         <is>
-          <t xml:space="preserve">4/21/2027</t>
-        </is>
-      </c>
-      <c r="C364" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C364" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="365">
       <c t="inlineStr" r="A365">
         <is>
-          <t xml:space="preserve">Together Making Changes</t>
+          <t xml:space="preserve">The Society of the Cincinnati</t>
         </is>
       </c>
       <c t="inlineStr" r="B365">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C365" s="66">
-        <v>90.26</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="366">
       <c t="inlineStr" r="A366">
         <is>
-          <t xml:space="preserve">Trevecca Nazarene University</t>
+          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
         </is>
       </c>
       <c t="inlineStr" r="B366">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C366" s="66">
-        <v>87.82</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="367">
       <c t="inlineStr" r="A367">
         <is>
-          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
+          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B367">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">4/13/2027</t>
         </is>
       </c>
       <c r="C367" s="66">
-        <v>94.50</v>
+        <v>82.20</v>
       </c>
     </row>
     <row r="368">
       <c t="inlineStr" r="A368">
         <is>
-          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+          <t xml:space="preserve">The University of Montana Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B368">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C368" s="66">
-        <v>89.90</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="369">
       <c t="inlineStr" r="A369">
         <is>
-          <t xml:space="preserve">Trustees of Tufts College</t>
+          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B369">
         <is>
-          <t xml:space="preserve">7/2/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C369" s="66">
-        <v>85.00</v>
+        <v>76.00</v>
       </c>
     </row>
     <row r="370">
       <c t="inlineStr" r="A370">
         <is>
-          <t xml:space="preserve">Turning Point USA, Inc.</t>
+          <t xml:space="preserve">The Visiting Angels Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B370">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C370" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/20/2027</t>
+        </is>
+      </c>
+      <c r="C370" s="66">
+        <v>94.00</v>
       </c>
     </row>
     <row r="371">
       <c t="inlineStr" r="A371">
         <is>
-          <t xml:space="preserve">Twelveacres, Incorporated</t>
+          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B371">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
-        </is>
-      </c>
-      <c r="C371" s="66">
-        <v>79.93</v>
+          <t xml:space="preserve">10/15/2026</t>
+        </is>
+      </c>
+      <c r="C371" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="372">
       <c t="inlineStr" r="A372">
         <is>
-          <t xml:space="preserve">UATX</t>
+          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B372">
         <is>
-          <t xml:space="preserve">2/1/2027</t>
-        </is>
-      </c>
-      <c r="C372" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/30/2027</t>
+        </is>
+      </c>
+      <c r="C372" s="66">
+        <v>79.51</v>
       </c>
     </row>
     <row r="373">
       <c t="inlineStr" r="A373">
         <is>
-          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+          <t xml:space="preserve">The Wilderness Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B373">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C373" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C373" s="66">
+        <v>73.00</v>
       </c>
     </row>
     <row r="374">
       <c t="inlineStr" r="A374">
         <is>
-          <t xml:space="preserve">UMKC Foundation</t>
+          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B374">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">4/21/2027</t>
         </is>
       </c>
       <c r="C374" s="66">
-        <v>95.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="375">
       <c t="inlineStr" r="A375">
         <is>
-          <t xml:space="preserve">Unified Youth</t>
+          <t xml:space="preserve">Together Making Changes</t>
         </is>
       </c>
       <c t="inlineStr" r="B375">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C375" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/16/2027</t>
+        </is>
+      </c>
+      <c r="C375" s="66">
+        <v>90.26</v>
       </c>
     </row>
     <row r="376">
       <c t="inlineStr" r="A376">
         <is>
-          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+          <t xml:space="preserve">Trevecca Nazarene University</t>
         </is>
       </c>
       <c t="inlineStr" r="B376">
         <is>
-          <t xml:space="preserve">8/1/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C376" s="66">
-        <v>88.00</v>
+        <v>87.82</v>
       </c>
     </row>
     <row r="377">
       <c t="inlineStr" r="A377">
         <is>
-          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
+          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B377">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C377" s="66">
-        <v>84.01</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="378">
       <c t="inlineStr" r="A378">
         <is>
-          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
         </is>
       </c>
       <c t="inlineStr" r="B378">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C378" s="66">
-        <v>85.00</v>
+        <v>89.90</v>
       </c>
     </row>
     <row r="379">
       <c t="inlineStr" r="A379">
         <is>
-          <t xml:space="preserve">united Service Organizations, Inc.</t>
+          <t xml:space="preserve">Trustees of Tufts College</t>
         </is>
       </c>
       <c t="inlineStr" r="B379">
         <is>
-          <t xml:space="preserve">11/10/2026</t>
+          <t xml:space="preserve">7/2/2027</t>
         </is>
       </c>
       <c r="C379" s="66">
-        <v>67.94</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="380">
       <c t="inlineStr" r="A380">
         <is>
-          <t xml:space="preserve">United States Association for UNHCR</t>
+          <t xml:space="preserve">Turning Point USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B380">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
-        </is>
-      </c>
-      <c r="C380" s="66">
-        <v>61.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C380" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="381">
       <c t="inlineStr" r="A381">
         <is>
-          <t xml:space="preserve">United States Center for SafeSport</t>
+          <t xml:space="preserve">Twelveacres, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B381">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C381" s="66">
-        <v>72.74</v>
+        <v>79.93</v>
       </c>
     </row>
     <row r="382">
       <c t="inlineStr" r="A382">
         <is>
-          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
+          <t xml:space="preserve">UATX</t>
         </is>
       </c>
       <c t="inlineStr" r="B382">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
-        </is>
-      </c>
-      <c r="C382" s="66">
-        <v>38.00</v>
+          <t xml:space="preserve">2/1/2027</t>
+        </is>
+      </c>
+      <c r="C382" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="383">
       <c t="inlineStr" r="A383">
         <is>
-          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
+          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B383">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C383" s="66">
-        <v>99.30</v>
+        <v>95.75</v>
       </c>
     </row>
     <row r="384">
       <c t="inlineStr" r="A384">
         <is>
-          <t xml:space="preserve">University of Colorado</t>
+          <t xml:space="preserve">UMKC Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B384">
         <is>
-          <t xml:space="preserve">10/7/2026</t>
-        </is>
-      </c>
-      <c r="C384" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/27/2027</t>
+        </is>
+      </c>
+      <c r="C384" s="66">
+        <v>95.00</v>
       </c>
     </row>
     <row r="385">
       <c t="inlineStr" r="A385">
         <is>
-          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
+          <t xml:space="preserve">Unified Youth</t>
         </is>
       </c>
       <c t="inlineStr" r="B385">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
-        </is>
-      </c>
-      <c r="C385" s="66">
-        <v>93.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C385" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="386">
       <c t="inlineStr" r="A386">
         <is>
-          <t xml:space="preserve">University of Nebraska Foundation</t>
+          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B386">
         <is>
-          <t xml:space="preserve">7/15/2027</t>
+          <t xml:space="preserve">8/1/2027</t>
         </is>
       </c>
       <c r="C386" s="66">
-        <v>81.10</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="387">
       <c t="inlineStr" r="A387">
         <is>
-          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
+          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B387">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C387" s="66">
-        <v>77.00</v>
+        <v>84.01</v>
       </c>
     </row>
     <row r="388">
       <c t="inlineStr" r="A388">
         <is>
-          <t xml:space="preserve">University of Pacific</t>
+          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B388">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C388" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C388" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="389">
       <c t="inlineStr" r="A389">
         <is>
-          <t xml:space="preserve">University of Richmond</t>
+          <t xml:space="preserve">united Service Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B389">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">11/10/2026</t>
         </is>
       </c>
       <c r="C389" s="66">
-        <v>82.18</v>
+        <v>67.94</v>
       </c>
     </row>
     <row r="390">
       <c t="inlineStr" r="A390">
         <is>
-          <t xml:space="preserve">Veterans Community Project</t>
+          <t xml:space="preserve">United States Association for UNHCR</t>
         </is>
       </c>
       <c t="inlineStr" r="B390">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C390" s="66">
-        <v>88.83</v>
+        <v>61.00</v>
       </c>
     </row>
     <row r="391">
       <c t="inlineStr" r="A391">
         <is>
-          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
+          <t xml:space="preserve">United States Center for SafeSport</t>
         </is>
       </c>
       <c t="inlineStr" r="B391">
         <is>
-          <t xml:space="preserve">7/13/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C391" s="66">
-        <v>72.00</v>
+        <v>72.74</v>
       </c>
     </row>
     <row r="392">
       <c t="inlineStr" r="A392">
         <is>
-          <t xml:space="preserve">Violet Research Institute, Inc.</t>
+          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B392">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C392" s="66">
-        <v>80.00</v>
+        <v>38.00</v>
       </c>
     </row>
     <row r="393">
       <c t="inlineStr" r="A393">
         <is>
-          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B393">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C393" s="66">
-        <v>28.00</v>
+        <v>99.30</v>
       </c>
     </row>
     <row r="394">
       <c t="inlineStr" r="A394">
         <is>
-          <t xml:space="preserve">VoteAmerica, Inc.</t>
+          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B394">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C394" s="66">
-        <v>93.37</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="395">
       <c t="inlineStr" r="A395">
         <is>
-          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+          <t xml:space="preserve">University of Nebraska Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B395">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C395" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/15/2027</t>
+        </is>
+      </c>
+      <c r="C395" s="66">
+        <v>81.10</v>
       </c>
     </row>
     <row r="396">
       <c t="inlineStr" r="A396">
         <is>
-          <t xml:space="preserve">Washington State University Foundation</t>
+          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B396">
         <is>
-          <t xml:space="preserve">7/8/2027</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C396" s="66">
-        <v>75.03</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="397">
       <c t="inlineStr" r="A397">
         <is>
-          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+          <t xml:space="preserve">University of Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B397">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
-        </is>
-      </c>
-      <c r="C397" s="66">
-        <v>82.68</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C397" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="398">
       <c t="inlineStr" r="A398">
         <is>
-          <t xml:space="preserve">Wildlife Conservation Network</t>
+          <t xml:space="preserve">University of Richmond</t>
         </is>
       </c>
       <c t="inlineStr" r="B398">
         <is>
-          <t xml:space="preserve">8/13/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C398" s="66">
-        <v>92.13</v>
+        <v>82.18</v>
       </c>
     </row>
     <row r="399">
       <c t="inlineStr" r="A399">
         <is>
-          <t xml:space="preserve">Winning for Women, Inc.</t>
+          <t xml:space="preserve">Veterans Community Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B399">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C399" s="66">
-        <v>66.70</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="400">
       <c t="inlineStr" r="A400">
         <is>
-          <t xml:space="preserve">Women for Women International</t>
+          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B400">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">7/13/2027</t>
         </is>
       </c>
       <c r="C400" s="66">
-        <v>79.06</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="401">
       <c t="inlineStr" r="A401">
         <is>
-          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+          <t xml:space="preserve">Violet Research Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B401">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C401" s="66">
-        <v>71.40</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="402">
       <c t="inlineStr" r="A402">
         <is>
-          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B402">
         <is>
-          <t xml:space="preserve">2/20/2027</t>
-        </is>
-      </c>
-      <c r="C402" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C402" s="66">
+        <v>28.00</v>
       </c>
     </row>
     <row r="403">
       <c t="inlineStr" r="A403">
         <is>
-          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+          <t xml:space="preserve">VoteAmerica, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B403">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C403" s="66">
-        <v>79.00</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="404">
       <c t="inlineStr" r="A404">
         <is>
-          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B404">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
-        </is>
-      </c>
-      <c r="C404" s="66">
-        <v>70.36</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C404" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="405">
       <c t="inlineStr" r="A405">
         <is>
-          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
+          <t xml:space="preserve">Washington State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B405">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
+          <t xml:space="preserve">7/8/2027</t>
         </is>
       </c>
       <c r="C405" s="66">
-        <v>39.45</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="406">
       <c t="inlineStr" r="A406">
         <is>
-          <t xml:space="preserve">YMCA of the Rockies</t>
+          <t xml:space="preserve">Western Illinois University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B406">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C406" s="66">
-        <v>81.65</v>
+        <v>77.54</v>
       </c>
     </row>
     <row r="407">
       <c t="inlineStr" r="A407">
         <is>
+          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B407">
+        <is>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C407" s="66">
+        <v>82.68</v>
+      </c>
+    </row>
+    <row r="408">
+      <c t="inlineStr" r="A408">
+        <is>
+          <t xml:space="preserve">Wildlife Conservation Network</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B408">
+        <is>
+          <t xml:space="preserve">8/13/2027</t>
+        </is>
+      </c>
+      <c r="C408" s="66">
+        <v>92.13</v>
+      </c>
+    </row>
+    <row r="409">
+      <c t="inlineStr" r="A409">
+        <is>
+          <t xml:space="preserve">Winning for Women, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B409">
+        <is>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C409" s="66">
+        <v>66.70</v>
+      </c>
+    </row>
+    <row r="410">
+      <c t="inlineStr" r="A410">
+        <is>
+          <t xml:space="preserve">Women for Women International</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B410">
+        <is>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C410" s="66">
+        <v>79.06</v>
+      </c>
+    </row>
+    <row r="411">
+      <c t="inlineStr" r="A411">
+        <is>
+          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B411">
+        <is>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C411" s="66">
+        <v>71.40</v>
+      </c>
+    </row>
+    <row r="412">
+      <c t="inlineStr" r="A412">
+        <is>
+          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B412">
+        <is>
+          <t xml:space="preserve">2/20/2027</t>
+        </is>
+      </c>
+      <c r="C412" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c t="inlineStr" r="A413">
+        <is>
+          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B413">
+        <is>
+          <t xml:space="preserve">5/20/2027</t>
+        </is>
+      </c>
+      <c r="C413" s="66">
+        <v>79.00</v>
+      </c>
+    </row>
+    <row r="414">
+      <c t="inlineStr" r="A414">
+        <is>
+          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B414">
+        <is>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C414" s="66">
+        <v>70.36</v>
+      </c>
+    </row>
+    <row r="415">
+      <c t="inlineStr" r="A415">
+        <is>
+          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B415">
+        <is>
+          <t xml:space="preserve">8/24/2027</t>
+        </is>
+      </c>
+      <c r="C415" s="66">
+        <v>39.45</v>
+      </c>
+    </row>
+    <row r="416">
+      <c t="inlineStr" r="A416">
+        <is>
+          <t xml:space="preserve">YMCA of the Rockies</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B416">
+        <is>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C416" s="66">
+        <v>81.65</v>
+      </c>
+    </row>
+    <row r="417">
+      <c t="inlineStr" r="A417">
+        <is>
           <t xml:space="preserve">Young Judaea Global, Inc.</t>
         </is>
       </c>
-      <c t="inlineStr" r="B407">
+      <c t="inlineStr" r="B417">
         <is>
           <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
-      <c r="C407" s="66">
+      <c r="C417" s="66">
         <v>71.20</v>
       </c>
     </row>

--- a/downloadable-data/LA.xlsx
+++ b/downloadable-data/LA.xlsx
@@ -688,11 +688,11 @@
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">10/16/2026</t>
-        </is>
-      </c>
-      <c r="C33" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/1/2027</t>
+        </is>
+      </c>
+      <c r="C33" s="66">
+        <v>81.82</v>
       </c>
     </row>
     <row r="34">
@@ -713,247 +713,247 @@
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">American Foundation for the Blind, Inc.</t>
+          <t xml:space="preserve">American Farm Bureau Foundation for Agriculture</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C35" s="66">
-        <v>66.78</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">American Heart Association, Inc.</t>
+          <t xml:space="preserve">American Foundation for the Blind, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">8/18/2027</t>
-        </is>
-      </c>
-      <c r="C36" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C36" s="66">
+        <v>66.78</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">American Indian College Fund</t>
+          <t xml:space="preserve">American Heart Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">11/13/2026</t>
-        </is>
-      </c>
-      <c r="C37" s="66">
-        <v>78.00</v>
+          <t xml:space="preserve">8/18/2027</t>
+        </is>
+      </c>
+      <c r="C37" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">American Institute for Cancer Research</t>
+          <t xml:space="preserve">American Indian College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">11/13/2026</t>
         </is>
       </c>
       <c r="C38" s="66">
-        <v>67.00</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">American Institute for Economic Research</t>
+          <t xml:space="preserve">American Institute for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C39" s="66">
-        <v>78.63</v>
+        <v>67.00</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">American Institute of Chemical Engineers</t>
+          <t xml:space="preserve">American Institute for Economic Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C40" s="66">
-        <v>82.15</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">American Kidney Fund, Inc.</t>
+          <t xml:space="preserve">American Institute of Chemical Engineers</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">5/12/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C41" s="66">
-        <v>95.70</v>
+        <v>82.15</v>
       </c>
     </row>
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">American Lebanese Syrian Associated Charities, Inc</t>
+          <t xml:space="preserve">American Kidney Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">5/12/2027</t>
         </is>
       </c>
       <c r="C42" s="66">
-        <v>75.96</v>
+        <v>95.70</v>
       </c>
     </row>
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
+          <t xml:space="preserve">American Lebanese Syrian Associated Charities, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C43" s="66">
-        <v>75.08</v>
+        <v>75.96</v>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">American Lung Association</t>
+          <t xml:space="preserve">American Leprosy Missions, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">5/26/2027</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C44" s="66">
-        <v>85.00</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">American Near East Refugee Aid, Inc</t>
+          <t xml:space="preserve">American Lung Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">5/26/2027</t>
         </is>
       </c>
       <c r="C45" s="66">
-        <v>95.44</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">Americans For Fair Treatment</t>
+          <t xml:space="preserve">American Near East Refugee Aid, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C46" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C46" s="66">
+        <v>95.44</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">Americares Foundation, Inc.</t>
+          <t xml:space="preserve">Americans For Fair Treatment</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
-        </is>
-      </c>
-      <c r="C47" s="66">
-        <v>98.06</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">Amnesty International of the USA, Inc.</t>
+          <t xml:space="preserve">Americares Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C48" s="66">
-        <v>71.00</v>
+        <v>98.06</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">Animals' Angels, Incorporated</t>
+          <t xml:space="preserve">Animals Asia Foundation US Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">9/12/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C49" s="66">
-        <v>77.41</v>
+        <v>62.30</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">Anti-Defamation League</t>
+          <t xml:space="preserve">Animals' Angels, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">9/12/2027</t>
         </is>
       </c>
       <c r="C50" s="66">
-        <v>75.00</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">Arkansas Tech University Foundation</t>
+          <t xml:space="preserve">Anti-Defamation League</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
@@ -962,33 +962,33 @@
         </is>
       </c>
       <c r="C51" s="66">
-        <v>94.06</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
+          <t xml:space="preserve">Arkansas Tech University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C52" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C52" s="66">
+        <v>94.06</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">Association of American Education Foundation</t>
+          <t xml:space="preserve">Armed Services YMCA of the U.S.A.</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C53" s="65">
@@ -998,97 +998,97 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Austin College</t>
+          <t xml:space="preserve">Association of American Education Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
-        </is>
-      </c>
-      <c r="C54" s="66">
-        <v>85.11</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C54" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
+          <t xml:space="preserve">Austin College</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">3/23/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C55" s="66">
-        <v>81.00</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">Autism Speaks, Inc.</t>
+          <t xml:space="preserve">Autism on the Seas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C56" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/23/2027</t>
+        </is>
+      </c>
+      <c r="C56" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
+          <t xml:space="preserve">Autism Speaks, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C57" s="66">
-        <v>44.00</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C57" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">B'nai B'rith International</t>
+          <t xml:space="preserve">Autism Spectrum Disorder Foundation, dba Autistic</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C58" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="66">
+        <v>44.00</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">Back Bay Mission, Inc.</t>
+          <t xml:space="preserve">B'nai B'rith International</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
-        </is>
-      </c>
-      <c r="C59" s="66">
-        <v>83.67</v>
+          <t xml:space="preserve">12/18/2026</t>
+        </is>
+      </c>
+      <c r="C59" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Base Ministry</t>
+          <t xml:space="preserve">Back Bay Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
@@ -1097,73 +1097,73 @@
         </is>
       </c>
       <c r="C60" s="66">
-        <v>71.89</v>
+        <v>83.67</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">Blessings International</t>
+          <t xml:space="preserve">Base Ministry</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">9/2/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C61" s="66">
-        <v>91.00</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Blood Cancer United, Inc.</t>
+          <t xml:space="preserve">Blessings International</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">9/2/2027</t>
         </is>
       </c>
       <c r="C62" s="66">
-        <v>75.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Bobby Jones Chiari &amp; Syringomyelia Foundation</t>
+          <t xml:space="preserve">Blood Cancer United, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C63" s="66">
-        <v>70.00</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">Brady Campaign to Prevent Gun Violence</t>
+          <t xml:space="preserve">Bobby Jones Chiari &amp; Syringomyelia Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C64" s="66">
-        <v>45.00</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
+          <t xml:space="preserve">Brady Campaign to Prevent Gun Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
@@ -1172,318 +1172,318 @@
         </is>
       </c>
       <c r="C65" s="66">
-        <v>71.00</v>
+        <v>45.00</v>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
+          <t xml:space="preserve">Brady Center to Prevent Gun Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C66" s="66">
-        <v>78.58</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">Business Action Fund</t>
+          <t xml:space="preserve">Buffalo Bill Memorial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C67" s="66">
-        <v>54.00</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">Cair-Foundation, Inc.</t>
+          <t xml:space="preserve">Business Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C68" s="66">
-        <v>66.00</v>
+        <v>54.00</v>
       </c>
     </row>
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">CAMFED USA Foundation</t>
+          <t xml:space="preserve">Cair-Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
+          <t xml:space="preserve">1/14/2027</t>
         </is>
       </c>
       <c r="C69" s="66">
-        <v>91.78</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Captain Joseph House Foundation</t>
+          <t xml:space="preserve">CAMFED USA Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C70" s="66">
-        <v>67.20</v>
+        <v>91.78</v>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">Carolina Tiger Rescue</t>
+          <t xml:space="preserve">Captain Joseph House Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">9/18/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C71" s="66">
-        <v>68.00</v>
+        <v>67.20</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
+          <t xml:space="preserve">Carolina Tiger Rescue</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">10/14/2026</t>
+          <t xml:space="preserve">9/18/2027</t>
         </is>
       </c>
       <c r="C72" s="66">
-        <v>97.00</v>
+        <v>68.00</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">Center for Community Change Action</t>
+          <t xml:space="preserve">Catholic Medical Mission Board, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">10/14/2027</t>
         </is>
       </c>
       <c r="C73" s="66">
-        <v>95.00</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">Central Asia Institute</t>
+          <t xml:space="preserve">Center for Community Change Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C74" s="66">
-        <v>77.29</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">CHADD, Inc. (Children &amp; Adults with Attention-Defi</t>
+          <t xml:space="preserve">Central Asia Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">6/30/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C75" s="66">
-        <v>77.80</v>
+        <v>77.29</v>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">Chapel Haven Schleifer Center, Inc.</t>
+          <t xml:space="preserve">CHADD, Inc. (Children &amp; Adults with Attention-Defi</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">6/30/2027</t>
         </is>
       </c>
       <c r="C76" s="66">
-        <v>81.41</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">Charities Aid Foundation America</t>
+          <t xml:space="preserve">Chapel Haven Schleifer Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C77" s="66">
-        <v>0.01</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">ChildFund International, USA</t>
+          <t xml:space="preserve">Charities Aid Foundation America</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C78" s="66">
-        <v>75.00</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">Childhelp, Inc.</t>
+          <t xml:space="preserve">ChildFund International, USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">6/30/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C79" s="66">
-        <v>70.00</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
+          <t xml:space="preserve">Childhelp, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">12/18/2026</t>
-        </is>
-      </c>
-      <c r="C80" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/30/2027</t>
+        </is>
+      </c>
+      <c r="C80" s="66">
+        <v>70.00</v>
       </c>
     </row>
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">Children's Miracle Network</t>
+          <t xml:space="preserve">Children's Leukemia Research Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C81" s="66">
-        <v>80.77</v>
+          <t xml:space="preserve">12/18/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
+          <t xml:space="preserve">Children's Miracle Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C82" s="66">
-        <v>89.98</v>
+        <v>80.77</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
+          <t xml:space="preserve">Choice Books of Northern Virginia, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C83" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/15/2027</t>
+        </is>
+      </c>
+      <c r="C83" s="66">
+        <v>91.41</v>
       </c>
     </row>
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
+          <t xml:space="preserve">Christian Advocates Serving Evangelism, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">9/10/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C84" s="66">
-        <v>96.00</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Christian Relief Services, Inc.</t>
+          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C85" s="66">
-        <v>90.70</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
+          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C86" s="65">
@@ -1493,162 +1493,162 @@
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Christian Union, Inc.</t>
+          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C87" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/10/2027</t>
+        </is>
+      </c>
+      <c r="C87" s="66">
+        <v>96.00</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Church World Service, Inc.</t>
+          <t xml:space="preserve">Christian Relief Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">8/25/2027</t>
+          <t xml:space="preserve">2/10/2027</t>
         </is>
       </c>
       <c r="C88" s="66">
-        <v>84.00</v>
+        <v>90.70</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">City Rescue Mission, Inc.</t>
+          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
-        </is>
-      </c>
-      <c r="C89" s="66">
-        <v>85.32</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C89" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">City Year, Inc.</t>
+          <t xml:space="preserve">Christian Union, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C90" s="66">
-        <v>82.62</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Civil Rights Corps</t>
+          <t xml:space="preserve">Church World Service, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/25/2027</t>
         </is>
       </c>
       <c r="C91" s="66">
-        <v>82.10</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
+          <t xml:space="preserve">City Rescue Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">11/20/2026</t>
-        </is>
-      </c>
-      <c r="C92" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C92" s="66">
+        <v>85.32</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
+          <t xml:space="preserve">City Year, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C93" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C93" s="66">
+        <v>82.62</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
+          <t xml:space="preserve">Civil Rights Corps</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C94" s="66">
-        <v>65.99</v>
+        <v>82.10</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Compassion and Choices</t>
+          <t xml:space="preserve">Colon Cancer Coalition</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C95" s="66">
-        <v>84.00</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Compassion and Choices Action Network</t>
+          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
-        </is>
-      </c>
-      <c r="C96" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">11/20/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Concerns of Police Survivors</t>
+          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C97" s="65">
@@ -1658,882 +1658,882 @@
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Consumer Reports, Inc.</t>
+          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">4/9/2027</t>
         </is>
       </c>
       <c r="C98" s="66">
-        <v>84.00</v>
+        <v>65.99</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
+          <t xml:space="preserve">Compassion and Choices</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">6/25/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C99" s="66">
-        <v>73.00</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
+          <t xml:space="preserve">Compassion and Choices Action Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C100" s="66">
-        <v>74.25</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Covenant House</t>
+          <t xml:space="preserve">Compassion In World Farming, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
-        </is>
-      </c>
-      <c r="C101" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">10/10/2027</t>
+        </is>
+      </c>
+      <c r="C101" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Covenant House New Orleans</t>
+          <t xml:space="preserve">Concerns of Police Survivors</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">7/28/2028</t>
+          <t xml:space="preserve">10/7/2027</t>
         </is>
       </c>
       <c r="C102" s="66">
-        <v>80.00</v>
+        <v>92.30</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
+          <t xml:space="preserve">Consumer Reports, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C103" s="66">
-        <v>84.38</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
+          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C104" s="66">
-        <v>85.18</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
+          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C105" s="66">
-        <v>64.30</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">D.A.R.E. America</t>
+          <t xml:space="preserve">Covenant House</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C106" s="66">
-        <v>44.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
+          <t xml:space="preserve">Covenant House New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C107" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/28/2028</t>
+        </is>
+      </c>
+      <c r="C107" s="66">
+        <v>80.00</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">Deep South Today</t>
+          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">12/4/2026</t>
         </is>
       </c>
       <c r="C108" s="66">
-        <v>74.56</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
+          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">6/6/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C109" s="66">
-        <v>68.82</v>
+        <v>85.18</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
+          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C110" s="66">
-        <v>49.00</v>
+        <v>64.30</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">DTCare</t>
+          <t xml:space="preserve">D.A.R.E. America</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C111" s="66">
-        <v>55.44</v>
+        <v>44.00</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
+          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
-        </is>
-      </c>
-      <c r="C112" s="66">
-        <v>61.48</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C112" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">Easter Seals, Inc.</t>
+          <t xml:space="preserve">Deep South Today</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C113" s="66">
-        <v>68.00</v>
+        <v>74.56</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">EB Research Partnership, Inc.</t>
+          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C114" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/6/2027</t>
+        </is>
+      </c>
+      <c r="C114" s="66">
+        <v>68.82</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">ELT Ventures</t>
+          <t xml:space="preserve">Disaster Recovery International Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C115" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/4/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="66">
+        <v>49.00</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">Empire State University Foundation</t>
+          <t xml:space="preserve">DTCare</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C116" s="66">
-        <v>82.78</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
+          <t xml:space="preserve">East Coast Assistance Dogs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C117" s="66">
-        <v>48.32</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">Environmental Defense Fund, Inc.</t>
+          <t xml:space="preserve">EB Research Partnership, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">9/25/2027</t>
-        </is>
-      </c>
-      <c r="C118" s="66">
-        <v>88.20</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C118" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
+          <t xml:space="preserve">ELT Ventures</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">3/6/2027</t>
-        </is>
-      </c>
-      <c r="C119" s="66">
-        <v>87.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C119" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">Fairplay, Inc.</t>
+          <t xml:space="preserve">Empire State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">6/25/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C120" s="66">
-        <v>83.42</v>
+        <v>82.78</v>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">Faith and Freedom Coalition, Inc.</t>
+          <t xml:space="preserve">Endowment Fund of the Phi Kappa Psi Fraternity</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C121" s="66">
-        <v>72.00</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">Family Policy Alliance</t>
+          <t xml:space="preserve">Environmental and Energy Study Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">10/7/2027</t>
         </is>
       </c>
       <c r="C122" s="66">
-        <v>80.48</v>
+        <v>65.49</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
+          <t xml:space="preserve">Environmental Defense Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C123" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/25/2027</t>
+        </is>
+      </c>
+      <c r="C123" s="66">
+        <v>88.20</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">Feed The Children, Inc.</t>
+          <t xml:space="preserve">Faces: The National Craniofacial Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
+          <t xml:space="preserve">3/6/2027</t>
         </is>
       </c>
       <c r="C124" s="66">
-        <v>91.00</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">Feeding Pets of the Homeless</t>
+          <t xml:space="preserve">Fairplay, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C125" s="66">
-        <v>75.17</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
+          <t xml:space="preserve">Faith and Freedom Coalition, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C126" s="66">
-        <v>82.48</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">FINCA International, Inc.</t>
+          <t xml:space="preserve">Family Policy Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">5/7/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C127" s="66">
-        <v>81.47</v>
+        <v>80.48</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">Find The Children</t>
+          <t xml:space="preserve">Farm Sanctuary, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
-        </is>
-      </c>
-      <c r="C128" s="66">
-        <v>50.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">Firefighters Charitable Foundation, Inc.</t>
+          <t xml:space="preserve">Feed The Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">9/23/2027</t>
+          <t xml:space="preserve">5/19/2027</t>
         </is>
       </c>
       <c r="C129" s="66">
-        <v>8.20</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">Food Bank of Northeast Louisiana, Inc.</t>
+          <t xml:space="preserve">Feeding America</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C130" s="66">
-        <v>99.00</v>
+          <t xml:space="preserve">10/1/2027</t>
+        </is>
+      </c>
+      <c r="C130" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
+          <t xml:space="preserve">Feeding Pets of the Homeless</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C131" s="66">
-        <v>89.30</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">For Others Collective, Inc.</t>
+          <t xml:space="preserve">Fellowship of Associates of Medical Evangelism</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C132" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/9/2027</t>
+        </is>
+      </c>
+      <c r="C132" s="66">
+        <v>82.48</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
+          <t xml:space="preserve">FINCA International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C133" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/7/2027</t>
+        </is>
+      </c>
+      <c r="C133" s="66">
+        <v>81.47</v>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">Fractracker Alliance</t>
+          <t xml:space="preserve">Find The Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C134" s="66">
-        <v>77.78</v>
+        <v>50.00</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
+          <t xml:space="preserve">Firefighters Charitable Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
+          <t xml:space="preserve">9/23/2027</t>
         </is>
       </c>
       <c r="C135" s="66">
-        <v>68.41</v>
+        <v>8.20</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
+          <t xml:space="preserve">Food Bank of Northeast Louisiana, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C136" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C136" s="66">
+        <v>99.00</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">Friends of KEXP</t>
+          <t xml:space="preserve">Food for  the  Poor,   Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C137" s="66">
-        <v>65.74</v>
+        <v>89.30</v>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">Friends of the Neuberger Museum of Art, Inc.</t>
+          <t xml:space="preserve">For Others Collective, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C138" s="66">
-        <v>66.80</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C138" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
+          <t xml:space="preserve">Foundation for Moral Law, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C139" s="66">
-        <v>75.34</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C139" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">Futures Without Violence</t>
+          <t xml:space="preserve">Fractracker Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C140" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C140" s="66">
+        <v>77.78</v>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">Girls Who Code, Inc.</t>
+          <t xml:space="preserve">Frances Clark Center for Keyboard Pedagogy</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">7/24/2027</t>
+          <t xml:space="preserve">7/1/2027</t>
         </is>
       </c>
       <c r="C141" s="66">
-        <v>73.24</v>
+        <v>68.41</v>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">Givinga Foundation</t>
+          <t xml:space="preserve">Friends of Katahdin Woods and Water</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">10/30/2026</t>
-        </is>
-      </c>
-      <c r="C142" s="66">
-        <v>94.03</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C142" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
+          <t xml:space="preserve">Friends of KEXP</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">3/11/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C143" s="66">
-        <v>49.91</v>
+        <v>65.74</v>
       </c>
     </row>
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">Go Campaign</t>
+          <t xml:space="preserve">Friends of the Neuberger Museum of Art, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C144" s="66">
-        <v>77.86</v>
+        <v>66.80</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">Goodwill Industries International, Inc</t>
+          <t xml:space="preserve">Froedtert Hospital Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C145" s="66">
-        <v>87.00</v>
+        <v>75.34</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">Green America</t>
+          <t xml:space="preserve">Futures Without Violence</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C146" s="66">
-        <v>87.47</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C146" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
+          <t xml:space="preserve">Girls Who Code, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">7/24/2027</t>
         </is>
       </c>
       <c r="C147" s="66">
-        <v>76.85</v>
+        <v>73.24</v>
       </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">Greenpeace, Inc.</t>
+          <t xml:space="preserve">Givinga Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">10/30/2026</t>
         </is>
       </c>
       <c r="C148" s="66">
-        <v>62.56</v>
+        <v>94.03</v>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">Gustavus Adolphus College</t>
+          <t xml:space="preserve">Global War on Terrorism Memorial Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">2/24/2027</t>
+          <t xml:space="preserve">3/11/2027</t>
         </is>
       </c>
       <c r="C149" s="66">
-        <v>93.00</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">Habitat for Horses, Inc.</t>
+          <t xml:space="preserve">Go Campaign</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C150" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/20/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="66">
+        <v>77.86</v>
       </c>
     </row>
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
+          <t xml:space="preserve">Goodwill Industries International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C151" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/9/2027</t>
+        </is>
+      </c>
+      <c r="C151" s="66">
+        <v>87.00</v>
       </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">Healing Justice Project</t>
+          <t xml:space="preserve">Green America</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C152" s="66">
-        <v>82.48</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">Healing Protectors</t>
+          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C153" s="66">
-        <v>47.19</v>
+        <v>76.85</v>
       </c>
     </row>
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">Heifer Project International</t>
+          <t xml:space="preserve">Greenpeace, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">3/19/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C154" s="66">
-        <v>72.90</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
+          <t xml:space="preserve">Gustavus Adolphus College</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C155" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/24/2027</t>
+        </is>
+      </c>
+      <c r="C155" s="66">
+        <v>93.00</v>
       </c>
     </row>
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">Herzog Tomorrow Foundation</t>
+          <t xml:space="preserve">Habitat for Horses, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">10/22/2026</t>
         </is>
       </c>
       <c r="C156" s="65">
@@ -2543,12 +2543,12 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">HIAS Foundation, Inc.</t>
+          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C157" s="65">
@@ -2558,132 +2558,132 @@
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
+          <t xml:space="preserve">Healing Justice Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C158" s="66">
-        <v>81.00</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">Home Builders Institute</t>
+          <t xml:space="preserve">Healing Protectors</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C159" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/2/2027</t>
+        </is>
+      </c>
+      <c r="C159" s="66">
+        <v>47.19</v>
       </c>
     </row>
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">Human Appeal, Inc.</t>
+          <t xml:space="preserve">Heifer Project International</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">1/12/2027</t>
+          <t xml:space="preserve">3/19/2027</t>
         </is>
       </c>
       <c r="C160" s="66">
-        <v>54.20</v>
+        <v>72.90</v>
       </c>
     </row>
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
+          <t xml:space="preserve">Help Me See, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C161" s="66">
-        <v>63.39</v>
+        <v>83.00</v>
       </c>
     </row>
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">Human Rights Watch, Inc.</t>
+          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C162" s="66">
-        <v>72.65</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">Human-I-T</t>
+          <t xml:space="preserve">Herzog Tomorrow Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">8/30/2027</t>
-        </is>
-      </c>
-      <c r="C163" s="66">
-        <v>1.00</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C163" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">Humane Society of Missouri</t>
+          <t xml:space="preserve">HIAS Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
-        </is>
-      </c>
-      <c r="C164" s="66">
-        <v>80.50</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C164" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">Illinois State University Foundation</t>
+          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">5/21/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C165" s="66">
-        <v>61.30</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
+          <t xml:space="preserve">Home Builders Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C166" s="65">
@@ -2693,192 +2693,192 @@
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">In Medias Res</t>
+          <t xml:space="preserve">Human Appeal, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C167" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/12/2027</t>
+        </is>
+      </c>
+      <c r="C167" s="66">
+        <v>54.20</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">Independent Council on Women's Sport</t>
+          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C168" s="66">
-        <v>94.44</v>
+        <v>63.39</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">Infact</t>
+          <t xml:space="preserve">Human Rights Watch, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C169" s="66">
-        <v>89.97</v>
+        <v>68.67</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
+          <t xml:space="preserve">Human-I-T</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C170" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/30/2027</t>
+        </is>
+      </c>
+      <c r="C170" s="66">
+        <v>1.00</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
+          <t xml:space="preserve">Humane Society of Missouri</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C171" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/7/2027</t>
+        </is>
+      </c>
+      <c r="C171" s="66">
+        <v>80.50</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">International Justice Mission</t>
+          <t xml:space="preserve">Illinois State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
-        </is>
-      </c>
-      <c r="C172" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/21/2027</t>
+        </is>
+      </c>
+      <c r="C172" s="66">
+        <v>61.30</v>
       </c>
     </row>
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
+          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C173" s="66">
-        <v>83.13</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C173" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">International Union of Police Associations</t>
+          <t xml:space="preserve">In Medias Res</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C174" s="66">
-        <v>47.90</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C174" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">Iona University</t>
+          <t xml:space="preserve">Independent Council on Women's Sport</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C175" s="66">
-        <v>89.81</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">Isaad Foundation</t>
+          <t xml:space="preserve">Infact</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">9/18/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C176" s="66">
-        <v>96.30</v>
+        <v>89.97</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
+          <t xml:space="preserve">INROADS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
+          <t xml:space="preserve">10/1/2027</t>
         </is>
       </c>
       <c r="C177" s="66">
-        <v>75.43</v>
+        <v>47.80</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">Jewish Democratic Council of America</t>
+          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C178" s="66">
-        <v>50.07</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">Jewish Voice Ministries International</t>
+          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C179" s="65">
@@ -2888,52 +2888,52 @@
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
+          <t xml:space="preserve">International Justice Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
-        </is>
-      </c>
-      <c r="C180" s="66">
-        <v>89.00</v>
+          <t xml:space="preserve">3/24/2027</t>
+        </is>
+      </c>
+      <c r="C180" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
+          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C181" s="66">
-        <v>75.00</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
+          <t xml:space="preserve">International Union of Police Associations</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">9/5/2027</t>
-        </is>
-      </c>
-      <c r="C182" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C182" s="66">
+        <v>47.90</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
+          <t xml:space="preserve">Iona University</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
@@ -2942,483 +2942,483 @@
         </is>
       </c>
       <c r="C183" s="66">
-        <v>98.28</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">Khan Academy, Inc.</t>
+          <t xml:space="preserve">Isaad Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">9/18/2027</t>
         </is>
       </c>
       <c r="C184" s="66">
-        <v>86.36</v>
+        <v>96.30</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
+          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C185" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/27/2027</t>
+        </is>
+      </c>
+      <c r="C185" s="66">
+        <v>75.43</v>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">L.E.A.D. Inc.</t>
+          <t xml:space="preserve">Jewish Democratic Council of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C186" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C186" s="66">
+        <v>50.07</v>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">La Leche League International, Inc.</t>
+          <t xml:space="preserve">Jewish Voice Ministries International</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
-        </is>
-      </c>
-      <c r="C187" s="66">
-        <v>57.00</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C187" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
+          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C188" s="66">
-        <v>63.00</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">Lasell University</t>
+          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C189" s="66">
-        <v>86.90</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
+          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
-        </is>
-      </c>
-      <c r="C190" s="66">
-        <v>10.60</v>
+          <t xml:space="preserve">9/5/2027</t>
+        </is>
+      </c>
+      <c r="C190" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">League of Conservation Voters, Inc.</t>
+          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">9/23/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C191" s="66">
-        <v>92.00</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
+          <t xml:space="preserve">Khan Academy, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">10/28/2026</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C192" s="66">
-        <v>96.80</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">Life Teen, Inc.</t>
+          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C193" s="66">
-        <v>76.40</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C193" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">Live Action</t>
+          <t xml:space="preserve">L.E.A.D. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C194" s="66">
-        <v>81.13</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C194" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">Living Waters for the World</t>
+          <t xml:space="preserve">La Leche League International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C195" s="66">
-        <v>78.81</v>
+        <v>57.00</v>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
+          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C196" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C196" s="66">
+        <v>63.00</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
+          <t xml:space="preserve">Lasell University</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C197" s="66">
-        <v>76.03</v>
+        <v>86.90</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
+          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C198" s="66">
-        <v>62.00</v>
+        <v>10.60</v>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">Madison House</t>
+          <t xml:space="preserve">League of Conservation Voters, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">9/23/2027</t>
         </is>
       </c>
       <c r="C199" s="66">
-        <v>77.79</v>
+        <v>92.00</v>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
+          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">8/6/2027</t>
+          <t xml:space="preserve">10/28/2026</t>
         </is>
       </c>
       <c r="C200" s="66">
-        <v>86.00</v>
+        <v>96.80</v>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">MAP International, Inc.</t>
+          <t xml:space="preserve">Life Teen, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C201" s="66">
-        <v>99.00</v>
+        <v>76.40</v>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">March of Dimes</t>
+          <t xml:space="preserve">Live Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">12/30/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C202" s="66">
-        <v>74.00</v>
+        <v>81.13</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">Marist University</t>
+          <t xml:space="preserve">Living Waters for the World</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C203" s="66">
-        <v>91.00</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
+          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
-        </is>
-      </c>
-      <c r="C204" s="66">
-        <v>91.74</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C204" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">Meals on Wheels America</t>
+          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">5/27/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C205" s="66">
-        <v>59.00</v>
+        <v>76.03</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
+          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">6/9/2027</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C206" s="66">
-        <v>80.94</v>
+        <v>62.00</v>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
+          <t xml:space="preserve">Madison House</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">12/8/2026</t>
-        </is>
-      </c>
-      <c r="C207" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C207" s="66">
+        <v>77.79</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
+          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">8/6/2027</t>
         </is>
       </c>
       <c r="C208" s="66">
-        <v>91.00</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">Mercatus Center, Inc.</t>
+          <t xml:space="preserve">MAP International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C209" s="66">
-        <v>90.25</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">Mercy for Animals, Inc.</t>
+          <t xml:space="preserve">March of Dimes</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">12/30/2026</t>
         </is>
       </c>
       <c r="C210" s="66">
-        <v>75.82</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">Mercy Hospital, Cedar Rapids, Iowa Endowment Found</t>
+          <t xml:space="preserve">Marist University</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C211" s="66">
-        <v>93.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">Mercy Ships</t>
+          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">8/26/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C212" s="66">
-        <v>78.18</v>
+        <v>91.74</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">Middle East Policy Network, Inc.</t>
+          <t xml:space="preserve">Meals on Wheels America</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">5/27/2027</t>
         </is>
       </c>
       <c r="C213" s="66">
-        <v>73.83</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
+          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">6/9/2027</t>
         </is>
       </c>
       <c r="C214" s="66">
-        <v>88.00</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">Minutes Matter-MCADD</t>
+          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">7/19/2027</t>
+          <t xml:space="preserve">12/8/2026</t>
         </is>
       </c>
       <c r="C215" s="65">
@@ -3428,342 +3428,342 @@
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">Miracle Flights</t>
+          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C216" s="66">
-        <v>52.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
+          <t xml:space="preserve">Mercatus Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C217" s="66">
-        <v>94.50</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">mothers2mothers United States, Inc.</t>
+          <t xml:space="preserve">Mercy for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C218" s="66">
-        <v>60.00</v>
+        <v>75.82</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">Mount Saint Marys University</t>
+          <t xml:space="preserve">Mercy Hospital, Cedar Rapids, Iowa Endowment Found</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C219" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C219" s="66">
+        <v>93.00</v>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">Mountain States Legal Foundation</t>
+          <t xml:space="preserve">Mercy Ships</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/26/2027</t>
         </is>
       </c>
       <c r="C220" s="66">
-        <v>69.99</v>
+        <v>78.18</v>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">MrCharity, Inc.</t>
+          <t xml:space="preserve">Middle East Policy Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
-        </is>
-      </c>
-      <c r="C221" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/16/2027</t>
+        </is>
+      </c>
+      <c r="C221" s="66">
+        <v>73.83</v>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
+          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C222" s="66">
-        <v>54.00</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
+          <t xml:space="preserve">Minutes Matter-MCADD</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
-        </is>
-      </c>
-      <c r="C223" s="66">
-        <v>77.80</v>
+          <t xml:space="preserve">7/19/2027</t>
+        </is>
+      </c>
+      <c r="C223" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
+          <t xml:space="preserve">Miracle Flights</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">12/19/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C224" s="66">
-        <v>66.90</v>
+        <v>52.00</v>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">Naropa University</t>
+          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C225" s="66">
-        <v>76.21</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
+          <t xml:space="preserve">mothers2mothers United States, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">4/27/2027</t>
         </is>
       </c>
       <c r="C226" s="66">
-        <v>65.00</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">National Audubon Society, Inc.</t>
+          <t xml:space="preserve">Mount Saint Marys University</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C227" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C227" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
+          <t xml:space="preserve">Mountain States Legal Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C228" s="66">
-        <v>81.00</v>
+        <v>69.99</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
+          <t xml:space="preserve">MrCharity, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
-        </is>
-      </c>
-      <c r="C229" s="66">
-        <v>92.28</v>
+          <t xml:space="preserve">2/23/2027</t>
+        </is>
+      </c>
+      <c r="C229" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">National Council of Nonprofits</t>
+          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C230" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/20/2026</t>
+        </is>
+      </c>
+      <c r="C230" s="66">
+        <v>54.00</v>
       </c>
     </row>
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
+          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">6/24/2027</t>
         </is>
       </c>
       <c r="C231" s="66">
-        <v>49.00</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">National Foundation for Cancer Research</t>
+          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C232" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/19/2026</t>
+        </is>
+      </c>
+      <c r="C232" s="66">
+        <v>66.90</v>
       </c>
     </row>
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">National Geographic Society</t>
+          <t xml:space="preserve">Naropa University</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">3/18/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C233" s="66">
-        <v>77.00</v>
+        <v>76.21</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">National LGBTQ Task Force</t>
+          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C234" s="66">
-        <v>80.00</v>
+        <v>65.00</v>
       </c>
     </row>
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">National Network of Abortion Funds</t>
+          <t xml:space="preserve">National Audubon Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
-        </is>
-      </c>
-      <c r="C235" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C235" s="66">
+        <v>80.00</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">National Park Foundation</t>
+          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C236" s="66">
-        <v>72.00</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">National PKU Alliance, Inc.</t>
+          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C237" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/7/2027</t>
+        </is>
+      </c>
+      <c r="C237" s="66">
+        <v>92.28</v>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
+          <t xml:space="preserve">National Council of Nonprofits</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C238" s="65">
@@ -3773,27 +3773,27 @@
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
+          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C239" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C239" s="66">
+        <v>49.00</v>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">National Space Society</t>
+          <t xml:space="preserve">National Foundation for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">12/1/2026</t>
         </is>
       </c>
       <c r="C240" s="65">
@@ -3803,117 +3803,117 @@
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">National University</t>
+          <t xml:space="preserve">National Geographic Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">3/18/2027</t>
         </is>
       </c>
       <c r="C241" s="66">
-        <v>42.69</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">National Veterans Memorial and Museum</t>
+          <t xml:space="preserve">National LGBTQ Task Force</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C242" s="66">
-        <v>72.63</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">National Wheelchair Basketball Association</t>
+          <t xml:space="preserve">National Network of Abortion Funds</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
-        </is>
-      </c>
-      <c r="C243" s="66">
-        <v>77.80</v>
+          <t xml:space="preserve">9/11/2027</t>
+        </is>
+      </c>
+      <c r="C243" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">National Wildlife Federation</t>
+          <t xml:space="preserve">National Park Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C244" s="66">
-        <v>86.00</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
+          <t xml:space="preserve">National PKU Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
-        </is>
-      </c>
-      <c r="C245" s="66">
-        <v>1.60</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C245" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">Network for Good, Inc</t>
+          <t xml:space="preserve">National Rifle Association of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/1/2027</t>
         </is>
       </c>
       <c r="C246" s="66">
-        <v>97.80</v>
+        <v>62.91</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">New Harvest, Inc.</t>
+          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C247" s="66">
-        <v>88.49</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C247" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
+          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">1/9/2027</t>
         </is>
       </c>
       <c r="C248" s="65">
@@ -3923,7 +3923,7 @@
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">Nurse-Family Partnership</t>
+          <t xml:space="preserve">National Space Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
@@ -3938,162 +3938,162 @@
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">Ocean Conservancy</t>
+          <t xml:space="preserve">National University</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C250" s="66">
-        <v>74.06</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
+          <t xml:space="preserve">National Veterans Memorial and Museum</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C251" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C251" s="66">
+        <v>72.63</v>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">Operation Smile, Inc.</t>
+          <t xml:space="preserve">National Wheelchair Basketball Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C252" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/12/2027</t>
+        </is>
+      </c>
+      <c r="C252" s="66">
+        <v>77.80</v>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
+          <t xml:space="preserve">National Wildlife Federation</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">8/18/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C253" s="66">
-        <v>77.59</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">Our Change Foundation</t>
+          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C254" s="66">
-        <v>80.46</v>
+        <v>1.60</v>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">Pace University</t>
+          <t xml:space="preserve">Network for Good, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C255" s="66">
-        <v>88.30</v>
+        <v>97.80</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
+          <t xml:space="preserve">New Harvest, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C256" s="66">
-        <v>55.43</v>
+        <v>88.49</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">Panorama Global</t>
+          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
-        </is>
-      </c>
-      <c r="C257" s="66">
-        <v>84.52</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C257" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">Paralyzed Veterans of America</t>
+          <t xml:space="preserve">Nurse-Family Partnership</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
-        </is>
-      </c>
-      <c r="C258" s="66">
-        <v>59.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C258" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
+          <t xml:space="preserve">Ocean Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">2/9/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C259" s="66">
-        <v>90.00</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
+          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C260" s="65">
@@ -4103,132 +4103,132 @@
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">Pathfinder International</t>
+          <t xml:space="preserve">Operation Smile, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
-        </is>
-      </c>
-      <c r="C261" s="66">
-        <v>85.33</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C261" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">patriotic Hearts, Inc.</t>
+          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">8/18/2027</t>
         </is>
       </c>
       <c r="C262" s="66">
-        <v>56.00</v>
+        <v>77.59</v>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">People for the American Way Foundation</t>
+          <t xml:space="preserve">Our Change Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">10/13/2027</t>
         </is>
       </c>
       <c r="C263" s="66">
-        <v>60.00</v>
+        <v>71.30</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
+          <t xml:space="preserve">Pace University</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">7/1/2027</t>
         </is>
       </c>
       <c r="C264" s="66">
-        <v>83.76</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
+          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C265" s="66">
-        <v>58.00</v>
+        <v>55.43</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
+          <t xml:space="preserve">Panorama Global</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">8/28/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C266" s="66">
-        <v>79.00</v>
+        <v>84.52</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
+          <t xml:space="preserve">Paralyzed Veterans of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C267" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/16/2027</t>
+        </is>
+      </c>
+      <c r="C267" s="66">
+        <v>59.00</v>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
+          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C268" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/9/2027</t>
+        </is>
+      </c>
+      <c r="C268" s="66">
+        <v>90.00</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
+          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C269" s="65">
@@ -4238,102 +4238,102 @@
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">Pledgeling Foundation</t>
+          <t xml:space="preserve">Pathfinder International</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C270" s="66">
-        <v>65.93</v>
+        <v>85.33</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">Polar Bears International</t>
+          <t xml:space="preserve">patriotic Hearts, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">2/2/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C271" s="66">
-        <v>86.00</v>
+        <v>56.00</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
+          <t xml:space="preserve">People for the American Way Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C272" s="66">
-        <v>85.54</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">Pratt Institute</t>
+          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C273" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C273" s="66">
+        <v>83.76</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">Primo Cares, Inc.</t>
+          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C274" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/12/2027</t>
+        </is>
+      </c>
+      <c r="C274" s="66">
+        <v>58.00</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries</t>
+          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">8/28/2027</t>
         </is>
       </c>
       <c r="C275" s="66">
-        <v>68.60</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
+          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">11/3/2026</t>
         </is>
       </c>
       <c r="C276" s="65">
@@ -4343,102 +4343,102 @@
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">Project Cure, Inc.</t>
+          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
-        </is>
-      </c>
-      <c r="C277" s="66">
-        <v>27.00</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C277" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
+          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C278" s="66">
-        <v>88.71</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C278" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">Proteus Fund, Inc.</t>
+          <t xml:space="preserve">Pledgeling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C279" s="66">
-        <v>81.25</v>
+        <v>65.93</v>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">Providence House</t>
+          <t xml:space="preserve">Polar Bears International</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">2/2/2027</t>
         </is>
       </c>
       <c r="C280" s="66">
-        <v>92.06</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">Public Health Foundation Enterprise, Inc</t>
+          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">3/27/2027</t>
         </is>
       </c>
       <c r="C281" s="66">
-        <v>94.97</v>
+        <v>85.54</v>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
+          <t xml:space="preserve">Pratt Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C282" s="66">
-        <v>84.22</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C282" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">Re:Power</t>
+          <t xml:space="preserve">Primo Cares, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C283" s="65">
@@ -4448,177 +4448,177 @@
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">Reproductive Freedom for All</t>
+          <t xml:space="preserve">Prison Fellowship Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C284" s="66">
-        <v>70.00</v>
+        <v>68.60</v>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">RezilientKidz</t>
+          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C285" s="66">
-        <v>94.35</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C285" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">Rodale Institute</t>
+          <t xml:space="preserve">Project Cure, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C286" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C286" s="66">
+        <v>27.00</v>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
+          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">12/12/2026</t>
-        </is>
-      </c>
-      <c r="C287" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C287" s="66">
+        <v>88.71</v>
       </c>
     </row>
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
+          <t xml:space="preserve">Proteus Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C288" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/2/2027</t>
+        </is>
+      </c>
+      <c r="C288" s="66">
+        <v>81.25</v>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">Rush University Medical Center</t>
+          <t xml:space="preserve">Providence House</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C289" s="66">
-        <v>91.41</v>
+        <v>92.06</v>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">Rutgers University Foundation</t>
+          <t xml:space="preserve">Public Health Foundation Enterprise, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C290" s="66">
-        <v>87.46</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">Sagamore Institute, Inc.</t>
+          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C291" s="66">
-        <v>91.61</v>
+        <v>84.22</v>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">Saint John's University</t>
+          <t xml:space="preserve">Re:Power</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
-        </is>
-      </c>
-      <c r="C292" s="66">
-        <v>88.76</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C292" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="293">
       <c t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">Save the Chimps, Inc.</t>
+          <t xml:space="preserve">Reproductive Freedom for All</t>
         </is>
       </c>
       <c t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C293" s="66">
-        <v>79.70</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="294">
       <c t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">Seattle Pacific University</t>
+          <t xml:space="preserve">RezilientKidz</t>
         </is>
       </c>
       <c t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C294" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C294" s="66">
+        <v>94.35</v>
       </c>
     </row>
     <row r="295">
       <c t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">Second Harvest Food Bank of Greater New Orleans</t>
+          <t xml:space="preserve">Rodale Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
+          <t xml:space="preserve">11/18/2026</t>
         </is>
       </c>
       <c r="C295" s="65">
@@ -4628,327 +4628,327 @@
     <row r="296">
       <c t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
+          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
         </is>
       </c>
       <c t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
-        </is>
-      </c>
-      <c r="C296" s="66">
-        <v>94.00</v>
+          <t xml:space="preserve">12/12/2026</t>
+        </is>
+      </c>
+      <c r="C296" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">Share Our Strength</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
         </is>
       </c>
       <c t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
-        </is>
-      </c>
-      <c r="C297" s="66">
-        <v>58.73</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C297" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
+          <t xml:space="preserve">Rush University Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C298" s="66">
-        <v>97.29</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">Sierra  Club</t>
+          <t xml:space="preserve">Rutgers University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">12/22/2026</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C299" s="66">
-        <v>82.00</v>
+        <v>87.46</v>
       </c>
     </row>
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">Sister Rising Worldwide</t>
+          <t xml:space="preserve">Sagamore Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">1/28/2027</t>
-        </is>
-      </c>
-      <c r="C300" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C300" s="66">
+        <v>91.61</v>
       </c>
     </row>
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">Sixpoint, Inc.</t>
+          <t xml:space="preserve">Saint John's University</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C301" s="66">
-        <v>77.16</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
+          <t xml:space="preserve">Save the Chimps, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">4/22/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C302" s="66">
-        <v>90.00</v>
+        <v>79.70</v>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">Social Purpose Corrections</t>
+          <t xml:space="preserve">Seattle Pacific University</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C303" s="66">
-        <v>12.95</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C303" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
+          <t xml:space="preserve">Second Harvest Food Bank of Greater New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">9/2/2027</t>
-        </is>
-      </c>
-      <c r="C304" s="66">
-        <v>72.80</v>
+          <t xml:space="preserve">5/20/2027</t>
+        </is>
+      </c>
+      <c r="C304" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">Society for the Preservation and Encouragement</t>
+          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
-        </is>
-      </c>
-      <c r="C305" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C305" s="66">
+        <v>94.00</v>
       </c>
     </row>
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
+          <t xml:space="preserve">Seti Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">7/29/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C306" s="66">
-        <v>86.00</v>
+        <v>69.60</v>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">South Dakota State University Foundation</t>
+          <t xml:space="preserve">Share Our Strength</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C307" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C307" s="66">
+        <v>58.73</v>
       </c>
     </row>
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
+          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C308" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C308" s="66">
+        <v>97.29</v>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">Special Olympics, Inc.</t>
+          <t xml:space="preserve">Sierra  Club</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C309" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/22/2026</t>
+        </is>
+      </c>
+      <c r="C309" s="66">
+        <v>82.00</v>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">SPLC Action Fund</t>
+          <t xml:space="preserve">Sister Rising Worldwide</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">9/17/2027</t>
-        </is>
-      </c>
-      <c r="C310" s="66">
-        <v>72.81</v>
+          <t xml:space="preserve">1/28/2027</t>
+        </is>
+      </c>
+      <c r="C310" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
+          <t xml:space="preserve">Sixpoint, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C311" s="66">
-        <v>85.31</v>
+        <v>77.16</v>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">State University of Iowa Foundation</t>
+          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">9/4/2027</t>
+          <t xml:space="preserve">4/22/2027</t>
         </is>
       </c>
       <c r="C312" s="66">
-        <v>79.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
+          <t xml:space="preserve">Social Purpose Corrections</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C313" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/12/2027</t>
+        </is>
+      </c>
+      <c r="C313" s="66">
+        <v>47.93</v>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
+          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
+          <t xml:space="preserve">9/2/2027</t>
         </is>
       </c>
       <c r="C314" s="66">
-        <v>92.00</v>
+        <v>72.80</v>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">Students for Life Action, Inc.</t>
+          <t xml:space="preserve">Soldiers' Angels</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">11/7/2026</t>
-        </is>
-      </c>
-      <c r="C315" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C315" s="66">
+        <v>93.33</v>
       </c>
     </row>
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
+          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">8/12/2027</t>
+          <t xml:space="preserve">7/29/2027</t>
         </is>
       </c>
       <c r="C316" s="66">
-        <v>89.29</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">Teacher Freedom Alliance</t>
+          <t xml:space="preserve">South Dakota State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C317" s="65">
@@ -4958,87 +4958,87 @@
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">The Actors' Fund of America</t>
+          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
-        </is>
-      </c>
-      <c r="C318" s="66">
-        <v>86.73</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C318" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Special Olympics, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
-        </is>
-      </c>
-      <c r="C319" s="66">
-        <v>39.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C319" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">The American Society for the Prevention of Cruelty</t>
+          <t xml:space="preserve">SPLC Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">9/17/2027</t>
         </is>
       </c>
       <c r="C320" s="66">
-        <v>75.00</v>
+        <v>72.81</v>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">The American University</t>
+          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C321" s="66">
-        <v>90.23</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+          <t xml:space="preserve">State University of Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C322" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/4/2027</t>
+        </is>
+      </c>
+      <c r="C322" s="66">
+        <v>79.00</v>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">The Anthony Davis Foundation</t>
+          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">11/24/2026</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C323" s="65">
@@ -5048,112 +5048,112 @@
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
+          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">10/24/2026</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C324" s="66">
-        <v>90.00</v>
+        <v>92.00</v>
       </c>
     </row>
     <row r="325">
       <c t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">The Barack Obama Foundation</t>
+          <t xml:space="preserve">Students for Life Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C325" s="66">
-        <v>55.90</v>
+          <t xml:space="preserve">11/7/2026</t>
+        </is>
+      </c>
+      <c r="C325" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="326">
       <c t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">The Baruch College Fund</t>
+          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">8/12/2027</t>
         </is>
       </c>
       <c r="C326" s="66">
-        <v>84.00</v>
+        <v>89.29</v>
       </c>
     </row>
     <row r="327">
       <c t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">The Call of Duty Endowment</t>
+          <t xml:space="preserve">Teacher Freedom Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
-        </is>
-      </c>
-      <c r="C327" s="66">
-        <v>73.00</v>
+          <t xml:space="preserve">6/24/2027</t>
+        </is>
+      </c>
+      <c r="C327" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="328">
       <c t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">The Center for Alcohol Policy</t>
+          <t xml:space="preserve">The Actors' Fund of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">12/10/2026</t>
         </is>
       </c>
       <c r="C328" s="66">
-        <v>73.40</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="329">
       <c t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">The Center for Investigative Reporting</t>
+          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C329" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/15/2027</t>
+        </is>
+      </c>
+      <c r="C329" s="66">
+        <v>39.00</v>
       </c>
     </row>
     <row r="330">
       <c t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
+          <t xml:space="preserve">The American Society for the Prevention of Cruelty</t>
         </is>
       </c>
       <c t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C330" s="66">
-        <v>71.00</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="331">
       <c t="inlineStr" r="A331">
         <is>
-          <t xml:space="preserve">The Center for Victims of Torture</t>
+          <t xml:space="preserve">The American University</t>
         </is>
       </c>
       <c t="inlineStr" r="B331">
@@ -5162,603 +5162,603 @@
         </is>
       </c>
       <c r="C331" s="66">
-        <v>74.00</v>
+        <v>90.23</v>
       </c>
     </row>
     <row r="332">
       <c t="inlineStr" r="A332">
         <is>
-          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
+          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B332">
         <is>
-          <t xml:space="preserve">7/6/2027</t>
-        </is>
-      </c>
-      <c r="C332" s="66">
-        <v>71.00</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C332" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c t="inlineStr" r="A333">
         <is>
-          <t xml:space="preserve">The Colorado College</t>
+          <t xml:space="preserve">The Anthony Davis Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B333">
         <is>
-          <t xml:space="preserve">10/29/2027</t>
-        </is>
-      </c>
-      <c r="C333" s="66">
-        <v>90.00</v>
+          <t xml:space="preserve">11/24/2026</t>
+        </is>
+      </c>
+      <c r="C333" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="334">
       <c t="inlineStr" r="A334">
         <is>
-          <t xml:space="preserve">The Denver Rescue Mission</t>
+          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B334">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">10/24/2026</t>
         </is>
       </c>
       <c r="C334" s="66">
-        <v>82.96</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="335">
       <c t="inlineStr" r="A335">
         <is>
-          <t xml:space="preserve">The Edison Institute</t>
+          <t xml:space="preserve">The Barack Obama Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B335">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C335" s="66">
-        <v>78.00</v>
+        <v>55.90</v>
       </c>
     </row>
     <row r="336">
       <c t="inlineStr" r="A336">
         <is>
-          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+          <t xml:space="preserve">The Baruch College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B336">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C336" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C336" s="66">
+        <v>84.00</v>
       </c>
     </row>
     <row r="337">
       <c t="inlineStr" r="A337">
         <is>
-          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+          <t xml:space="preserve">The Call of Duty Endowment</t>
         </is>
       </c>
       <c t="inlineStr" r="B337">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C337" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C337" s="66">
+        <v>73.00</v>
       </c>
     </row>
     <row r="338">
       <c t="inlineStr" r="A338">
         <is>
-          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
+          <t xml:space="preserve">The Center for Alcohol Policy</t>
         </is>
       </c>
       <c t="inlineStr" r="B338">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C338" s="66">
-        <v>76.48</v>
+        <v>73.40</v>
       </c>
     </row>
     <row r="339">
       <c t="inlineStr" r="A339">
         <is>
-          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
+          <t xml:space="preserve">The Center for Investigative Reporting</t>
         </is>
       </c>
       <c t="inlineStr" r="B339">
         <is>
-          <t xml:space="preserve">5/15/2027</t>
-        </is>
-      </c>
-      <c r="C339" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C339" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="340">
       <c t="inlineStr" r="A340">
         <is>
-          <t xml:space="preserve">The Heritage Foundation</t>
+          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B340">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C340" s="66">
-        <v>83.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="341">
       <c t="inlineStr" r="A341">
         <is>
-          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
+          <t xml:space="preserve">The Center for Victims of Torture</t>
         </is>
       </c>
       <c t="inlineStr" r="B341">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C341" s="66">
-        <v>89.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="342">
       <c t="inlineStr" r="A342">
         <is>
-          <t xml:space="preserve">The Independent Institute</t>
+          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
         </is>
       </c>
       <c t="inlineStr" r="B342">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">7/6/2027</t>
         </is>
       </c>
       <c r="C342" s="66">
-        <v>77.51</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="343">
       <c t="inlineStr" r="A343">
         <is>
-          <t xml:space="preserve">The International Wildlife Rehab. Council</t>
+          <t xml:space="preserve">The Colorado College</t>
         </is>
       </c>
       <c t="inlineStr" r="B343">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">10/29/2027</t>
         </is>
       </c>
       <c r="C343" s="66">
-        <v>81.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="344">
       <c t="inlineStr" r="A344">
         <is>
-          <t xml:space="preserve">The Jane Goodall Institute for Wildlife Research</t>
+          <t xml:space="preserve">The Denver Rescue Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B344">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
-        </is>
-      </c>
-      <c r="C344" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/20/2027</t>
+        </is>
+      </c>
+      <c r="C344" s="66">
+        <v>82.96</v>
       </c>
     </row>
     <row r="345">
       <c t="inlineStr" r="A345">
         <is>
-          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
+          <t xml:space="preserve">The Edison Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B345">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C345" s="66">
-        <v>84.00</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="346">
       <c t="inlineStr" r="A346">
         <is>
-          <t xml:space="preserve">The Just Trust for Education</t>
+          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B346">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
-        </is>
-      </c>
-      <c r="C346" s="66">
-        <v>85.13</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C346" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="347">
       <c t="inlineStr" r="A347">
         <is>
-          <t xml:space="preserve">The Kansas University Endowment Association</t>
+          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
         </is>
       </c>
       <c t="inlineStr" r="B347">
         <is>
-          <t xml:space="preserve">7/21/2027</t>
-        </is>
-      </c>
-      <c r="C347" s="66">
-        <v>91.34</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C347" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="348">
       <c t="inlineStr" r="A348">
         <is>
-          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
         </is>
       </c>
       <c t="inlineStr" r="B348">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C348" s="66">
-        <v>83.06</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="349">
       <c t="inlineStr" r="A349">
         <is>
-          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
+          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B349">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">5/15/2027</t>
         </is>
       </c>
       <c r="C349" s="66">
-        <v>91.99</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="350">
       <c t="inlineStr" r="A350">
         <is>
-          <t xml:space="preserve">The Memorial Foundation</t>
+          <t xml:space="preserve">The Heritage Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B350">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C350" s="66">
-        <v>72.00</v>
+        <v>83.00</v>
       </c>
     </row>
     <row r="351">
       <c t="inlineStr" r="A351">
         <is>
-          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B351">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C351" s="66">
-        <v>74.58</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="352">
       <c t="inlineStr" r="A352">
         <is>
-          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
+          <t xml:space="preserve">The Independent Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B352">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C352" s="66">
-        <v>60.00</v>
+        <v>77.51</v>
       </c>
     </row>
     <row r="353">
       <c t="inlineStr" r="A353">
         <is>
-          <t xml:space="preserve">The National World War II Museum, Inc.</t>
+          <t xml:space="preserve">The International Wildlife Rehab. Council</t>
         </is>
       </c>
       <c t="inlineStr" r="B353">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C353" s="66">
-        <v>80.00</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="354">
       <c t="inlineStr" r="A354">
         <is>
-          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+          <t xml:space="preserve">The Jane Goodall Institute for Wildlife Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B354">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C354" s="66">
-        <v>80.64</v>
+          <t xml:space="preserve">5/19/2027</t>
+        </is>
+      </c>
+      <c r="C354" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="355">
       <c t="inlineStr" r="A355">
         <is>
-          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
+          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B355">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C355" s="66">
-        <v>87.40</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="356">
       <c t="inlineStr" r="A356">
         <is>
-          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
+          <t xml:space="preserve">The Just Trust for Education</t>
         </is>
       </c>
       <c t="inlineStr" r="B356">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C356" s="66">
-        <v>60.00</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="357">
       <c t="inlineStr" r="A357">
         <is>
-          <t xml:space="preserve">The Ohio University Foundation</t>
+          <t xml:space="preserve">The Kansas University Endowment Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B357">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">7/21/2027</t>
         </is>
       </c>
       <c r="C357" s="66">
-        <v>74.14</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="358">
       <c t="inlineStr" r="A358">
         <is>
-          <t xml:space="preserve">The OneStar Foundation</t>
+          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B358">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C358" s="66">
-        <v>62.50</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="359">
       <c t="inlineStr" r="A359">
         <is>
-          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B359">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C359" s="66">
-        <v>88.30</v>
+        <v>91.99</v>
       </c>
     </row>
     <row r="360">
       <c t="inlineStr" r="A360">
         <is>
-          <t xml:space="preserve">The Planetary Society</t>
+          <t xml:space="preserve">The Memorial Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B360">
         <is>
-          <t xml:space="preserve">7/14/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C360" s="66">
-        <v>66.00</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="361">
       <c t="inlineStr" r="A361">
         <is>
-          <t xml:space="preserve">The Principia Corporation</t>
+          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B361">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
-        </is>
-      </c>
-      <c r="C361" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/27/2027</t>
+        </is>
+      </c>
+      <c r="C361" s="66">
+        <v>74.58</v>
       </c>
     </row>
     <row r="362">
       <c t="inlineStr" r="A362">
         <is>
-          <t xml:space="preserve">The Purchase College Foundation</t>
+          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B362">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C362" s="66">
-        <v>78.12</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="363">
       <c t="inlineStr" r="A363">
         <is>
-          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
+          <t xml:space="preserve">The National World War II Museum, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B363">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C363" s="66">
-        <v>81.26</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="364">
       <c t="inlineStr" r="A364">
         <is>
-          <t xml:space="preserve">The Ruth Collective</t>
+          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
         </is>
       </c>
       <c t="inlineStr" r="B364">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C364" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C364" s="66">
+        <v>80.64</v>
       </c>
     </row>
     <row r="365">
       <c t="inlineStr" r="A365">
         <is>
-          <t xml:space="preserve">The Society of the Cincinnati</t>
+          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
         </is>
       </c>
       <c t="inlineStr" r="B365">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C365" s="66">
-        <v>73.00</v>
+        <v>87.40</v>
       </c>
     </row>
     <row r="366">
       <c t="inlineStr" r="A366">
         <is>
-          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B366">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">8/24/2027</t>
         </is>
       </c>
       <c r="C366" s="66">
-        <v>94.00</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="367">
       <c t="inlineStr" r="A367">
         <is>
-          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+          <t xml:space="preserve">The Ohio University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B367">
         <is>
-          <t xml:space="preserve">4/13/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C367" s="66">
-        <v>82.20</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="368">
       <c t="inlineStr" r="A368">
         <is>
-          <t xml:space="preserve">The University of Montana Foundation</t>
+          <t xml:space="preserve">The OneStar Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B368">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">1/14/2027</t>
         </is>
       </c>
       <c r="C368" s="66">
-        <v>79.00</v>
+        <v>62.50</v>
       </c>
     </row>
     <row r="369">
       <c t="inlineStr" r="A369">
         <is>
-          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
+          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B369">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C369" s="66">
-        <v>76.00</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="370">
       <c t="inlineStr" r="A370">
         <is>
-          <t xml:space="preserve">The Visiting Angels Foundation</t>
+          <t xml:space="preserve">The Planetary Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B370">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">7/14/2027</t>
         </is>
       </c>
       <c r="C370" s="66">
-        <v>94.00</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="371">
       <c t="inlineStr" r="A371">
         <is>
-          <t xml:space="preserve">The Wawa Foundation, Inc.</t>
+          <t xml:space="preserve">The Principia Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B371">
         <is>
-          <t xml:space="preserve">10/15/2026</t>
+          <t xml:space="preserve">5/19/2027</t>
         </is>
       </c>
       <c r="C371" s="65">
@@ -5768,252 +5768,252 @@
     <row r="372">
       <c t="inlineStr" r="A372">
         <is>
-          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+          <t xml:space="preserve">The Purchase College Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B372">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C372" s="66">
-        <v>79.51</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="373">
       <c t="inlineStr" r="A373">
         <is>
-          <t xml:space="preserve">The Wilderness Society</t>
+          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
         </is>
       </c>
       <c t="inlineStr" r="B373">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C373" s="66">
-        <v>73.00</v>
+        <v>81.26</v>
       </c>
     </row>
     <row r="374">
       <c t="inlineStr" r="A374">
         <is>
-          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
+          <t xml:space="preserve">The Ruth Collective</t>
         </is>
       </c>
       <c t="inlineStr" r="B374">
         <is>
-          <t xml:space="preserve">4/21/2027</t>
-        </is>
-      </c>
-      <c r="C374" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C374" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="375">
       <c t="inlineStr" r="A375">
         <is>
-          <t xml:space="preserve">Together Making Changes</t>
+          <t xml:space="preserve">The Society of the Cincinnati</t>
         </is>
       </c>
       <c t="inlineStr" r="B375">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C375" s="66">
-        <v>90.26</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="376">
       <c t="inlineStr" r="A376">
         <is>
-          <t xml:space="preserve">Trevecca Nazarene University</t>
+          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
         </is>
       </c>
       <c t="inlineStr" r="B376">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C376" s="66">
-        <v>87.82</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="377">
       <c t="inlineStr" r="A377">
         <is>
-          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
+          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B377">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">4/13/2027</t>
         </is>
       </c>
       <c r="C377" s="66">
-        <v>94.50</v>
+        <v>82.20</v>
       </c>
     </row>
     <row r="378">
       <c t="inlineStr" r="A378">
         <is>
-          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+          <t xml:space="preserve">The University of Montana Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B378">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C378" s="66">
-        <v>89.90</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="379">
       <c t="inlineStr" r="A379">
         <is>
-          <t xml:space="preserve">Trustees of Tufts College</t>
+          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B379">
         <is>
-          <t xml:space="preserve">7/2/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C379" s="66">
-        <v>85.00</v>
+        <v>76.00</v>
       </c>
     </row>
     <row r="380">
       <c t="inlineStr" r="A380">
         <is>
-          <t xml:space="preserve">Turning Point USA, Inc.</t>
+          <t xml:space="preserve">The Visiting Angels Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B380">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C380" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/20/2027</t>
+        </is>
+      </c>
+      <c r="C380" s="66">
+        <v>94.00</v>
       </c>
     </row>
     <row r="381">
       <c t="inlineStr" r="A381">
         <is>
-          <t xml:space="preserve">Twelveacres, Incorporated</t>
+          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B381">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C381" s="66">
-        <v>79.93</v>
+        <v>79.51</v>
       </c>
     </row>
     <row r="382">
       <c t="inlineStr" r="A382">
         <is>
-          <t xml:space="preserve">UATX</t>
+          <t xml:space="preserve">The Wilderness Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B382">
         <is>
-          <t xml:space="preserve">2/1/2027</t>
-        </is>
-      </c>
-      <c r="C382" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C382" s="66">
+        <v>73.00</v>
       </c>
     </row>
     <row r="383">
       <c t="inlineStr" r="A383">
         <is>
-          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B383">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">4/21/2027</t>
         </is>
       </c>
       <c r="C383" s="66">
-        <v>95.75</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="384">
       <c t="inlineStr" r="A384">
         <is>
-          <t xml:space="preserve">UMKC Foundation</t>
+          <t xml:space="preserve">Together Making Changes</t>
         </is>
       </c>
       <c t="inlineStr" r="B384">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C384" s="66">
-        <v>95.00</v>
+        <v>90.26</v>
       </c>
     </row>
     <row r="385">
       <c t="inlineStr" r="A385">
         <is>
-          <t xml:space="preserve">Unified Youth</t>
+          <t xml:space="preserve">Trevecca Nazarene University</t>
         </is>
       </c>
       <c t="inlineStr" r="B385">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C385" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/30/2027</t>
+        </is>
+      </c>
+      <c r="C385" s="66">
+        <v>87.82</v>
       </c>
     </row>
     <row r="386">
       <c t="inlineStr" r="A386">
         <is>
-          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B386">
         <is>
-          <t xml:space="preserve">8/1/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C386" s="66">
-        <v>88.00</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="387">
       <c t="inlineStr" r="A387">
         <is>
-          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
+          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
         </is>
       </c>
       <c t="inlineStr" r="B387">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C387" s="66">
-        <v>84.01</v>
+        <v>89.90</v>
       </c>
     </row>
     <row r="388">
       <c t="inlineStr" r="A388">
         <is>
-          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Trustees of Tufts College</t>
         </is>
       </c>
       <c t="inlineStr" r="B388">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">7/2/2027</t>
         </is>
       </c>
       <c r="C388" s="66">
@@ -6023,435 +6023,615 @@
     <row r="389">
       <c t="inlineStr" r="A389">
         <is>
-          <t xml:space="preserve">united Service Organizations, Inc.</t>
+          <t xml:space="preserve">Turning Point USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B389">
         <is>
-          <t xml:space="preserve">11/10/2026</t>
-        </is>
-      </c>
-      <c r="C389" s="66">
-        <v>67.94</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C389" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="390">
       <c t="inlineStr" r="A390">
         <is>
-          <t xml:space="preserve">United States Association for UNHCR</t>
+          <t xml:space="preserve">Twelveacres, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B390">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C390" s="66">
-        <v>61.00</v>
+        <v>79.93</v>
       </c>
     </row>
     <row r="391">
       <c t="inlineStr" r="A391">
         <is>
-          <t xml:space="preserve">United States Center for SafeSport</t>
+          <t xml:space="preserve">UATX</t>
         </is>
       </c>
       <c t="inlineStr" r="B391">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
-        </is>
-      </c>
-      <c r="C391" s="66">
-        <v>72.74</v>
+          <t xml:space="preserve">2/1/2027</t>
+        </is>
+      </c>
+      <c r="C391" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="392">
       <c t="inlineStr" r="A392">
         <is>
-          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
+          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B392">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C392" s="66">
-        <v>38.00</v>
+        <v>95.75</v>
       </c>
     </row>
     <row r="393">
       <c t="inlineStr" r="A393">
         <is>
-          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
+          <t xml:space="preserve">UMKC Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B393">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C393" s="66">
-        <v>99.30</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="394">
       <c t="inlineStr" r="A394">
         <is>
-          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
+          <t xml:space="preserve">Unified Youth</t>
         </is>
       </c>
       <c t="inlineStr" r="B394">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
-        </is>
-      </c>
-      <c r="C394" s="66">
-        <v>93.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C394" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="395">
       <c t="inlineStr" r="A395">
         <is>
-          <t xml:space="preserve">University of Nebraska Foundation</t>
+          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B395">
         <is>
-          <t xml:space="preserve">7/15/2027</t>
+          <t xml:space="preserve">8/1/2027</t>
         </is>
       </c>
       <c r="C395" s="66">
-        <v>81.10</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="396">
       <c t="inlineStr" r="A396">
         <is>
-          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
+          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B396">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C396" s="66">
-        <v>77.00</v>
+        <v>84.01</v>
       </c>
     </row>
     <row r="397">
       <c t="inlineStr" r="A397">
         <is>
-          <t xml:space="preserve">University of Pacific</t>
+          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B397">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C397" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C397" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="398">
       <c t="inlineStr" r="A398">
         <is>
-          <t xml:space="preserve">University of Richmond</t>
+          <t xml:space="preserve">united Service Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B398">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">11/10/2026</t>
         </is>
       </c>
       <c r="C398" s="66">
-        <v>82.18</v>
+        <v>67.94</v>
       </c>
     </row>
     <row r="399">
       <c t="inlineStr" r="A399">
         <is>
-          <t xml:space="preserve">Veterans Community Project</t>
+          <t xml:space="preserve">United States Association for UNHCR</t>
         </is>
       </c>
       <c t="inlineStr" r="B399">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C399" s="66">
-        <v>88.83</v>
+        <v>61.00</v>
       </c>
     </row>
     <row r="400">
       <c t="inlineStr" r="A400">
         <is>
-          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
+          <t xml:space="preserve">United States Center for SafeSport</t>
         </is>
       </c>
       <c t="inlineStr" r="B400">
         <is>
-          <t xml:space="preserve">7/13/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C400" s="66">
-        <v>72.00</v>
+        <v>72.74</v>
       </c>
     </row>
     <row r="401">
       <c t="inlineStr" r="A401">
         <is>
-          <t xml:space="preserve">Violet Research Institute, Inc.</t>
+          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B401">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C401" s="66">
-        <v>80.00</v>
+        <v>38.00</v>
       </c>
     </row>
     <row r="402">
       <c t="inlineStr" r="A402">
         <is>
-          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B402">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C402" s="66">
-        <v>28.00</v>
+        <v>99.30</v>
       </c>
     </row>
     <row r="403">
       <c t="inlineStr" r="A403">
         <is>
-          <t xml:space="preserve">VoteAmerica, Inc.</t>
+          <t xml:space="preserve">University of Colorado</t>
         </is>
       </c>
       <c t="inlineStr" r="B403">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">10/6/2027</t>
         </is>
       </c>
       <c r="C403" s="66">
-        <v>93.37</v>
+        <v>76.40</v>
       </c>
     </row>
     <row r="404">
       <c t="inlineStr" r="A404">
         <is>
-          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B404">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C404" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C404" s="66">
+        <v>93.00</v>
       </c>
     </row>
     <row r="405">
       <c t="inlineStr" r="A405">
         <is>
-          <t xml:space="preserve">Washington State University Foundation</t>
+          <t xml:space="preserve">University of Nebraska Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B405">
         <is>
-          <t xml:space="preserve">7/8/2027</t>
+          <t xml:space="preserve">7/15/2027</t>
         </is>
       </c>
       <c r="C405" s="66">
-        <v>75.03</v>
+        <v>81.10</v>
       </c>
     </row>
     <row r="406">
       <c t="inlineStr" r="A406">
         <is>
-          <t xml:space="preserve">Western Illinois University Foundation</t>
+          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B406">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C406" s="66">
-        <v>77.54</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="407">
       <c t="inlineStr" r="A407">
         <is>
-          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+          <t xml:space="preserve">University of Northern Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B407">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">10/1/2027</t>
         </is>
       </c>
       <c r="C407" s="66">
-        <v>82.68</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="408">
       <c t="inlineStr" r="A408">
         <is>
-          <t xml:space="preserve">Wildlife Conservation Network</t>
+          <t xml:space="preserve">University of Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B408">
         <is>
-          <t xml:space="preserve">8/13/2027</t>
-        </is>
-      </c>
-      <c r="C408" s="66">
-        <v>92.13</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C408" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="409">
       <c t="inlineStr" r="A409">
         <is>
-          <t xml:space="preserve">Winning for Women, Inc.</t>
+          <t xml:space="preserve">University of Richmond</t>
         </is>
       </c>
       <c t="inlineStr" r="B409">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C409" s="66">
-        <v>66.70</v>
+        <v>82.18</v>
       </c>
     </row>
     <row r="410">
       <c t="inlineStr" r="A410">
         <is>
-          <t xml:space="preserve">Women for Women International</t>
+          <t xml:space="preserve">University of the Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B410">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C410" s="66">
-        <v>79.06</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="411">
       <c t="inlineStr" r="A411">
         <is>
-          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+          <t xml:space="preserve">Veterans Community Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B411">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C411" s="66">
-        <v>71.40</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="412">
       <c t="inlineStr" r="A412">
         <is>
-          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B412">
         <is>
-          <t xml:space="preserve">2/20/2027</t>
-        </is>
-      </c>
-      <c r="C412" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/13/2027</t>
+        </is>
+      </c>
+      <c r="C412" s="66">
+        <v>72.00</v>
       </c>
     </row>
     <row r="413">
       <c t="inlineStr" r="A413">
         <is>
-          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+          <t xml:space="preserve">Violet Research Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B413">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C413" s="66">
-        <v>79.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="414">
       <c t="inlineStr" r="A414">
         <is>
-          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B414">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">11/5/2026</t>
         </is>
       </c>
       <c r="C414" s="66">
-        <v>70.36</v>
+        <v>28.00</v>
       </c>
     </row>
     <row r="415">
       <c t="inlineStr" r="A415">
         <is>
-          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
+          <t xml:space="preserve">VoteAmerica, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B415">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C415" s="66">
-        <v>39.45</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="416">
       <c t="inlineStr" r="A416">
         <is>
-          <t xml:space="preserve">YMCA of the Rockies</t>
+          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B416">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C416" s="66">
-        <v>81.65</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C416" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="417">
       <c t="inlineStr" r="A417">
         <is>
+          <t xml:space="preserve">Washington State University Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B417">
+        <is>
+          <t xml:space="preserve">7/8/2027</t>
+        </is>
+      </c>
+      <c r="C417" s="66">
+        <v>75.03</v>
+      </c>
+    </row>
+    <row r="418">
+      <c t="inlineStr" r="A418">
+        <is>
+          <t xml:space="preserve">Western Illinois University Foundation</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B418">
+        <is>
+          <t xml:space="preserve">9/22/2027</t>
+        </is>
+      </c>
+      <c r="C418" s="66">
+        <v>77.54</v>
+      </c>
+    </row>
+    <row r="419">
+      <c t="inlineStr" r="A419">
+        <is>
+          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B419">
+        <is>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C419" s="66">
+        <v>82.68</v>
+      </c>
+    </row>
+    <row r="420">
+      <c t="inlineStr" r="A420">
+        <is>
+          <t xml:space="preserve">Wildlife Conservation Network</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B420">
+        <is>
+          <t xml:space="preserve">8/13/2027</t>
+        </is>
+      </c>
+      <c r="C420" s="66">
+        <v>92.13</v>
+      </c>
+    </row>
+    <row r="421">
+      <c t="inlineStr" r="A421">
+        <is>
+          <t xml:space="preserve">Winning for Women, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B421">
+        <is>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C421" s="66">
+        <v>66.70</v>
+      </c>
+    </row>
+    <row r="422">
+      <c t="inlineStr" r="A422">
+        <is>
+          <t xml:space="preserve">Women for Women International</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B422">
+        <is>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C422" s="66">
+        <v>79.06</v>
+      </c>
+    </row>
+    <row r="423">
+      <c t="inlineStr" r="A423">
+        <is>
+          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B423">
+        <is>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C423" s="66">
+        <v>71.40</v>
+      </c>
+    </row>
+    <row r="424">
+      <c t="inlineStr" r="A424">
+        <is>
+          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B424">
+        <is>
+          <t xml:space="preserve">2/20/2027</t>
+        </is>
+      </c>
+      <c r="C424" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c t="inlineStr" r="A425">
+        <is>
+          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B425">
+        <is>
+          <t xml:space="preserve">5/20/2027</t>
+        </is>
+      </c>
+      <c r="C425" s="66">
+        <v>79.00</v>
+      </c>
+    </row>
+    <row r="426">
+      <c t="inlineStr" r="A426">
+        <is>
+          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B426">
+        <is>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C426" s="66">
+        <v>70.36</v>
+      </c>
+    </row>
+    <row r="427">
+      <c t="inlineStr" r="A427">
+        <is>
+          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B427">
+        <is>
+          <t xml:space="preserve">8/24/2027</t>
+        </is>
+      </c>
+      <c r="C427" s="66">
+        <v>39.45</v>
+      </c>
+    </row>
+    <row r="428">
+      <c t="inlineStr" r="A428">
+        <is>
+          <t xml:space="preserve">YMCA of the Rockies</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B428">
+        <is>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C428" s="66">
+        <v>81.65</v>
+      </c>
+    </row>
+    <row r="429">
+      <c t="inlineStr" r="A429">
+        <is>
           <t xml:space="preserve">Young Judaea Global, Inc.</t>
         </is>
       </c>
-      <c t="inlineStr" r="B417">
+      <c t="inlineStr" r="B429">
         <is>
           <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
-      <c r="C417" s="66">
+      <c r="C429" s="66">
         <v>71.20</v>
       </c>
     </row>

--- a/downloadable-data/LA.xlsx
+++ b/downloadable-data/LA.xlsx
@@ -1418,52 +1418,52 @@
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Children's Miracle Network</t>
+          <t xml:space="preserve">Choice Books of Northern Virginia, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">10/15/2027</t>
         </is>
       </c>
       <c r="C82" s="66">
-        <v>80.77</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">Choice Books of Northern Virginia, Inc.</t>
+          <t xml:space="preserve">Christian Advocates Serving Evangelism, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">10/15/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C83" s="66">
-        <v>91.41</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Christian Advocates Serving Evangelism, Inc.</t>
+          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C84" s="66">
-        <v>1.17</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
+          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
@@ -1471,64 +1471,64 @@
           <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
-      <c r="C85" s="66">
-        <v>89.98</v>
+      <c r="C85" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
+          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C86" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/10/2027</t>
+        </is>
+      </c>
+      <c r="C86" s="66">
+        <v>96.00</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
+          <t xml:space="preserve">Christian Relief Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">9/10/2027</t>
+          <t xml:space="preserve">2/10/2027</t>
         </is>
       </c>
       <c r="C87" s="66">
-        <v>96.00</v>
+        <v>90.70</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Christian Relief Services, Inc.</t>
+          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
-        </is>
-      </c>
-      <c r="C88" s="66">
-        <v>90.70</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C88" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
+          <t xml:space="preserve">Christian Union, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">12/5/2026</t>
         </is>
       </c>
       <c r="C89" s="65">
@@ -1538,102 +1538,102 @@
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">Christian Union, Inc.</t>
+          <t xml:space="preserve">Church World Service, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C90" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/25/2027</t>
+        </is>
+      </c>
+      <c r="C90" s="66">
+        <v>84.00</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Church World Service, Inc.</t>
+          <t xml:space="preserve">City Rescue Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">8/25/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C91" s="66">
-        <v>84.00</v>
+        <v>85.32</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">City Rescue Mission, Inc.</t>
+          <t xml:space="preserve">City Year, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C92" s="66">
-        <v>85.32</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">City Year, Inc.</t>
+          <t xml:space="preserve">Civil Rights Corps</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C93" s="66">
-        <v>82.62</v>
+        <v>82.10</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Civil Rights Corps</t>
+          <t xml:space="preserve">Colon Cancer Coalition</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C94" s="66">
-        <v>82.10</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Colon Cancer Coalition</t>
+          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C95" s="66">
-        <v>86.73</v>
+          <t xml:space="preserve">11/20/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
+          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">11/20/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C96" s="65">
@@ -1643,37 +1643,37 @@
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
+          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C97" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/9/2027</t>
+        </is>
+      </c>
+      <c r="C97" s="66">
+        <v>65.99</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
+          <t xml:space="preserve">Compassion and Choices</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C98" s="66">
-        <v>65.99</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">Compassion and Choices</t>
+          <t xml:space="preserve">Compassion and Choices Action Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
@@ -1682,108 +1682,108 @@
         </is>
       </c>
       <c r="C99" s="66">
-        <v>84.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">Compassion and Choices Action Network</t>
+          <t xml:space="preserve">Compassion In World Farming, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
-        </is>
-      </c>
-      <c r="C100" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">10/10/2027</t>
+        </is>
+      </c>
+      <c r="C100" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Compassion In World Farming, Inc.</t>
+          <t xml:space="preserve">Concerns of Police Survivors</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">10/10/2027</t>
-        </is>
-      </c>
-      <c r="C101" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/7/2027</t>
+        </is>
+      </c>
+      <c r="C101" s="66">
+        <v>92.30</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Concerns of Police Survivors</t>
+          <t xml:space="preserve">Consumer Reports, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">10/7/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C102" s="66">
-        <v>92.30</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Consumer Reports, Inc.</t>
+          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C103" s="66">
-        <v>84.00</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
+          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">6/25/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C104" s="66">
-        <v>73.00</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
+          <t xml:space="preserve">Covenant House</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C105" s="66">
-        <v>74.25</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Covenant House</t>
+          <t xml:space="preserve">Covenant House New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">7/28/2028</t>
         </is>
       </c>
       <c r="C106" s="66">
@@ -1793,121 +1793,121 @@
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Covenant House New Orleans</t>
+          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">7/28/2028</t>
+          <t xml:space="preserve">12/4/2026</t>
         </is>
       </c>
       <c r="C107" s="66">
-        <v>80.00</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
+          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C108" s="66">
-        <v>84.38</v>
+        <v>85.18</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
+          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C109" s="66">
-        <v>85.18</v>
+        <v>64.30</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
+          <t xml:space="preserve">D.A.R.E. America</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C110" s="66">
-        <v>64.30</v>
+        <v>44.00</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">D.A.R.E. America</t>
+          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
-        </is>
-      </c>
-      <c r="C111" s="66">
-        <v>44.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C111" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
+          <t xml:space="preserve">Deep South Today</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C112" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/17/2027</t>
+        </is>
+      </c>
+      <c r="C112" s="66">
+        <v>74.56</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">Deep South Today</t>
+          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">6/6/2027</t>
         </is>
       </c>
       <c r="C113" s="66">
-        <v>74.56</v>
+        <v>68.82</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
+          <t xml:space="preserve">Disabled Veterans National Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">6/6/2027</t>
+          <t xml:space="preserve">10/19/2027</t>
         </is>
       </c>
       <c r="C114" s="66">
-        <v>68.82</v>
+        <v>31.01</v>
       </c>
     </row>
     <row r="115">
@@ -2438,52 +2438,52 @@
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">Go Campaign</t>
+          <t xml:space="preserve">Goodwill Industries International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C150" s="66">
-        <v>77.86</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Goodwill Industries International, Inc</t>
+          <t xml:space="preserve">Green America</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C151" s="66">
-        <v>87.00</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">Green America</t>
+          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C152" s="66">
-        <v>87.47</v>
+        <v>76.85</v>
       </c>
     </row>
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
+          <t xml:space="preserve">Greenpeace, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
@@ -2492,153 +2492,153 @@
         </is>
       </c>
       <c r="C153" s="66">
-        <v>76.85</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">Greenpeace, Inc.</t>
+          <t xml:space="preserve">Gustavus Adolphus College</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">2/24/2027</t>
         </is>
       </c>
       <c r="C154" s="66">
-        <v>62.56</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">Gustavus Adolphus College</t>
+          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">2/24/2027</t>
-        </is>
-      </c>
-      <c r="C155" s="66">
-        <v>93.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">Habitat for Horses, Inc.</t>
+          <t xml:space="preserve">Healing Justice Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C156" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C156" s="66">
+        <v>82.48</v>
       </c>
     </row>
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
+          <t xml:space="preserve">Healing Protectors</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C157" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/2/2027</t>
+        </is>
+      </c>
+      <c r="C157" s="66">
+        <v>47.19</v>
       </c>
     </row>
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">Healing Justice Project</t>
+          <t xml:space="preserve">Heifer Project International</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">3/19/2027</t>
         </is>
       </c>
       <c r="C158" s="66">
-        <v>82.48</v>
+        <v>72.90</v>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">Healing Protectors</t>
+          <t xml:space="preserve">Help Me See, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C159" s="66">
-        <v>47.19</v>
+        <v>83.00</v>
       </c>
     </row>
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">Heifer Project International</t>
+          <t xml:space="preserve">Herzog Tomorrow Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">3/19/2027</t>
-        </is>
-      </c>
-      <c r="C160" s="66">
-        <v>72.90</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C160" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">Help Me See, Inc.</t>
+          <t xml:space="preserve">HIAS Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
-        </is>
-      </c>
-      <c r="C161" s="66">
-        <v>83.00</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C161" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
+          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C162" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C162" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">Herzog Tomorrow Foundation</t>
+          <t xml:space="preserve">Home Builders Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C163" s="65">
@@ -2648,357 +2648,357 @@
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">HIAS Foundation, Inc.</t>
+          <t xml:space="preserve">Human Appeal, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C164" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/12/2027</t>
+        </is>
+      </c>
+      <c r="C164" s="66">
+        <v>54.20</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
+          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C165" s="66">
-        <v>81.00</v>
+        <v>63.39</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">Home Builders Institute</t>
+          <t xml:space="preserve">Human Rights Watch, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C166" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C166" s="66">
+        <v>68.67</v>
       </c>
     </row>
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">Human Appeal, Inc.</t>
+          <t xml:space="preserve">Human-I-T</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">1/12/2027</t>
+          <t xml:space="preserve">8/30/2027</t>
         </is>
       </c>
       <c r="C167" s="66">
-        <v>54.20</v>
+        <v>1.00</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
+          <t xml:space="preserve">Humane Society of Missouri</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/7/2027</t>
         </is>
       </c>
       <c r="C168" s="66">
-        <v>63.39</v>
+        <v>80.50</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">Human Rights Watch, Inc.</t>
+          <t xml:space="preserve">Illinois State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">5/21/2027</t>
         </is>
       </c>
       <c r="C169" s="66">
-        <v>68.67</v>
+        <v>61.30</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">Human-I-T</t>
+          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">8/30/2027</t>
-        </is>
-      </c>
-      <c r="C170" s="66">
-        <v>1.00</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C170" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">Humane Society of Missouri</t>
+          <t xml:space="preserve">In Medias Res</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
-        </is>
-      </c>
-      <c r="C171" s="66">
-        <v>80.50</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C171" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">Illinois State University Foundation</t>
+          <t xml:space="preserve">Independent Council on Women's Sport</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">5/21/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C172" s="66">
-        <v>61.30</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
+          <t xml:space="preserve">Infact</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C173" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C173" s="66">
+        <v>89.97</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">In Medias Res</t>
+          <t xml:space="preserve">INROADS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C174" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/1/2027</t>
+        </is>
+      </c>
+      <c r="C174" s="66">
+        <v>47.80</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">Independent Council on Women's Sport</t>
+          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C175" s="66">
-        <v>94.44</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">Infact</t>
+          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
-        </is>
-      </c>
-      <c r="C176" s="66">
-        <v>89.97</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">INROADS, Inc.</t>
+          <t xml:space="preserve">International Justice Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">10/1/2027</t>
-        </is>
-      </c>
-      <c r="C177" s="66">
-        <v>47.80</v>
+          <t xml:space="preserve">3/24/2027</t>
+        </is>
+      </c>
+      <c r="C177" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
+          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C178" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C178" s="66">
+        <v>83.13</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
+          <t xml:space="preserve">International Union of Police Associations</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C179" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="66">
+        <v>47.90</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">International Justice Mission</t>
+          <t xml:space="preserve">Iona University</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
-        </is>
-      </c>
-      <c r="C180" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C180" s="66">
+        <v>89.81</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
+          <t xml:space="preserve">Isaad Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">9/18/2027</t>
         </is>
       </c>
       <c r="C181" s="66">
-        <v>83.13</v>
+        <v>96.30</v>
       </c>
     </row>
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">International Union of Police Associations</t>
+          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">4/27/2027</t>
         </is>
       </c>
       <c r="C182" s="66">
-        <v>47.90</v>
+        <v>75.43</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">Iona University</t>
+          <t xml:space="preserve">Jewish Democratic Council of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C183" s="66">
-        <v>89.81</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">Isaad Foundation</t>
+          <t xml:space="preserve">Jewish Voice Ministries International</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">9/18/2027</t>
-        </is>
-      </c>
-      <c r="C184" s="66">
-        <v>96.30</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C184" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
+          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C185" s="66">
-        <v>75.43</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">Jewish Democratic Council of America</t>
+          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C186" s="66">
-        <v>50.07</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">Jewish Voice Ministries International</t>
+          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
+          <t xml:space="preserve">9/5/2027</t>
         </is>
       </c>
       <c r="C187" s="65">
@@ -3008,42 +3008,42 @@
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
+          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C188" s="66">
-        <v>89.00</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
+          <t xml:space="preserve">Khan Academy, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C189" s="66">
-        <v>75.00</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
+          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">9/5/2027</t>
+          <t xml:space="preserve">11/12/2026</t>
         </is>
       </c>
       <c r="C190" s="65">
@@ -3053,747 +3053,747 @@
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
+          <t xml:space="preserve">L.E.A.D. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C191" s="66">
-        <v>98.28</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C191" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">Khan Academy, Inc.</t>
+          <t xml:space="preserve">La Leche League International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C192" s="66">
-        <v>86.36</v>
+        <v>57.00</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
+          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C193" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C193" s="66">
+        <v>63.00</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">L.E.A.D. Inc.</t>
+          <t xml:space="preserve">Lasell University</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C194" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/22/2027</t>
+        </is>
+      </c>
+      <c r="C194" s="66">
+        <v>86.90</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">La Leche League International, Inc.</t>
+          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C195" s="66">
-        <v>57.00</v>
+        <v>10.60</v>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
+          <t xml:space="preserve">League of Conservation Voters, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">9/23/2027</t>
         </is>
       </c>
       <c r="C196" s="66">
-        <v>63.00</v>
+        <v>92.00</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">Lasell University</t>
+          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
+          <t xml:space="preserve">10/28/2026</t>
         </is>
       </c>
       <c r="C197" s="66">
-        <v>86.90</v>
+        <v>96.80</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
+          <t xml:space="preserve">Life Teen, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C198" s="66">
-        <v>10.60</v>
+        <v>76.40</v>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">League of Conservation Voters, Inc.</t>
+          <t xml:space="preserve">Live Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">9/23/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C199" s="66">
-        <v>92.00</v>
+        <v>81.13</v>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
+          <t xml:space="preserve">Living Waters for the World</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">10/28/2026</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C200" s="66">
-        <v>96.80</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">Life Teen, Inc.</t>
+          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C201" s="66">
-        <v>76.40</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C201" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">Live Action</t>
+          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C202" s="66">
-        <v>81.13</v>
+        <v>76.03</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">Living Waters for the World</t>
+          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C203" s="66">
-        <v>78.81</v>
+        <v>62.00</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
+          <t xml:space="preserve">Madison House</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C204" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C204" s="66">
+        <v>77.79</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
+          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">8/6/2027</t>
         </is>
       </c>
       <c r="C205" s="66">
-        <v>76.03</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
+          <t xml:space="preserve">MAP International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C206" s="66">
-        <v>62.00</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">Madison House</t>
+          <t xml:space="preserve">March of Dimes</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">12/30/2026</t>
         </is>
       </c>
       <c r="C207" s="66">
-        <v>77.79</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
+          <t xml:space="preserve">Marist University</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">8/6/2027</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C208" s="66">
-        <v>86.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">MAP International, Inc.</t>
+          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C209" s="66">
-        <v>99.00</v>
+        <v>91.74</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">March of Dimes</t>
+          <t xml:space="preserve">Meals on Wheels America</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">12/30/2026</t>
+          <t xml:space="preserve">5/27/2027</t>
         </is>
       </c>
       <c r="C210" s="66">
-        <v>74.00</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">Marist University</t>
+          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">6/9/2027</t>
         </is>
       </c>
       <c r="C211" s="66">
-        <v>91.00</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
+          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
-        </is>
-      </c>
-      <c r="C212" s="66">
-        <v>91.74</v>
+          <t xml:space="preserve">12/8/2026</t>
+        </is>
+      </c>
+      <c r="C212" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">Meals on Wheels America</t>
+          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">5/27/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C213" s="66">
-        <v>59.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
+          <t xml:space="preserve">Mercatus Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">6/9/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C214" s="66">
-        <v>80.94</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
+          <t xml:space="preserve">Mercy for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">12/8/2026</t>
-        </is>
-      </c>
-      <c r="C215" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C215" s="66">
+        <v>75.82</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
+          <t xml:space="preserve">Mercy Hospital, Cedar Rapids, Iowa Endowment Found</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C216" s="66">
-        <v>91.00</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">Mercatus Center, Inc.</t>
+          <t xml:space="preserve">Mercy Ships</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">8/26/2027</t>
         </is>
       </c>
       <c r="C217" s="66">
-        <v>90.25</v>
+        <v>78.18</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">Mercy for Animals, Inc.</t>
+          <t xml:space="preserve">Middle East Policy Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C218" s="66">
-        <v>75.82</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">Mercy Hospital, Cedar Rapids, Iowa Endowment Found</t>
+          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C219" s="66">
-        <v>93.00</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">Mercy Ships</t>
+          <t xml:space="preserve">Minutes Matter-MCADD</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">8/26/2027</t>
-        </is>
-      </c>
-      <c r="C220" s="66">
-        <v>78.18</v>
+          <t xml:space="preserve">7/19/2027</t>
+        </is>
+      </c>
+      <c r="C220" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">Middle East Policy Network, Inc.</t>
+          <t xml:space="preserve">Miracle Flights</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C221" s="66">
-        <v>73.83</v>
+        <v>52.00</v>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
+          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C222" s="66">
-        <v>88.00</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">Minutes Matter-MCADD</t>
+          <t xml:space="preserve">mothers2mothers United States, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">7/19/2027</t>
-        </is>
-      </c>
-      <c r="C223" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/27/2027</t>
+        </is>
+      </c>
+      <c r="C223" s="66">
+        <v>60.00</v>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">Miracle Flights</t>
+          <t xml:space="preserve">Mount Saint Marys University</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C224" s="66">
-        <v>52.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C224" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
+          <t xml:space="preserve">Mountain States Legal Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C225" s="66">
-        <v>94.50</v>
+        <v>69.99</v>
       </c>
     </row>
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">mothers2mothers United States, Inc.</t>
+          <t xml:space="preserve">MrCharity, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
-        </is>
-      </c>
-      <c r="C226" s="66">
-        <v>60.00</v>
+          <t xml:space="preserve">2/23/2027</t>
+        </is>
+      </c>
+      <c r="C226" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">Mount Saint Marys University</t>
+          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C227" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/24/2027</t>
+        </is>
+      </c>
+      <c r="C227" s="66">
+        <v>77.80</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">Mountain States Legal Foundation</t>
+          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">12/19/2026</t>
         </is>
       </c>
       <c r="C228" s="66">
-        <v>69.99</v>
+        <v>66.90</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">MrCharity, Inc.</t>
+          <t xml:space="preserve">Naropa University</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
-        </is>
-      </c>
-      <c r="C229" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C229" s="66">
+        <v>76.21</v>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
+          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C230" s="66">
-        <v>54.00</v>
+        <v>65.00</v>
       </c>
     </row>
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
+          <t xml:space="preserve">National Audubon Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C231" s="66">
-        <v>77.80</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
+          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">12/19/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C232" s="66">
-        <v>66.90</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">Naropa University</t>
+          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">8/7/2027</t>
         </is>
       </c>
       <c r="C233" s="66">
-        <v>76.21</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
+          <t xml:space="preserve">National Council of Nonprofits</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C234" s="66">
-        <v>65.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C234" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">National Audubon Society, Inc.</t>
+          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C235" s="66">
-        <v>80.00</v>
+        <v>49.00</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
+          <t xml:space="preserve">National Foundation for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C236" s="66">
-        <v>81.00</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C236" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
+          <t xml:space="preserve">National Geographic Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
+          <t xml:space="preserve">3/18/2027</t>
         </is>
       </c>
       <c r="C237" s="66">
-        <v>92.28</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">National Council of Nonprofits</t>
+          <t xml:space="preserve">National LGBTQ Task Force</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C238" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C238" s="66">
+        <v>80.00</v>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
+          <t xml:space="preserve">National Network of Abortion Funds</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C239" s="66">
-        <v>49.00</v>
+          <t xml:space="preserve">9/11/2027</t>
+        </is>
+      </c>
+      <c r="C239" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">National Foundation for Cancer Research</t>
+          <t xml:space="preserve">National PKU Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C240" s="65">
@@ -3803,42 +3803,42 @@
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">National Geographic Society</t>
+          <t xml:space="preserve">National Rifle Association of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">3/18/2027</t>
+          <t xml:space="preserve">10/1/2027</t>
         </is>
       </c>
       <c r="C241" s="66">
-        <v>77.00</v>
+        <v>62.91</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">National LGBTQ Task Force</t>
+          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C242" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C242" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">National Network of Abortion Funds</t>
+          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">1/9/2027</t>
         </is>
       </c>
       <c r="C243" s="65">
@@ -3848,522 +3848,522 @@
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">National Park Foundation</t>
+          <t xml:space="preserve">National Space Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C244" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C244" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">National PKU Alliance, Inc.</t>
+          <t xml:space="preserve">National University</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C245" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C245" s="66">
+        <v>42.69</v>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">National Rifle Association of America</t>
+          <t xml:space="preserve">National Veterans Memorial and Museum</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">10/1/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C246" s="66">
-        <v>62.91</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
+          <t xml:space="preserve">National Wheelchair Basketball Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C247" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/12/2027</t>
+        </is>
+      </c>
+      <c r="C247" s="66">
+        <v>77.80</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
+          <t xml:space="preserve">National Wildlife Federation</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C248" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C248" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">National Space Society</t>
+          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C249" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/22/2027</t>
+        </is>
+      </c>
+      <c r="C249" s="66">
+        <v>1.60</v>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">National University</t>
+          <t xml:space="preserve">Network for Good, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C250" s="66">
-        <v>42.69</v>
+        <v>97.80</v>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">National Veterans Memorial and Museum</t>
+          <t xml:space="preserve">New Harvest, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C251" s="66">
-        <v>72.63</v>
+        <v>88.49</v>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">National Wheelchair Basketball Association</t>
+          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
-        </is>
-      </c>
-      <c r="C252" s="66">
-        <v>77.80</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C252" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">National Wildlife Federation</t>
+          <t xml:space="preserve">Nurse-Family Partnership</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
-        </is>
-      </c>
-      <c r="C253" s="66">
-        <v>86.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C253" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
+          <t xml:space="preserve">Ocean Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C254" s="66">
-        <v>1.60</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">Network for Good, Inc</t>
+          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C255" s="66">
-        <v>97.80</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C255" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">New Harvest, Inc.</t>
+          <t xml:space="preserve">Operation Smile, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C256" s="66">
-        <v>88.49</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C256" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
+          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C257" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/18/2027</t>
+        </is>
+      </c>
+      <c r="C257" s="66">
+        <v>77.59</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">Nurse-Family Partnership</t>
+          <t xml:space="preserve">Our Change Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C258" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/13/2027</t>
+        </is>
+      </c>
+      <c r="C258" s="66">
+        <v>71.30</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">Ocean Conservancy</t>
+          <t xml:space="preserve">Pace University</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">7/1/2027</t>
         </is>
       </c>
       <c r="C259" s="66">
-        <v>74.06</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
+          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C260" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/16/2027</t>
+        </is>
+      </c>
+      <c r="C260" s="66">
+        <v>55.43</v>
       </c>
     </row>
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">Operation Smile, Inc.</t>
+          <t xml:space="preserve">Panorama Global</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C261" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C261" s="66">
+        <v>84.52</v>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
+          <t xml:space="preserve">Paralyzed Veterans of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">8/18/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C262" s="66">
-        <v>77.59</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">Our Change Foundation</t>
+          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">10/13/2027</t>
+          <t xml:space="preserve">2/9/2027</t>
         </is>
       </c>
       <c r="C263" s="66">
-        <v>71.30</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">Pace University</t>
+          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
-        </is>
-      </c>
-      <c r="C264" s="66">
-        <v>88.30</v>
+          <t xml:space="preserve">7/16/2027</t>
+        </is>
+      </c>
+      <c r="C264" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
+          <t xml:space="preserve">Pathfinder International</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C265" s="66">
-        <v>55.43</v>
+        <v>85.33</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">Panorama Global</t>
+          <t xml:space="preserve">patriotic Hearts, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C266" s="66">
-        <v>84.52</v>
+        <v>56.00</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">Paralyzed Veterans of America</t>
+          <t xml:space="preserve">People for the American Way</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C267" s="66">
-        <v>59.00</v>
+        <v>38.00</v>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
+          <t xml:space="preserve">People for the American Way Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">2/9/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C268" s="66">
-        <v>90.00</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
+          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
-        </is>
-      </c>
-      <c r="C269" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C269" s="66">
+        <v>83.76</v>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">Pathfinder International</t>
+          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C270" s="66">
-        <v>85.33</v>
+        <v>58.00</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">patriotic Hearts, Inc.</t>
+          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">8/28/2027</t>
         </is>
       </c>
       <c r="C271" s="66">
-        <v>56.00</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">People for the American Way Foundation</t>
+          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
-        </is>
-      </c>
-      <c r="C272" s="66">
-        <v>60.00</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C272" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
+          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
-        </is>
-      </c>
-      <c r="C273" s="66">
-        <v>83.76</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C273" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
+          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
-        </is>
-      </c>
-      <c r="C274" s="66">
-        <v>58.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C274" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
+          <t xml:space="preserve">Pledgeling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">8/28/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C275" s="66">
-        <v>79.00</v>
+        <v>65.93</v>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
+          <t xml:space="preserve">Polar Bears International</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C276" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/2/2027</t>
+        </is>
+      </c>
+      <c r="C276" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
+          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C277" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/27/2027</t>
+        </is>
+      </c>
+      <c r="C277" s="66">
+        <v>85.54</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
+          <t xml:space="preserve">Pratt Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">11/12/2026</t>
         </is>
       </c>
       <c r="C278" s="65">
@@ -4373,207 +4373,207 @@
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">Pledgeling Foundation</t>
+          <t xml:space="preserve">Primo Cares, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
-        </is>
-      </c>
-      <c r="C279" s="66">
-        <v>65.93</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C279" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">Polar Bears International</t>
+          <t xml:space="preserve">Prison Fellowship Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">2/2/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C280" s="66">
-        <v>86.00</v>
+        <v>68.60</v>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
+          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
-        </is>
-      </c>
-      <c r="C281" s="66">
-        <v>85.54</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C281" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">Pratt Institute</t>
+          <t xml:space="preserve">Project Cure, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C282" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C282" s="66">
+        <v>27.00</v>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">Primo Cares, Inc.</t>
+          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C283" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C283" s="66">
+        <v>88.71</v>
       </c>
     </row>
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries</t>
+          <t xml:space="preserve">Proteus Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">3/2/2027</t>
         </is>
       </c>
       <c r="C284" s="66">
-        <v>68.60</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
+          <t xml:space="preserve">Providence House</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C285" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C285" s="66">
+        <v>92.06</v>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">Project Cure, Inc.</t>
+          <t xml:space="preserve">Public Health Foundation Enterprise, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C286" s="66">
-        <v>27.00</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
+          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C287" s="66">
-        <v>88.71</v>
+        <v>84.22</v>
       </c>
     </row>
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">Proteus Fund, Inc.</t>
+          <t xml:space="preserve">Re:Power</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
-        </is>
-      </c>
-      <c r="C288" s="66">
-        <v>81.25</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C288" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">Providence House</t>
+          <t xml:space="preserve">Reproductive Freedom for All</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C289" s="66">
-        <v>92.06</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">Public Health Foundation Enterprise, Inc</t>
+          <t xml:space="preserve">RezilientKidz</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C290" s="66">
-        <v>94.97</v>
+        <v>94.35</v>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
+          <t xml:space="preserve">Rodale Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C291" s="66">
-        <v>84.22</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C291" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">Re:Power</t>
+          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">12/12/2026</t>
         </is>
       </c>
       <c r="C292" s="65">
@@ -4583,1072 +4583,1072 @@
     <row r="293">
       <c t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">Reproductive Freedom for All</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
         </is>
       </c>
       <c t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">10/19/2027</t>
         </is>
       </c>
       <c r="C293" s="66">
-        <v>70.00</v>
+        <v>4.60</v>
       </c>
     </row>
     <row r="294">
       <c t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">RezilientKidz</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
         </is>
       </c>
       <c t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C294" s="66">
-        <v>94.35</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C294" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">Rodale Institute</t>
+          <t xml:space="preserve">Rush University Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C295" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/23/2027</t>
+        </is>
+      </c>
+      <c r="C295" s="66">
+        <v>91.41</v>
       </c>
     </row>
     <row r="296">
       <c t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
+          <t xml:space="preserve">Rutgers University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">12/12/2026</t>
-        </is>
-      </c>
-      <c r="C296" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C296" s="66">
+        <v>87.46</v>
       </c>
     </row>
     <row r="297">
       <c t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
+          <t xml:space="preserve">Sagamore Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C297" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C297" s="66">
+        <v>91.61</v>
       </c>
     </row>
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">Rush University Medical Center</t>
+          <t xml:space="preserve">Saint John's University</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C298" s="66">
-        <v>91.41</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">Rutgers University Foundation</t>
+          <t xml:space="preserve">Save the Chimps, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C299" s="66">
-        <v>87.46</v>
+        <v>79.70</v>
       </c>
     </row>
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">Sagamore Institute, Inc.</t>
+          <t xml:space="preserve">Seattle Pacific University</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
-        </is>
-      </c>
-      <c r="C300" s="66">
-        <v>91.61</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C300" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">Saint John's University</t>
+          <t xml:space="preserve">Second Harvest Food Bank of Greater New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
-        </is>
-      </c>
-      <c r="C301" s="66">
-        <v>92.91</v>
+          <t xml:space="preserve">5/20/2027</t>
+        </is>
+      </c>
+      <c r="C301" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">Save the Chimps, Inc.</t>
+          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C302" s="66">
-        <v>79.70</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">Seattle Pacific University</t>
+          <t xml:space="preserve">Seti Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C303" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C303" s="66">
+        <v>69.60</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">Second Harvest Food Bank of Greater New Orleans</t>
+          <t xml:space="preserve">Share Our Strength</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
-        </is>
-      </c>
-      <c r="C304" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C304" s="66">
+        <v>58.73</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
+          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C305" s="66">
-        <v>94.00</v>
+        <v>97.29</v>
       </c>
     </row>
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">Seti Institute</t>
+          <t xml:space="preserve">Sierra  Club</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">12/22/2026</t>
         </is>
       </c>
       <c r="C306" s="66">
-        <v>69.60</v>
+        <v>82.00</v>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">Share Our Strength</t>
+          <t xml:space="preserve">Sister Rising Worldwide</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
-        </is>
-      </c>
-      <c r="C307" s="66">
-        <v>58.73</v>
+          <t xml:space="preserve">1/28/2027</t>
+        </is>
+      </c>
+      <c r="C307" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
+          <t xml:space="preserve">Sixpoint, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C308" s="66">
-        <v>97.29</v>
+        <v>77.16</v>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">Sierra  Club</t>
+          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">12/22/2026</t>
+          <t xml:space="preserve">4/22/2027</t>
         </is>
       </c>
       <c r="C309" s="66">
-        <v>82.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">Sister Rising Worldwide</t>
+          <t xml:space="preserve">Social Purpose Corrections</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">1/28/2027</t>
-        </is>
-      </c>
-      <c r="C310" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/12/2027</t>
+        </is>
+      </c>
+      <c r="C310" s="66">
+        <v>47.93</v>
       </c>
     </row>
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">Sixpoint, Inc.</t>
+          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">9/2/2027</t>
         </is>
       </c>
       <c r="C311" s="66">
-        <v>77.16</v>
+        <v>72.80</v>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
+          <t xml:space="preserve">Soldiers' Angels</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">4/22/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C312" s="66">
-        <v>90.00</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">Social Purpose Corrections</t>
+          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
+          <t xml:space="preserve">7/29/2027</t>
         </is>
       </c>
       <c r="C313" s="66">
-        <v>47.93</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
+          <t xml:space="preserve">South Dakota State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">9/2/2027</t>
-        </is>
-      </c>
-      <c r="C314" s="66">
-        <v>72.80</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C314" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">Soldiers' Angels</t>
+          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C315" s="66">
-        <v>93.33</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C315" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
+          <t xml:space="preserve">Special Olympics, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">7/29/2027</t>
-        </is>
-      </c>
-      <c r="C316" s="66">
-        <v>86.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C316" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">South Dakota State University Foundation</t>
+          <t xml:space="preserve">SPLC Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C317" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/17/2027</t>
+        </is>
+      </c>
+      <c r="C317" s="66">
+        <v>72.81</v>
       </c>
     </row>
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
+          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C318" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/31/2027</t>
+        </is>
+      </c>
+      <c r="C318" s="66">
+        <v>85.31</v>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">Special Olympics, Inc.</t>
+          <t xml:space="preserve">State University of Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C319" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/4/2027</t>
+        </is>
+      </c>
+      <c r="C319" s="66">
+        <v>79.00</v>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">SPLC Action Fund</t>
+          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">9/17/2027</t>
-        </is>
-      </c>
-      <c r="C320" s="66">
-        <v>72.81</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C320" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
+          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C321" s="66">
-        <v>85.31</v>
+        <v>92.00</v>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">State University of Iowa Foundation</t>
+          <t xml:space="preserve">Students for Life Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">9/4/2027</t>
-        </is>
-      </c>
-      <c r="C322" s="66">
-        <v>79.00</v>
+          <t xml:space="preserve">11/7/2026</t>
+        </is>
+      </c>
+      <c r="C322" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
+          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C323" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/12/2027</t>
+        </is>
+      </c>
+      <c r="C323" s="66">
+        <v>89.29</v>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
+          <t xml:space="preserve">Teacher Freedom Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
-        </is>
-      </c>
-      <c r="C324" s="66">
-        <v>92.00</v>
+          <t xml:space="preserve">6/24/2027</t>
+        </is>
+      </c>
+      <c r="C324" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">Students for Life Action, Inc.</t>
+          <t xml:space="preserve">The Actors' Fund of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">11/7/2026</t>
-        </is>
-      </c>
-      <c r="C325" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/10/2026</t>
+        </is>
+      </c>
+      <c r="C325" s="66">
+        <v>86.73</v>
       </c>
     </row>
     <row r="326">
       <c t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
+          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">8/12/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C326" s="66">
-        <v>89.29</v>
+        <v>39.00</v>
       </c>
     </row>
     <row r="327">
       <c t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">Teacher Freedom Alliance</t>
+          <t xml:space="preserve">The American Society for the Prevention of Cruelty</t>
         </is>
       </c>
       <c t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
-        </is>
-      </c>
-      <c r="C327" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/16/2027</t>
+        </is>
+      </c>
+      <c r="C327" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="328">
       <c t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">The Actors' Fund of America</t>
+          <t xml:space="preserve">The American University</t>
         </is>
       </c>
       <c t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C328" s="66">
-        <v>86.73</v>
+        <v>90.23</v>
       </c>
     </row>
     <row r="329">
       <c t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
-        </is>
-      </c>
-      <c r="C329" s="66">
-        <v>39.00</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C329" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">The American Society for the Prevention of Cruelty</t>
+          <t xml:space="preserve">The Anthony Davis Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
-        </is>
-      </c>
-      <c r="C330" s="66">
-        <v>75.00</v>
+          <t xml:space="preserve">11/24/2026</t>
+        </is>
+      </c>
+      <c r="C330" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="331">
       <c t="inlineStr" r="A331">
         <is>
-          <t xml:space="preserve">The American University</t>
+          <t xml:space="preserve">The Barack Obama Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B331">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C331" s="66">
-        <v>90.23</v>
+        <v>55.90</v>
       </c>
     </row>
     <row r="332">
       <c t="inlineStr" r="A332">
         <is>
-          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+          <t xml:space="preserve">The Baruch College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B332">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C332" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C332" s="66">
+        <v>84.00</v>
       </c>
     </row>
     <row r="333">
       <c t="inlineStr" r="A333">
         <is>
-          <t xml:space="preserve">The Anthony Davis Foundation</t>
+          <t xml:space="preserve">The Call of Duty Endowment</t>
         </is>
       </c>
       <c t="inlineStr" r="B333">
         <is>
-          <t xml:space="preserve">11/24/2026</t>
-        </is>
-      </c>
-      <c r="C333" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C333" s="66">
+        <v>73.00</v>
       </c>
     </row>
     <row r="334">
       <c t="inlineStr" r="A334">
         <is>
-          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
+          <t xml:space="preserve">The Center for Alcohol Policy</t>
         </is>
       </c>
       <c t="inlineStr" r="B334">
         <is>
-          <t xml:space="preserve">10/24/2026</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C334" s="66">
-        <v>90.00</v>
+        <v>73.40</v>
       </c>
     </row>
     <row r="335">
       <c t="inlineStr" r="A335">
         <is>
-          <t xml:space="preserve">The Barack Obama Foundation</t>
+          <t xml:space="preserve">The Center for Investigative Reporting</t>
         </is>
       </c>
       <c t="inlineStr" r="B335">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C335" s="66">
-        <v>55.90</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C335" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c t="inlineStr" r="A336">
         <is>
-          <t xml:space="preserve">The Baruch College Fund</t>
+          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B336">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C336" s="66">
-        <v>84.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="337">
       <c t="inlineStr" r="A337">
         <is>
-          <t xml:space="preserve">The Call of Duty Endowment</t>
+          <t xml:space="preserve">The Center for Victims of Torture</t>
         </is>
       </c>
       <c t="inlineStr" r="B337">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C337" s="66">
-        <v>73.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="338">
       <c t="inlineStr" r="A338">
         <is>
-          <t xml:space="preserve">The Center for Alcohol Policy</t>
+          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
         </is>
       </c>
       <c t="inlineStr" r="B338">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">7/6/2027</t>
         </is>
       </c>
       <c r="C338" s="66">
-        <v>73.40</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="339">
       <c t="inlineStr" r="A339">
         <is>
-          <t xml:space="preserve">The Center for Investigative Reporting</t>
+          <t xml:space="preserve">The Cleveland Clinic Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B339">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C339" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/23/2027</t>
+        </is>
+      </c>
+      <c r="C339" s="66">
+        <v>89.51</v>
       </c>
     </row>
     <row r="340">
       <c t="inlineStr" r="A340">
         <is>
-          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
+          <t xml:space="preserve">The Colorado College</t>
         </is>
       </c>
       <c t="inlineStr" r="B340">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">10/29/2027</t>
         </is>
       </c>
       <c r="C340" s="66">
-        <v>71.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="341">
       <c t="inlineStr" r="A341">
         <is>
-          <t xml:space="preserve">The Center for Victims of Torture</t>
+          <t xml:space="preserve">The Denver Rescue Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B341">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">7/20/2027</t>
         </is>
       </c>
       <c r="C341" s="66">
-        <v>74.00</v>
+        <v>82.96</v>
       </c>
     </row>
     <row r="342">
       <c t="inlineStr" r="A342">
         <is>
-          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
+          <t xml:space="preserve">The Edison Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B342">
         <is>
-          <t xml:space="preserve">7/6/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C342" s="66">
-        <v>71.00</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="343">
       <c t="inlineStr" r="A343">
         <is>
-          <t xml:space="preserve">The Colorado College</t>
+          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B343">
         <is>
-          <t xml:space="preserve">10/29/2027</t>
-        </is>
-      </c>
-      <c r="C343" s="66">
-        <v>90.00</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C343" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="344">
       <c t="inlineStr" r="A344">
         <is>
-          <t xml:space="preserve">The Denver Rescue Mission</t>
+          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
         </is>
       </c>
       <c t="inlineStr" r="B344">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
-        </is>
-      </c>
-      <c r="C344" s="66">
-        <v>82.96</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C344" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c t="inlineStr" r="A345">
         <is>
-          <t xml:space="preserve">The Edison Institute</t>
+          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
         </is>
       </c>
       <c t="inlineStr" r="B345">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C345" s="66">
-        <v>78.00</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="346">
       <c t="inlineStr" r="A346">
         <is>
-          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B346">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C346" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/15/2027</t>
+        </is>
+      </c>
+      <c r="C346" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="347">
       <c t="inlineStr" r="A347">
         <is>
-          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+          <t xml:space="preserve">The Heritage Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B347">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C347" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C347" s="66">
+        <v>83.00</v>
       </c>
     </row>
     <row r="348">
       <c t="inlineStr" r="A348">
         <is>
-          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
+          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B348">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C348" s="66">
-        <v>76.48</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="349">
       <c t="inlineStr" r="A349">
         <is>
-          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
+          <t xml:space="preserve">The Independent Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B349">
         <is>
-          <t xml:space="preserve">5/15/2027</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C349" s="66">
-        <v>85.00</v>
+        <v>77.51</v>
       </c>
     </row>
     <row r="350">
       <c t="inlineStr" r="A350">
         <is>
-          <t xml:space="preserve">The Heritage Foundation</t>
+          <t xml:space="preserve">The International Wildlife Rehab. Council</t>
         </is>
       </c>
       <c t="inlineStr" r="B350">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C350" s="66">
-        <v>83.00</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="351">
       <c t="inlineStr" r="A351">
         <is>
-          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
+          <t xml:space="preserve">The Jane Goodall Institute for Wildlife Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B351">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
-        </is>
-      </c>
-      <c r="C351" s="66">
-        <v>89.00</v>
+          <t xml:space="preserve">5/19/2027</t>
+        </is>
+      </c>
+      <c r="C351" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="352">
       <c t="inlineStr" r="A352">
         <is>
-          <t xml:space="preserve">The Independent Institute</t>
+          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B352">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C352" s="66">
-        <v>77.51</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="353">
       <c t="inlineStr" r="A353">
         <is>
-          <t xml:space="preserve">The International Wildlife Rehab. Council</t>
+          <t xml:space="preserve">The Just Trust for Education</t>
         </is>
       </c>
       <c t="inlineStr" r="B353">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C353" s="66">
-        <v>81.00</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="354">
       <c t="inlineStr" r="A354">
         <is>
-          <t xml:space="preserve">The Jane Goodall Institute for Wildlife Research</t>
+          <t xml:space="preserve">The Kansas University Endowment Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B354">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
-        </is>
-      </c>
-      <c r="C354" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/21/2027</t>
+        </is>
+      </c>
+      <c r="C354" s="66">
+        <v>91.34</v>
       </c>
     </row>
     <row r="355">
       <c t="inlineStr" r="A355">
         <is>
-          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
+          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B355">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C355" s="66">
-        <v>84.00</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="356">
       <c t="inlineStr" r="A356">
         <is>
-          <t xml:space="preserve">The Just Trust for Education</t>
+          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B356">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C356" s="66">
-        <v>85.13</v>
+        <v>91.99</v>
       </c>
     </row>
     <row r="357">
       <c t="inlineStr" r="A357">
         <is>
-          <t xml:space="preserve">The Kansas University Endowment Association</t>
+          <t xml:space="preserve">The Memorial Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B357">
         <is>
-          <t xml:space="preserve">7/21/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C357" s="66">
-        <v>91.34</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="358">
       <c t="inlineStr" r="A358">
         <is>
-          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B358">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C358" s="66">
-        <v>83.06</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="359">
       <c t="inlineStr" r="A359">
         <is>
-          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
+          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B359">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C359" s="66">
-        <v>91.99</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="360">
       <c t="inlineStr" r="A360">
         <is>
-          <t xml:space="preserve">The Memorial Foundation</t>
+          <t xml:space="preserve">The National World War II Museum, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B360">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C360" s="66">
-        <v>72.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="361">
       <c t="inlineStr" r="A361">
         <is>
-          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
         </is>
       </c>
       <c t="inlineStr" r="B361">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C361" s="66">
-        <v>74.58</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="362">
       <c t="inlineStr" r="A362">
         <is>
-          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
+          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
         </is>
       </c>
       <c t="inlineStr" r="B362">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C362" s="66">
-        <v>60.00</v>
+        <v>87.40</v>
       </c>
     </row>
     <row r="363">
       <c t="inlineStr" r="A363">
         <is>
-          <t xml:space="preserve">The National World War II Museum, Inc.</t>
+          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B363">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">8/24/2027</t>
         </is>
       </c>
       <c r="C363" s="66">
-        <v>80.00</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="364">
       <c t="inlineStr" r="A364">
         <is>
-          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+          <t xml:space="preserve">The Ohio University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B364">
@@ -5657,108 +5657,108 @@
         </is>
       </c>
       <c r="C364" s="66">
-        <v>80.64</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="365">
       <c t="inlineStr" r="A365">
         <is>
-          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
+          <t xml:space="preserve">The OneStar Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B365">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">1/14/2027</t>
         </is>
       </c>
       <c r="C365" s="66">
-        <v>87.40</v>
+        <v>62.50</v>
       </c>
     </row>
     <row r="366">
       <c t="inlineStr" r="A366">
         <is>
-          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
+          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B366">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C366" s="66">
-        <v>60.00</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="367">
       <c t="inlineStr" r="A367">
         <is>
-          <t xml:space="preserve">The Ohio University Foundation</t>
+          <t xml:space="preserve">The Planetary Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B367">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">7/14/2027</t>
         </is>
       </c>
       <c r="C367" s="66">
-        <v>74.14</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="368">
       <c t="inlineStr" r="A368">
         <is>
-          <t xml:space="preserve">The OneStar Foundation</t>
+          <t xml:space="preserve">The Principia Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B368">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
-        </is>
-      </c>
-      <c r="C368" s="66">
-        <v>62.50</v>
+          <t xml:space="preserve">5/19/2027</t>
+        </is>
+      </c>
+      <c r="C368" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="369">
       <c t="inlineStr" r="A369">
         <is>
-          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+          <t xml:space="preserve">The Purchase College Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B369">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C369" s="66">
-        <v>88.30</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="370">
       <c t="inlineStr" r="A370">
         <is>
-          <t xml:space="preserve">The Planetary Society</t>
+          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
         </is>
       </c>
       <c t="inlineStr" r="B370">
         <is>
-          <t xml:space="preserve">7/14/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C370" s="66">
-        <v>66.00</v>
+        <v>81.26</v>
       </c>
     </row>
     <row r="371">
       <c t="inlineStr" r="A371">
         <is>
-          <t xml:space="preserve">The Principia Corporation</t>
+          <t xml:space="preserve">The Ruth Collective</t>
         </is>
       </c>
       <c t="inlineStr" r="B371">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C371" s="65">
@@ -5768,297 +5768,297 @@
     <row r="372">
       <c t="inlineStr" r="A372">
         <is>
-          <t xml:space="preserve">The Purchase College Foundation</t>
+          <t xml:space="preserve">The Society of the Cincinnati</t>
         </is>
       </c>
       <c t="inlineStr" r="B372">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C372" s="66">
-        <v>78.12</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="373">
       <c t="inlineStr" r="A373">
         <is>
-          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
+          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
         </is>
       </c>
       <c t="inlineStr" r="B373">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C373" s="66">
-        <v>81.26</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="374">
       <c t="inlineStr" r="A374">
         <is>
-          <t xml:space="preserve">The Ruth Collective</t>
+          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B374">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C374" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/13/2027</t>
+        </is>
+      </c>
+      <c r="C374" s="66">
+        <v>82.20</v>
       </c>
     </row>
     <row r="375">
       <c t="inlineStr" r="A375">
         <is>
-          <t xml:space="preserve">The Society of the Cincinnati</t>
+          <t xml:space="preserve">The University of Montana Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B375">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C375" s="66">
-        <v>73.00</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="376">
       <c t="inlineStr" r="A376">
         <is>
-          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B376">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C376" s="66">
-        <v>94.00</v>
+        <v>76.00</v>
       </c>
     </row>
     <row r="377">
       <c t="inlineStr" r="A377">
         <is>
-          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+          <t xml:space="preserve">The Visiting Angels Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B377">
         <is>
-          <t xml:space="preserve">4/13/2027</t>
+          <t xml:space="preserve">7/20/2027</t>
         </is>
       </c>
       <c r="C377" s="66">
-        <v>82.20</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="378">
       <c t="inlineStr" r="A378">
         <is>
-          <t xml:space="preserve">The University of Montana Foundation</t>
+          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B378">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C378" s="66">
-        <v>79.00</v>
+        <v>79.51</v>
       </c>
     </row>
     <row r="379">
       <c t="inlineStr" r="A379">
         <is>
-          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
+          <t xml:space="preserve">The Wilderness Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B379">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C379" s="66">
-        <v>76.00</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="380">
       <c t="inlineStr" r="A380">
         <is>
-          <t xml:space="preserve">The Visiting Angels Foundation</t>
+          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B380">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">4/21/2027</t>
         </is>
       </c>
       <c r="C380" s="66">
-        <v>94.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="381">
       <c t="inlineStr" r="A381">
         <is>
-          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+          <t xml:space="preserve">Together Making Changes</t>
         </is>
       </c>
       <c t="inlineStr" r="B381">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C381" s="66">
-        <v>79.51</v>
+        <v>90.26</v>
       </c>
     </row>
     <row r="382">
       <c t="inlineStr" r="A382">
         <is>
-          <t xml:space="preserve">The Wilderness Society</t>
+          <t xml:space="preserve">Trevecca Nazarene University</t>
         </is>
       </c>
       <c t="inlineStr" r="B382">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C382" s="66">
-        <v>73.00</v>
+        <v>87.82</v>
       </c>
     </row>
     <row r="383">
       <c t="inlineStr" r="A383">
         <is>
-          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
+          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B383">
         <is>
-          <t xml:space="preserve">4/21/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C383" s="66">
-        <v>85.00</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="384">
       <c t="inlineStr" r="A384">
         <is>
-          <t xml:space="preserve">Together Making Changes</t>
+          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
         </is>
       </c>
       <c t="inlineStr" r="B384">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C384" s="66">
-        <v>90.26</v>
+        <v>89.90</v>
       </c>
     </row>
     <row r="385">
       <c t="inlineStr" r="A385">
         <is>
-          <t xml:space="preserve">Trevecca Nazarene University</t>
+          <t xml:space="preserve">Trustees of Tufts College</t>
         </is>
       </c>
       <c t="inlineStr" r="B385">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">7/2/2027</t>
         </is>
       </c>
       <c r="C385" s="66">
-        <v>87.82</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="386">
       <c t="inlineStr" r="A386">
         <is>
-          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
+          <t xml:space="preserve">Turning Point USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B386">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C386" s="66">
-        <v>94.50</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C386" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="387">
       <c t="inlineStr" r="A387">
         <is>
-          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+          <t xml:space="preserve">Twelveacres, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B387">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C387" s="66">
-        <v>89.90</v>
+        <v>79.93</v>
       </c>
     </row>
     <row r="388">
       <c t="inlineStr" r="A388">
         <is>
-          <t xml:space="preserve">Trustees of Tufts College</t>
+          <t xml:space="preserve">UATX</t>
         </is>
       </c>
       <c t="inlineStr" r="B388">
         <is>
-          <t xml:space="preserve">7/2/2027</t>
-        </is>
-      </c>
-      <c r="C388" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">2/1/2027</t>
+        </is>
+      </c>
+      <c r="C388" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="389">
       <c t="inlineStr" r="A389">
         <is>
-          <t xml:space="preserve">Turning Point USA, Inc.</t>
+          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B389">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C389" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C389" s="66">
+        <v>95.75</v>
       </c>
     </row>
     <row r="390">
       <c t="inlineStr" r="A390">
         <is>
-          <t xml:space="preserve">Twelveacres, Incorporated</t>
+          <t xml:space="preserve">UMKC Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B390">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C390" s="66">
-        <v>79.93</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="391">
       <c t="inlineStr" r="A391">
         <is>
-          <t xml:space="preserve">UATX</t>
+          <t xml:space="preserve">Unified Youth</t>
         </is>
       </c>
       <c t="inlineStr" r="B391">
         <is>
-          <t xml:space="preserve">2/1/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C391" s="65">
@@ -6068,37 +6068,37 @@
     <row r="392">
       <c t="inlineStr" r="A392">
         <is>
-          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B392">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">8/1/2027</t>
         </is>
       </c>
       <c r="C392" s="66">
-        <v>95.75</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="393">
       <c t="inlineStr" r="A393">
         <is>
-          <t xml:space="preserve">UMKC Foundation</t>
+          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B393">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C393" s="66">
-        <v>95.00</v>
+        <v>84.01</v>
       </c>
     </row>
     <row r="394">
       <c t="inlineStr" r="A394">
         <is>
-          <t xml:space="preserve">Unified Youth</t>
+          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B394">
@@ -6106,532 +6106,487 @@
           <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
-      <c r="C394" s="65">
-        <v>0</v>
+      <c r="C394" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="395">
       <c t="inlineStr" r="A395">
         <is>
-          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+          <t xml:space="preserve">united Service Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B395">
         <is>
-          <t xml:space="preserve">8/1/2027</t>
+          <t xml:space="preserve">11/10/2026</t>
         </is>
       </c>
       <c r="C395" s="66">
-        <v>88.00</v>
+        <v>67.94</v>
       </c>
     </row>
     <row r="396">
       <c t="inlineStr" r="A396">
         <is>
-          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
+          <t xml:space="preserve">United States Association for UNHCR</t>
         </is>
       </c>
       <c t="inlineStr" r="B396">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C396" s="66">
-        <v>84.01</v>
+        <v>61.00</v>
       </c>
     </row>
     <row r="397">
       <c t="inlineStr" r="A397">
         <is>
-          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">United States Center for SafeSport</t>
         </is>
       </c>
       <c t="inlineStr" r="B397">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C397" s="66">
-        <v>85.00</v>
+        <v>72.74</v>
       </c>
     </row>
     <row r="398">
       <c t="inlineStr" r="A398">
         <is>
-          <t xml:space="preserve">united Service Organizations, Inc.</t>
+          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B398">
         <is>
-          <t xml:space="preserve">11/10/2026</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C398" s="66">
-        <v>67.94</v>
+        <v>38.00</v>
       </c>
     </row>
     <row r="399">
       <c t="inlineStr" r="A399">
         <is>
-          <t xml:space="preserve">United States Association for UNHCR</t>
+          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B399">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C399" s="66">
-        <v>61.00</v>
+        <v>99.30</v>
       </c>
     </row>
     <row r="400">
       <c t="inlineStr" r="A400">
         <is>
-          <t xml:space="preserve">United States Center for SafeSport</t>
+          <t xml:space="preserve">University of Colorado</t>
         </is>
       </c>
       <c t="inlineStr" r="B400">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">10/6/2027</t>
         </is>
       </c>
       <c r="C400" s="66">
-        <v>72.74</v>
+        <v>76.40</v>
       </c>
     </row>
     <row r="401">
       <c t="inlineStr" r="A401">
         <is>
-          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
+          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B401">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C401" s="66">
-        <v>38.00</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="402">
       <c t="inlineStr" r="A402">
         <is>
-          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
+          <t xml:space="preserve">University of Nebraska Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B402">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">7/15/2027</t>
         </is>
       </c>
       <c r="C402" s="66">
-        <v>99.30</v>
+        <v>81.10</v>
       </c>
     </row>
     <row r="403">
       <c t="inlineStr" r="A403">
         <is>
-          <t xml:space="preserve">University of Colorado</t>
+          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B403">
         <is>
-          <t xml:space="preserve">10/6/2027</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C403" s="66">
-        <v>76.40</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="404">
       <c t="inlineStr" r="A404">
         <is>
-          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
+          <t xml:space="preserve">University of Northern Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B404">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">10/1/2027</t>
         </is>
       </c>
       <c r="C404" s="66">
-        <v>93.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="405">
       <c t="inlineStr" r="A405">
         <is>
-          <t xml:space="preserve">University of Nebraska Foundation</t>
+          <t xml:space="preserve">University of Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B405">
         <is>
-          <t xml:space="preserve">7/15/2027</t>
-        </is>
-      </c>
-      <c r="C405" s="66">
-        <v>81.10</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C405" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
       <c t="inlineStr" r="A406">
         <is>
-          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
+          <t xml:space="preserve">University of Richmond</t>
         </is>
       </c>
       <c t="inlineStr" r="B406">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C406" s="66">
-        <v>77.00</v>
+        <v>82.18</v>
       </c>
     </row>
     <row r="407">
       <c t="inlineStr" r="A407">
         <is>
-          <t xml:space="preserve">University of Northern Iowa Foundation</t>
+          <t xml:space="preserve">University of the Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B407">
         <is>
-          <t xml:space="preserve">10/1/2027</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C407" s="66">
-        <v>74.00</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="408">
       <c t="inlineStr" r="A408">
         <is>
-          <t xml:space="preserve">University of Pacific</t>
+          <t xml:space="preserve">Veterans Community Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B408">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C408" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C408" s="66">
+        <v>88.83</v>
       </c>
     </row>
     <row r="409">
       <c t="inlineStr" r="A409">
         <is>
-          <t xml:space="preserve">University of Richmond</t>
+          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B409">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">7/13/2027</t>
         </is>
       </c>
       <c r="C409" s="66">
-        <v>82.18</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="410">
       <c t="inlineStr" r="A410">
         <is>
-          <t xml:space="preserve">University of the Pacific</t>
+          <t xml:space="preserve">Violet Research Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B410">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C410" s="66">
-        <v>95.48</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="411">
       <c t="inlineStr" r="A411">
         <is>
-          <t xml:space="preserve">Veterans Community Project</t>
+          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B411">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">11/5/2026</t>
         </is>
       </c>
       <c r="C411" s="66">
-        <v>88.83</v>
+        <v>28.00</v>
       </c>
     </row>
     <row r="412">
       <c t="inlineStr" r="A412">
         <is>
-          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
+          <t xml:space="preserve">VoteAmerica, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B412">
         <is>
-          <t xml:space="preserve">7/13/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C412" s="66">
-        <v>72.00</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="413">
       <c t="inlineStr" r="A413">
         <is>
-          <t xml:space="preserve">Violet Research Institute, Inc.</t>
+          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B413">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
-        </is>
-      </c>
-      <c r="C413" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C413" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="414">
       <c t="inlineStr" r="A414">
         <is>
-          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+          <t xml:space="preserve">Washington State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B414">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">7/8/2027</t>
         </is>
       </c>
       <c r="C414" s="66">
-        <v>28.00</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="415">
       <c t="inlineStr" r="A415">
         <is>
-          <t xml:space="preserve">VoteAmerica, Inc.</t>
+          <t xml:space="preserve">Western Illinois University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B415">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C415" s="66">
-        <v>93.37</v>
+        <v>77.54</v>
       </c>
     </row>
     <row r="416">
       <c t="inlineStr" r="A416">
         <is>
-          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B416">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C416" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C416" s="66">
+        <v>82.68</v>
       </c>
     </row>
     <row r="417">
       <c t="inlineStr" r="A417">
         <is>
-          <t xml:space="preserve">Washington State University Foundation</t>
+          <t xml:space="preserve">Wildlife Conservation Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B417">
         <is>
-          <t xml:space="preserve">7/8/2027</t>
+          <t xml:space="preserve">8/13/2027</t>
         </is>
       </c>
       <c r="C417" s="66">
-        <v>75.03</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="418">
       <c t="inlineStr" r="A418">
         <is>
-          <t xml:space="preserve">Western Illinois University Foundation</t>
+          <t xml:space="preserve">Winning for Women, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B418">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C418" s="66">
-        <v>77.54</v>
+        <v>66.70</v>
       </c>
     </row>
     <row r="419">
       <c t="inlineStr" r="A419">
         <is>
-          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+          <t xml:space="preserve">Women for Women International</t>
         </is>
       </c>
       <c t="inlineStr" r="B419">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C419" s="66">
-        <v>82.68</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="420">
       <c t="inlineStr" r="A420">
         <is>
-          <t xml:space="preserve">Wildlife Conservation Network</t>
+          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B420">
         <is>
-          <t xml:space="preserve">8/13/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C420" s="66">
-        <v>92.13</v>
+        <v>71.40</v>
       </c>
     </row>
     <row r="421">
       <c t="inlineStr" r="A421">
         <is>
-          <t xml:space="preserve">Winning for Women, Inc.</t>
+          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B421">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
-        </is>
-      </c>
-      <c r="C421" s="66">
-        <v>66.70</v>
+          <t xml:space="preserve">2/20/2027</t>
+        </is>
+      </c>
+      <c r="C421" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="422">
       <c t="inlineStr" r="A422">
         <is>
-          <t xml:space="preserve">Women for Women International</t>
+          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B422">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">5/20/2027</t>
         </is>
       </c>
       <c r="C422" s="66">
-        <v>79.06</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="423">
       <c t="inlineStr" r="A423">
         <is>
-          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B423">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C423" s="66">
-        <v>71.40</v>
+        <v>70.36</v>
       </c>
     </row>
     <row r="424">
       <c t="inlineStr" r="A424">
         <is>
-          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B424">
         <is>
-          <t xml:space="preserve">2/20/2027</t>
-        </is>
-      </c>
-      <c r="C424" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/24/2027</t>
+        </is>
+      </c>
+      <c r="C424" s="66">
+        <v>39.45</v>
       </c>
     </row>
     <row r="425">
       <c t="inlineStr" r="A425">
         <is>
-          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+          <t xml:space="preserve">YMCA of the Rockies</t>
         </is>
       </c>
       <c t="inlineStr" r="B425">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C425" s="66">
-        <v>79.00</v>
+        <v>81.65</v>
       </c>
     </row>
     <row r="426">
       <c t="inlineStr" r="A426">
         <is>
-          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+          <t xml:space="preserve">Young Judaea Global, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B426">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C426" s="66">
-        <v>70.36</v>
-      </c>
-    </row>
-    <row r="427">
-      <c t="inlineStr" r="A427">
-        <is>
-          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B427">
-        <is>
-          <t xml:space="preserve">8/24/2027</t>
-        </is>
-      </c>
-      <c r="C427" s="66">
-        <v>39.45</v>
-      </c>
-    </row>
-    <row r="428">
-      <c t="inlineStr" r="A428">
-        <is>
-          <t xml:space="preserve">YMCA of the Rockies</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B428">
-        <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C428" s="66">
-        <v>81.65</v>
-      </c>
-    </row>
-    <row r="429">
-      <c t="inlineStr" r="A429">
-        <is>
-          <t xml:space="preserve">Young Judaea Global, Inc.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B429">
-        <is>
-          <t xml:space="preserve">6/25/2027</t>
-        </is>
-      </c>
-      <c r="C429" s="66">
         <v>71.20</v>
       </c>
     </row>

--- a/downloadable-data/LA.xlsx
+++ b/downloadable-data/LA.xlsx
@@ -1418,52 +1418,52 @@
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Choice Books of Northern Virginia, Inc.</t>
+          <t xml:space="preserve">Children's Miracle Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">10/15/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C82" s="66">
-        <v>91.41</v>
+        <v>80.77</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">Christian Advocates Serving Evangelism, Inc.</t>
+          <t xml:space="preserve">Choice Books of Northern Virginia, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">10/15/2027</t>
         </is>
       </c>
       <c r="C83" s="66">
-        <v>1.17</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
+          <t xml:space="preserve">Christian Advocates Serving Evangelism, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C84" s="66">
-        <v>89.98</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
+          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
@@ -1471,64 +1471,64 @@
           <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
-      <c r="C85" s="65">
-        <v>0</v>
+      <c r="C85" s="66">
+        <v>89.98</v>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
+          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">9/10/2027</t>
-        </is>
-      </c>
-      <c r="C86" s="66">
-        <v>96.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C86" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Christian Relief Services, Inc.</t>
+          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
+          <t xml:space="preserve">9/10/2027</t>
         </is>
       </c>
       <c r="C87" s="66">
-        <v>90.70</v>
+        <v>96.00</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
+          <t xml:space="preserve">Christian Relief Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C88" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/10/2027</t>
+        </is>
+      </c>
+      <c r="C88" s="66">
+        <v>90.70</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">Christian Union, Inc.</t>
+          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
+          <t xml:space="preserve">2/6/2027</t>
         </is>
       </c>
       <c r="C89" s="65">
@@ -1538,102 +1538,102 @@
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">Church World Service, Inc.</t>
+          <t xml:space="preserve">Christian Union, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">8/25/2027</t>
-        </is>
-      </c>
-      <c r="C90" s="66">
-        <v>84.00</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">City Rescue Mission, Inc.</t>
+          <t xml:space="preserve">Church World Service, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">8/25/2027</t>
         </is>
       </c>
       <c r="C91" s="66">
-        <v>85.32</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">City Year, Inc.</t>
+          <t xml:space="preserve">City Rescue Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C92" s="66">
-        <v>82.62</v>
+        <v>85.32</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">Civil Rights Corps</t>
+          <t xml:space="preserve">City Year, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C93" s="66">
-        <v>82.10</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Colon Cancer Coalition</t>
+          <t xml:space="preserve">Civil Rights Corps</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C94" s="66">
-        <v>86.73</v>
+        <v>82.10</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
+          <t xml:space="preserve">Colon Cancer Coalition</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">11/20/2026</t>
-        </is>
-      </c>
-      <c r="C95" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C95" s="66">
+        <v>86.73</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
+          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">11/20/2026</t>
         </is>
       </c>
       <c r="C96" s="65">
@@ -1643,37 +1643,37 @@
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
+          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
-        </is>
-      </c>
-      <c r="C97" s="66">
-        <v>65.99</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C97" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Compassion and Choices</t>
+          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">4/9/2027</t>
         </is>
       </c>
       <c r="C98" s="66">
-        <v>84.00</v>
+        <v>65.99</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">Compassion and Choices Action Network</t>
+          <t xml:space="preserve">Compassion and Choices</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
@@ -1682,108 +1682,108 @@
         </is>
       </c>
       <c r="C99" s="66">
-        <v>85.00</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">Compassion In World Farming, Inc.</t>
+          <t xml:space="preserve">Compassion and Choices Action Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">10/10/2027</t>
-        </is>
-      </c>
-      <c r="C100" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C100" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Concerns of Police Survivors</t>
+          <t xml:space="preserve">Compassion In World Farming, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">10/7/2027</t>
-        </is>
-      </c>
-      <c r="C101" s="66">
-        <v>92.30</v>
+          <t xml:space="preserve">10/10/2027</t>
+        </is>
+      </c>
+      <c r="C101" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Consumer Reports, Inc.</t>
+          <t xml:space="preserve">Concerns of Police Survivors</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">10/7/2027</t>
         </is>
       </c>
       <c r="C102" s="66">
-        <v>84.00</v>
+        <v>92.30</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
+          <t xml:space="preserve">Consumer Reports, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">6/25/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C103" s="66">
-        <v>73.00</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
+          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C104" s="66">
-        <v>74.25</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Covenant House</t>
+          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C105" s="66">
-        <v>80.00</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Covenant House New Orleans</t>
+          <t xml:space="preserve">Covenant House</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">7/28/2028</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C106" s="66">
@@ -1793,121 +1793,121 @@
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
+          <t xml:space="preserve">Covenant House New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
+          <t xml:space="preserve">7/28/2028</t>
         </is>
       </c>
       <c r="C107" s="66">
-        <v>84.38</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
+          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">12/4/2026</t>
         </is>
       </c>
       <c r="C108" s="66">
-        <v>85.18</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
+          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C109" s="66">
-        <v>64.30</v>
+        <v>85.18</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">D.A.R.E. America</t>
+          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C110" s="66">
-        <v>44.00</v>
+        <v>64.30</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
+          <t xml:space="preserve">D.A.R.E. America</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C111" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/11/2027</t>
+        </is>
+      </c>
+      <c r="C111" s="66">
+        <v>44.00</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">Deep South Today</t>
+          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
-        </is>
-      </c>
-      <c r="C112" s="66">
-        <v>74.56</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C112" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
+          <t xml:space="preserve">Deep South Today</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">6/6/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C113" s="66">
-        <v>68.82</v>
+        <v>74.56</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Disabled Veterans National Foundation</t>
+          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">10/19/2027</t>
+          <t xml:space="preserve">6/6/2027</t>
         </is>
       </c>
       <c r="C114" s="66">
-        <v>31.01</v>
+        <v>68.82</v>
       </c>
     </row>
     <row r="115">
@@ -2281,8 +2281,8 @@
           <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
-      <c r="C139" s="65">
-        <v>0</v>
+      <c r="C139" s="66">
+        <v>48.00</v>
       </c>
     </row>
     <row r="140">
@@ -2438,52 +2438,52 @@
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">Goodwill Industries International, Inc</t>
+          <t xml:space="preserve">Go Campaign</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C150" s="66">
-        <v>87.00</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Green America</t>
+          <t xml:space="preserve">Goodwill Industries International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C151" s="66">
-        <v>87.47</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
+          <t xml:space="preserve">Green America</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C152" s="66">
-        <v>76.85</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">Greenpeace, Inc.</t>
+          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
@@ -2492,153 +2492,153 @@
         </is>
       </c>
       <c r="C153" s="66">
-        <v>62.56</v>
+        <v>76.85</v>
       </c>
     </row>
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">Gustavus Adolphus College</t>
+          <t xml:space="preserve">Greenpeace, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">2/24/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C154" s="66">
-        <v>93.00</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
+          <t xml:space="preserve">Gustavus Adolphus College</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C155" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/24/2027</t>
+        </is>
+      </c>
+      <c r="C155" s="66">
+        <v>93.00</v>
       </c>
     </row>
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">Healing Justice Project</t>
+          <t xml:space="preserve">Habitat for Horses, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
-        </is>
-      </c>
-      <c r="C156" s="66">
-        <v>82.48</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">Healing Protectors</t>
+          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
-        </is>
-      </c>
-      <c r="C157" s="66">
-        <v>47.19</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">Heifer Project International</t>
+          <t xml:space="preserve">Healing Justice Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">3/19/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C158" s="66">
-        <v>72.90</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">Help Me See, Inc.</t>
+          <t xml:space="preserve">Healing Protectors</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
+          <t xml:space="preserve">3/2/2027</t>
         </is>
       </c>
       <c r="C159" s="66">
-        <v>83.00</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">Herzog Tomorrow Foundation</t>
+          <t xml:space="preserve">Heifer Project International</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
-        </is>
-      </c>
-      <c r="C160" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/19/2027</t>
+        </is>
+      </c>
+      <c r="C160" s="66">
+        <v>72.90</v>
       </c>
     </row>
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">HIAS Foundation, Inc.</t>
+          <t xml:space="preserve">Help Me See, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C161" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/12/2027</t>
+        </is>
+      </c>
+      <c r="C161" s="66">
+        <v>83.00</v>
       </c>
     </row>
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
+          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
-        </is>
-      </c>
-      <c r="C162" s="66">
-        <v>81.00</v>
+          <t xml:space="preserve">10/22/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">Home Builders Institute</t>
+          <t xml:space="preserve">Herzog Tomorrow Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C163" s="65">
@@ -2648,357 +2648,357 @@
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">Human Appeal, Inc.</t>
+          <t xml:space="preserve">HIAS Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">1/12/2027</t>
-        </is>
-      </c>
-      <c r="C164" s="66">
-        <v>54.20</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C164" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
+          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C165" s="66">
-        <v>63.39</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">Human Rights Watch, Inc.</t>
+          <t xml:space="preserve">Home Builders Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C166" s="66">
-        <v>68.67</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C166" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">Human-I-T</t>
+          <t xml:space="preserve">Human Appeal, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">8/30/2027</t>
+          <t xml:space="preserve">1/12/2027</t>
         </is>
       </c>
       <c r="C167" s="66">
-        <v>1.00</v>
+        <v>54.20</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">Humane Society of Missouri</t>
+          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C168" s="66">
-        <v>80.50</v>
+        <v>63.39</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">Illinois State University Foundation</t>
+          <t xml:space="preserve">Human Rights Watch, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">5/21/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C169" s="66">
-        <v>61.30</v>
+        <v>68.67</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
+          <t xml:space="preserve">Human-I-T</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C170" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/30/2027</t>
+        </is>
+      </c>
+      <c r="C170" s="66">
+        <v>1.00</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">In Medias Res</t>
+          <t xml:space="preserve">Humane Society of Missouri</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C171" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/7/2027</t>
+        </is>
+      </c>
+      <c r="C171" s="66">
+        <v>80.50</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">Independent Council on Women's Sport</t>
+          <t xml:space="preserve">Illinois State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">5/21/2027</t>
         </is>
       </c>
       <c r="C172" s="66">
-        <v>94.44</v>
+        <v>61.30</v>
       </c>
     </row>
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">Infact</t>
+          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
-        </is>
-      </c>
-      <c r="C173" s="66">
-        <v>89.97</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C173" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">INROADS, Inc.</t>
+          <t xml:space="preserve">In Medias Res</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">10/1/2027</t>
-        </is>
-      </c>
-      <c r="C174" s="66">
-        <v>47.80</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C174" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
+          <t xml:space="preserve">Independent Council on Women's Sport</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C175" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C175" s="66">
+        <v>94.44</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
+          <t xml:space="preserve">Infact</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C176" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C176" s="66">
+        <v>89.97</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">International Justice Mission</t>
+          <t xml:space="preserve">INROADS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
-        </is>
-      </c>
-      <c r="C177" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/1/2027</t>
+        </is>
+      </c>
+      <c r="C177" s="66">
+        <v>47.80</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
+          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C178" s="66">
-        <v>83.13</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">International Union of Police Associations</t>
+          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C179" s="66">
-        <v>47.90</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">Iona University</t>
+          <t xml:space="preserve">International Justice Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C180" s="66">
-        <v>89.81</v>
+          <t xml:space="preserve">3/24/2027</t>
+        </is>
+      </c>
+      <c r="C180" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">Isaad Foundation</t>
+          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">9/18/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C181" s="66">
-        <v>96.30</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
+          <t xml:space="preserve">International Union of Police Associations</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C182" s="66">
-        <v>75.43</v>
+        <v>47.90</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">Jewish Democratic Council of America</t>
+          <t xml:space="preserve">Iona University</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C183" s="66">
-        <v>50.07</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">Jewish Voice Ministries International</t>
+          <t xml:space="preserve">Isaad Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C184" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/18/2027</t>
+        </is>
+      </c>
+      <c r="C184" s="66">
+        <v>96.30</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
+          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
+          <t xml:space="preserve">4/27/2027</t>
         </is>
       </c>
       <c r="C185" s="66">
-        <v>89.00</v>
+        <v>75.43</v>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
+          <t xml:space="preserve">Jewish Democratic Council of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C186" s="66">
-        <v>75.00</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
+          <t xml:space="preserve">Jewish Voice Ministries International</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">9/5/2027</t>
+          <t xml:space="preserve">12/9/2026</t>
         </is>
       </c>
       <c r="C187" s="65">
@@ -3008,42 +3008,42 @@
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
+          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C188" s="66">
-        <v>98.28</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">Khan Academy, Inc.</t>
+          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C189" s="66">
-        <v>86.36</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
+          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
+          <t xml:space="preserve">9/5/2027</t>
         </is>
       </c>
       <c r="C190" s="65">
@@ -3053,747 +3053,747 @@
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">L.E.A.D. Inc.</t>
+          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C191" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C191" s="66">
+        <v>98.28</v>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">La Leche League International, Inc.</t>
+          <t xml:space="preserve">Khan Academy, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C192" s="66">
-        <v>57.00</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
+          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C193" s="66">
-        <v>63.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C193" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">Lasell University</t>
+          <t xml:space="preserve">L.E.A.D. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
-        </is>
-      </c>
-      <c r="C194" s="66">
-        <v>86.90</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C194" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
+          <t xml:space="preserve">La Leche League International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C195" s="66">
-        <v>10.60</v>
+        <v>57.00</v>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">League of Conservation Voters, Inc.</t>
+          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">9/23/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C196" s="66">
-        <v>92.00</v>
+        <v>63.00</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
+          <t xml:space="preserve">Lasell University</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">10/28/2026</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C197" s="66">
-        <v>96.80</v>
+        <v>86.90</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">Life Teen, Inc.</t>
+          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C198" s="66">
-        <v>76.40</v>
+        <v>10.60</v>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">Live Action</t>
+          <t xml:space="preserve">League of Conservation Voters, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">9/23/2027</t>
         </is>
       </c>
       <c r="C199" s="66">
-        <v>81.13</v>
+        <v>92.00</v>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">Living Waters for the World</t>
+          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">10/28/2026</t>
         </is>
       </c>
       <c r="C200" s="66">
-        <v>78.81</v>
+        <v>96.80</v>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
+          <t xml:space="preserve">Life Teen, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C201" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C201" s="66">
+        <v>76.40</v>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
+          <t xml:space="preserve">Live Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C202" s="66">
-        <v>76.03</v>
+        <v>81.13</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
+          <t xml:space="preserve">Living Waters for the World</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C203" s="66">
-        <v>62.00</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">Madison House</t>
+          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
-        </is>
-      </c>
-      <c r="C204" s="66">
-        <v>77.79</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C204" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
+          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">8/6/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C205" s="66">
-        <v>86.00</v>
+        <v>76.03</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">MAP International, Inc.</t>
+          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C206" s="66">
-        <v>99.00</v>
+        <v>62.00</v>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">March of Dimes</t>
+          <t xml:space="preserve">Madison House</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">12/30/2026</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C207" s="66">
-        <v>74.00</v>
+        <v>77.79</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">Marist University</t>
+          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">8/6/2027</t>
         </is>
       </c>
       <c r="C208" s="66">
-        <v>91.00</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
+          <t xml:space="preserve">MAP International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C209" s="66">
-        <v>91.74</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">Meals on Wheels America</t>
+          <t xml:space="preserve">March of Dimes</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">5/27/2027</t>
+          <t xml:space="preserve">12/30/2026</t>
         </is>
       </c>
       <c r="C210" s="66">
-        <v>59.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
+          <t xml:space="preserve">Marist University</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">6/9/2027</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C211" s="66">
-        <v>80.94</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
+          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">12/8/2026</t>
-        </is>
-      </c>
-      <c r="C212" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/17/2027</t>
+        </is>
+      </c>
+      <c r="C212" s="66">
+        <v>91.74</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
+          <t xml:space="preserve">Meals on Wheels America</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">5/27/2027</t>
         </is>
       </c>
       <c r="C213" s="66">
-        <v>91.00</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">Mercatus Center, Inc.</t>
+          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">6/9/2027</t>
         </is>
       </c>
       <c r="C214" s="66">
-        <v>90.25</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">Mercy for Animals, Inc.</t>
+          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C215" s="66">
-        <v>75.82</v>
+          <t xml:space="preserve">12/8/2026</t>
+        </is>
+      </c>
+      <c r="C215" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">Mercy Hospital, Cedar Rapids, Iowa Endowment Found</t>
+          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C216" s="66">
-        <v>93.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">Mercy Ships</t>
+          <t xml:space="preserve">Mercatus Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">8/26/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C217" s="66">
-        <v>78.18</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">Middle East Policy Network, Inc.</t>
+          <t xml:space="preserve">Mercy for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C218" s="66">
-        <v>73.83</v>
+        <v>75.82</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
+          <t xml:space="preserve">Mercy Hospital, Cedar Rapids, Iowa Endowment Found</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C219" s="66">
-        <v>88.00</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">Minutes Matter-MCADD</t>
+          <t xml:space="preserve">Mercy Ships</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">7/19/2027</t>
-        </is>
-      </c>
-      <c r="C220" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/26/2027</t>
+        </is>
+      </c>
+      <c r="C220" s="66">
+        <v>78.18</v>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">Miracle Flights</t>
+          <t xml:space="preserve">Middle East Policy Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C221" s="66">
-        <v>52.00</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
+          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C222" s="66">
-        <v>94.50</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">mothers2mothers United States, Inc.</t>
+          <t xml:space="preserve">Minutes Matter-MCADD</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
-        </is>
-      </c>
-      <c r="C223" s="66">
-        <v>60.00</v>
+          <t xml:space="preserve">7/19/2027</t>
+        </is>
+      </c>
+      <c r="C223" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">Mount Saint Marys University</t>
+          <t xml:space="preserve">Miracle Flights</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C224" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C224" s="66">
+        <v>52.00</v>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">Mountain States Legal Foundation</t>
+          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C225" s="66">
-        <v>69.99</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">MrCharity, Inc.</t>
+          <t xml:space="preserve">mothers2mothers United States, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
-        </is>
-      </c>
-      <c r="C226" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/27/2027</t>
+        </is>
+      </c>
+      <c r="C226" s="66">
+        <v>60.00</v>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
+          <t xml:space="preserve">Mount Saint Marys University</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
-        </is>
-      </c>
-      <c r="C227" s="66">
-        <v>77.80</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C227" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
+          <t xml:space="preserve">Mountain States Legal Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">12/19/2026</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C228" s="66">
-        <v>66.90</v>
+        <v>69.99</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">Naropa University</t>
+          <t xml:space="preserve">MrCharity, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
-        </is>
-      </c>
-      <c r="C229" s="66">
-        <v>76.21</v>
+          <t xml:space="preserve">2/23/2027</t>
+        </is>
+      </c>
+      <c r="C229" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
+          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">10/20/2026</t>
         </is>
       </c>
       <c r="C230" s="66">
-        <v>65.00</v>
+        <v>54.00</v>
       </c>
     </row>
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">National Audubon Society, Inc.</t>
+          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">6/24/2027</t>
         </is>
       </c>
       <c r="C231" s="66">
-        <v>80.00</v>
+        <v>77.80</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
+          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">12/19/2026</t>
         </is>
       </c>
       <c r="C232" s="66">
-        <v>81.00</v>
+        <v>66.90</v>
       </c>
     </row>
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
+          <t xml:space="preserve">Naropa University</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C233" s="66">
-        <v>92.28</v>
+        <v>76.21</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">National Council of Nonprofits</t>
+          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C234" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C234" s="66">
+        <v>65.00</v>
       </c>
     </row>
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
+          <t xml:space="preserve">National Audubon Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C235" s="66">
-        <v>49.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">National Foundation for Cancer Research</t>
+          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C236" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C236" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">National Geographic Society</t>
+          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">3/18/2027</t>
+          <t xml:space="preserve">8/7/2027</t>
         </is>
       </c>
       <c r="C237" s="66">
-        <v>77.00</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">National LGBTQ Task Force</t>
+          <t xml:space="preserve">National Council of Nonprofits</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C238" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C238" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">National Network of Abortion Funds</t>
+          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
-        </is>
-      </c>
-      <c r="C239" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C239" s="66">
+        <v>49.00</v>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">National PKU Alliance, Inc.</t>
+          <t xml:space="preserve">National Foundation for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">12/1/2026</t>
         </is>
       </c>
       <c r="C240" s="65">
@@ -3803,42 +3803,42 @@
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">National Rifle Association of America</t>
+          <t xml:space="preserve">National Geographic Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">10/1/2027</t>
+          <t xml:space="preserve">3/18/2027</t>
         </is>
       </c>
       <c r="C241" s="66">
-        <v>62.91</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
+          <t xml:space="preserve">National LGBTQ Task Force</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C242" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C242" s="66">
+        <v>80.00</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
+          <t xml:space="preserve">National Network of Abortion Funds</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C243" s="65">
@@ -3848,522 +3848,522 @@
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">National Space Society</t>
+          <t xml:space="preserve">National Park Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C244" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/20/2026</t>
+        </is>
+      </c>
+      <c r="C244" s="66">
+        <v>72.00</v>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">National University</t>
+          <t xml:space="preserve">National PKU Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C245" s="66">
-        <v>42.69</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C245" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">National Veterans Memorial and Museum</t>
+          <t xml:space="preserve">National Rifle Association of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">10/1/2027</t>
         </is>
       </c>
       <c r="C246" s="66">
-        <v>72.63</v>
+        <v>62.91</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">National Wheelchair Basketball Association</t>
+          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
-        </is>
-      </c>
-      <c r="C247" s="66">
-        <v>77.80</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C247" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">National Wildlife Federation</t>
+          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
-        </is>
-      </c>
-      <c r="C248" s="66">
-        <v>86.00</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C248" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
+          <t xml:space="preserve">National Space Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
-        </is>
-      </c>
-      <c r="C249" s="66">
-        <v>1.60</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C249" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">Network for Good, Inc</t>
+          <t xml:space="preserve">National University</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C250" s="66">
-        <v>97.80</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">New Harvest, Inc.</t>
+          <t xml:space="preserve">National Veterans Memorial and Museum</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C251" s="66">
-        <v>88.49</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
+          <t xml:space="preserve">National Wheelchair Basketball Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C252" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/12/2027</t>
+        </is>
+      </c>
+      <c r="C252" s="66">
+        <v>77.80</v>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">Nurse-Family Partnership</t>
+          <t xml:space="preserve">National Wildlife Federation</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C253" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C253" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">Ocean Conservancy</t>
+          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C254" s="66">
-        <v>74.06</v>
+        <v>1.60</v>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
+          <t xml:space="preserve">Network for Good, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C255" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C255" s="66">
+        <v>97.80</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">Operation Smile, Inc.</t>
+          <t xml:space="preserve">New Harvest, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C256" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C256" s="66">
+        <v>88.49</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
+          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">8/18/2027</t>
-        </is>
-      </c>
-      <c r="C257" s="66">
-        <v>77.59</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C257" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">Our Change Foundation</t>
+          <t xml:space="preserve">Nurse-Family Partnership</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">10/13/2027</t>
-        </is>
-      </c>
-      <c r="C258" s="66">
-        <v>71.30</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C258" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">Pace University</t>
+          <t xml:space="preserve">Ocean Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C259" s="66">
-        <v>88.30</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
+          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">10/16/2027</t>
-        </is>
-      </c>
-      <c r="C260" s="66">
-        <v>55.43</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C260" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">Panorama Global</t>
+          <t xml:space="preserve">Operation Smile, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
-        </is>
-      </c>
-      <c r="C261" s="66">
-        <v>84.52</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C261" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">Paralyzed Veterans of America</t>
+          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">8/18/2027</t>
         </is>
       </c>
       <c r="C262" s="66">
-        <v>59.00</v>
+        <v>77.59</v>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
+          <t xml:space="preserve">Our Change Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">2/9/2027</t>
+          <t xml:space="preserve">10/13/2027</t>
         </is>
       </c>
       <c r="C263" s="66">
-        <v>90.00</v>
+        <v>71.30</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
+          <t xml:space="preserve">Pace University</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
-        </is>
-      </c>
-      <c r="C264" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/1/2027</t>
+        </is>
+      </c>
+      <c r="C264" s="66">
+        <v>88.30</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">Pathfinder International</t>
+          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C265" s="66">
-        <v>85.33</v>
+        <v>55.43</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">patriotic Hearts, Inc.</t>
+          <t xml:space="preserve">Panorama Global</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C266" s="66">
-        <v>56.00</v>
+        <v>84.52</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">People for the American Way</t>
+          <t xml:space="preserve">Paralyzed Veterans of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C267" s="66">
-        <v>38.00</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">People for the American Way Foundation</t>
+          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">2/9/2027</t>
         </is>
       </c>
       <c r="C268" s="66">
-        <v>60.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
+          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
-        </is>
-      </c>
-      <c r="C269" s="66">
-        <v>83.76</v>
+          <t xml:space="preserve">7/16/2027</t>
+        </is>
+      </c>
+      <c r="C269" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
+          <t xml:space="preserve">Pathfinder International</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C270" s="66">
-        <v>58.00</v>
+        <v>85.33</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
+          <t xml:space="preserve">patriotic Hearts, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">8/28/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C271" s="66">
-        <v>79.00</v>
+        <v>56.00</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
+          <t xml:space="preserve">People for the American Way Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C272" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C272" s="66">
+        <v>60.00</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
+          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C273" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C273" s="66">
+        <v>83.76</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
+          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C274" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/12/2027</t>
+        </is>
+      </c>
+      <c r="C274" s="66">
+        <v>58.00</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">Pledgeling Foundation</t>
+          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">8/28/2027</t>
         </is>
       </c>
       <c r="C275" s="66">
-        <v>65.93</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">Polar Bears International</t>
+          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">2/2/2027</t>
-        </is>
-      </c>
-      <c r="C276" s="66">
-        <v>86.00</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C276" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
+          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
-        </is>
-      </c>
-      <c r="C277" s="66">
-        <v>85.54</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C277" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">Pratt Institute</t>
+          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C278" s="65">
@@ -4373,207 +4373,207 @@
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">Primo Cares, Inc.</t>
+          <t xml:space="preserve">Pledgeling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C279" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/27/2027</t>
+        </is>
+      </c>
+      <c r="C279" s="66">
+        <v>65.93</v>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries</t>
+          <t xml:space="preserve">Polar Bears International</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">2/2/2027</t>
         </is>
       </c>
       <c r="C280" s="66">
-        <v>68.60</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
+          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C281" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/27/2027</t>
+        </is>
+      </c>
+      <c r="C281" s="66">
+        <v>85.54</v>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">Project Cure, Inc.</t>
+          <t xml:space="preserve">Pratt Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
-        </is>
-      </c>
-      <c r="C282" s="66">
-        <v>27.00</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C282" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
+          <t xml:space="preserve">Primo Cares, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C283" s="66">
-        <v>88.71</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C283" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">Proteus Fund, Inc.</t>
+          <t xml:space="preserve">Prison Fellowship Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C284" s="66">
-        <v>81.25</v>
+        <v>68.60</v>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">Providence House</t>
+          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
-        </is>
-      </c>
-      <c r="C285" s="66">
-        <v>92.06</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C285" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">Public Health Foundation Enterprise, Inc</t>
+          <t xml:space="preserve">Project Cure, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C286" s="66">
-        <v>94.97</v>
+        <v>27.00</v>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
+          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C287" s="66">
-        <v>84.22</v>
+        <v>88.71</v>
       </c>
     </row>
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">Re:Power</t>
+          <t xml:space="preserve">Proteus Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C288" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/2/2027</t>
+        </is>
+      </c>
+      <c r="C288" s="66">
+        <v>81.25</v>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">Reproductive Freedom for All</t>
+          <t xml:space="preserve">Providence House</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C289" s="66">
-        <v>70.00</v>
+        <v>92.06</v>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">RezilientKidz</t>
+          <t xml:space="preserve">Public Health Foundation Enterprise, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C290" s="66">
-        <v>94.35</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">Rodale Institute</t>
+          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C291" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/10/2027</t>
+        </is>
+      </c>
+      <c r="C291" s="66">
+        <v>84.22</v>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
+          <t xml:space="preserve">Re:Power</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">12/12/2026</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C292" s="65">
@@ -4583,1072 +4583,1072 @@
     <row r="293">
       <c t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
+          <t xml:space="preserve">Reproductive Freedom for All</t>
         </is>
       </c>
       <c t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">10/19/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C293" s="66">
-        <v>4.60</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="294">
       <c t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
+          <t xml:space="preserve">RezilientKidz</t>
         </is>
       </c>
       <c t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C294" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C294" s="66">
+        <v>94.35</v>
       </c>
     </row>
     <row r="295">
       <c t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">Rush University Medical Center</t>
+          <t xml:space="preserve">Rodale Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
-        </is>
-      </c>
-      <c r="C295" s="66">
-        <v>91.41</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C295" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">Rutgers University Foundation</t>
+          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
         </is>
       </c>
       <c t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
-        </is>
-      </c>
-      <c r="C296" s="66">
-        <v>87.46</v>
+          <t xml:space="preserve">12/12/2026</t>
+        </is>
+      </c>
+      <c r="C296" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">Sagamore Institute, Inc.</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
         </is>
       </c>
       <c t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
-        </is>
-      </c>
-      <c r="C297" s="66">
-        <v>91.61</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C297" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">Saint John's University</t>
+          <t xml:space="preserve">Rush University Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
+          <t xml:space="preserve">7/23/2027</t>
         </is>
       </c>
       <c r="C298" s="66">
-        <v>92.91</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">Save the Chimps, Inc.</t>
+          <t xml:space="preserve">Rutgers University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C299" s="66">
-        <v>79.70</v>
+        <v>87.46</v>
       </c>
     </row>
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">Seattle Pacific University</t>
+          <t xml:space="preserve">Sagamore Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C300" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C300" s="66">
+        <v>91.61</v>
       </c>
     </row>
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">Second Harvest Food Bank of Greater New Orleans</t>
+          <t xml:space="preserve">Saint John's University</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
-        </is>
-      </c>
-      <c r="C301" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/12/2027</t>
+        </is>
+      </c>
+      <c r="C301" s="66">
+        <v>92.91</v>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
+          <t xml:space="preserve">Save the Chimps, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C302" s="66">
-        <v>94.00</v>
+        <v>79.70</v>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">Seti Institute</t>
+          <t xml:space="preserve">Seattle Pacific University</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C303" s="66">
-        <v>69.60</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C303" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">Share Our Strength</t>
+          <t xml:space="preserve">Second Harvest Food Bank of Greater New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
-        </is>
-      </c>
-      <c r="C304" s="66">
-        <v>58.73</v>
+          <t xml:space="preserve">5/20/2027</t>
+        </is>
+      </c>
+      <c r="C304" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
+          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C305" s="66">
-        <v>97.29</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">Sierra  Club</t>
+          <t xml:space="preserve">Seti Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">12/22/2026</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C306" s="66">
-        <v>82.00</v>
+        <v>69.60</v>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">Sister Rising Worldwide</t>
+          <t xml:space="preserve">Share Our Strength</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">1/28/2027</t>
-        </is>
-      </c>
-      <c r="C307" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C307" s="66">
+        <v>58.73</v>
       </c>
     </row>
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">Sixpoint, Inc.</t>
+          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C308" s="66">
-        <v>77.16</v>
+        <v>97.29</v>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
+          <t xml:space="preserve">Sierra  Club</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">4/22/2027</t>
+          <t xml:space="preserve">12/22/2026</t>
         </is>
       </c>
       <c r="C309" s="66">
-        <v>90.00</v>
+        <v>82.00</v>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">Social Purpose Corrections</t>
+          <t xml:space="preserve">Sister Rising Worldwide</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
-        </is>
-      </c>
-      <c r="C310" s="66">
-        <v>47.93</v>
+          <t xml:space="preserve">1/28/2027</t>
+        </is>
+      </c>
+      <c r="C310" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
+          <t xml:space="preserve">Sixpoint, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">9/2/2027</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C311" s="66">
-        <v>72.80</v>
+        <v>77.16</v>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">Soldiers' Angels</t>
+          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">4/22/2027</t>
         </is>
       </c>
       <c r="C312" s="66">
-        <v>93.33</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
+          <t xml:space="preserve">Social Purpose Corrections</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">7/29/2027</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C313" s="66">
-        <v>86.00</v>
+        <v>47.93</v>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">South Dakota State University Foundation</t>
+          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C314" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/2/2027</t>
+        </is>
+      </c>
+      <c r="C314" s="66">
+        <v>72.80</v>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
+          <t xml:space="preserve">Soldiers' Angels</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C315" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C315" s="66">
+        <v>93.33</v>
       </c>
     </row>
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">Special Olympics, Inc.</t>
+          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C316" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/29/2027</t>
+        </is>
+      </c>
+      <c r="C316" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">SPLC Action Fund</t>
+          <t xml:space="preserve">South Dakota State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">9/17/2027</t>
-        </is>
-      </c>
-      <c r="C317" s="66">
-        <v>72.81</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C317" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
+          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
-        </is>
-      </c>
-      <c r="C318" s="66">
-        <v>85.31</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C318" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">State University of Iowa Foundation</t>
+          <t xml:space="preserve">Special Olympics, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">9/4/2027</t>
-        </is>
-      </c>
-      <c r="C319" s="66">
-        <v>79.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C319" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
+          <t xml:space="preserve">SPLC Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C320" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/17/2027</t>
+        </is>
+      </c>
+      <c r="C320" s="66">
+        <v>72.81</v>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
+          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C321" s="66">
-        <v>92.00</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">Students for Life Action, Inc.</t>
+          <t xml:space="preserve">State University of Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">11/7/2026</t>
-        </is>
-      </c>
-      <c r="C322" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/4/2027</t>
+        </is>
+      </c>
+      <c r="C322" s="66">
+        <v>79.00</v>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
+          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">8/12/2027</t>
-        </is>
-      </c>
-      <c r="C323" s="66">
-        <v>89.29</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C323" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">Teacher Freedom Alliance</t>
+          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
-        </is>
-      </c>
-      <c r="C324" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/24/2027</t>
+        </is>
+      </c>
+      <c r="C324" s="66">
+        <v>92.00</v>
       </c>
     </row>
     <row r="325">
       <c t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">The Actors' Fund of America</t>
+          <t xml:space="preserve">Students for Life Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
-        </is>
-      </c>
-      <c r="C325" s="66">
-        <v>86.73</v>
+          <t xml:space="preserve">11/7/2026</t>
+        </is>
+      </c>
+      <c r="C325" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="326">
       <c t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">8/12/2027</t>
         </is>
       </c>
       <c r="C326" s="66">
-        <v>39.00</v>
+        <v>89.29</v>
       </c>
     </row>
     <row r="327">
       <c t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">The American Society for the Prevention of Cruelty</t>
+          <t xml:space="preserve">Teacher Freedom Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
-        </is>
-      </c>
-      <c r="C327" s="66">
-        <v>75.00</v>
+          <t xml:space="preserve">6/24/2027</t>
+        </is>
+      </c>
+      <c r="C327" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="328">
       <c t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">The American University</t>
+          <t xml:space="preserve">The Actors' Fund of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">12/10/2026</t>
         </is>
       </c>
       <c r="C328" s="66">
-        <v>90.23</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="329">
       <c t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C329" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/15/2027</t>
+        </is>
+      </c>
+      <c r="C329" s="66">
+        <v>39.00</v>
       </c>
     </row>
     <row r="330">
       <c t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">The Anthony Davis Foundation</t>
+          <t xml:space="preserve">The American Society for the Prevention of Cruelty</t>
         </is>
       </c>
       <c t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">11/24/2026</t>
-        </is>
-      </c>
-      <c r="C330" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/16/2027</t>
+        </is>
+      </c>
+      <c r="C330" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="331">
       <c t="inlineStr" r="A331">
         <is>
-          <t xml:space="preserve">The Barack Obama Foundation</t>
+          <t xml:space="preserve">The American University</t>
         </is>
       </c>
       <c t="inlineStr" r="B331">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C331" s="66">
-        <v>55.90</v>
+        <v>90.23</v>
       </c>
     </row>
     <row r="332">
       <c t="inlineStr" r="A332">
         <is>
-          <t xml:space="preserve">The Baruch College Fund</t>
+          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B332">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
-        </is>
-      </c>
-      <c r="C332" s="66">
-        <v>84.00</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C332" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c t="inlineStr" r="A333">
         <is>
-          <t xml:space="preserve">The Call of Duty Endowment</t>
+          <t xml:space="preserve">The Anthony Davis Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B333">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
-        </is>
-      </c>
-      <c r="C333" s="66">
-        <v>73.00</v>
+          <t xml:space="preserve">11/24/2026</t>
+        </is>
+      </c>
+      <c r="C333" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="334">
       <c t="inlineStr" r="A334">
         <is>
-          <t xml:space="preserve">The Center for Alcohol Policy</t>
+          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B334">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">10/24/2026</t>
         </is>
       </c>
       <c r="C334" s="66">
-        <v>73.40</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="335">
       <c t="inlineStr" r="A335">
         <is>
-          <t xml:space="preserve">The Center for Investigative Reporting</t>
+          <t xml:space="preserve">The Barack Obama Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B335">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C335" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C335" s="66">
+        <v>55.90</v>
       </c>
     </row>
     <row r="336">
       <c t="inlineStr" r="A336">
         <is>
-          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
+          <t xml:space="preserve">The Baruch College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B336">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C336" s="66">
-        <v>71.00</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="337">
       <c t="inlineStr" r="A337">
         <is>
-          <t xml:space="preserve">The Center for Victims of Torture</t>
+          <t xml:space="preserve">The Call of Duty Endowment</t>
         </is>
       </c>
       <c t="inlineStr" r="B337">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C337" s="66">
-        <v>74.00</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="338">
       <c t="inlineStr" r="A338">
         <is>
-          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
+          <t xml:space="preserve">The Center for Alcohol Policy</t>
         </is>
       </c>
       <c t="inlineStr" r="B338">
         <is>
-          <t xml:space="preserve">7/6/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C338" s="66">
-        <v>71.00</v>
+        <v>73.40</v>
       </c>
     </row>
     <row r="339">
       <c t="inlineStr" r="A339">
         <is>
-          <t xml:space="preserve">The Cleveland Clinic Foundation</t>
+          <t xml:space="preserve">The Center for Investigative Reporting</t>
         </is>
       </c>
       <c t="inlineStr" r="B339">
         <is>
-          <t xml:space="preserve">10/23/2027</t>
-        </is>
-      </c>
-      <c r="C339" s="66">
-        <v>89.51</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C339" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="340">
       <c t="inlineStr" r="A340">
         <is>
-          <t xml:space="preserve">The Colorado College</t>
+          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B340">
         <is>
-          <t xml:space="preserve">10/29/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C340" s="66">
-        <v>90.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="341">
       <c t="inlineStr" r="A341">
         <is>
-          <t xml:space="preserve">The Denver Rescue Mission</t>
+          <t xml:space="preserve">The Center for Victims of Torture</t>
         </is>
       </c>
       <c t="inlineStr" r="B341">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C341" s="66">
-        <v>82.96</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="342">
       <c t="inlineStr" r="A342">
         <is>
-          <t xml:space="preserve">The Edison Institute</t>
+          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
         </is>
       </c>
       <c t="inlineStr" r="B342">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">7/6/2027</t>
         </is>
       </c>
       <c r="C342" s="66">
-        <v>78.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="343">
       <c t="inlineStr" r="A343">
         <is>
-          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+          <t xml:space="preserve">The Colorado College</t>
         </is>
       </c>
       <c t="inlineStr" r="B343">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C343" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/29/2027</t>
+        </is>
+      </c>
+      <c r="C343" s="66">
+        <v>90.00</v>
       </c>
     </row>
     <row r="344">
       <c t="inlineStr" r="A344">
         <is>
-          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+          <t xml:space="preserve">The Denver Rescue Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B344">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C344" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/20/2027</t>
+        </is>
+      </c>
+      <c r="C344" s="66">
+        <v>82.96</v>
       </c>
     </row>
     <row r="345">
       <c t="inlineStr" r="A345">
         <is>
-          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
+          <t xml:space="preserve">The Edison Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B345">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C345" s="66">
-        <v>76.48</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="346">
       <c t="inlineStr" r="A346">
         <is>
-          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
+          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B346">
         <is>
-          <t xml:space="preserve">5/15/2027</t>
-        </is>
-      </c>
-      <c r="C346" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C346" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="347">
       <c t="inlineStr" r="A347">
         <is>
-          <t xml:space="preserve">The Heritage Foundation</t>
+          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
         </is>
       </c>
       <c t="inlineStr" r="B347">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C347" s="66">
-        <v>83.00</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C347" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="348">
       <c t="inlineStr" r="A348">
         <is>
-          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
+          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
         </is>
       </c>
       <c t="inlineStr" r="B348">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C348" s="66">
-        <v>89.00</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="349">
       <c t="inlineStr" r="A349">
         <is>
-          <t xml:space="preserve">The Independent Institute</t>
+          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B349">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">5/15/2027</t>
         </is>
       </c>
       <c r="C349" s="66">
-        <v>77.51</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="350">
       <c t="inlineStr" r="A350">
         <is>
-          <t xml:space="preserve">The International Wildlife Rehab. Council</t>
+          <t xml:space="preserve">The Heritage Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B350">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C350" s="66">
-        <v>81.00</v>
+        <v>83.00</v>
       </c>
     </row>
     <row r="351">
       <c t="inlineStr" r="A351">
         <is>
-          <t xml:space="preserve">The Jane Goodall Institute for Wildlife Research</t>
+          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B351">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
-        </is>
-      </c>
-      <c r="C351" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/28/2027</t>
+        </is>
+      </c>
+      <c r="C351" s="66">
+        <v>89.00</v>
       </c>
     </row>
     <row r="352">
       <c t="inlineStr" r="A352">
         <is>
-          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
+          <t xml:space="preserve">The Independent Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B352">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C352" s="66">
-        <v>84.00</v>
+        <v>77.51</v>
       </c>
     </row>
     <row r="353">
       <c t="inlineStr" r="A353">
         <is>
-          <t xml:space="preserve">The Just Trust for Education</t>
+          <t xml:space="preserve">The International Wildlife Rehab. Council</t>
         </is>
       </c>
       <c t="inlineStr" r="B353">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C353" s="66">
-        <v>85.13</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="354">
       <c t="inlineStr" r="A354">
         <is>
-          <t xml:space="preserve">The Kansas University Endowment Association</t>
+          <t xml:space="preserve">The Jane Goodall Institute for Wildlife Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B354">
         <is>
-          <t xml:space="preserve">7/21/2027</t>
-        </is>
-      </c>
-      <c r="C354" s="66">
-        <v>91.34</v>
+          <t xml:space="preserve">5/19/2027</t>
+        </is>
+      </c>
+      <c r="C354" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="355">
       <c t="inlineStr" r="A355">
         <is>
-          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B355">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C355" s="66">
-        <v>83.06</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="356">
       <c t="inlineStr" r="A356">
         <is>
-          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
+          <t xml:space="preserve">The Just Trust for Education</t>
         </is>
       </c>
       <c t="inlineStr" r="B356">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C356" s="66">
-        <v>91.99</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="357">
       <c t="inlineStr" r="A357">
         <is>
-          <t xml:space="preserve">The Memorial Foundation</t>
+          <t xml:space="preserve">The Kansas University Endowment Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B357">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">7/21/2027</t>
         </is>
       </c>
       <c r="C357" s="66">
-        <v>72.00</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="358">
       <c t="inlineStr" r="A358">
         <is>
-          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B358">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C358" s="66">
-        <v>74.58</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="359">
       <c t="inlineStr" r="A359">
         <is>
-          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
+          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B359">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C359" s="66">
-        <v>60.00</v>
+        <v>91.99</v>
       </c>
     </row>
     <row r="360">
       <c t="inlineStr" r="A360">
         <is>
-          <t xml:space="preserve">The National World War II Museum, Inc.</t>
+          <t xml:space="preserve">The Memorial Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B360">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C360" s="66">
-        <v>80.00</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="361">
       <c t="inlineStr" r="A361">
         <is>
-          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B361">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C361" s="66">
-        <v>80.64</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="362">
       <c t="inlineStr" r="A362">
         <is>
-          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
+          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B362">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C362" s="66">
-        <v>87.40</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="363">
       <c t="inlineStr" r="A363">
         <is>
-          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
+          <t xml:space="preserve">The National World War II Museum, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B363">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C363" s="66">
-        <v>60.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="364">
       <c t="inlineStr" r="A364">
         <is>
-          <t xml:space="preserve">The Ohio University Foundation</t>
+          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
         </is>
       </c>
       <c t="inlineStr" r="B364">
@@ -5657,108 +5657,108 @@
         </is>
       </c>
       <c r="C364" s="66">
-        <v>74.14</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="365">
       <c t="inlineStr" r="A365">
         <is>
-          <t xml:space="preserve">The OneStar Foundation</t>
+          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
         </is>
       </c>
       <c t="inlineStr" r="B365">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C365" s="66">
-        <v>62.50</v>
+        <v>87.40</v>
       </c>
     </row>
     <row r="366">
       <c t="inlineStr" r="A366">
         <is>
-          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B366">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/24/2027</t>
         </is>
       </c>
       <c r="C366" s="66">
-        <v>88.30</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="367">
       <c t="inlineStr" r="A367">
         <is>
-          <t xml:space="preserve">The Planetary Society</t>
+          <t xml:space="preserve">The Ohio University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B367">
         <is>
-          <t xml:space="preserve">7/14/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C367" s="66">
-        <v>66.00</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="368">
       <c t="inlineStr" r="A368">
         <is>
-          <t xml:space="preserve">The Principia Corporation</t>
+          <t xml:space="preserve">The OneStar Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B368">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
-        </is>
-      </c>
-      <c r="C368" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/14/2027</t>
+        </is>
+      </c>
+      <c r="C368" s="66">
+        <v>62.50</v>
       </c>
     </row>
     <row r="369">
       <c t="inlineStr" r="A369">
         <is>
-          <t xml:space="preserve">The Purchase College Foundation</t>
+          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B369">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C369" s="66">
-        <v>78.12</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="370">
       <c t="inlineStr" r="A370">
         <is>
-          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
+          <t xml:space="preserve">The Planetary Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B370">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">7/14/2027</t>
         </is>
       </c>
       <c r="C370" s="66">
-        <v>81.26</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="371">
       <c t="inlineStr" r="A371">
         <is>
-          <t xml:space="preserve">The Ruth Collective</t>
+          <t xml:space="preserve">The Principia Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B371">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
+          <t xml:space="preserve">5/19/2027</t>
         </is>
       </c>
       <c r="C371" s="65">
@@ -5768,297 +5768,297 @@
     <row r="372">
       <c t="inlineStr" r="A372">
         <is>
-          <t xml:space="preserve">The Society of the Cincinnati</t>
+          <t xml:space="preserve">The Purchase College Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B372">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C372" s="66">
-        <v>73.00</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="373">
       <c t="inlineStr" r="A373">
         <is>
-          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
         </is>
       </c>
       <c t="inlineStr" r="B373">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C373" s="66">
-        <v>94.00</v>
+        <v>81.26</v>
       </c>
     </row>
     <row r="374">
       <c t="inlineStr" r="A374">
         <is>
-          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+          <t xml:space="preserve">The Ruth Collective</t>
         </is>
       </c>
       <c t="inlineStr" r="B374">
         <is>
-          <t xml:space="preserve">4/13/2027</t>
-        </is>
-      </c>
-      <c r="C374" s="66">
-        <v>82.20</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C374" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="375">
       <c t="inlineStr" r="A375">
         <is>
-          <t xml:space="preserve">The University of Montana Foundation</t>
+          <t xml:space="preserve">The Society of the Cincinnati</t>
         </is>
       </c>
       <c t="inlineStr" r="B375">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C375" s="66">
-        <v>79.00</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="376">
       <c t="inlineStr" r="A376">
         <is>
-          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
+          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
         </is>
       </c>
       <c t="inlineStr" r="B376">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C376" s="66">
-        <v>76.00</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="377">
       <c t="inlineStr" r="A377">
         <is>
-          <t xml:space="preserve">The Visiting Angels Foundation</t>
+          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B377">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">4/13/2027</t>
         </is>
       </c>
       <c r="C377" s="66">
-        <v>94.00</v>
+        <v>82.20</v>
       </c>
     </row>
     <row r="378">
       <c t="inlineStr" r="A378">
         <is>
-          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+          <t xml:space="preserve">The University of Montana Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B378">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C378" s="66">
-        <v>79.51</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="379">
       <c t="inlineStr" r="A379">
         <is>
-          <t xml:space="preserve">The Wilderness Society</t>
+          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B379">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C379" s="66">
-        <v>73.00</v>
+        <v>76.00</v>
       </c>
     </row>
     <row r="380">
       <c t="inlineStr" r="A380">
         <is>
-          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
+          <t xml:space="preserve">The Visiting Angels Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B380">
         <is>
-          <t xml:space="preserve">4/21/2027</t>
+          <t xml:space="preserve">7/20/2027</t>
         </is>
       </c>
       <c r="C380" s="66">
-        <v>85.00</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="381">
       <c t="inlineStr" r="A381">
         <is>
-          <t xml:space="preserve">Together Making Changes</t>
+          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B381">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C381" s="66">
-        <v>90.26</v>
+        <v>79.51</v>
       </c>
     </row>
     <row r="382">
       <c t="inlineStr" r="A382">
         <is>
-          <t xml:space="preserve">Trevecca Nazarene University</t>
+          <t xml:space="preserve">The Wilderness Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B382">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C382" s="66">
-        <v>87.82</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="383">
       <c t="inlineStr" r="A383">
         <is>
-          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
+          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B383">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">4/21/2027</t>
         </is>
       </c>
       <c r="C383" s="66">
-        <v>94.50</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="384">
       <c t="inlineStr" r="A384">
         <is>
-          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+          <t xml:space="preserve">Together Making Changes</t>
         </is>
       </c>
       <c t="inlineStr" r="B384">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C384" s="66">
-        <v>89.90</v>
+        <v>90.26</v>
       </c>
     </row>
     <row r="385">
       <c t="inlineStr" r="A385">
         <is>
-          <t xml:space="preserve">Trustees of Tufts College</t>
+          <t xml:space="preserve">Trevecca Nazarene University</t>
         </is>
       </c>
       <c t="inlineStr" r="B385">
         <is>
-          <t xml:space="preserve">7/2/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C385" s="66">
-        <v>85.00</v>
+        <v>87.82</v>
       </c>
     </row>
     <row r="386">
       <c t="inlineStr" r="A386">
         <is>
-          <t xml:space="preserve">Turning Point USA, Inc.</t>
+          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B386">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C386" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C386" s="66">
+        <v>94.50</v>
       </c>
     </row>
     <row r="387">
       <c t="inlineStr" r="A387">
         <is>
-          <t xml:space="preserve">Twelveacres, Incorporated</t>
+          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
         </is>
       </c>
       <c t="inlineStr" r="B387">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C387" s="66">
-        <v>79.93</v>
+        <v>89.90</v>
       </c>
     </row>
     <row r="388">
       <c t="inlineStr" r="A388">
         <is>
-          <t xml:space="preserve">UATX</t>
+          <t xml:space="preserve">Trustees of Tufts College</t>
         </is>
       </c>
       <c t="inlineStr" r="B388">
         <is>
-          <t xml:space="preserve">2/1/2027</t>
-        </is>
-      </c>
-      <c r="C388" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/2/2027</t>
+        </is>
+      </c>
+      <c r="C388" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="389">
       <c t="inlineStr" r="A389">
         <is>
-          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+          <t xml:space="preserve">Turning Point USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B389">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C389" s="66">
-        <v>95.75</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C389" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="390">
       <c t="inlineStr" r="A390">
         <is>
-          <t xml:space="preserve">UMKC Foundation</t>
+          <t xml:space="preserve">Twelveacres, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B390">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C390" s="66">
-        <v>95.00</v>
+        <v>79.93</v>
       </c>
     </row>
     <row r="391">
       <c t="inlineStr" r="A391">
         <is>
-          <t xml:space="preserve">Unified Youth</t>
+          <t xml:space="preserve">UATX</t>
         </is>
       </c>
       <c t="inlineStr" r="B391">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">2/1/2027</t>
         </is>
       </c>
       <c r="C391" s="65">
@@ -6068,37 +6068,37 @@
     <row r="392">
       <c t="inlineStr" r="A392">
         <is>
-          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B392">
         <is>
-          <t xml:space="preserve">8/1/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C392" s="66">
-        <v>88.00</v>
+        <v>95.75</v>
       </c>
     </row>
     <row r="393">
       <c t="inlineStr" r="A393">
         <is>
-          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
+          <t xml:space="preserve">UMKC Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B393">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C393" s="66">
-        <v>84.01</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="394">
       <c t="inlineStr" r="A394">
         <is>
-          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">Unified Youth</t>
         </is>
       </c>
       <c t="inlineStr" r="B394">
@@ -6106,487 +6106,532 @@
           <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
-      <c r="C394" s="66">
-        <v>85.00</v>
+      <c r="C394" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="395">
       <c t="inlineStr" r="A395">
         <is>
-          <t xml:space="preserve">united Service Organizations, Inc.</t>
+          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B395">
         <is>
-          <t xml:space="preserve">11/10/2026</t>
+          <t xml:space="preserve">8/1/2027</t>
         </is>
       </c>
       <c r="C395" s="66">
-        <v>67.94</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="396">
       <c t="inlineStr" r="A396">
         <is>
-          <t xml:space="preserve">United States Association for UNHCR</t>
+          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B396">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C396" s="66">
-        <v>61.00</v>
+        <v>84.01</v>
       </c>
     </row>
     <row r="397">
       <c t="inlineStr" r="A397">
         <is>
-          <t xml:space="preserve">United States Center for SafeSport</t>
+          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B397">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C397" s="66">
-        <v>72.74</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="398">
       <c t="inlineStr" r="A398">
         <is>
-          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
+          <t xml:space="preserve">united Service Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B398">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">11/10/2026</t>
         </is>
       </c>
       <c r="C398" s="66">
-        <v>38.00</v>
+        <v>67.94</v>
       </c>
     </row>
     <row r="399">
       <c t="inlineStr" r="A399">
         <is>
-          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
+          <t xml:space="preserve">United States Association for UNHCR</t>
         </is>
       </c>
       <c t="inlineStr" r="B399">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C399" s="66">
-        <v>99.30</v>
+        <v>61.00</v>
       </c>
     </row>
     <row r="400">
       <c t="inlineStr" r="A400">
         <is>
-          <t xml:space="preserve">University of Colorado</t>
+          <t xml:space="preserve">United States Center for SafeSport</t>
         </is>
       </c>
       <c t="inlineStr" r="B400">
         <is>
-          <t xml:space="preserve">10/6/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C400" s="66">
-        <v>76.40</v>
+        <v>72.74</v>
       </c>
     </row>
     <row r="401">
       <c t="inlineStr" r="A401">
         <is>
-          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
+          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B401">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C401" s="66">
-        <v>93.00</v>
+        <v>38.00</v>
       </c>
     </row>
     <row r="402">
       <c t="inlineStr" r="A402">
         <is>
-          <t xml:space="preserve">University of Nebraska Foundation</t>
+          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B402">
         <is>
-          <t xml:space="preserve">7/15/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C402" s="66">
-        <v>81.10</v>
+        <v>99.30</v>
       </c>
     </row>
     <row r="403">
       <c t="inlineStr" r="A403">
         <is>
-          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
+          <t xml:space="preserve">University of Colorado</t>
         </is>
       </c>
       <c t="inlineStr" r="B403">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
+          <t xml:space="preserve">10/6/2027</t>
         </is>
       </c>
       <c r="C403" s="66">
-        <v>77.00</v>
+        <v>76.40</v>
       </c>
     </row>
     <row r="404">
       <c t="inlineStr" r="A404">
         <is>
-          <t xml:space="preserve">University of Northern Iowa Foundation</t>
+          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B404">
         <is>
-          <t xml:space="preserve">10/1/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C404" s="66">
-        <v>74.00</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="405">
       <c t="inlineStr" r="A405">
         <is>
-          <t xml:space="preserve">University of Pacific</t>
+          <t xml:space="preserve">University of Nebraska Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B405">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C405" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/15/2027</t>
+        </is>
+      </c>
+      <c r="C405" s="66">
+        <v>81.10</v>
       </c>
     </row>
     <row r="406">
       <c t="inlineStr" r="A406">
         <is>
-          <t xml:space="preserve">University of Richmond</t>
+          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B406">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C406" s="66">
-        <v>82.18</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="407">
       <c t="inlineStr" r="A407">
         <is>
-          <t xml:space="preserve">University of the Pacific</t>
+          <t xml:space="preserve">University of Northern Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B407">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
+          <t xml:space="preserve">10/1/2027</t>
         </is>
       </c>
       <c r="C407" s="66">
-        <v>95.48</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="408">
       <c t="inlineStr" r="A408">
         <is>
-          <t xml:space="preserve">Veterans Community Project</t>
+          <t xml:space="preserve">University of Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B408">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C408" s="66">
-        <v>88.83</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C408" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="409">
       <c t="inlineStr" r="A409">
         <is>
-          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
+          <t xml:space="preserve">University of Richmond</t>
         </is>
       </c>
       <c t="inlineStr" r="B409">
         <is>
-          <t xml:space="preserve">7/13/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C409" s="66">
-        <v>72.00</v>
+        <v>82.18</v>
       </c>
     </row>
     <row r="410">
       <c t="inlineStr" r="A410">
         <is>
-          <t xml:space="preserve">Violet Research Institute, Inc.</t>
+          <t xml:space="preserve">University of the Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B410">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C410" s="66">
-        <v>80.00</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="411">
       <c t="inlineStr" r="A411">
         <is>
-          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+          <t xml:space="preserve">Veterans Community Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B411">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C411" s="66">
-        <v>28.00</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="412">
       <c t="inlineStr" r="A412">
         <is>
-          <t xml:space="preserve">VoteAmerica, Inc.</t>
+          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B412">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">7/13/2027</t>
         </is>
       </c>
       <c r="C412" s="66">
-        <v>93.37</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="413">
       <c t="inlineStr" r="A413">
         <is>
-          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+          <t xml:space="preserve">Violet Research Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B413">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C413" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/28/2027</t>
+        </is>
+      </c>
+      <c r="C413" s="66">
+        <v>80.00</v>
       </c>
     </row>
     <row r="414">
       <c t="inlineStr" r="A414">
         <is>
-          <t xml:space="preserve">Washington State University Foundation</t>
+          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B414">
         <is>
-          <t xml:space="preserve">7/8/2027</t>
+          <t xml:space="preserve">11/5/2026</t>
         </is>
       </c>
       <c r="C414" s="66">
-        <v>75.03</v>
+        <v>28.00</v>
       </c>
     </row>
     <row r="415">
       <c t="inlineStr" r="A415">
         <is>
-          <t xml:space="preserve">Western Illinois University Foundation</t>
+          <t xml:space="preserve">VoteAmerica, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B415">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C415" s="66">
-        <v>77.54</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="416">
       <c t="inlineStr" r="A416">
         <is>
-          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B416">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
-        </is>
-      </c>
-      <c r="C416" s="66">
-        <v>82.68</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C416" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="417">
       <c t="inlineStr" r="A417">
         <is>
-          <t xml:space="preserve">Wildlife Conservation Network</t>
+          <t xml:space="preserve">Washington State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B417">
         <is>
-          <t xml:space="preserve">8/13/2027</t>
+          <t xml:space="preserve">7/8/2027</t>
         </is>
       </c>
       <c r="C417" s="66">
-        <v>92.13</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="418">
       <c t="inlineStr" r="A418">
         <is>
-          <t xml:space="preserve">Winning for Women, Inc.</t>
+          <t xml:space="preserve">Western Illinois University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B418">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C418" s="66">
-        <v>66.70</v>
+        <v>77.54</v>
       </c>
     </row>
     <row r="419">
       <c t="inlineStr" r="A419">
         <is>
-          <t xml:space="preserve">Women for Women International</t>
+          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B419">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">11/5/2026</t>
         </is>
       </c>
       <c r="C419" s="66">
-        <v>79.06</v>
+        <v>82.68</v>
       </c>
     </row>
     <row r="420">
       <c t="inlineStr" r="A420">
         <is>
-          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+          <t xml:space="preserve">Wildlife Conservation Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B420">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">8/13/2027</t>
         </is>
       </c>
       <c r="C420" s="66">
-        <v>71.40</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="421">
       <c t="inlineStr" r="A421">
         <is>
-          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+          <t xml:space="preserve">Winning for Women, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B421">
         <is>
-          <t xml:space="preserve">2/20/2027</t>
-        </is>
-      </c>
-      <c r="C421" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C421" s="66">
+        <v>66.70</v>
       </c>
     </row>
     <row r="422">
       <c t="inlineStr" r="A422">
         <is>
-          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+          <t xml:space="preserve">Women for Women International</t>
         </is>
       </c>
       <c t="inlineStr" r="B422">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C422" s="66">
-        <v>79.00</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="423">
       <c t="inlineStr" r="A423">
         <is>
-          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B423">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C423" s="66">
-        <v>70.36</v>
+        <v>71.40</v>
       </c>
     </row>
     <row r="424">
       <c t="inlineStr" r="A424">
         <is>
-          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
+          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B424">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
-        </is>
-      </c>
-      <c r="C424" s="66">
-        <v>39.45</v>
+          <t xml:space="preserve">2/20/2027</t>
+        </is>
+      </c>
+      <c r="C424" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="425">
       <c t="inlineStr" r="A425">
         <is>
-          <t xml:space="preserve">YMCA of the Rockies</t>
+          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B425">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">5/20/2027</t>
         </is>
       </c>
       <c r="C425" s="66">
-        <v>81.65</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="426">
       <c t="inlineStr" r="A426">
         <is>
+          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B426">
+        <is>
+          <t xml:space="preserve">8/31/2027</t>
+        </is>
+      </c>
+      <c r="C426" s="66">
+        <v>70.36</v>
+      </c>
+    </row>
+    <row r="427">
+      <c t="inlineStr" r="A427">
+        <is>
+          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B427">
+        <is>
+          <t xml:space="preserve">8/24/2027</t>
+        </is>
+      </c>
+      <c r="C427" s="66">
+        <v>39.45</v>
+      </c>
+    </row>
+    <row r="428">
+      <c t="inlineStr" r="A428">
+        <is>
+          <t xml:space="preserve">YMCA of the Rockies</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B428">
+        <is>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C428" s="66">
+        <v>81.65</v>
+      </c>
+    </row>
+    <row r="429">
+      <c t="inlineStr" r="A429">
+        <is>
           <t xml:space="preserve">Young Judaea Global, Inc.</t>
         </is>
       </c>
-      <c t="inlineStr" r="B426">
+      <c t="inlineStr" r="B429">
         <is>
           <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
-      <c r="C426" s="66">
+      <c r="C429" s="66">
         <v>71.20</v>
       </c>
     </row>

--- a/downloadable-data/LA.xlsx
+++ b/downloadable-data/LA.xlsx
@@ -1418,52 +1418,52 @@
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Children's Miracle Network</t>
+          <t xml:space="preserve">Choice Books of Northern Virginia, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">10/15/2027</t>
         </is>
       </c>
       <c r="C82" s="66">
-        <v>80.77</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">Choice Books of Northern Virginia, Inc.</t>
+          <t xml:space="preserve">Christian Advocates Serving Evangelism, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">10/15/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C83" s="66">
-        <v>91.41</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">Christian Advocates Serving Evangelism, Inc.</t>
+          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C84" s="66">
-        <v>1.17</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">Christian Appalachian Project, Inc.</t>
+          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
@@ -1471,64 +1471,64 @@
           <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
-      <c r="C85" s="66">
-        <v>89.98</v>
+      <c r="C85" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Christian Embassy Jerusalem-USA</t>
+          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C86" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/10/2027</t>
+        </is>
+      </c>
+      <c r="C86" s="66">
+        <v>96.00</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Christian Healthcare Ministries, Inc.</t>
+          <t xml:space="preserve">Christian Relief Services, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">9/10/2027</t>
+          <t xml:space="preserve">2/10/2027</t>
         </is>
       </c>
       <c r="C87" s="66">
-        <v>96.00</v>
+        <v>90.70</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">Christian Relief Services, Inc.</t>
+          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">2/10/2027</t>
-        </is>
-      </c>
-      <c r="C88" s="66">
-        <v>90.70</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C88" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">Christian Solidarity International, Inc.</t>
+          <t xml:space="preserve">Christian Union, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
+          <t xml:space="preserve">12/5/2026</t>
         </is>
       </c>
       <c r="C89" s="65">
@@ -1538,102 +1538,102 @@
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">Christian Union, Inc.</t>
+          <t xml:space="preserve">Church World Service, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C90" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/25/2027</t>
+        </is>
+      </c>
+      <c r="C90" s="66">
+        <v>84.00</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Church World Service, Inc.</t>
+          <t xml:space="preserve">City Rescue Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">8/25/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C91" s="66">
-        <v>84.00</v>
+        <v>85.32</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">City Rescue Mission, Inc.</t>
+          <t xml:space="preserve">City Year, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C92" s="66">
-        <v>85.32</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">City Year, Inc.</t>
+          <t xml:space="preserve">Civil Rights Corps</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C93" s="66">
-        <v>82.62</v>
+        <v>82.10</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Civil Rights Corps</t>
+          <t xml:space="preserve">Colon Cancer Coalition</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C94" s="66">
-        <v>82.10</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Colon Cancer Coalition</t>
+          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C95" s="66">
-        <v>86.73</v>
+          <t xml:space="preserve">11/20/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Colonial Williamsburg Foundation</t>
+          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">11/20/2026</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C96" s="65">
@@ -1643,37 +1643,37 @@
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Combined Jewish Philanthropies of Greater Boston,</t>
+          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C97" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/9/2027</t>
+        </is>
+      </c>
+      <c r="C97" s="66">
+        <v>65.99</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Common Wealth Fund for KET, Inc.</t>
+          <t xml:space="preserve">Compassion and Choices</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">4/9/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C98" s="66">
-        <v>65.99</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">Compassion and Choices</t>
+          <t xml:space="preserve">Compassion and Choices Action Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
@@ -1682,108 +1682,108 @@
         </is>
       </c>
       <c r="C99" s="66">
-        <v>84.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">Compassion and Choices Action Network</t>
+          <t xml:space="preserve">Compassion In World Farming, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
-        </is>
-      </c>
-      <c r="C100" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">10/10/2027</t>
+        </is>
+      </c>
+      <c r="C100" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Compassion In World Farming, Inc.</t>
+          <t xml:space="preserve">Concerns of Police Survivors</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">10/10/2027</t>
-        </is>
-      </c>
-      <c r="C101" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/7/2027</t>
+        </is>
+      </c>
+      <c r="C101" s="66">
+        <v>92.30</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Concerns of Police Survivors</t>
+          <t xml:space="preserve">Consumer Reports, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">10/7/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C102" s="66">
-        <v>92.30</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Consumer Reports, Inc.</t>
+          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C103" s="66">
-        <v>84.00</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">CORE Community Organized Relief Effort</t>
+          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">6/25/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C104" s="66">
-        <v>73.00</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Cortland College Foundation, Inc.</t>
+          <t xml:space="preserve">Covenant House</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C105" s="66">
-        <v>74.25</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Covenant House</t>
+          <t xml:space="preserve">Covenant House New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
+          <t xml:space="preserve">7/28/2028</t>
         </is>
       </c>
       <c r="C106" s="66">
@@ -1793,121 +1793,121 @@
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">Covenant House New Orleans</t>
+          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">7/28/2028</t>
+          <t xml:space="preserve">12/4/2026</t>
         </is>
       </c>
       <c r="C107" s="66">
-        <v>80.00</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">Crohn's &amp; Colitis Foundation, Inc.</t>
+          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">12/4/2026</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C108" s="66">
-        <v>84.38</v>
+        <v>85.18</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">CrossRoad Institute, Inc.</t>
+          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">3/13/2027</t>
         </is>
       </c>
       <c r="C109" s="66">
-        <v>85.18</v>
+        <v>64.30</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">Crown Financial Ministries, Inc.</t>
+          <t xml:space="preserve">D.A.R.E. America</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C110" s="66">
-        <v>64.30</v>
+        <v>44.00</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">D.A.R.E. America</t>
+          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
-        </is>
-      </c>
-      <c r="C111" s="66">
-        <v>44.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C111" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">Dave Thomas Foundation for Adoption</t>
+          <t xml:space="preserve">Deep South Today</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C112" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/17/2027</t>
+        </is>
+      </c>
+      <c r="C112" s="66">
+        <v>74.56</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">Deep South Today</t>
+          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">6/6/2027</t>
         </is>
       </c>
       <c r="C113" s="66">
-        <v>74.56</v>
+        <v>68.82</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">Des Moines University Osteopathic Medical Center</t>
+          <t xml:space="preserve">Disabled Veterans National Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">6/6/2027</t>
+          <t xml:space="preserve">10/19/2027</t>
         </is>
       </c>
       <c r="C114" s="66">
-        <v>68.82</v>
+        <v>31.01</v>
       </c>
     </row>
     <row r="115">
@@ -2281,8 +2281,8 @@
           <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
-      <c r="C139" s="66">
-        <v>48.00</v>
+      <c r="C139" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -2438,52 +2438,52 @@
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">Go Campaign</t>
+          <t xml:space="preserve">Goodwill Industries International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C150" s="66">
-        <v>77.86</v>
+        <v>87.00</v>
       </c>
     </row>
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">Goodwill Industries International, Inc</t>
+          <t xml:space="preserve">Green America</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C151" s="66">
-        <v>87.00</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">Green America</t>
+          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C152" s="66">
-        <v>87.47</v>
+        <v>76.85</v>
       </c>
     </row>
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">Greenpeace Fund, Inc.</t>
+          <t xml:space="preserve">Greenpeace, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
@@ -2492,153 +2492,153 @@
         </is>
       </c>
       <c r="C153" s="66">
-        <v>76.85</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">Greenpeace, Inc.</t>
+          <t xml:space="preserve">Gustavus Adolphus College</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">2/24/2027</t>
         </is>
       </c>
       <c r="C154" s="66">
-        <v>62.56</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">Gustavus Adolphus College</t>
+          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">2/24/2027</t>
-        </is>
-      </c>
-      <c r="C155" s="66">
-        <v>93.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">Habitat for Horses, Inc.</t>
+          <t xml:space="preserve">Healing Justice Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C156" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C156" s="66">
+        <v>82.48</v>
       </c>
     </row>
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">Habitat for Humanity International, Inc.</t>
+          <t xml:space="preserve">Healing Protectors</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C157" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/2/2027</t>
+        </is>
+      </c>
+      <c r="C157" s="66">
+        <v>47.19</v>
       </c>
     </row>
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">Healing Justice Project</t>
+          <t xml:space="preserve">Heifer Project International</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">3/19/2027</t>
         </is>
       </c>
       <c r="C158" s="66">
-        <v>82.48</v>
+        <v>72.90</v>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">Healing Protectors</t>
+          <t xml:space="preserve">Help Me See, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C159" s="66">
-        <v>47.19</v>
+        <v>83.00</v>
       </c>
     </row>
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">Heifer Project International</t>
+          <t xml:space="preserve">Herzog Tomorrow Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">3/19/2027</t>
-        </is>
-      </c>
-      <c r="C160" s="66">
-        <v>72.90</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C160" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">Help Me See, Inc.</t>
+          <t xml:space="preserve">HIAS Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
-        </is>
-      </c>
-      <c r="C161" s="66">
-        <v>83.00</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C161" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">Hero Kids Foundation, LLC</t>
+          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">10/22/2026</t>
-        </is>
-      </c>
-      <c r="C162" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C162" s="66">
+        <v>81.00</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">Herzog Tomorrow Foundation</t>
+          <t xml:space="preserve">Home Builders Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">1/5/2027</t>
         </is>
       </c>
       <c r="C163" s="65">
@@ -2648,357 +2648,357 @@
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">HIAS Foundation, Inc.</t>
+          <t xml:space="preserve">Human Appeal, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C164" s="65">
-        <v>0</v>
+          <t xml:space="preserve">1/12/2027</t>
+        </is>
+      </c>
+      <c r="C164" s="66">
+        <v>54.20</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">Hillel: The Foundation for Jewish Campus Life</t>
+          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C165" s="66">
-        <v>81.00</v>
+        <v>63.39</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">Home Builders Institute</t>
+          <t xml:space="preserve">Human Rights Watch, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C166" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C166" s="66">
+        <v>68.67</v>
       </c>
     </row>
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">Human Appeal, Inc.</t>
+          <t xml:space="preserve">Human-I-T</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">1/12/2027</t>
+          <t xml:space="preserve">8/30/2027</t>
         </is>
       </c>
       <c r="C167" s="66">
-        <v>54.20</v>
+        <v>1.00</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">Human Rights Campaign, Inc.</t>
+          <t xml:space="preserve">Humane Society of Missouri</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">8/7/2027</t>
         </is>
       </c>
       <c r="C168" s="66">
-        <v>63.39</v>
+        <v>80.50</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">Human Rights Watch, Inc.</t>
+          <t xml:space="preserve">Illinois State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">5/21/2027</t>
         </is>
       </c>
       <c r="C169" s="66">
-        <v>68.67</v>
+        <v>61.30</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">Human-I-T</t>
+          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">8/30/2027</t>
-        </is>
-      </c>
-      <c r="C170" s="66">
-        <v>1.00</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C170" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">Humane Society of Missouri</t>
+          <t xml:space="preserve">In Medias Res</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
-        </is>
-      </c>
-      <c r="C171" s="66">
-        <v>80.50</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C171" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">Illinois State University Foundation</t>
+          <t xml:space="preserve">Independent Council on Women's Sport</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">5/21/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C172" s="66">
-        <v>61.30</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">Immigrant Justice Corps., Inc.</t>
+          <t xml:space="preserve">Infact</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C173" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C173" s="66">
+        <v>89.97</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">In Medias Res</t>
+          <t xml:space="preserve">INROADS, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C174" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/1/2027</t>
+        </is>
+      </c>
+      <c r="C174" s="66">
+        <v>47.80</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">Independent Council on Women's Sport</t>
+          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C175" s="66">
-        <v>94.44</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">Infact</t>
+          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
-        </is>
-      </c>
-      <c r="C176" s="66">
-        <v>89.97</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">INROADS, Inc.</t>
+          <t xml:space="preserve">International Justice Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">10/1/2027</t>
-        </is>
-      </c>
-      <c r="C177" s="66">
-        <v>47.80</v>
+          <t xml:space="preserve">3/24/2027</t>
+        </is>
+      </c>
+      <c r="C177" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">International F.O.P. Association, Inc.</t>
+          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
-        </is>
-      </c>
-      <c r="C178" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C178" s="66">
+        <v>83.13</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">International Fellowship of Christians &amp; Jews, Inc</t>
+          <t xml:space="preserve">International Union of Police Associations</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C179" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/29/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="66">
+        <v>47.90</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">International Justice Mission</t>
+          <t xml:space="preserve">Iona University</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
-        </is>
-      </c>
-      <c r="C180" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C180" s="66">
+        <v>89.81</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">International Refugee Assistance Project, Inc.</t>
+          <t xml:space="preserve">Isaad Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">9/18/2027</t>
         </is>
       </c>
       <c r="C181" s="66">
-        <v>83.13</v>
+        <v>96.30</v>
       </c>
     </row>
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">International Union of Police Associations</t>
+          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">4/27/2027</t>
         </is>
       </c>
       <c r="C182" s="66">
-        <v>47.90</v>
+        <v>75.43</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">Iona University</t>
+          <t xml:space="preserve">Jewish Democratic Council of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C183" s="66">
-        <v>89.81</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">Isaad Foundation</t>
+          <t xml:space="preserve">Jewish Voice Ministries International</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">9/18/2027</t>
-        </is>
-      </c>
-      <c r="C184" s="66">
-        <v>96.30</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C184" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">James Whitcomb Riley Memorial Association, Inc.</t>
+          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
+          <t xml:space="preserve">11/4/2026</t>
         </is>
       </c>
       <c r="C185" s="66">
-        <v>75.43</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">Jewish Democratic Council of America</t>
+          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C186" s="66">
-        <v>50.07</v>
+        <v>75.00</v>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">Jewish Voice Ministries International</t>
+          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
+          <t xml:space="preserve">9/5/2027</t>
         </is>
       </c>
       <c r="C187" s="65">
@@ -3008,42 +3008,42 @@
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">John Paul II Shrine and Institute, Inc.</t>
+          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">11/4/2026</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C188" s="66">
-        <v>89.00</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">Jumpstart for Young Children, Inc.</t>
+          <t xml:space="preserve">Khan Academy, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">4/14/2027</t>
         </is>
       </c>
       <c r="C189" s="66">
-        <v>75.00</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">Keep Teachers in the Classroom, Inc.</t>
+          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">9/5/2027</t>
+          <t xml:space="preserve">11/12/2026</t>
         </is>
       </c>
       <c r="C190" s="65">
@@ -3053,747 +3053,747 @@
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">Kennesaw State University Foundation, Inc.</t>
+          <t xml:space="preserve">L.E.A.D. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C191" s="66">
-        <v>98.28</v>
+          <t xml:space="preserve">1/13/2027</t>
+        </is>
+      </c>
+      <c r="C191" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">Khan Academy, Inc.</t>
+          <t xml:space="preserve">La Leche League International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">4/14/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C192" s="66">
-        <v>86.36</v>
+        <v>57.00</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">Knights of Columbus Charities, Inc.</t>
+          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C193" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/11/2027</t>
+        </is>
+      </c>
+      <c r="C193" s="66">
+        <v>63.00</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">L.E.A.D. Inc.</t>
+          <t xml:space="preserve">Lasell University</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
-        </is>
-      </c>
-      <c r="C194" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/22/2027</t>
+        </is>
+      </c>
+      <c r="C194" s="66">
+        <v>86.90</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">La Leche League International, Inc.</t>
+          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C195" s="66">
-        <v>57.00</v>
+        <v>10.60</v>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">Lambda Legal Defense &amp; Education Fund, Inc.</t>
+          <t xml:space="preserve">League of Conservation Voters, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">9/23/2027</t>
         </is>
       </c>
       <c r="C196" s="66">
-        <v>63.00</v>
+        <v>92.00</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">Lasell University</t>
+          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
+          <t xml:space="preserve">10/28/2026</t>
         </is>
       </c>
       <c r="C197" s="66">
-        <v>86.90</v>
+        <v>96.80</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">Law Enforcement Officers Relief Fund, Inc.</t>
+          <t xml:space="preserve">Life Teen, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C198" s="66">
-        <v>10.60</v>
+        <v>76.40</v>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">League of Conservation Voters, Inc.</t>
+          <t xml:space="preserve">Live Action</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">9/23/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C199" s="66">
-        <v>92.00</v>
+        <v>81.13</v>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">LeSEA Global Feed the Hungry, Inc.</t>
+          <t xml:space="preserve">Living Waters for the World</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">10/28/2026</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C200" s="66">
-        <v>96.80</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">Life Teen, Inc.</t>
+          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C201" s="66">
-        <v>76.40</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C201" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">Live Action</t>
+          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">9/11/2027</t>
         </is>
       </c>
       <c r="C202" s="66">
-        <v>81.13</v>
+        <v>76.03</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">Living Waters for the World</t>
+          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C203" s="66">
-        <v>78.81</v>
+        <v>62.00</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">Louie's Pizza and Prayer, Inc.</t>
+          <t xml:space="preserve">Madison House</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C204" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C204" s="66">
+        <v>77.79</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">Louis August Jonas Foundation, Inc.</t>
+          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">8/6/2027</t>
         </is>
       </c>
       <c r="C205" s="66">
-        <v>76.03</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">Macular Degeneration Association, Inc.</t>
+          <t xml:space="preserve">MAP International, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C206" s="66">
-        <v>62.00</v>
+        <v>99.00</v>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">Madison House</t>
+          <t xml:space="preserve">March of Dimes</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">12/30/2026</t>
         </is>
       </c>
       <c r="C207" s="66">
-        <v>77.79</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">Manhattan Institute For Policy Research, Inc.</t>
+          <t xml:space="preserve">Marist University</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">8/6/2027</t>
+          <t xml:space="preserve">6/26/2027</t>
         </is>
       </c>
       <c r="C208" s="66">
-        <v>86.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">MAP International, Inc.</t>
+          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C209" s="66">
-        <v>99.00</v>
+        <v>91.74</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">March of Dimes</t>
+          <t xml:space="preserve">Meals on Wheels America</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">12/30/2026</t>
+          <t xml:space="preserve">5/27/2027</t>
         </is>
       </c>
       <c r="C210" s="66">
-        <v>74.00</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">Marist University</t>
+          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">6/26/2027</t>
+          <t xml:space="preserve">6/9/2027</t>
         </is>
       </c>
       <c r="C211" s="66">
-        <v>91.00</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">Marquez Brothers of Texas,  Inc</t>
+          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
-        </is>
-      </c>
-      <c r="C212" s="66">
-        <v>91.74</v>
+          <t xml:space="preserve">12/8/2026</t>
+        </is>
+      </c>
+      <c r="C212" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">Meals on Wheels America</t>
+          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">5/27/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C213" s="66">
-        <v>59.00</v>
+        <v>91.00</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">Medal of Honor Foundation, Inc.</t>
+          <t xml:space="preserve">Mercatus Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">6/9/2027</t>
+          <t xml:space="preserve">8/3/2027</t>
         </is>
       </c>
       <c r="C214" s="66">
-        <v>80.94</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">Medecins Sans Frontieres USA, Inc./Doctors Without</t>
+          <t xml:space="preserve">Mercy for Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">12/8/2026</t>
-        </is>
-      </c>
-      <c r="C215" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C215" s="66">
+        <v>75.82</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">Memorial Sloan-Kettering Cancer Center</t>
+          <t xml:space="preserve">Mercy Hospital, Cedar Rapids, Iowa Endowment Found</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C216" s="66">
-        <v>91.00</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">Mercatus Center, Inc.</t>
+          <t xml:space="preserve">Mercy Ships</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
+          <t xml:space="preserve">8/26/2027</t>
         </is>
       </c>
       <c r="C217" s="66">
-        <v>90.25</v>
+        <v>78.18</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">Mercy for Animals, Inc.</t>
+          <t xml:space="preserve">Middle East Policy Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">9/16/2027</t>
         </is>
       </c>
       <c r="C218" s="66">
-        <v>75.82</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">Mercy Hospital, Cedar Rapids, Iowa Endowment Found</t>
+          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C219" s="66">
-        <v>93.00</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">Mercy Ships</t>
+          <t xml:space="preserve">Minutes Matter-MCADD</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">8/26/2027</t>
-        </is>
-      </c>
-      <c r="C220" s="66">
-        <v>78.18</v>
+          <t xml:space="preserve">7/19/2027</t>
+        </is>
+      </c>
+      <c r="C220" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">Middle East Policy Network, Inc.</t>
+          <t xml:space="preserve">Miracle Flights</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
+          <t xml:space="preserve">6/4/2027</t>
         </is>
       </c>
       <c r="C221" s="66">
-        <v>73.83</v>
+        <v>52.00</v>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">Minnesota Landscape Arboretum Foundation</t>
+          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C222" s="66">
-        <v>88.00</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">Minutes Matter-MCADD</t>
+          <t xml:space="preserve">mothers2mothers United States, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">7/19/2027</t>
-        </is>
-      </c>
-      <c r="C223" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/27/2027</t>
+        </is>
+      </c>
+      <c r="C223" s="66">
+        <v>60.00</v>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">Miracle Flights</t>
+          <t xml:space="preserve">Mount Saint Marys University</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
-        </is>
-      </c>
-      <c r="C224" s="66">
-        <v>52.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C224" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">Morgan State University Foundation, Inc.</t>
+          <t xml:space="preserve">Mountain States Legal Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C225" s="66">
-        <v>94.50</v>
+        <v>69.99</v>
       </c>
     </row>
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">mothers2mothers United States, Inc.</t>
+          <t xml:space="preserve">MrCharity, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">4/27/2027</t>
-        </is>
-      </c>
-      <c r="C226" s="66">
-        <v>60.00</v>
+          <t xml:space="preserve">2/23/2027</t>
+        </is>
+      </c>
+      <c r="C226" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">Mount Saint Marys University</t>
+          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C227" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/24/2027</t>
+        </is>
+      </c>
+      <c r="C227" s="66">
+        <v>77.80</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">Mountain States Legal Foundation</t>
+          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">12/19/2026</t>
         </is>
       </c>
       <c r="C228" s="66">
-        <v>69.99</v>
+        <v>66.90</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">MrCharity, Inc.</t>
+          <t xml:space="preserve">Naropa University</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">2/23/2027</t>
-        </is>
-      </c>
-      <c r="C229" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C229" s="66">
+        <v>76.21</v>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">Multiple Sclerosis Association of America, Inc.</t>
+          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C230" s="66">
-        <v>54.00</v>
+        <v>65.00</v>
       </c>
     </row>
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">Myasthenia Gravis Foundation of America, Inc.</t>
+          <t xml:space="preserve">National Audubon Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C231" s="66">
-        <v>77.80</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">NAACP Empowerment Programs, Inc.</t>
+          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">12/19/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C232" s="66">
-        <v>66.90</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">Naropa University</t>
+          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">8/7/2027</t>
         </is>
       </c>
       <c r="C233" s="66">
-        <v>76.21</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">National Association of Police Organizations, Inc.</t>
+          <t xml:space="preserve">National Council of Nonprofits</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C234" s="66">
-        <v>65.00</v>
+          <t xml:space="preserve">2/19/2027</t>
+        </is>
+      </c>
+      <c r="C234" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">National Audubon Society, Inc.</t>
+          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C235" s="66">
-        <v>80.00</v>
+        <v>49.00</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">National Brussels Griffon Rescue, Inc.</t>
+          <t xml:space="preserve">National Foundation for Cancer Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C236" s="66">
-        <v>81.00</v>
+          <t xml:space="preserve">12/1/2026</t>
+        </is>
+      </c>
+      <c r="C236" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">National Center for Missing and Exploited Children</t>
+          <t xml:space="preserve">National Geographic Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">8/7/2027</t>
+          <t xml:space="preserve">3/18/2027</t>
         </is>
       </c>
       <c r="C237" s="66">
-        <v>92.28</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">National Council of Nonprofits</t>
+          <t xml:space="preserve">National LGBTQ Task Force</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C238" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C238" s="66">
+        <v>80.00</v>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">National D-Day Memorial Foundation, Ltd.</t>
+          <t xml:space="preserve">National Network of Abortion Funds</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C239" s="66">
-        <v>49.00</v>
+          <t xml:space="preserve">9/11/2027</t>
+        </is>
+      </c>
+      <c r="C239" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">National Foundation for Cancer Research</t>
+          <t xml:space="preserve">National PKU Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">12/1/2026</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C240" s="65">
@@ -3803,42 +3803,42 @@
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">National Geographic Society</t>
+          <t xml:space="preserve">National Rifle Association of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">3/18/2027</t>
+          <t xml:space="preserve">10/1/2027</t>
         </is>
       </c>
       <c r="C241" s="66">
-        <v>77.00</v>
+        <v>62.91</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">National LGBTQ Task Force</t>
+          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C242" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">1/9/2027</t>
+        </is>
+      </c>
+      <c r="C242" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">National Network of Abortion Funds</t>
+          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">9/11/2027</t>
+          <t xml:space="preserve">1/9/2027</t>
         </is>
       </c>
       <c r="C243" s="65">
@@ -3848,522 +3848,522 @@
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">National Park Foundation</t>
+          <t xml:space="preserve">National Space Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">10/20/2026</t>
-        </is>
-      </c>
-      <c r="C244" s="66">
-        <v>72.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C244" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">National PKU Alliance, Inc.</t>
+          <t xml:space="preserve">National University</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C245" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C245" s="66">
+        <v>42.69</v>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">National Rifle Association of America</t>
+          <t xml:space="preserve">National Veterans Memorial and Museum</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">10/1/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C246" s="66">
-        <v>62.91</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">National Right to Life Committee, Inc.</t>
+          <t xml:space="preserve">National Wheelchair Basketball Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C247" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/12/2027</t>
+        </is>
+      </c>
+      <c r="C247" s="66">
+        <v>77.80</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">National Right to Life Educational Foundation, Inc</t>
+          <t xml:space="preserve">National Wildlife Federation</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">1/9/2027</t>
-        </is>
-      </c>
-      <c r="C248" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/4/2027</t>
+        </is>
+      </c>
+      <c r="C248" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">National Space Society</t>
+          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C249" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/22/2027</t>
+        </is>
+      </c>
+      <c r="C249" s="66">
+        <v>1.60</v>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">National University</t>
+          <t xml:space="preserve">Network for Good, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C250" s="66">
-        <v>42.69</v>
+        <v>97.80</v>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">National Veterans Memorial and Museum</t>
+          <t xml:space="preserve">New Harvest, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C251" s="66">
-        <v>72.63</v>
+        <v>88.49</v>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">National Wheelchair Basketball Association</t>
+          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
-        </is>
-      </c>
-      <c r="C252" s="66">
-        <v>77.80</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C252" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">National Wildlife Federation</t>
+          <t xml:space="preserve">Nurse-Family Partnership</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
-        </is>
-      </c>
-      <c r="C253" s="66">
-        <v>86.00</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C253" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">NAWBO Institute for Entrepreneurial Development</t>
+          <t xml:space="preserve">Ocean Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C254" s="66">
-        <v>1.60</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">Network for Good, Inc</t>
+          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
-        </is>
-      </c>
-      <c r="C255" s="66">
-        <v>97.80</v>
+          <t xml:space="preserve">3/13/2027</t>
+        </is>
+      </c>
+      <c r="C255" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">New Harvest, Inc.</t>
+          <t xml:space="preserve">Operation Smile, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
-        </is>
-      </c>
-      <c r="C256" s="66">
-        <v>88.49</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C256" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">North Shore Animal League America, Inc.</t>
+          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C257" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/18/2027</t>
+        </is>
+      </c>
+      <c r="C257" s="66">
+        <v>77.59</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">Nurse-Family Partnership</t>
+          <t xml:space="preserve">Our Change Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
-        </is>
-      </c>
-      <c r="C258" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/13/2027</t>
+        </is>
+      </c>
+      <c r="C258" s="66">
+        <v>71.30</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">Ocean Conservancy</t>
+          <t xml:space="preserve">Pace University</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">7/1/2027</t>
         </is>
       </c>
       <c r="C259" s="66">
-        <v>74.06</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">Olympia Snowe Women's Leadership Inst.</t>
+          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">3/13/2027</t>
-        </is>
-      </c>
-      <c r="C260" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/16/2027</t>
+        </is>
+      </c>
+      <c r="C260" s="66">
+        <v>55.43</v>
       </c>
     </row>
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">Operation Smile, Inc.</t>
+          <t xml:space="preserve">Panorama Global</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C261" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C261" s="66">
+        <v>84.52</v>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">Oregon Health and Sciences University Foundation</t>
+          <t xml:space="preserve">Paralyzed Veterans of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">8/18/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C262" s="66">
-        <v>77.59</v>
+        <v>59.00</v>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">Our Change Foundation</t>
+          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">10/13/2027</t>
+          <t xml:space="preserve">2/9/2027</t>
         </is>
       </c>
       <c r="C263" s="66">
-        <v>71.30</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">Pace University</t>
+          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">7/1/2027</t>
-        </is>
-      </c>
-      <c r="C264" s="66">
-        <v>88.30</v>
+          <t xml:space="preserve">7/16/2027</t>
+        </is>
+      </c>
+      <c r="C264" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">Pancreatic Cancer Action Network, Inc.</t>
+          <t xml:space="preserve">Pathfinder International</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C265" s="66">
-        <v>55.43</v>
+        <v>85.33</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">Panorama Global</t>
+          <t xml:space="preserve">patriotic Hearts, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C266" s="66">
-        <v>84.52</v>
+        <v>56.00</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">Paralyzed Veterans of America</t>
+          <t xml:space="preserve">People for the American Way</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C267" s="66">
-        <v>59.00</v>
+        <v>38.00</v>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">Parkinson's Foundation, Inc.</t>
+          <t xml:space="preserve">People for the American Way Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">2/9/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C268" s="66">
-        <v>90.00</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">Partners in Health, A Nonprofit Corporation</t>
+          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
-        </is>
-      </c>
-      <c r="C269" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/22/2027</t>
+        </is>
+      </c>
+      <c r="C269" s="66">
+        <v>83.76</v>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">Pathfinder International</t>
+          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">3/12/2027</t>
         </is>
       </c>
       <c r="C270" s="66">
-        <v>85.33</v>
+        <v>58.00</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">patriotic Hearts, Inc.</t>
+          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">8/28/2027</t>
         </is>
       </c>
       <c r="C271" s="66">
-        <v>56.00</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">People for the American Way Foundation</t>
+          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
-        </is>
-      </c>
-      <c r="C272" s="66">
-        <v>60.00</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C272" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">People for the Ethical Treatment of Animals, Inc.</t>
+          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
-        </is>
-      </c>
-      <c r="C273" s="66">
-        <v>83.76</v>
+          <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="C273" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">Phi Mu Foundation, Inc.</t>
+          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">3/12/2027</t>
-        </is>
-      </c>
-      <c r="C274" s="66">
-        <v>58.00</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C274" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">Phoenix Gospel Mission, Inc.</t>
+          <t xml:space="preserve">Pledgeling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">8/28/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C275" s="66">
-        <v>79.00</v>
+        <v>65.93</v>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">Planned Parenthood Action Fund, Inc.</t>
+          <t xml:space="preserve">Polar Bears International</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C276" s="65">
-        <v>0</v>
+          <t xml:space="preserve">2/2/2027</t>
+        </is>
+      </c>
+      <c r="C276" s="66">
+        <v>86.00</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">Planned Parenthood Federation of America, Inc.</t>
+          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="C277" s="65">
-        <v>0</v>
+          <t xml:space="preserve">3/27/2027</t>
+        </is>
+      </c>
+      <c r="C277" s="66">
+        <v>85.54</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">Planned parenthood of Arkansas and Eastern Oklahom</t>
+          <t xml:space="preserve">Pratt Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">11/12/2026</t>
         </is>
       </c>
       <c r="C278" s="65">
@@ -4373,207 +4373,207 @@
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">Pledgeling Foundation</t>
+          <t xml:space="preserve">Primo Cares, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
-        </is>
-      </c>
-      <c r="C279" s="66">
-        <v>65.93</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C279" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">Polar Bears International</t>
+          <t xml:space="preserve">Prison Fellowship Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">2/2/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C280" s="66">
-        <v>86.00</v>
+        <v>68.60</v>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">Potsdam College Foundation, Inc.</t>
+          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">3/27/2027</t>
-        </is>
-      </c>
-      <c r="C281" s="66">
-        <v>85.54</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C281" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">Pratt Institute</t>
+          <t xml:space="preserve">Project Cure, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C282" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C282" s="66">
+        <v>27.00</v>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">Primo Cares, Inc.</t>
+          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C283" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/14/2026</t>
+        </is>
+      </c>
+      <c r="C283" s="66">
+        <v>88.71</v>
       </c>
     </row>
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries</t>
+          <t xml:space="preserve">Proteus Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">3/2/2027</t>
         </is>
       </c>
       <c r="C284" s="66">
-        <v>68.60</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">Prison Fellowship Ministries Foundation</t>
+          <t xml:space="preserve">Providence House</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
-        </is>
-      </c>
-      <c r="C285" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/7/2027</t>
+        </is>
+      </c>
+      <c r="C285" s="66">
+        <v>92.06</v>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">Project Cure, Inc.</t>
+          <t xml:space="preserve">Public Health Foundation Enterprise, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C286" s="66">
-        <v>27.00</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">Project HOPE - The People-to-People Health Fnd.</t>
+          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C287" s="66">
-        <v>88.71</v>
+        <v>84.22</v>
       </c>
     </row>
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">Proteus Fund, Inc.</t>
+          <t xml:space="preserve">Re:Power</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">3/2/2027</t>
-        </is>
-      </c>
-      <c r="C288" s="66">
-        <v>81.25</v>
+          <t xml:space="preserve">1/5/2027</t>
+        </is>
+      </c>
+      <c r="C288" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">Providence House</t>
+          <t xml:space="preserve">Reproductive Freedom for All</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">9/3/2027</t>
         </is>
       </c>
       <c r="C289" s="66">
-        <v>92.06</v>
+        <v>70.00</v>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">Public Health Foundation Enterprise, Inc</t>
+          <t xml:space="preserve">RezilientKidz</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C290" s="66">
-        <v>94.97</v>
+        <v>94.35</v>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">Public Relations Society of America Fdn. Inc.</t>
+          <t xml:space="preserve">Rodale Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
-        </is>
-      </c>
-      <c r="C291" s="66">
-        <v>84.22</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C291" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">Re:Power</t>
+          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">1/5/2027</t>
+          <t xml:space="preserve">12/12/2026</t>
         </is>
       </c>
       <c r="C292" s="65">
@@ -4583,1072 +4583,1072 @@
     <row r="293">
       <c t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">Reproductive Freedom for All</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Indiana- Michia</t>
         </is>
       </c>
       <c t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">10/19/2027</t>
         </is>
       </c>
       <c r="C293" s="66">
-        <v>70.00</v>
+        <v>4.60</v>
       </c>
     </row>
     <row r="294">
       <c t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">RezilientKidz</t>
+          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
         </is>
       </c>
       <c t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C294" s="66">
-        <v>94.35</v>
+          <t xml:space="preserve">3/9/2027</t>
+        </is>
+      </c>
+      <c r="C294" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">Rodale Institute</t>
+          <t xml:space="preserve">Rush University Medical Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C295" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/23/2027</t>
+        </is>
+      </c>
+      <c r="C295" s="66">
+        <v>91.41</v>
       </c>
     </row>
     <row r="296">
       <c t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities Greater Houston, I</t>
+          <t xml:space="preserve">Rutgers University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">12/12/2026</t>
-        </is>
-      </c>
-      <c r="C296" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/3/2027</t>
+        </is>
+      </c>
+      <c r="C296" s="66">
+        <v>87.46</v>
       </c>
     </row>
     <row r="297">
       <c t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">Ronald McDonald House Charities of Northern Nevada</t>
+          <t xml:space="preserve">Sagamore Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
-        </is>
-      </c>
-      <c r="C297" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/3/2027</t>
+        </is>
+      </c>
+      <c r="C297" s="66">
+        <v>91.61</v>
       </c>
     </row>
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">Rush University Medical Center</t>
+          <t xml:space="preserve">Saint John's University</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">7/23/2027</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C298" s="66">
-        <v>91.41</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">Rutgers University Foundation</t>
+          <t xml:space="preserve">Save the Chimps, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">9/3/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C299" s="66">
-        <v>87.46</v>
+        <v>79.70</v>
       </c>
     </row>
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">Sagamore Institute, Inc.</t>
+          <t xml:space="preserve">Seattle Pacific University</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">8/3/2027</t>
-        </is>
-      </c>
-      <c r="C300" s="66">
-        <v>91.61</v>
+          <t xml:space="preserve">10/27/2026</t>
+        </is>
+      </c>
+      <c r="C300" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">Saint John's University</t>
+          <t xml:space="preserve">Second Harvest Food Bank of Greater New Orleans</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
-        </is>
-      </c>
-      <c r="C301" s="66">
-        <v>92.91</v>
+          <t xml:space="preserve">5/20/2027</t>
+        </is>
+      </c>
+      <c r="C301" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">Save the Chimps, Inc.</t>
+          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">8/4/2027</t>
         </is>
       </c>
       <c r="C302" s="66">
-        <v>79.70</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">Seattle Pacific University</t>
+          <t xml:space="preserve">Seti Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
-        </is>
-      </c>
-      <c r="C303" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/5/2027</t>
+        </is>
+      </c>
+      <c r="C303" s="66">
+        <v>69.60</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">Second Harvest Food Bank of Greater New Orleans</t>
+          <t xml:space="preserve">Share Our Strength</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
-        </is>
-      </c>
-      <c r="C304" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/8/2027</t>
+        </is>
+      </c>
+      <c r="C304" s="66">
+        <v>58.73</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">Second Harvest of Silicon Valley</t>
+          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">8/4/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C305" s="66">
-        <v>94.00</v>
+        <v>97.29</v>
       </c>
     </row>
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">Seti Institute</t>
+          <t xml:space="preserve">Sierra  Club</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
+          <t xml:space="preserve">12/22/2026</t>
         </is>
       </c>
       <c r="C306" s="66">
-        <v>69.60</v>
+        <v>82.00</v>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">Share Our Strength</t>
+          <t xml:space="preserve">Sister Rising Worldwide</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
-        </is>
-      </c>
-      <c r="C307" s="66">
-        <v>58.73</v>
+          <t xml:space="preserve">1/28/2027</t>
+        </is>
+      </c>
+      <c r="C307" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">Shepherds Foundation, Inc.</t>
+          <t xml:space="preserve">Sixpoint, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">7/9/2027</t>
         </is>
       </c>
       <c r="C308" s="66">
-        <v>97.29</v>
+        <v>77.16</v>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">Sierra  Club</t>
+          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">12/22/2026</t>
+          <t xml:space="preserve">4/22/2027</t>
         </is>
       </c>
       <c r="C309" s="66">
-        <v>82.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">Sister Rising Worldwide</t>
+          <t xml:space="preserve">Social Purpose Corrections</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">1/28/2027</t>
-        </is>
-      </c>
-      <c r="C310" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/12/2027</t>
+        </is>
+      </c>
+      <c r="C310" s="66">
+        <v>47.93</v>
       </c>
     </row>
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">Sixpoint, Inc.</t>
+          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">7/9/2027</t>
+          <t xml:space="preserve">9/2/2027</t>
         </is>
       </c>
       <c r="C311" s="66">
-        <v>77.16</v>
+        <v>72.80</v>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">Snooky's Shelter, Inc.</t>
+          <t xml:space="preserve">Soldiers' Angels</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">4/22/2027</t>
+          <t xml:space="preserve">10/5/2027</t>
         </is>
       </c>
       <c r="C312" s="66">
-        <v>90.00</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">Social Purpose Corrections</t>
+          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
+          <t xml:space="preserve">7/29/2027</t>
         </is>
       </c>
       <c r="C313" s="66">
-        <v>47.93</v>
+        <v>86.00</v>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">Society for American Baseball Research, Inc.</t>
+          <t xml:space="preserve">South Dakota State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">9/2/2027</t>
-        </is>
-      </c>
-      <c r="C314" s="66">
-        <v>72.80</v>
+          <t xml:space="preserve">2/6/2027</t>
+        </is>
+      </c>
+      <c r="C314" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">Soldiers' Angels</t>
+          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">10/5/2027</t>
-        </is>
-      </c>
-      <c r="C315" s="66">
-        <v>93.33</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C315" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">South Dakota School of Mines &amp; Technology Center</t>
+          <t xml:space="preserve">Special Olympics, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">7/29/2027</t>
-        </is>
-      </c>
-      <c r="C316" s="66">
-        <v>86.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C316" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">South Dakota State University Foundation</t>
+          <t xml:space="preserve">SPLC Action Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">2/6/2027</t>
-        </is>
-      </c>
-      <c r="C317" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/17/2027</t>
+        </is>
+      </c>
+      <c r="C317" s="66">
+        <v>72.81</v>
       </c>
     </row>
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">Southern Utah Wilderness Alliance</t>
+          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C318" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/31/2027</t>
+        </is>
+      </c>
+      <c r="C318" s="66">
+        <v>85.31</v>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">Special Olympics, Inc.</t>
+          <t xml:space="preserve">State University of Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C319" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/4/2027</t>
+        </is>
+      </c>
+      <c r="C319" s="66">
+        <v>79.00</v>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">SPLC Action Fund</t>
+          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">9/17/2027</t>
-        </is>
-      </c>
-      <c r="C320" s="66">
-        <v>72.81</v>
+          <t xml:space="preserve">12/11/2026</t>
+        </is>
+      </c>
+      <c r="C320" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">St. Mary?s College of Maryland Foundation, Inc.</t>
+          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">9/24/2027</t>
         </is>
       </c>
       <c r="C321" s="66">
-        <v>85.31</v>
+        <v>92.00</v>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">State University of Iowa Foundation</t>
+          <t xml:space="preserve">Students for Life Action, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">9/4/2027</t>
-        </is>
-      </c>
-      <c r="C322" s="66">
-        <v>79.00</v>
+          <t xml:space="preserve">11/7/2026</t>
+        </is>
+      </c>
+      <c r="C322" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">Stephen Siller Tunnel to Towers Foundation</t>
+          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C323" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/12/2027</t>
+        </is>
+      </c>
+      <c r="C323" s="66">
+        <v>89.29</v>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">Stop Predatory Gambling Foundation</t>
+          <t xml:space="preserve">Teacher Freedom Alliance</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">9/24/2027</t>
-        </is>
-      </c>
-      <c r="C324" s="66">
-        <v>92.00</v>
+          <t xml:space="preserve">6/24/2027</t>
+        </is>
+      </c>
+      <c r="C324" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">Students for Life Action, Inc.</t>
+          <t xml:space="preserve">The Actors' Fund of America</t>
         </is>
       </c>
       <c t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">11/7/2026</t>
-        </is>
-      </c>
-      <c r="C325" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/10/2026</t>
+        </is>
+      </c>
+      <c r="C325" s="66">
+        <v>86.73</v>
       </c>
     </row>
     <row r="326">
       <c t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">Surgical Eye Expeditions International, Inc</t>
+          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">8/12/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C326" s="66">
-        <v>89.29</v>
+        <v>39.00</v>
       </c>
     </row>
     <row r="327">
       <c t="inlineStr" r="A327">
         <is>
-          <t xml:space="preserve">Teacher Freedom Alliance</t>
+          <t xml:space="preserve">The American Society for the Prevention of Cruelty</t>
         </is>
       </c>
       <c t="inlineStr" r="B327">
         <is>
-          <t xml:space="preserve">6/24/2027</t>
-        </is>
-      </c>
-      <c r="C327" s="65">
-        <v>0</v>
+          <t xml:space="preserve">9/16/2027</t>
+        </is>
+      </c>
+      <c r="C327" s="66">
+        <v>75.00</v>
       </c>
     </row>
     <row r="328">
       <c t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">The Actors' Fund of America</t>
+          <t xml:space="preserve">The American University</t>
         </is>
       </c>
       <c t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C328" s="66">
-        <v>86.73</v>
+        <v>90.23</v>
       </c>
     </row>
     <row r="329">
       <c t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">The American Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
-        </is>
-      </c>
-      <c r="C329" s="66">
-        <v>39.00</v>
+          <t xml:space="preserve">1/21/2027</t>
+        </is>
+      </c>
+      <c r="C329" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c t="inlineStr" r="A330">
         <is>
-          <t xml:space="preserve">The American Society for the Prevention of Cruelty</t>
+          <t xml:space="preserve">The Anthony Davis Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B330">
         <is>
-          <t xml:space="preserve">9/16/2027</t>
-        </is>
-      </c>
-      <c r="C330" s="66">
-        <v>75.00</v>
+          <t xml:space="preserve">11/24/2026</t>
+        </is>
+      </c>
+      <c r="C330" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="331">
       <c t="inlineStr" r="A331">
         <is>
-          <t xml:space="preserve">The American University</t>
+          <t xml:space="preserve">The Barack Obama Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B331">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">11/14/2026</t>
         </is>
       </c>
       <c r="C331" s="66">
-        <v>90.23</v>
+        <v>55.90</v>
       </c>
     </row>
     <row r="332">
       <c t="inlineStr" r="A332">
         <is>
-          <t xml:space="preserve">The Amyotrophic Lateral Sclerosis Association</t>
+          <t xml:space="preserve">The Baruch College Fund</t>
         </is>
       </c>
       <c t="inlineStr" r="B332">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
-        </is>
-      </c>
-      <c r="C332" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/8/2027</t>
+        </is>
+      </c>
+      <c r="C332" s="66">
+        <v>84.00</v>
       </c>
     </row>
     <row r="333">
       <c t="inlineStr" r="A333">
         <is>
-          <t xml:space="preserve">The Anthony Davis Foundation</t>
+          <t xml:space="preserve">The Call of Duty Endowment</t>
         </is>
       </c>
       <c t="inlineStr" r="B333">
         <is>
-          <t xml:space="preserve">11/24/2026</t>
-        </is>
-      </c>
-      <c r="C333" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/11/2027</t>
+        </is>
+      </c>
+      <c r="C333" s="66">
+        <v>73.00</v>
       </c>
     </row>
     <row r="334">
       <c t="inlineStr" r="A334">
         <is>
-          <t xml:space="preserve">The Arthritis Foundation, Inc.</t>
+          <t xml:space="preserve">The Center for Alcohol Policy</t>
         </is>
       </c>
       <c t="inlineStr" r="B334">
         <is>
-          <t xml:space="preserve">10/24/2026</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C334" s="66">
-        <v>90.00</v>
+        <v>73.40</v>
       </c>
     </row>
     <row r="335">
       <c t="inlineStr" r="A335">
         <is>
-          <t xml:space="preserve">The Barack Obama Foundation</t>
+          <t xml:space="preserve">The Center for Investigative Reporting</t>
         </is>
       </c>
       <c t="inlineStr" r="B335">
         <is>
-          <t xml:space="preserve">11/14/2026</t>
-        </is>
-      </c>
-      <c r="C335" s="66">
-        <v>55.90</v>
+          <t xml:space="preserve">12/9/2026</t>
+        </is>
+      </c>
+      <c r="C335" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c t="inlineStr" r="A336">
         <is>
-          <t xml:space="preserve">The Baruch College Fund</t>
+          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B336">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">6/15/2027</t>
         </is>
       </c>
       <c r="C336" s="66">
-        <v>84.00</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="337">
       <c t="inlineStr" r="A337">
         <is>
-          <t xml:space="preserve">The Call of Duty Endowment</t>
+          <t xml:space="preserve">The Center for Victims of Torture</t>
         </is>
       </c>
       <c t="inlineStr" r="B337">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C337" s="66">
-        <v>73.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="338">
       <c t="inlineStr" r="A338">
         <is>
-          <t xml:space="preserve">The Center for Alcohol Policy</t>
+          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
         </is>
       </c>
       <c t="inlineStr" r="B338">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">7/6/2027</t>
         </is>
       </c>
       <c r="C338" s="66">
-        <v>73.40</v>
+        <v>71.00</v>
       </c>
     </row>
     <row r="339">
       <c t="inlineStr" r="A339">
         <is>
-          <t xml:space="preserve">The Center for Investigative Reporting</t>
+          <t xml:space="preserve">The Cleveland Clinic Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B339">
         <is>
-          <t xml:space="preserve">12/9/2026</t>
-        </is>
-      </c>
-      <c r="C339" s="65">
-        <v>0</v>
+          <t xml:space="preserve">10/23/2027</t>
+        </is>
+      </c>
+      <c r="C339" s="66">
+        <v>89.51</v>
       </c>
     </row>
     <row r="340">
       <c t="inlineStr" r="A340">
         <is>
-          <t xml:space="preserve">The Center for Reproductive Rights, Inc.</t>
+          <t xml:space="preserve">The Colorado College</t>
         </is>
       </c>
       <c t="inlineStr" r="B340">
         <is>
-          <t xml:space="preserve">6/15/2027</t>
+          <t xml:space="preserve">10/29/2027</t>
         </is>
       </c>
       <c r="C340" s="66">
-        <v>71.00</v>
+        <v>90.00</v>
       </c>
     </row>
     <row r="341">
       <c t="inlineStr" r="A341">
         <is>
-          <t xml:space="preserve">The Center for Victims of Torture</t>
+          <t xml:space="preserve">The Denver Rescue Mission</t>
         </is>
       </c>
       <c t="inlineStr" r="B341">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">7/20/2027</t>
         </is>
       </c>
       <c r="C341" s="66">
-        <v>74.00</v>
+        <v>82.96</v>
       </c>
     </row>
     <row r="342">
       <c t="inlineStr" r="A342">
         <is>
-          <t xml:space="preserve">The Claremont Institute for the Study of Statesman</t>
+          <t xml:space="preserve">The Edison Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B342">
         <is>
-          <t xml:space="preserve">7/6/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C342" s="66">
-        <v>71.00</v>
+        <v>78.00</v>
       </c>
     </row>
     <row r="343">
       <c t="inlineStr" r="A343">
         <is>
-          <t xml:space="preserve">The Colorado College</t>
+          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B343">
         <is>
-          <t xml:space="preserve">10/29/2027</t>
-        </is>
-      </c>
-      <c r="C343" s="66">
-        <v>90.00</v>
+          <t xml:space="preserve">12/5/2026</t>
+        </is>
+      </c>
+      <c r="C343" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="344">
       <c t="inlineStr" r="A344">
         <is>
-          <t xml:space="preserve">The Denver Rescue Mission</t>
+          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
         </is>
       </c>
       <c t="inlineStr" r="B344">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
-        </is>
-      </c>
-      <c r="C344" s="66">
-        <v>82.96</v>
+          <t xml:space="preserve">4/23/2027</t>
+        </is>
+      </c>
+      <c r="C344" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c t="inlineStr" r="A345">
         <is>
-          <t xml:space="preserve">The Edison Institute</t>
+          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
         </is>
       </c>
       <c t="inlineStr" r="B345">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C345" s="66">
-        <v>78.00</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="346">
       <c t="inlineStr" r="A346">
         <is>
-          <t xml:space="preserve">The Florida Aquarium, Inc.</t>
+          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B346">
         <is>
-          <t xml:space="preserve">12/5/2026</t>
-        </is>
-      </c>
-      <c r="C346" s="65">
-        <v>0</v>
+          <t xml:space="preserve">5/15/2027</t>
+        </is>
+      </c>
+      <c r="C346" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="347">
       <c t="inlineStr" r="A347">
         <is>
-          <t xml:space="preserve">The General Richard G. Stilwell Korean War Veteran</t>
+          <t xml:space="preserve">The Heritage Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B347">
         <is>
-          <t xml:space="preserve">4/23/2027</t>
-        </is>
-      </c>
-      <c r="C347" s="65">
-        <v>0</v>
+          <t xml:space="preserve">12/16/2026</t>
+        </is>
+      </c>
+      <c r="C347" s="66">
+        <v>83.00</v>
       </c>
     </row>
     <row r="348">
       <c t="inlineStr" r="A348">
         <is>
-          <t xml:space="preserve">The General Society of Mayflower Descendants</t>
+          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B348">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C348" s="66">
-        <v>76.48</v>
+        <v>89.00</v>
       </c>
     </row>
     <row r="349">
       <c t="inlineStr" r="A349">
         <is>
-          <t xml:space="preserve">The Harold Grinspoon Foundation</t>
+          <t xml:space="preserve">The Independent Institute</t>
         </is>
       </c>
       <c t="inlineStr" r="B349">
         <is>
-          <t xml:space="preserve">5/15/2027</t>
+          <t xml:space="preserve">5/29/2027</t>
         </is>
       </c>
       <c r="C349" s="66">
-        <v>85.00</v>
+        <v>77.51</v>
       </c>
     </row>
     <row r="350">
       <c t="inlineStr" r="A350">
         <is>
-          <t xml:space="preserve">The Heritage Foundation</t>
+          <t xml:space="preserve">The International Wildlife Rehab. Council</t>
         </is>
       </c>
       <c t="inlineStr" r="B350">
         <is>
-          <t xml:space="preserve">12/16/2026</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C350" s="66">
-        <v>83.00</v>
+        <v>81.00</v>
       </c>
     </row>
     <row r="351">
       <c t="inlineStr" r="A351">
         <is>
-          <t xml:space="preserve">The Hunter College Foundation, Inc.</t>
+          <t xml:space="preserve">The Jane Goodall Institute for Wildlife Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B351">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
-        </is>
-      </c>
-      <c r="C351" s="66">
-        <v>89.00</v>
+          <t xml:space="preserve">5/19/2027</t>
+        </is>
+      </c>
+      <c r="C351" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="352">
       <c t="inlineStr" r="A352">
         <is>
-          <t xml:space="preserve">The Independent Institute</t>
+          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B352">
         <is>
-          <t xml:space="preserve">5/29/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C352" s="66">
-        <v>77.51</v>
+        <v>84.00</v>
       </c>
     </row>
     <row r="353">
       <c t="inlineStr" r="A353">
         <is>
-          <t xml:space="preserve">The International Wildlife Rehab. Council</t>
+          <t xml:space="preserve">The Just Trust for Education</t>
         </is>
       </c>
       <c t="inlineStr" r="B353">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">7/17/2027</t>
         </is>
       </c>
       <c r="C353" s="66">
-        <v>81.00</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="354">
       <c t="inlineStr" r="A354">
         <is>
-          <t xml:space="preserve">The Jane Goodall Institute for Wildlife Research</t>
+          <t xml:space="preserve">The Kansas University Endowment Association</t>
         </is>
       </c>
       <c t="inlineStr" r="B354">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
-        </is>
-      </c>
-      <c r="C354" s="65">
-        <v>0</v>
+          <t xml:space="preserve">7/21/2027</t>
+        </is>
+      </c>
+      <c r="C354" s="66">
+        <v>91.34</v>
       </c>
     </row>
     <row r="355">
       <c t="inlineStr" r="A355">
         <is>
-          <t xml:space="preserve">The Jesse Helms Center Foundation</t>
+          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B355">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">4/10/2027</t>
         </is>
       </c>
       <c r="C355" s="66">
-        <v>84.00</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="356">
       <c t="inlineStr" r="A356">
         <is>
-          <t xml:space="preserve">The Just Trust for Education</t>
+          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B356">
         <is>
-          <t xml:space="preserve">7/17/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C356" s="66">
-        <v>85.13</v>
+        <v>91.99</v>
       </c>
     </row>
     <row r="357">
       <c t="inlineStr" r="A357">
         <is>
-          <t xml:space="preserve">The Kansas University Endowment Association</t>
+          <t xml:space="preserve">The Memorial Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B357">
         <is>
-          <t xml:space="preserve">7/21/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C357" s="66">
-        <v>91.34</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="358">
       <c t="inlineStr" r="A358">
         <is>
-          <t xml:space="preserve">The Marfan Foundation, Inc.</t>
+          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B358">
         <is>
-          <t xml:space="preserve">4/10/2027</t>
+          <t xml:space="preserve">8/27/2027</t>
         </is>
       </c>
       <c r="C358" s="66">
-        <v>83.06</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="359">
       <c t="inlineStr" r="A359">
         <is>
-          <t xml:space="preserve">The Medical College of Wisconsin, Inc.</t>
+          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B359">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C359" s="66">
-        <v>91.99</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="360">
       <c t="inlineStr" r="A360">
         <is>
-          <t xml:space="preserve">The Memorial Foundation</t>
+          <t xml:space="preserve">The National World War II Museum, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B360">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">7/7/2027</t>
         </is>
       </c>
       <c r="C360" s="66">
-        <v>72.00</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="361">
       <c t="inlineStr" r="A361">
         <is>
-          <t xml:space="preserve">The Museum of the Bible, Inc.</t>
+          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
         </is>
       </c>
       <c t="inlineStr" r="B361">
         <is>
-          <t xml:space="preserve">8/27/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C361" s="66">
-        <v>74.58</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="362">
       <c t="inlineStr" r="A362">
         <is>
-          <t xml:space="preserve">The National Children's Cancer Society, Inc.</t>
+          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
         </is>
       </c>
       <c t="inlineStr" r="B362">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C362" s="66">
-        <v>60.00</v>
+        <v>87.40</v>
       </c>
     </row>
     <row r="363">
       <c t="inlineStr" r="A363">
         <is>
-          <t xml:space="preserve">The National World War II Museum, Inc.</t>
+          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B363">
         <is>
-          <t xml:space="preserve">7/7/2027</t>
+          <t xml:space="preserve">8/24/2027</t>
         </is>
       </c>
       <c r="C363" s="66">
-        <v>80.00</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="364">
       <c t="inlineStr" r="A364">
         <is>
-          <t xml:space="preserve">The New Museum at the Bradford Brinton Ranch</t>
+          <t xml:space="preserve">The Ohio University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B364">
@@ -5657,108 +5657,108 @@
         </is>
       </c>
       <c r="C364" s="66">
-        <v>80.64</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="365">
       <c t="inlineStr" r="A365">
         <is>
-          <t xml:space="preserve">The New York Public Library, Astor, Lenox and Tild</t>
+          <t xml:space="preserve">The OneStar Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B365">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">1/14/2027</t>
         </is>
       </c>
       <c r="C365" s="66">
-        <v>87.40</v>
+        <v>62.50</v>
       </c>
     </row>
     <row r="366">
       <c t="inlineStr" r="A366">
         <is>
-          <t xml:space="preserve">The Ohio State University Alumni Association, Inc.</t>
+          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
         </is>
       </c>
       <c t="inlineStr" r="B366">
         <is>
-          <t xml:space="preserve">8/24/2027</t>
+          <t xml:space="preserve">12/29/2026</t>
         </is>
       </c>
       <c r="C366" s="66">
-        <v>60.00</v>
+        <v>88.30</v>
       </c>
     </row>
     <row r="367">
       <c t="inlineStr" r="A367">
         <is>
-          <t xml:space="preserve">The Ohio University Foundation</t>
+          <t xml:space="preserve">The Planetary Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B367">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">7/14/2027</t>
         </is>
       </c>
       <c r="C367" s="66">
-        <v>74.14</v>
+        <v>66.00</v>
       </c>
     </row>
     <row r="368">
       <c t="inlineStr" r="A368">
         <is>
-          <t xml:space="preserve">The OneStar Foundation</t>
+          <t xml:space="preserve">The Principia Corporation</t>
         </is>
       </c>
       <c t="inlineStr" r="B368">
         <is>
-          <t xml:space="preserve">1/14/2027</t>
-        </is>
-      </c>
-      <c r="C368" s="66">
-        <v>62.50</v>
+          <t xml:space="preserve">5/19/2027</t>
+        </is>
+      </c>
+      <c r="C368" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="369">
       <c t="inlineStr" r="A369">
         <is>
-          <t xml:space="preserve">The Parent Project for Muscular Dystrophy Research</t>
+          <t xml:space="preserve">The Purchase College Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B369">
         <is>
-          <t xml:space="preserve">12/29/2026</t>
+          <t xml:space="preserve">3/24/2027</t>
         </is>
       </c>
       <c r="C369" s="66">
-        <v>88.30</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="370">
       <c t="inlineStr" r="A370">
         <is>
-          <t xml:space="preserve">The Planetary Society</t>
+          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
         </is>
       </c>
       <c t="inlineStr" r="B370">
         <is>
-          <t xml:space="preserve">7/14/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C370" s="66">
-        <v>66.00</v>
+        <v>81.26</v>
       </c>
     </row>
     <row r="371">
       <c t="inlineStr" r="A371">
         <is>
-          <t xml:space="preserve">The Principia Corporation</t>
+          <t xml:space="preserve">The Ruth Collective</t>
         </is>
       </c>
       <c t="inlineStr" r="B371">
         <is>
-          <t xml:space="preserve">5/19/2027</t>
+          <t xml:space="preserve">12/11/2026</t>
         </is>
       </c>
       <c r="C371" s="65">
@@ -5768,297 +5768,297 @@
     <row r="372">
       <c t="inlineStr" r="A372">
         <is>
-          <t xml:space="preserve">The Purchase College Foundation</t>
+          <t xml:space="preserve">The Society of the Cincinnati</t>
         </is>
       </c>
       <c t="inlineStr" r="B372">
         <is>
-          <t xml:space="preserve">3/24/2027</t>
+          <t xml:space="preserve">5/11/2027</t>
         </is>
       </c>
       <c r="C372" s="66">
-        <v>78.12</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="373">
       <c t="inlineStr" r="A373">
         <is>
-          <t xml:space="preserve">The Ronald Reagan Presidential Foundation and Inst</t>
+          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
         </is>
       </c>
       <c t="inlineStr" r="B373">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">1/21/2027</t>
         </is>
       </c>
       <c r="C373" s="66">
-        <v>81.26</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="374">
       <c t="inlineStr" r="A374">
         <is>
-          <t xml:space="preserve">The Ruth Collective</t>
+          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B374">
         <is>
-          <t xml:space="preserve">12/11/2026</t>
-        </is>
-      </c>
-      <c r="C374" s="65">
-        <v>0</v>
+          <t xml:space="preserve">4/13/2027</t>
+        </is>
+      </c>
+      <c r="C374" s="66">
+        <v>82.20</v>
       </c>
     </row>
     <row r="375">
       <c t="inlineStr" r="A375">
         <is>
-          <t xml:space="preserve">The Society of the Cincinnati</t>
+          <t xml:space="preserve">The University of Montana Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B375">
         <is>
-          <t xml:space="preserve">5/11/2027</t>
+          <t xml:space="preserve">6/16/2027</t>
         </is>
       </c>
       <c r="C375" s="66">
-        <v>73.00</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="376">
       <c t="inlineStr" r="A376">
         <is>
-          <t xml:space="preserve">The U.S. Charitable Gift Trust</t>
+          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B376">
         <is>
-          <t xml:space="preserve">1/21/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C376" s="66">
-        <v>94.00</v>
+        <v>76.00</v>
       </c>
     </row>
     <row r="377">
       <c t="inlineStr" r="A377">
         <is>
-          <t xml:space="preserve">The University of Baltimore Foundation, Inc.</t>
+          <t xml:space="preserve">The Visiting Angels Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B377">
         <is>
-          <t xml:space="preserve">4/13/2027</t>
+          <t xml:space="preserve">7/20/2027</t>
         </is>
       </c>
       <c r="C377" s="66">
-        <v>82.20</v>
+        <v>94.00</v>
       </c>
     </row>
     <row r="378">
       <c t="inlineStr" r="A378">
         <is>
-          <t xml:space="preserve">The University of Montana Foundation</t>
+          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B378">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">1/30/2027</t>
         </is>
       </c>
       <c r="C378" s="66">
-        <v>79.00</v>
+        <v>79.51</v>
       </c>
     </row>
     <row r="379">
       <c t="inlineStr" r="A379">
         <is>
-          <t xml:space="preserve">The University of New Mexico Foundation, Inc.</t>
+          <t xml:space="preserve">The Wilderness Society</t>
         </is>
       </c>
       <c t="inlineStr" r="B379">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">9/8/2027</t>
         </is>
       </c>
       <c r="C379" s="66">
-        <v>76.00</v>
+        <v>73.00</v>
       </c>
     </row>
     <row r="380">
       <c t="inlineStr" r="A380">
         <is>
-          <t xml:space="preserve">The Visiting Angels Foundation</t>
+          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B380">
         <is>
-          <t xml:space="preserve">7/20/2027</t>
+          <t xml:space="preserve">4/21/2027</t>
         </is>
       </c>
       <c r="C380" s="66">
-        <v>94.00</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="381">
       <c t="inlineStr" r="A381">
         <is>
-          <t xml:space="preserve">The White Coat Waste Project, Inc.</t>
+          <t xml:space="preserve">Together Making Changes</t>
         </is>
       </c>
       <c t="inlineStr" r="B381">
         <is>
-          <t xml:space="preserve">1/30/2027</t>
+          <t xml:space="preserve">7/16/2027</t>
         </is>
       </c>
       <c r="C381" s="66">
-        <v>79.51</v>
+        <v>90.26</v>
       </c>
     </row>
     <row r="382">
       <c t="inlineStr" r="A382">
         <is>
-          <t xml:space="preserve">The Wilderness Society</t>
+          <t xml:space="preserve">Trevecca Nazarene University</t>
         </is>
       </c>
       <c t="inlineStr" r="B382">
         <is>
-          <t xml:space="preserve">9/8/2027</t>
+          <t xml:space="preserve">7/30/2027</t>
         </is>
       </c>
       <c r="C382" s="66">
-        <v>73.00</v>
+        <v>87.82</v>
       </c>
     </row>
     <row r="383">
       <c t="inlineStr" r="A383">
         <is>
-          <t xml:space="preserve">The William Paterson Univ. of NJ Fnd. Inc.</t>
+          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B383">
         <is>
-          <t xml:space="preserve">4/21/2027</t>
+          <t xml:space="preserve">8/11/2027</t>
         </is>
       </c>
       <c r="C383" s="66">
-        <v>85.00</v>
+        <v>94.50</v>
       </c>
     </row>
     <row r="384">
       <c t="inlineStr" r="A384">
         <is>
-          <t xml:space="preserve">Together Making Changes</t>
+          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
         </is>
       </c>
       <c t="inlineStr" r="B384">
         <is>
-          <t xml:space="preserve">7/16/2027</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C384" s="66">
-        <v>90.26</v>
+        <v>89.90</v>
       </c>
     </row>
     <row r="385">
       <c t="inlineStr" r="A385">
         <is>
-          <t xml:space="preserve">Trevecca Nazarene University</t>
+          <t xml:space="preserve">Trustees of Tufts College</t>
         </is>
       </c>
       <c t="inlineStr" r="B385">
         <is>
-          <t xml:space="preserve">7/30/2027</t>
+          <t xml:space="preserve">7/2/2027</t>
         </is>
       </c>
       <c r="C385" s="66">
-        <v>87.82</v>
+        <v>85.00</v>
       </c>
     </row>
     <row r="386">
       <c t="inlineStr" r="A386">
         <is>
-          <t xml:space="preserve">Tricycle Foundation, Inc.</t>
+          <t xml:space="preserve">Turning Point USA, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B386">
         <is>
-          <t xml:space="preserve">8/11/2027</t>
-        </is>
-      </c>
-      <c r="C386" s="66">
-        <v>94.50</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C386" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="387">
       <c t="inlineStr" r="A387">
         <is>
-          <t xml:space="preserve">Trustees of the University of Pennsylvania</t>
+          <t xml:space="preserve">Twelveacres, Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="B387">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">1/16/2027</t>
         </is>
       </c>
       <c r="C387" s="66">
-        <v>89.90</v>
+        <v>79.93</v>
       </c>
     </row>
     <row r="388">
       <c t="inlineStr" r="A388">
         <is>
-          <t xml:space="preserve">Trustees of Tufts College</t>
+          <t xml:space="preserve">UATX</t>
         </is>
       </c>
       <c t="inlineStr" r="B388">
         <is>
-          <t xml:space="preserve">7/2/2027</t>
-        </is>
-      </c>
-      <c r="C388" s="66">
-        <v>85.00</v>
+          <t xml:space="preserve">2/1/2027</t>
+        </is>
+      </c>
+      <c r="C388" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="389">
       <c t="inlineStr" r="A389">
         <is>
-          <t xml:space="preserve">Turning Point USA, Inc.</t>
+          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B389">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C389" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/16/2027</t>
+        </is>
+      </c>
+      <c r="C389" s="66">
+        <v>95.75</v>
       </c>
     </row>
     <row r="390">
       <c t="inlineStr" r="A390">
         <is>
-          <t xml:space="preserve">Twelveacres, Incorporated</t>
+          <t xml:space="preserve">UMKC Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B390">
         <is>
-          <t xml:space="preserve">1/16/2027</t>
+          <t xml:space="preserve">1/27/2027</t>
         </is>
       </c>
       <c r="C390" s="66">
-        <v>79.93</v>
+        <v>95.00</v>
       </c>
     </row>
     <row r="391">
       <c t="inlineStr" r="A391">
         <is>
-          <t xml:space="preserve">UATX</t>
+          <t xml:space="preserve">Unified Youth</t>
         </is>
       </c>
       <c t="inlineStr" r="B391">
         <is>
-          <t xml:space="preserve">2/1/2027</t>
+          <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
       <c r="C391" s="65">
@@ -6068,37 +6068,37 @@
     <row r="392">
       <c t="inlineStr" r="A392">
         <is>
-          <t xml:space="preserve">Ulta Beauty Charitable Foundation</t>
+          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B392">
         <is>
-          <t xml:space="preserve">6/16/2027</t>
+          <t xml:space="preserve">8/1/2027</t>
         </is>
       </c>
       <c r="C392" s="66">
-        <v>95.75</v>
+        <v>88.00</v>
       </c>
     </row>
     <row r="393">
       <c t="inlineStr" r="A393">
         <is>
-          <t xml:space="preserve">UMKC Foundation</t>
+          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B393">
         <is>
-          <t xml:space="preserve">1/27/2027</t>
+          <t xml:space="preserve">8/17/2027</t>
         </is>
       </c>
       <c r="C393" s="66">
-        <v>95.00</v>
+        <v>84.01</v>
       </c>
     </row>
     <row r="394">
       <c t="inlineStr" r="A394">
         <is>
-          <t xml:space="preserve">Unified Youth</t>
+          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B394">
@@ -6106,532 +6106,487 @@
           <t xml:space="preserve">2/19/2027</t>
         </is>
       </c>
-      <c r="C394" s="65">
-        <v>0</v>
+      <c r="C394" s="66">
+        <v>85.00</v>
       </c>
     </row>
     <row r="395">
       <c t="inlineStr" r="A395">
         <is>
-          <t xml:space="preserve">Union of Concerned Scientists, Inc.</t>
+          <t xml:space="preserve">united Service Organizations, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B395">
         <is>
-          <t xml:space="preserve">8/1/2027</t>
+          <t xml:space="preserve">11/10/2026</t>
         </is>
       </c>
       <c r="C395" s="66">
-        <v>88.00</v>
+        <v>67.94</v>
       </c>
     </row>
     <row r="396">
       <c t="inlineStr" r="A396">
         <is>
-          <t xml:space="preserve">Unitarian Universalists Service Committee, Inc.</t>
+          <t xml:space="preserve">United States Association for UNHCR</t>
         </is>
       </c>
       <c t="inlineStr" r="B396">
         <is>
-          <t xml:space="preserve">8/17/2027</t>
+          <t xml:space="preserve">6/1/2027</t>
         </is>
       </c>
       <c r="C396" s="66">
-        <v>84.01</v>
+        <v>61.00</v>
       </c>
     </row>
     <row r="397">
       <c t="inlineStr" r="A397">
         <is>
-          <t xml:space="preserve">United Breast Cancer Foundation, Inc.</t>
+          <t xml:space="preserve">United States Center for SafeSport</t>
         </is>
       </c>
       <c t="inlineStr" r="B397">
         <is>
-          <t xml:space="preserve">2/19/2027</t>
+          <t xml:space="preserve">2/27/2027</t>
         </is>
       </c>
       <c r="C397" s="66">
-        <v>85.00</v>
+        <v>72.74</v>
       </c>
     </row>
     <row r="398">
       <c t="inlineStr" r="A398">
         <is>
-          <t xml:space="preserve">united Service Organizations, Inc.</t>
+          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B398">
         <is>
-          <t xml:space="preserve">11/10/2026</t>
+          <t xml:space="preserve">9/9/2027</t>
         </is>
       </c>
       <c r="C398" s="66">
-        <v>67.94</v>
+        <v>38.00</v>
       </c>
     </row>
     <row r="399">
       <c t="inlineStr" r="A399">
         <is>
-          <t xml:space="preserve">United States Association for UNHCR</t>
+          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B399">
         <is>
-          <t xml:space="preserve">6/1/2027</t>
+          <t xml:space="preserve">7/31/2027</t>
         </is>
       </c>
       <c r="C399" s="66">
-        <v>61.00</v>
+        <v>99.30</v>
       </c>
     </row>
     <row r="400">
       <c t="inlineStr" r="A400">
         <is>
-          <t xml:space="preserve">United States Center for SafeSport</t>
+          <t xml:space="preserve">University of Colorado</t>
         </is>
       </c>
       <c t="inlineStr" r="B400">
         <is>
-          <t xml:space="preserve">2/27/2027</t>
+          <t xml:space="preserve">10/6/2027</t>
         </is>
       </c>
       <c r="C400" s="66">
-        <v>72.74</v>
+        <v>76.40</v>
       </c>
     </row>
     <row r="401">
       <c t="inlineStr" r="A401">
         <is>
-          <t xml:space="preserve">United States Law Enforcement Foundation, Inc.</t>
+          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B401">
         <is>
-          <t xml:space="preserve">9/9/2027</t>
+          <t xml:space="preserve">6/8/2027</t>
         </is>
       </c>
       <c r="C401" s="66">
-        <v>38.00</v>
+        <v>93.00</v>
       </c>
     </row>
     <row r="402">
       <c t="inlineStr" r="A402">
         <is>
-          <t xml:space="preserve">University at Buffalo Foundation, Inc.</t>
+          <t xml:space="preserve">University of Nebraska Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B402">
         <is>
-          <t xml:space="preserve">7/31/2027</t>
+          <t xml:space="preserve">7/15/2027</t>
         </is>
       </c>
       <c r="C402" s="66">
-        <v>99.30</v>
+        <v>81.10</v>
       </c>
     </row>
     <row r="403">
       <c t="inlineStr" r="A403">
         <is>
-          <t xml:space="preserve">University of Colorado</t>
+          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B403">
         <is>
-          <t xml:space="preserve">10/6/2027</t>
+          <t xml:space="preserve">6/23/2027</t>
         </is>
       </c>
       <c r="C403" s="66">
-        <v>76.40</v>
+        <v>77.00</v>
       </c>
     </row>
     <row r="404">
       <c t="inlineStr" r="A404">
         <is>
-          <t xml:space="preserve">University of Louisiana at Lafayette Foundation</t>
+          <t xml:space="preserve">University of Northern Iowa Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B404">
         <is>
-          <t xml:space="preserve">6/8/2027</t>
+          <t xml:space="preserve">10/1/2027</t>
         </is>
       </c>
       <c r="C404" s="66">
-        <v>93.00</v>
+        <v>74.00</v>
       </c>
     </row>
     <row r="405">
       <c t="inlineStr" r="A405">
         <is>
-          <t xml:space="preserve">University of Nebraska Foundation</t>
+          <t xml:space="preserve">University of Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B405">
         <is>
-          <t xml:space="preserve">7/15/2027</t>
-        </is>
-      </c>
-      <c r="C405" s="66">
-        <v>81.10</v>
+          <t xml:space="preserve">11/12/2026</t>
+        </is>
+      </c>
+      <c r="C405" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
       <c t="inlineStr" r="A406">
         <is>
-          <t xml:space="preserve">University of Nevada, Las Vegas Foundation</t>
+          <t xml:space="preserve">University of Richmond</t>
         </is>
       </c>
       <c t="inlineStr" r="B406">
         <is>
-          <t xml:space="preserve">6/23/2027</t>
+          <t xml:space="preserve">6/22/2027</t>
         </is>
       </c>
       <c r="C406" s="66">
-        <v>77.00</v>
+        <v>82.18</v>
       </c>
     </row>
     <row r="407">
       <c t="inlineStr" r="A407">
         <is>
-          <t xml:space="preserve">University of Northern Iowa Foundation</t>
+          <t xml:space="preserve">University of the Pacific</t>
         </is>
       </c>
       <c t="inlineStr" r="B407">
         <is>
-          <t xml:space="preserve">10/1/2027</t>
+          <t xml:space="preserve">10/12/2027</t>
         </is>
       </c>
       <c r="C407" s="66">
-        <v>74.00</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="408">
       <c t="inlineStr" r="A408">
         <is>
-          <t xml:space="preserve">University of Pacific</t>
+          <t xml:space="preserve">Veterans Community Project</t>
         </is>
       </c>
       <c t="inlineStr" r="B408">
         <is>
-          <t xml:space="preserve">11/12/2026</t>
-        </is>
-      </c>
-      <c r="C408" s="65">
-        <v>0</v>
+          <t xml:space="preserve">6/4/2027</t>
+        </is>
+      </c>
+      <c r="C408" s="66">
+        <v>88.83</v>
       </c>
     </row>
     <row r="409">
       <c t="inlineStr" r="A409">
         <is>
-          <t xml:space="preserve">University of Richmond</t>
+          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B409">
         <is>
-          <t xml:space="preserve">6/22/2027</t>
+          <t xml:space="preserve">7/13/2027</t>
         </is>
       </c>
       <c r="C409" s="66">
-        <v>82.18</v>
+        <v>72.00</v>
       </c>
     </row>
     <row r="410">
       <c t="inlineStr" r="A410">
         <is>
-          <t xml:space="preserve">University of the Pacific</t>
+          <t xml:space="preserve">Violet Research Institute, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B410">
         <is>
-          <t xml:space="preserve">10/12/2027</t>
+          <t xml:space="preserve">7/28/2027</t>
         </is>
       </c>
       <c r="C410" s="66">
-        <v>95.48</v>
+        <v>80.00</v>
       </c>
     </row>
     <row r="411">
       <c t="inlineStr" r="A411">
         <is>
-          <t xml:space="preserve">Veterans Community Project</t>
+          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B411">
         <is>
-          <t xml:space="preserve">6/4/2027</t>
+          <t xml:space="preserve">11/5/2026</t>
         </is>
       </c>
       <c r="C411" s="66">
-        <v>88.83</v>
+        <v>28.00</v>
       </c>
     </row>
     <row r="412">
       <c t="inlineStr" r="A412">
         <is>
-          <t xml:space="preserve">Vietnam Veterans Memorial Fund, Inc.</t>
+          <t xml:space="preserve">VoteAmerica, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B412">
         <is>
-          <t xml:space="preserve">7/13/2027</t>
+          <t xml:space="preserve">3/9/2027</t>
         </is>
       </c>
       <c r="C412" s="66">
-        <v>72.00</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="413">
       <c t="inlineStr" r="A413">
         <is>
-          <t xml:space="preserve">Violet Research Institute, Inc.</t>
+          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="B413">
         <is>
-          <t xml:space="preserve">7/28/2027</t>
-        </is>
-      </c>
-      <c r="C413" s="66">
-        <v>80.00</v>
+          <t xml:space="preserve">11/18/2026</t>
+        </is>
+      </c>
+      <c r="C413" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="414">
       <c t="inlineStr" r="A414">
         <is>
-          <t xml:space="preserve">Volunteer Firefighter Alliance, Inc.</t>
+          <t xml:space="preserve">Washington State University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B414">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">7/8/2027</t>
         </is>
       </c>
       <c r="C414" s="66">
-        <v>28.00</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="415">
       <c t="inlineStr" r="A415">
         <is>
-          <t xml:space="preserve">VoteAmerica, Inc.</t>
+          <t xml:space="preserve">Western Illinois University Foundation</t>
         </is>
       </c>
       <c t="inlineStr" r="B415">
         <is>
-          <t xml:space="preserve">3/9/2027</t>
+          <t xml:space="preserve">9/22/2027</t>
         </is>
       </c>
       <c r="C415" s="66">
-        <v>93.37</v>
+        <v>77.54</v>
       </c>
     </row>
     <row r="416">
       <c t="inlineStr" r="A416">
         <is>
-          <t xml:space="preserve">Walker Cancer Research Institute, Inc</t>
+          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
         </is>
       </c>
       <c t="inlineStr" r="B416">
         <is>
-          <t xml:space="preserve">11/18/2026</t>
-        </is>
-      </c>
-      <c r="C416" s="65">
-        <v>0</v>
+          <t xml:space="preserve">11/5/2026</t>
+        </is>
+      </c>
+      <c r="C416" s="66">
+        <v>82.68</v>
       </c>
     </row>
     <row r="417">
       <c t="inlineStr" r="A417">
         <is>
-          <t xml:space="preserve">Washington State University Foundation</t>
+          <t xml:space="preserve">Wildlife Conservation Network</t>
         </is>
       </c>
       <c t="inlineStr" r="B417">
         <is>
-          <t xml:space="preserve">7/8/2027</t>
+          <t xml:space="preserve">8/13/2027</t>
         </is>
       </c>
       <c r="C417" s="66">
-        <v>75.03</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="418">
       <c t="inlineStr" r="A418">
         <is>
-          <t xml:space="preserve">Western Illinois University Foundation</t>
+          <t xml:space="preserve">Winning for Women, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B418">
         <is>
-          <t xml:space="preserve">9/22/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C418" s="66">
-        <v>77.54</v>
+        <v>66.70</v>
       </c>
     </row>
     <row r="419">
       <c t="inlineStr" r="A419">
         <is>
-          <t xml:space="preserve">Western Pennsylvania Conservancy</t>
+          <t xml:space="preserve">Women for Women International</t>
         </is>
       </c>
       <c t="inlineStr" r="B419">
         <is>
-          <t xml:space="preserve">11/5/2026</t>
+          <t xml:space="preserve">10/27/2026</t>
         </is>
       </c>
       <c r="C419" s="66">
-        <v>82.68</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="420">
       <c t="inlineStr" r="A420">
         <is>
-          <t xml:space="preserve">Wildlife Conservation Network</t>
+          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
         </is>
       </c>
       <c t="inlineStr" r="B420">
         <is>
-          <t xml:space="preserve">8/13/2027</t>
+          <t xml:space="preserve">1/13/2027</t>
         </is>
       </c>
       <c r="C420" s="66">
-        <v>92.13</v>
+        <v>71.40</v>
       </c>
     </row>
     <row r="421">
       <c t="inlineStr" r="A421">
         <is>
-          <t xml:space="preserve">Winning for Women, Inc.</t>
+          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B421">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
-        </is>
-      </c>
-      <c r="C421" s="66">
-        <v>66.70</v>
+          <t xml:space="preserve">2/20/2027</t>
+        </is>
+      </c>
+      <c r="C421" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="422">
       <c t="inlineStr" r="A422">
         <is>
-          <t xml:space="preserve">Women for Women International</t>
+          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B422">
         <is>
-          <t xml:space="preserve">10/27/2026</t>
+          <t xml:space="preserve">5/20/2027</t>
         </is>
       </c>
       <c r="C422" s="66">
-        <v>79.06</v>
+        <v>79.00</v>
       </c>
     </row>
     <row r="423">
       <c t="inlineStr" r="A423">
         <is>
-          <t xml:space="preserve">Word on Fire Catholic Ministries</t>
+          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B423">
         <is>
-          <t xml:space="preserve">1/13/2027</t>
+          <t xml:space="preserve">8/31/2027</t>
         </is>
       </c>
       <c r="C423" s="66">
-        <v>71.40</v>
+        <v>70.36</v>
       </c>
     </row>
     <row r="424">
       <c t="inlineStr" r="A424">
         <is>
-          <t xml:space="preserve">World Aquaculture Society, Inc.</t>
+          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B424">
         <is>
-          <t xml:space="preserve">2/20/2027</t>
-        </is>
-      </c>
-      <c r="C424" s="65">
-        <v>0</v>
+          <t xml:space="preserve">8/24/2027</t>
+        </is>
+      </c>
+      <c r="C424" s="66">
+        <v>39.45</v>
       </c>
     </row>
     <row r="425">
       <c t="inlineStr" r="A425">
         <is>
-          <t xml:space="preserve">World Wildlife Fund, Inc.</t>
+          <t xml:space="preserve">YMCA of the Rockies</t>
         </is>
       </c>
       <c t="inlineStr" r="B425">
         <is>
-          <t xml:space="preserve">5/20/2027</t>
+          <t xml:space="preserve">12/16/2026</t>
         </is>
       </c>
       <c r="C425" s="66">
-        <v>79.00</v>
+        <v>81.65</v>
       </c>
     </row>
     <row r="426">
       <c t="inlineStr" r="A426">
         <is>
-          <t xml:space="preserve">Wounded Warrior Project, Inc.</t>
+          <t xml:space="preserve">Young Judaea Global, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="B426">
         <is>
-          <t xml:space="preserve">8/31/2027</t>
+          <t xml:space="preserve">6/25/2027</t>
         </is>
       </c>
       <c r="C426" s="66">
-        <v>70.36</v>
-      </c>
-    </row>
-    <row r="427">
-      <c t="inlineStr" r="A427">
-        <is>
-          <t xml:space="preserve">Yellowstone Boys and Girls Ranch Foundation, Inc.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B427">
-        <is>
-          <t xml:space="preserve">8/24/2027</t>
-        </is>
-      </c>
-      <c r="C427" s="66">
-        <v>39.45</v>
-      </c>
-    </row>
-    <row r="428">
-      <c t="inlineStr" r="A428">
-        <is>
-          <t xml:space="preserve">YMCA of the Rockies</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B428">
-        <is>
-          <t xml:space="preserve">12/16/2026</t>
-        </is>
-      </c>
-      <c r="C428" s="66">
-        <v>81.65</v>
-      </c>
-    </row>
-    <row r="429">
-      <c t="inlineStr" r="A429">
-        <is>
-          <t xml:space="preserve">Young Judaea Global, Inc.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B429">
-        <is>
-          <t xml:space="preserve">6/25/2027</t>
-        </is>
-      </c>
-      <c r="C429" s="66">
         <v>71.20</v>
       </c>
     </row>
